--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="157">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -129,12 +129,12 @@
     <t>101701 - 1</t>
   </si>
   <si>
+    <t>Victor Costa</t>
+  </si>
+  <si>
     <t>DECORA INTERIORES LTDA</t>
   </si>
   <si>
-    <t>Victor Costa</t>
-  </si>
-  <si>
     <t>05/10/2026</t>
   </si>
   <si>
@@ -147,18 +147,18 @@
     <t>PFP-Previsões Financeiras a Pagar</t>
   </si>
   <si>
+    <t>1 - 8</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>Hostgator</t>
+  </si>
+  <si>
     <t>1 - 9</t>
   </si>
   <si>
-    <t>1 - 8</t>
-  </si>
-  <si>
-    <t>Hostgator</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
     <t>100901 - 1</t>
   </si>
   <si>
@@ -177,12 +177,12 @@
     <t>06/10/2026</t>
   </si>
   <si>
+    <t>FELIPE DOMINGOS BARBOSA</t>
+  </si>
+  <si>
     <t>ROSANGELA PACHECO</t>
   </si>
   <si>
-    <t>FELIPE DOMINGOS BARBOSA</t>
-  </si>
-  <si>
     <t>BIANCA RODRIGUES</t>
   </si>
   <si>
@@ -204,12 +204,6 @@
     <t>08/10/2026</t>
   </si>
   <si>
-    <t>12 - 9</t>
-  </si>
-  <si>
-    <t>Promob</t>
-  </si>
-  <si>
     <t>56102 - 1</t>
   </si>
   <si>
@@ -228,108 +222,117 @@
     <t>101401 - 1</t>
   </si>
   <si>
+    <t>DMP-Duplicata Manual do Contas a pagar</t>
+  </si>
+  <si>
+    <t>92401 - 0</t>
+  </si>
+  <si>
+    <t>Antonio Jesus</t>
+  </si>
+  <si>
+    <t>92801 - 0</t>
+  </si>
+  <si>
+    <t>96601 - 3</t>
+  </si>
+  <si>
+    <t>96601 - 2</t>
+  </si>
+  <si>
+    <t>101401 - 2</t>
+  </si>
+  <si>
+    <t>101401 - 3</t>
+  </si>
+  <si>
+    <t>10/10/2026</t>
+  </si>
+  <si>
+    <t>100501 - 1</t>
+  </si>
+  <si>
+    <t>100501 - 2</t>
+  </si>
+  <si>
+    <t>100501 - 3</t>
+  </si>
+  <si>
+    <t>PREFEITURA SP- ISS</t>
+  </si>
+  <si>
+    <t>12/10/2026</t>
+  </si>
+  <si>
+    <t>2 - 9</t>
+  </si>
+  <si>
+    <t>Enel</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>1630 - 1</t>
+  </si>
+  <si>
+    <t>49501 - 2</t>
+  </si>
+  <si>
+    <t>100301 - 1</t>
+  </si>
+  <si>
+    <t>102101 - 1</t>
+  </si>
+  <si>
+    <t>1630 - 3</t>
+  </si>
+  <si>
+    <t>1630 - 2</t>
+  </si>
+  <si>
+    <t>100301 - 2</t>
+  </si>
+  <si>
+    <t>100301 - 3</t>
+  </si>
+  <si>
+    <t>102101 - 2</t>
+  </si>
+  <si>
+    <t>102101 - 3</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>101201 - 1</t>
+  </si>
+  <si>
+    <t>101801 - 1</t>
+  </si>
+  <si>
+    <t>101201 - 3</t>
+  </si>
+  <si>
+    <t>101201 - 2</t>
+  </si>
+  <si>
+    <t>101801 - 2</t>
+  </si>
+  <si>
+    <t>101801 - 3</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>101101 - 1</t>
+  </si>
+  <si>
     <t>DUP-Duplicata de Contrato</t>
   </si>
   <si>
-    <t>100901 - 0</t>
-  </si>
-  <si>
-    <t>Mariana Andrade Derossi</t>
-  </si>
-  <si>
-    <t>96601 - 3</t>
-  </si>
-  <si>
-    <t>96601 - 2</t>
-  </si>
-  <si>
-    <t>101401 - 2</t>
-  </si>
-  <si>
-    <t>101401 - 3</t>
-  </si>
-  <si>
-    <t>10/10/2026</t>
-  </si>
-  <si>
-    <t>100501 - 1</t>
-  </si>
-  <si>
-    <t>100501 - 3</t>
-  </si>
-  <si>
-    <t>100501 - 4</t>
-  </si>
-  <si>
-    <t>100501 - 2</t>
-  </si>
-  <si>
-    <t>PREFEITURA SP- ISS</t>
-  </si>
-  <si>
-    <t>Roger Duarte Pinheiro Me</t>
-  </si>
-  <si>
-    <t>12/10/2026</t>
-  </si>
-  <si>
-    <t>2 - 9</t>
-  </si>
-  <si>
-    <t>Enel</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>49501 - 2</t>
-  </si>
-  <si>
-    <t>100301 - 1</t>
-  </si>
-  <si>
-    <t>102101 - 1</t>
-  </si>
-  <si>
-    <t>100301 - 3</t>
-  </si>
-  <si>
-    <t>100301 - 2</t>
-  </si>
-  <si>
-    <t>102101 - 2</t>
-  </si>
-  <si>
-    <t>102101 - 3</t>
-  </si>
-  <si>
-    <t>14/10/2026</t>
-  </si>
-  <si>
-    <t>101201 - 1</t>
-  </si>
-  <si>
-    <t>101801 - 1</t>
-  </si>
-  <si>
-    <t>101201 - 2</t>
-  </si>
-  <si>
-    <t>101201 - 3</t>
-  </si>
-  <si>
-    <t>101801 - 3</t>
-  </si>
-  <si>
-    <t>101801 - 2</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>101101 - 1</t>
-  </si>
-  <si>
     <t>103501 - 0</t>
   </si>
   <si>
@@ -390,12 +393,12 @@
     <t>INSS- Previdenciária</t>
   </si>
   <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
     <t>Simples Nacional - DAS</t>
   </si>
   <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
     <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
   </si>
   <si>
@@ -435,12 +438,12 @@
     <t>27/10/2026</t>
   </si>
   <si>
+    <t>100901 - 3</t>
+  </si>
+  <si>
     <t>100901 - 4</t>
   </si>
   <si>
-    <t>100901 - 3</t>
-  </si>
-  <si>
     <t>29/10/2026</t>
   </si>
   <si>
@@ -453,28 +456,34 @@
     <t>GABRIEL DE CARVALHO MELLO</t>
   </si>
   <si>
+    <t>SEFAZ SP DARE - ICMS</t>
+  </si>
+  <si>
     <t>Facebook</t>
   </si>
   <si>
-    <t>SEFAZ SP DARE - ICMS</t>
+    <t>31/10/2026</t>
+  </si>
+  <si>
+    <t>96101 - 2</t>
   </si>
   <si>
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>23.081,24</t>
+    <t>6.156,53</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>257.080,88</t>
+    <t>261.055,13</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-233.999,64</t>
+    <t>-254.898,60</t>
   </si>
 </sst>
 </file>
@@ -542,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H135"/>
+  <dimension ref="A2:H138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -765,10 +774,10 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n" s="1">
-        <v>30.0</v>
+        <v>21.0</v>
       </c>
       <c r="H22" t="n" s="1">
-        <v>-30.0</v>
+        <v>-21.0</v>
       </c>
     </row>
     <row r="23">
@@ -791,10 +800,10 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n" s="1">
-        <v>21.0</v>
+        <v>30.0</v>
       </c>
       <c r="H23" t="n" s="1">
-        <v>-21.0</v>
+        <v>-30.0</v>
       </c>
     </row>
     <row r="24">
@@ -837,16 +846,16 @@
         <v>44</v>
       </c>
       <c r="E25" t="s" s="1">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F25" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G25" t="n" s="1">
-        <v>14250.0</v>
+        <v>2536.0</v>
       </c>
       <c r="H25" t="n" s="1">
-        <v>-14250.0</v>
+        <v>-2536.0</v>
       </c>
     </row>
     <row r="26">
@@ -860,7 +869,7 @@
         <v>43</v>
       </c>
       <c r="D26" t="s" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s" s="1">
         <v>46</v>
@@ -886,19 +895,19 @@
         <v>43</v>
       </c>
       <c r="D27" t="s" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s" s="1">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G27" t="n" s="1">
-        <v>2536.0</v>
+        <v>14250.0</v>
       </c>
       <c r="H27" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-14250.0</v>
       </c>
     </row>
     <row r="28">
@@ -967,7 +976,7 @@
         <v>51</v>
       </c>
       <c r="E30" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F30" t="n" s="1">
         <v>0.0</v>
@@ -1019,7 +1028,7 @@
         <v>52</v>
       </c>
       <c r="E32" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F32" t="n" s="1">
         <v>0.0</v>
@@ -1071,16 +1080,16 @@
         <v>48</v>
       </c>
       <c r="E34" t="s" s="1">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F34" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G34" t="n" s="1">
-        <v>4255.67</v>
+        <v>6079.52</v>
       </c>
       <c r="H34" t="n" s="1">
-        <v>-4255.67</v>
+        <v>-6079.52</v>
       </c>
     </row>
     <row r="35">
@@ -1097,7 +1106,7 @@
         <v>48</v>
       </c>
       <c r="E35" t="s" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F35" t="n" s="1">
         <v>0.0</v>
@@ -1123,16 +1132,16 @@
         <v>48</v>
       </c>
       <c r="E36" t="s" s="1">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F36" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G36" t="n" s="1">
-        <v>6079.52</v>
+        <v>4255.67</v>
       </c>
       <c r="H36" t="n" s="1">
-        <v>-6079.52</v>
+        <v>-4255.67</v>
       </c>
     </row>
     <row r="37">
@@ -1149,7 +1158,7 @@
         <v>41</v>
       </c>
       <c r="E37" t="s" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F37" t="n" s="1">
         <v>0.0</v>
@@ -1201,7 +1210,7 @@
         <v>41</v>
       </c>
       <c r="E39" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F39" t="n" s="1">
         <v>0.0</v>
@@ -1227,7 +1236,7 @@
         <v>58</v>
       </c>
       <c r="E40" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F40" t="n" s="1">
         <v>0.0</v>
@@ -1305,7 +1314,7 @@
         <v>60</v>
       </c>
       <c r="E43" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F43" t="n" s="1">
         <v>0.0</v>
@@ -1389,10 +1398,10 @@
         <v>0.0</v>
       </c>
       <c r="G46" t="n" s="1">
-        <v>599.0</v>
+        <v>180.0</v>
       </c>
       <c r="H46" t="n" s="1">
-        <v>-599.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="47">
@@ -1403,22 +1412,22 @@
         <v>62</v>
       </c>
       <c r="C47" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E47" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="E47" t="s" s="1">
-        <v>66</v>
-      </c>
       <c r="F47" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G47" t="n" s="1">
-        <v>180.0</v>
+        <v>12.47</v>
       </c>
       <c r="H47" t="n" s="1">
-        <v>-180.0</v>
+        <v>-12.47</v>
       </c>
     </row>
     <row r="48">
@@ -1435,7 +1444,7 @@
         <v>59</v>
       </c>
       <c r="E48" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F48" t="n" s="1">
         <v>0.0</v>
@@ -1458,19 +1467,19 @@
         <v>36</v>
       </c>
       <c r="D49" t="s" s="1">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E49" t="s" s="1">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="F49" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G49" t="n" s="1">
-        <v>12.47</v>
+        <v>332.0</v>
       </c>
       <c r="H49" t="n" s="1">
-        <v>-12.47</v>
+        <v>-332.0</v>
       </c>
     </row>
     <row r="50">
@@ -1487,16 +1496,16 @@
         <v>61</v>
       </c>
       <c r="E50" t="s" s="1">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F50" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G50" t="n" s="1">
-        <v>332.0</v>
+        <v>99.6</v>
       </c>
       <c r="H50" t="n" s="1">
-        <v>-332.0</v>
+        <v>-99.6</v>
       </c>
     </row>
     <row r="51">
@@ -1519,10 +1528,10 @@
         <v>0.0</v>
       </c>
       <c r="G51" t="n" s="1">
-        <v>99.6</v>
+        <v>232.4</v>
       </c>
       <c r="H51" t="n" s="1">
-        <v>-99.6</v>
+        <v>-232.4</v>
       </c>
     </row>
     <row r="52">
@@ -1530,25 +1539,25 @@
         <v>26</v>
       </c>
       <c r="B52" t="s" s="1">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s" s="1">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E52" t="s" s="1">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F52" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G52" t="n" s="1">
-        <v>232.4</v>
+        <v>1039.5</v>
       </c>
       <c r="H52" t="n" s="1">
-        <v>-232.4</v>
+        <v>-1039.5</v>
       </c>
     </row>
     <row r="53">
@@ -1556,13 +1565,13 @@
         <v>26</v>
       </c>
       <c r="B53" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D53" t="s" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E53" t="s" s="1">
         <v>30</v>
@@ -1582,16 +1591,16 @@
         <v>26</v>
       </c>
       <c r="B54" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C54" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D54" t="s" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E54" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F54" t="n" s="1">
         <v>0.0</v>
@@ -1608,25 +1617,25 @@
         <v>26</v>
       </c>
       <c r="B55" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D55" t="s" s="1">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E55" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F55" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G55" t="n" s="1">
-        <v>1039.5</v>
+        <v>12242.58</v>
       </c>
       <c r="H55" t="n" s="1">
-        <v>-1039.5</v>
+        <v>-12242.58</v>
       </c>
     </row>
     <row r="56">
@@ -1634,25 +1643,25 @@
         <v>26</v>
       </c>
       <c r="B56" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C56" t="s" s="1">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="D56" t="s" s="1">
         <v>70</v>
       </c>
       <c r="E56" t="s" s="1">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G56" t="n" s="1">
-        <v>12242.58</v>
+        <v>2163.0</v>
       </c>
       <c r="H56" t="n" s="1">
-        <v>-12242.58</v>
+        <v>-2163.0</v>
       </c>
     </row>
     <row r="57">
@@ -1660,25 +1669,25 @@
         <v>26</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C57" t="s" s="1">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s" s="1">
         <v>72</v>
       </c>
       <c r="E57" t="s" s="1">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F57" t="n" s="1">
-        <v>16924.71</v>
+        <v>0.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>0.0</v>
+        <v>1821.02</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>16924.71</v>
+        <v>-1821.02</v>
       </c>
     </row>
     <row r="58">
@@ -1686,13 +1695,13 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E58" t="s" s="1">
         <v>35</v>
@@ -1712,13 +1721,13 @@
         <v>26</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C59" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E59" t="s" s="1">
         <v>33</v>
@@ -1738,7 +1747,7 @@
         <v>26</v>
       </c>
       <c r="B60" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s" s="1">
         <v>31</v>
@@ -1764,13 +1773,13 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C61" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D61" t="s" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E61" t="s" s="1">
         <v>33</v>
@@ -1790,13 +1799,13 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D62" t="s" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s" s="1">
         <v>35</v>
@@ -1816,13 +1825,13 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
+        <v>77</v>
+      </c>
+      <c r="C63" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s" s="1">
         <v>78</v>
-      </c>
-      <c r="C63" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D63" t="s" s="1">
-        <v>79</v>
       </c>
       <c r="E63" t="s" s="1">
         <v>30</v>
@@ -1842,25 +1851,25 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
+        <v>77</v>
+      </c>
+      <c r="C64" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D64" t="s" s="1">
         <v>78</v>
       </c>
-      <c r="C64" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D64" t="s" s="1">
-        <v>80</v>
-      </c>
       <c r="E64" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F64" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>699.37</v>
+        <v>1019.7</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-699.37</v>
+        <v>-1019.7</v>
       </c>
     </row>
     <row r="65">
@@ -1868,25 +1877,25 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E65" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>1019.7</v>
+        <v>686.33</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-1019.7</v>
+        <v>-686.33</v>
       </c>
     </row>
     <row r="66">
@@ -1894,25 +1903,25 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>686.33</v>
+        <v>699.37</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-686.33</v>
+        <v>-699.37</v>
       </c>
     </row>
     <row r="67">
@@ -1920,16 +1929,16 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C67" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
@@ -1946,13 +1955,13 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C68" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D68" t="s" s="1">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="E68" t="s" s="1">
         <v>84</v>
@@ -1961,10 +1970,10 @@
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>968.0</v>
+        <v>750.0</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-968.0</v>
+        <v>-750.0</v>
       </c>
     </row>
     <row r="69">
@@ -1975,22 +1984,22 @@
         <v>85</v>
       </c>
       <c r="C69" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
         <v>86</v>
       </c>
       <c r="E69" t="s" s="1">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F69" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>750.0</v>
+        <v>260.15</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-750.0</v>
+        <v>-260.15</v>
       </c>
     </row>
     <row r="70">
@@ -1998,13 +2007,13 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E70" t="s" s="1">
         <v>30</v>
@@ -2024,25 +2033,25 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C71" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D71" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E71" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F71" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G71" t="n" s="1">
-        <v>1336.5</v>
+        <v>8758.14</v>
       </c>
       <c r="H71" t="n" s="1">
-        <v>-1336.5</v>
+        <v>-8758.14</v>
       </c>
     </row>
     <row r="72">
@@ -2050,25 +2059,25 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C72" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D72" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E72" t="s" s="1">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F72" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G72" t="n" s="1">
-        <v>8758.14</v>
+        <v>1336.5</v>
       </c>
       <c r="H72" t="n" s="1">
-        <v>-8758.14</v>
+        <v>-1336.5</v>
       </c>
     </row>
     <row r="73">
@@ -2076,25 +2085,25 @@
         <v>26</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C73" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D73" t="s" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E73" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G73" t="n" s="1">
-        <v>891.0</v>
+        <v>9559.08</v>
       </c>
       <c r="H73" t="n" s="1">
-        <v>-891.0</v>
+        <v>-9559.08</v>
       </c>
     </row>
     <row r="74">
@@ -2102,25 +2111,25 @@
         <v>26</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C74" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D74" t="s" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E74" t="s" s="1">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F74" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G74" t="n" s="1">
-        <v>9559.08</v>
+        <v>891.0</v>
       </c>
       <c r="H74" t="n" s="1">
-        <v>-9559.08</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="75">
@@ -2128,13 +2137,13 @@
         <v>26</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C75" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D75" t="s" s="1">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E75" t="s" s="1">
         <v>35</v>
@@ -2143,10 +2152,10 @@
         <v>0.0</v>
       </c>
       <c r="G75" t="n" s="1">
-        <v>714.08</v>
+        <v>21.19</v>
       </c>
       <c r="H75" t="n" s="1">
-        <v>-714.08</v>
+        <v>-21.19</v>
       </c>
     </row>
     <row r="76">
@@ -2154,13 +2163,13 @@
         <v>26</v>
       </c>
       <c r="B76" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C76" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D76" t="s" s="1">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E76" t="s" s="1">
         <v>33</v>
@@ -2169,10 +2178,10 @@
         <v>0.0</v>
       </c>
       <c r="G76" t="n" s="1">
-        <v>700.72</v>
+        <v>20.82</v>
       </c>
       <c r="H76" t="n" s="1">
-        <v>-700.72</v>
+        <v>-20.82</v>
       </c>
     </row>
     <row r="77">
@@ -2180,13 +2189,13 @@
         <v>26</v>
       </c>
       <c r="B77" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C77" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D77" t="s" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E77" t="s" s="1">
         <v>33</v>
@@ -2195,10 +2204,10 @@
         <v>0.0</v>
       </c>
       <c r="G77" t="n" s="1">
-        <v>764.9</v>
+        <v>700.72</v>
       </c>
       <c r="H77" t="n" s="1">
-        <v>-764.9</v>
+        <v>-700.72</v>
       </c>
     </row>
     <row r="78">
@@ -2206,13 +2215,13 @@
         <v>26</v>
       </c>
       <c r="B78" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D78" t="s" s="1">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E78" t="s" s="1">
         <v>35</v>
@@ -2221,10 +2230,10 @@
         <v>0.0</v>
       </c>
       <c r="G78" t="n" s="1">
-        <v>779.41</v>
+        <v>714.08</v>
       </c>
       <c r="H78" t="n" s="1">
-        <v>-779.41</v>
+        <v>-714.08</v>
       </c>
     </row>
     <row r="79">
@@ -2232,25 +2241,25 @@
         <v>26</v>
       </c>
       <c r="B79" t="s" s="1">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D79" t="s" s="1">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E79" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F79" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G79" t="n" s="1">
-        <v>6118.3</v>
+        <v>764.9</v>
       </c>
       <c r="H79" t="n" s="1">
-        <v>-6118.3</v>
+        <v>-764.9</v>
       </c>
     </row>
     <row r="80">
@@ -2258,25 +2267,25 @@
         <v>26</v>
       </c>
       <c r="B80" t="s" s="1">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D80" t="s" s="1">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F80" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G80" t="n" s="1">
-        <v>544.5</v>
+        <v>779.41</v>
       </c>
       <c r="H80" t="n" s="1">
-        <v>-544.5</v>
+        <v>-779.41</v>
       </c>
     </row>
     <row r="81">
@@ -2290,19 +2299,19 @@
         <v>28</v>
       </c>
       <c r="D81" t="s" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E81" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F81" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G81" t="n" s="1">
-        <v>891.0</v>
+        <v>544.5</v>
       </c>
       <c r="H81" t="n" s="1">
-        <v>-891.0</v>
+        <v>-544.5</v>
       </c>
     </row>
     <row r="82">
@@ -2313,22 +2322,22 @@
         <v>96</v>
       </c>
       <c r="C82" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D82" t="s" s="1">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E82" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F82" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G82" t="n" s="1">
-        <v>489.47</v>
+        <v>6118.3</v>
       </c>
       <c r="H82" t="n" s="1">
-        <v>-489.47</v>
+        <v>-6118.3</v>
       </c>
     </row>
     <row r="83">
@@ -2339,22 +2348,22 @@
         <v>96</v>
       </c>
       <c r="C83" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D83" t="s" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E83" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F83" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G83" t="n" s="1">
-        <v>498.88</v>
+        <v>891.0</v>
       </c>
       <c r="H83" t="n" s="1">
-        <v>-498.88</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="84">
@@ -2368,7 +2377,7 @@
         <v>31</v>
       </c>
       <c r="D84" t="s" s="1">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E84" t="s" s="1">
         <v>35</v>
@@ -2377,10 +2386,10 @@
         <v>0.0</v>
       </c>
       <c r="G84" t="n" s="1">
-        <v>644.44</v>
+        <v>498.88</v>
       </c>
       <c r="H84" t="n" s="1">
-        <v>-644.44</v>
+        <v>-498.88</v>
       </c>
     </row>
     <row r="85">
@@ -2394,7 +2403,7 @@
         <v>31</v>
       </c>
       <c r="D85" t="s" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E85" t="s" s="1">
         <v>33</v>
@@ -2403,10 +2412,10 @@
         <v>0.0</v>
       </c>
       <c r="G85" t="n" s="1">
-        <v>632.51</v>
+        <v>489.47</v>
       </c>
       <c r="H85" t="n" s="1">
-        <v>-632.51</v>
+        <v>-489.47</v>
       </c>
     </row>
     <row r="86">
@@ -2414,25 +2423,25 @@
         <v>26</v>
       </c>
       <c r="B86" t="s" s="1">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C86" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D86" t="s" s="1">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E86" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F86" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G86" t="n" s="1">
-        <v>21486.12</v>
+        <v>632.51</v>
       </c>
       <c r="H86" t="n" s="1">
-        <v>-21486.12</v>
+        <v>-632.51</v>
       </c>
     </row>
     <row r="87">
@@ -2440,25 +2449,25 @@
         <v>26</v>
       </c>
       <c r="B87" t="s" s="1">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C87" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D87" t="s" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E87" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F87" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G87" t="n" s="1">
-        <v>2227.5</v>
+        <v>644.44</v>
       </c>
       <c r="H87" t="n" s="1">
-        <v>-2227.5</v>
+        <v>-644.44</v>
       </c>
     </row>
     <row r="88">
@@ -2469,22 +2478,22 @@
         <v>103</v>
       </c>
       <c r="C88" t="s" s="1">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D88" t="s" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E88" t="s" s="1">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="F88" t="n" s="1">
-        <v>3500.0</v>
+        <v>0.0</v>
       </c>
       <c r="G88" t="n" s="1">
-        <v>0.0</v>
+        <v>21486.12</v>
       </c>
       <c r="H88" t="n" s="1">
-        <v>3500.0</v>
+        <v>-21486.12</v>
       </c>
     </row>
     <row r="89">
@@ -2495,22 +2504,22 @@
         <v>103</v>
       </c>
       <c r="C89" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D89" t="s" s="1">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E89" t="s" s="1">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F89" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G89" t="n" s="1">
-        <v>1718.89</v>
+        <v>2227.5</v>
       </c>
       <c r="H89" t="n" s="1">
-        <v>-1718.89</v>
+        <v>-2227.5</v>
       </c>
     </row>
     <row r="90">
@@ -2521,22 +2530,22 @@
         <v>103</v>
       </c>
       <c r="C90" t="s" s="1">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="D90" t="s" s="1">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E90" t="s" s="1">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="F90" t="n" s="1">
-        <v>0.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G90" t="n" s="1">
-        <v>1751.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n" s="1">
-        <v>-1751.0</v>
+        <v>3500.0</v>
       </c>
     </row>
     <row r="91">
@@ -2544,25 +2553,25 @@
         <v>26</v>
       </c>
       <c r="B91" t="s" s="1">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s" s="1">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E91" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F91" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G91" t="n" s="1">
-        <v>155.01</v>
+        <v>1718.89</v>
       </c>
       <c r="H91" t="n" s="1">
-        <v>-155.01</v>
+        <v>-1718.89</v>
       </c>
     </row>
     <row r="92">
@@ -2570,25 +2579,25 @@
         <v>26</v>
       </c>
       <c r="B92" t="s" s="1">
+        <v>103</v>
+      </c>
+      <c r="C92" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D92" t="s" s="1">
         <v>109</v>
       </c>
-      <c r="C92" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D92" t="s" s="1">
-        <v>111</v>
-      </c>
       <c r="E92" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F92" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G92" t="n" s="1">
-        <v>15066.07</v>
+        <v>1751.0</v>
       </c>
       <c r="H92" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-1751.0</v>
       </c>
     </row>
     <row r="93">
@@ -2596,7 +2605,7 @@
         <v>26</v>
       </c>
       <c r="B93" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C93" t="s" s="1">
         <v>28</v>
@@ -2605,16 +2614,16 @@
         <v>111</v>
       </c>
       <c r="E93" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F93" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G93" t="n" s="1">
-        <v>1435.5</v>
+        <v>155.01</v>
       </c>
       <c r="H93" t="n" s="1">
-        <v>-1435.5</v>
+        <v>-155.01</v>
       </c>
     </row>
     <row r="94">
@@ -2622,7 +2631,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C94" t="s" s="1">
         <v>28</v>
@@ -2637,10 +2646,10 @@
         <v>0.0</v>
       </c>
       <c r="G94" t="n" s="1">
-        <v>2283.05</v>
+        <v>15066.07</v>
       </c>
       <c r="H94" t="n" s="1">
-        <v>-2283.05</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="95">
@@ -2648,7 +2657,7 @@
         <v>26</v>
       </c>
       <c r="B95" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C95" t="s" s="1">
         <v>28</v>
@@ -2657,16 +2666,16 @@
         <v>112</v>
       </c>
       <c r="E95" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F95" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G95" t="n" s="1">
-        <v>297.0</v>
+        <v>1435.5</v>
       </c>
       <c r="H95" t="n" s="1">
-        <v>-297.0</v>
+        <v>-1435.5</v>
       </c>
     </row>
     <row r="96">
@@ -2674,25 +2683,25 @@
         <v>26</v>
       </c>
       <c r="B96" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C96" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D96" t="s" s="1">
         <v>113</v>
       </c>
       <c r="E96" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F96" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G96" t="n" s="1">
-        <v>1227.73</v>
+        <v>297.0</v>
       </c>
       <c r="H96" t="n" s="1">
-        <v>-1227.73</v>
+        <v>-297.0</v>
       </c>
     </row>
     <row r="97">
@@ -2700,25 +2709,25 @@
         <v>26</v>
       </c>
       <c r="B97" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C97" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D97" t="s" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E97" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F97" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G97" t="n" s="1">
-        <v>1205.61</v>
+        <v>2283.05</v>
       </c>
       <c r="H97" t="n" s="1">
-        <v>-1205.61</v>
+        <v>-2283.05</v>
       </c>
     </row>
     <row r="98">
@@ -2726,25 +2735,25 @@
         <v>26</v>
       </c>
       <c r="B98" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D98" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E98" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F98" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G98" t="n" s="1">
-        <v>182.66</v>
+        <v>1227.73</v>
       </c>
       <c r="H98" t="n" s="1">
-        <v>-182.66</v>
+        <v>-1227.73</v>
       </c>
     </row>
     <row r="99">
@@ -2752,25 +2761,25 @@
         <v>26</v>
       </c>
       <c r="B99" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C99" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D99" t="s" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E99" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F99" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G99" t="n" s="1">
-        <v>186.06</v>
+        <v>1205.61</v>
       </c>
       <c r="H99" t="n" s="1">
-        <v>-186.06</v>
+        <v>-1205.61</v>
       </c>
     </row>
     <row r="100">
@@ -2778,25 +2787,25 @@
         <v>26</v>
       </c>
       <c r="B100" t="s" s="1">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C100" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D100" t="s" s="1">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="E100" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F100" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G100" t="n" s="1">
-        <v>100.0</v>
+        <v>182.66</v>
       </c>
       <c r="H100" t="n" s="1">
-        <v>-100.0</v>
+        <v>-182.66</v>
       </c>
     </row>
     <row r="101">
@@ -2804,25 +2813,25 @@
         <v>26</v>
       </c>
       <c r="B101" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="C101" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D101" t="s" s="1">
         <v>117</v>
       </c>
-      <c r="C101" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D101" t="s" s="1">
-        <v>45</v>
-      </c>
       <c r="E101" t="s" s="1">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="F101" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G101" t="n" s="1">
-        <v>4588.5</v>
+        <v>186.06</v>
       </c>
       <c r="H101" t="n" s="1">
-        <v>-4588.5</v>
+        <v>-186.06</v>
       </c>
     </row>
     <row r="102">
@@ -2830,25 +2839,25 @@
         <v>26</v>
       </c>
       <c r="B102" t="s" s="1">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C102" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s" s="1">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="E102" t="s" s="1">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="F102" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G102" t="n" s="1">
-        <v>239.58</v>
+        <v>100.0</v>
       </c>
       <c r="H102" t="n" s="1">
-        <v>-239.58</v>
+        <v>-100.0</v>
       </c>
     </row>
     <row r="103">
@@ -2856,25 +2865,25 @@
         <v>26</v>
       </c>
       <c r="B103" t="s" s="1">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C103" t="s" s="1">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="D103" t="s" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E103" t="s" s="1">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F103" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G103" t="n" s="1">
-        <v>0.0</v>
+        <v>4588.5</v>
       </c>
       <c r="H103" t="n" s="1">
-        <v>840.0</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="104">
@@ -2882,25 +2891,25 @@
         <v>26</v>
       </c>
       <c r="B104" t="s" s="1">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C104" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D104" t="s" s="1">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="E104" t="s" s="1">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F104" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G104" t="n" s="1">
-        <v>1500.0</v>
+        <v>239.58</v>
       </c>
       <c r="H104" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="105">
@@ -2908,25 +2917,25 @@
         <v>26</v>
       </c>
       <c r="B105" t="s" s="1">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C105" t="s" s="1">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="D105" t="s" s="1">
         <v>44</v>
       </c>
       <c r="E105" t="s" s="1">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F105" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G105" t="n" s="1">
-        <v>15000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H105" t="n" s="1">
-        <v>-15000.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="106">
@@ -2934,25 +2943,25 @@
         <v>26</v>
       </c>
       <c r="B106" t="s" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C106" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D106" t="s" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E106" t="s" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F106" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G106" t="n" s="1">
-        <v>4500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="H106" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="107">
@@ -2960,25 +2969,25 @@
         <v>26</v>
       </c>
       <c r="B107" t="s" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C107" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D107" t="s" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E107" t="s" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F107" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G107" t="n" s="1">
-        <v>2000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H107" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="108">
@@ -2986,25 +2995,25 @@
         <v>26</v>
       </c>
       <c r="B108" t="s" s="1">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C108" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D108" t="s" s="1">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="E108" t="s" s="1">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F108" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G108" t="n" s="1">
-        <v>146.67</v>
+        <v>15000.0</v>
       </c>
       <c r="H108" t="n" s="1">
-        <v>-146.67</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="109">
@@ -3012,25 +3021,25 @@
         <v>26</v>
       </c>
       <c r="B109" t="s" s="1">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C109" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D109" t="s" s="1">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E109" t="s" s="1">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="F109" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G109" t="n" s="1">
-        <v>180.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H109" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="110">
@@ -3038,25 +3047,25 @@
         <v>26</v>
       </c>
       <c r="B110" t="s" s="1">
+        <v>129</v>
+      </c>
+      <c r="C110" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D110" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="E110" t="s" s="1">
         <v>131</v>
       </c>
-      <c r="C110" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D110" t="s" s="1">
-        <v>41</v>
-      </c>
-      <c r="E110" t="s" s="1">
-        <v>30</v>
-      </c>
       <c r="F110" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G110" t="n" s="1">
-        <v>9216.24</v>
+        <v>146.67</v>
       </c>
       <c r="H110" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="111">
@@ -3064,25 +3073,25 @@
         <v>26</v>
       </c>
       <c r="B111" t="s" s="1">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C111" t="s" s="1">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D111" t="s" s="1">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="E111" t="s" s="1">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F111" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G111" t="n" s="1">
-        <v>891.0</v>
+        <v>180.0</v>
       </c>
       <c r="H111" t="n" s="1">
-        <v>-891.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="112">
@@ -3090,25 +3099,25 @@
         <v>26</v>
       </c>
       <c r="B112" t="s" s="1">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C112" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D112" t="s" s="1">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="E112" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F112" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G112" t="n" s="1">
-        <v>750.99</v>
+        <v>9216.24</v>
       </c>
       <c r="H112" t="n" s="1">
-        <v>-750.99</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="113">
@@ -3116,25 +3125,25 @@
         <v>26</v>
       </c>
       <c r="B113" t="s" s="1">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C113" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D113" t="s" s="1">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E113" t="s" s="1">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F113" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G113" t="n" s="1">
-        <v>737.28</v>
+        <v>891.0</v>
       </c>
       <c r="H113" t="n" s="1">
-        <v>-737.28</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="114">
@@ -3142,25 +3151,25 @@
         <v>26</v>
       </c>
       <c r="B114" t="s" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C114" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D114" t="s" s="1">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E114" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F114" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G114" t="n" s="1">
-        <v>1544.4</v>
+        <v>737.28</v>
       </c>
       <c r="H114" t="n" s="1">
-        <v>-1544.4</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="115">
@@ -3168,25 +3177,25 @@
         <v>26</v>
       </c>
       <c r="B115" t="s" s="1">
+        <v>132</v>
+      </c>
+      <c r="C115" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D115" t="s" s="1">
         <v>133</v>
       </c>
-      <c r="C115" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D115" t="s" s="1">
-        <v>86</v>
-      </c>
       <c r="E115" t="s" s="1">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="F115" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G115" t="n" s="1">
-        <v>180.06</v>
+        <v>750.99</v>
       </c>
       <c r="H115" t="n" s="1">
-        <v>-180.06</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="116">
@@ -3194,25 +3203,25 @@
         <v>26</v>
       </c>
       <c r="B116" t="s" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C116" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D116" t="s" s="1">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="E116" t="s" s="1">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="F116" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G116" t="n" s="1">
-        <v>1925.0</v>
+        <v>1544.4</v>
       </c>
       <c r="H116" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="117">
@@ -3220,25 +3229,25 @@
         <v>26</v>
       </c>
       <c r="B117" t="s" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C117" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D117" t="s" s="1">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E117" t="s" s="1">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="F117" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G117" t="n" s="1">
-        <v>180.0</v>
+        <v>180.06</v>
       </c>
       <c r="H117" t="n" s="1">
-        <v>-180.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="118">
@@ -3246,25 +3255,25 @@
         <v>26</v>
       </c>
       <c r="B118" t="s" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C118" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D118" t="s" s="1">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="E118" t="s" s="1">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="F118" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G118" t="n" s="1">
-        <v>180.0</v>
+        <v>1925.0</v>
       </c>
       <c r="H118" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="119">
@@ -3272,25 +3281,25 @@
         <v>26</v>
       </c>
       <c r="B119" t="s" s="1">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C119" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D119" t="s" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E119" t="s" s="1">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="F119" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G119" t="n" s="1">
-        <v>1201.89</v>
+        <v>180.0</v>
       </c>
       <c r="H119" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="120">
@@ -3298,16 +3307,16 @@
         <v>26</v>
       </c>
       <c r="B120" t="s" s="1">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C120" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D120" t="s" s="1">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E120" t="s" s="1">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F120" t="n" s="1">
         <v>0.0</v>
@@ -3324,25 +3333,25 @@
         <v>26</v>
       </c>
       <c r="B121" t="s" s="1">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C121" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D121" t="s" s="1">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E121" t="s" s="1">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="F121" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G121" t="n" s="1">
-        <v>180.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H121" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="122">
@@ -3350,25 +3359,25 @@
         <v>26</v>
       </c>
       <c r="B122" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C122" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D122" t="s" s="1">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E122" t="s" s="1">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F122" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G122" t="n" s="1">
-        <v>2040.52</v>
+        <v>180.0</v>
       </c>
       <c r="H122" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="123">
@@ -3376,25 +3385,25 @@
         <v>26</v>
       </c>
       <c r="B123" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C123" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D123" t="s" s="1">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>2277.0</v>
+        <v>180.0</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="124">
@@ -3402,25 +3411,25 @@
         <v>26</v>
       </c>
       <c r="B124" t="s" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C124" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D124" t="s" s="1">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>2078.64</v>
+        <v>25504.78</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-2078.64</v>
+        <v>-25504.78</v>
       </c>
     </row>
     <row r="125">
@@ -3428,25 +3437,25 @@
         <v>26</v>
       </c>
       <c r="B125" t="s" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C125" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D125" t="s" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E125" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F125" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G125" t="n" s="1">
-        <v>25504.78</v>
+        <v>2040.52</v>
       </c>
       <c r="H125" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-2040.52</v>
       </c>
     </row>
     <row r="126">
@@ -3454,25 +3463,25 @@
         <v>26</v>
       </c>
       <c r="B126" t="s" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C126" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D126" t="s" s="1">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="E126" t="s" s="1">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="F126" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G126" t="n" s="1">
-        <v>180.0</v>
+        <v>2078.64</v>
       </c>
       <c r="H126" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2078.64</v>
       </c>
     </row>
     <row r="127">
@@ -3480,25 +3489,25 @@
         <v>26</v>
       </c>
       <c r="B127" t="s" s="1">
+        <v>140</v>
+      </c>
+      <c r="C127" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D127" t="s" s="1">
         <v>142</v>
       </c>
-      <c r="C127" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D127" t="s" s="1">
-        <v>112</v>
-      </c>
       <c r="E127" t="s" s="1">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="F127" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G127" t="n" s="1">
-        <v>180.0</v>
+        <v>2277.0</v>
       </c>
       <c r="H127" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2277.0</v>
       </c>
     </row>
     <row r="128">
@@ -3506,25 +3515,25 @@
         <v>26</v>
       </c>
       <c r="B128" t="s" s="1">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C128" t="s" s="1">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="D128" t="s" s="1">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="E128" t="s" s="1">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="F128" t="n" s="1">
-        <v>1816.53</v>
+        <v>0.0</v>
       </c>
       <c r="G128" t="n" s="1">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="H128" t="n" s="1">
-        <v>1816.53</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="129">
@@ -3538,19 +3547,19 @@
         <v>43</v>
       </c>
       <c r="D129" t="s" s="1">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>3750.0</v>
+        <v>180.0</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-3750.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="130">
@@ -3558,49 +3567,127 @@
         <v>26</v>
       </c>
       <c r="B130" t="s" s="1">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C130" t="s" s="1">
+        <v>105</v>
+      </c>
+      <c r="D130" t="s" s="1">
+        <v>145</v>
+      </c>
+      <c r="E130" t="s" s="1">
+        <v>146</v>
+      </c>
+      <c r="F130" t="n" s="1">
+        <v>1816.53</v>
+      </c>
+      <c r="G130" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H130" t="n" s="1">
+        <v>1816.53</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B131" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C131" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="D130" t="s" s="1">
-        <v>45</v>
-      </c>
-      <c r="E130" t="s" s="1">
+      <c r="D131" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="E131" t="s" s="1">
         <v>147</v>
       </c>
-      <c r="F130" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G130" t="n" s="1">
+      <c r="F131" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G131" t="n" s="1">
         <v>1000.0</v>
       </c>
-      <c r="H130" t="n" s="1">
+      <c r="H131" t="n" s="1">
         <v>-1000.0</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B132" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C132" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D132" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="E132" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="F132" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G132" t="n" s="1">
+        <v>3750.0</v>
+      </c>
+      <c r="H132" t="n" s="1">
+        <v>-3750.0</v>
+      </c>
+    </row>
     <row r="133">
-      <c r="A133" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B133" s="3" t="s">
+      <c r="A133" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B133" t="s" s="1">
         <v>149</v>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="s">
+      <c r="C133" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D133" t="s" s="1">
         <v>150</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="E133" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="F133" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G133" t="n" s="1">
+        <v>1255.07</v>
+      </c>
+      <c r="H133" t="n" s="1">
+        <v>-1255.07</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="s">
+      <c r="B136" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B135" s="3" t="s">
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="s">
         <v>153</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="166">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -150,12 +150,12 @@
     <t>1 - 8</t>
   </si>
   <si>
+    <t>Hostgator</t>
+  </si>
+  <si>
     <t>Eric Kevin de Souza Serpa</t>
   </si>
   <si>
-    <t>Hostgator</t>
-  </si>
-  <si>
     <t>1 - 9</t>
   </si>
   <si>
@@ -165,12 +165,12 @@
     <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
   </si>
   <si>
+    <t>100901 - 2</t>
+  </si>
+  <si>
     <t>TERESINHA ELVIRA MAXIMINO DE MENEZES</t>
   </si>
   <si>
-    <t>100901 - 2</t>
-  </si>
-  <si>
     <t>102301 - 2</t>
   </si>
   <si>
@@ -195,12 +195,12 @@
     <t>102901 - 1</t>
   </si>
   <si>
+    <t>103501 - 1</t>
+  </si>
+  <si>
     <t>103501 - 2</t>
   </si>
   <si>
-    <t>103501 - 1</t>
-  </si>
-  <si>
     <t>08/10/2026</t>
   </si>
   <si>
@@ -234,12 +234,12 @@
     <t>92801 - 0</t>
   </si>
   <si>
+    <t>96601 - 2</t>
+  </si>
+  <si>
     <t>96601 - 3</t>
   </si>
   <si>
-    <t>96601 - 2</t>
-  </si>
-  <si>
     <t>101401 - 2</t>
   </si>
   <si>
@@ -252,174 +252,204 @@
     <t>100501 - 1</t>
   </si>
   <si>
+    <t>100501 - 3</t>
+  </si>
+  <si>
     <t>100501 - 2</t>
   </si>
   <si>
-    <t>100501 - 3</t>
-  </si>
-  <si>
     <t>PREFEITURA SP- ISS</t>
   </si>
   <si>
-    <t>12/10/2026</t>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>1630 - 1</t>
+  </si>
+  <si>
+    <t>49501 - 2</t>
+  </si>
+  <si>
+    <t>100301 - 1</t>
+  </si>
+  <si>
+    <t>102101 - 1</t>
+  </si>
+  <si>
+    <t>1630 - 3</t>
+  </si>
+  <si>
+    <t>1630 - 2</t>
+  </si>
+  <si>
+    <t>100301 - 2</t>
+  </si>
+  <si>
+    <t>100301 - 3</t>
+  </si>
+  <si>
+    <t>102101 - 2</t>
+  </si>
+  <si>
+    <t>102101 - 3</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>1631 - 1</t>
+  </si>
+  <si>
+    <t>1632 - 1</t>
+  </si>
+  <si>
+    <t>1633 - 1</t>
+  </si>
+  <si>
+    <t>1634 - 1</t>
+  </si>
+  <si>
+    <t>101201 - 1</t>
+  </si>
+  <si>
+    <t>101801 - 1</t>
+  </si>
+  <si>
+    <t>1631 - 2</t>
+  </si>
+  <si>
+    <t>1631 - 3</t>
+  </si>
+  <si>
+    <t>1632 - 3</t>
+  </si>
+  <si>
+    <t>1632 - 2</t>
+  </si>
+  <si>
+    <t>1633 - 3</t>
+  </si>
+  <si>
+    <t>1633 - 2</t>
+  </si>
+  <si>
+    <t>1634 - 3</t>
+  </si>
+  <si>
+    <t>1634 - 2</t>
+  </si>
+  <si>
+    <t>101201 - 3</t>
+  </si>
+  <si>
+    <t>101201 - 2</t>
+  </si>
+  <si>
+    <t>101801 - 3</t>
+  </si>
+  <si>
+    <t>101801 - 2</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>101101 - 1</t>
+  </si>
+  <si>
+    <t>DUP-Duplicata de Contrato</t>
+  </si>
+  <si>
+    <t>103501 - 0</t>
+  </si>
+  <si>
+    <t>IL HEE PARK</t>
+  </si>
+  <si>
+    <t>101101 - 3</t>
+  </si>
+  <si>
+    <t>101101 - 2</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>92001 - 2</t>
+  </si>
+  <si>
+    <t>102401 - 1</t>
+  </si>
+  <si>
+    <t>102501 - 1</t>
+  </si>
+  <si>
+    <t>102401 - 3</t>
+  </si>
+  <si>
+    <t>102401 - 2</t>
+  </si>
+  <si>
+    <t>102501 - 2</t>
+  </si>
+  <si>
+    <t>102501 - 3</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>12 - 8</t>
+  </si>
+  <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>PFR-Previsões Financeiras a Receber</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>Simples Nacional - DAS</t>
+  </si>
+  <si>
+    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>64 - 4</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>102301 - 3</t>
+  </si>
+  <si>
+    <t>25/10/2026</t>
   </si>
   <si>
     <t>2 - 9</t>
   </si>
   <si>
-    <t>Enel</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>1630 - 1</t>
-  </si>
-  <si>
-    <t>49501 - 2</t>
-  </si>
-  <si>
-    <t>100301 - 1</t>
-  </si>
-  <si>
-    <t>102101 - 1</t>
-  </si>
-  <si>
-    <t>1630 - 3</t>
-  </si>
-  <si>
-    <t>1630 - 2</t>
-  </si>
-  <si>
-    <t>100301 - 2</t>
-  </si>
-  <si>
-    <t>100301 - 3</t>
-  </si>
-  <si>
-    <t>102101 - 2</t>
-  </si>
-  <si>
-    <t>102101 - 3</t>
-  </si>
-  <si>
-    <t>14/10/2026</t>
-  </si>
-  <si>
-    <t>101201 - 1</t>
-  </si>
-  <si>
-    <t>101801 - 1</t>
-  </si>
-  <si>
-    <t>101201 - 3</t>
-  </si>
-  <si>
-    <t>101201 - 2</t>
-  </si>
-  <si>
-    <t>101801 - 2</t>
-  </si>
-  <si>
-    <t>101801 - 3</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>101101 - 1</t>
-  </si>
-  <si>
-    <t>DUP-Duplicata de Contrato</t>
-  </si>
-  <si>
-    <t>103501 - 0</t>
-  </si>
-  <si>
-    <t>IL HEE PARK</t>
-  </si>
-  <si>
-    <t>101101 - 2</t>
-  </si>
-  <si>
-    <t>101101 - 3</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>92001 - 2</t>
-  </si>
-  <si>
-    <t>102401 - 1</t>
-  </si>
-  <si>
-    <t>102501 - 1</t>
-  </si>
-  <si>
-    <t>102401 - 3</t>
-  </si>
-  <si>
-    <t>102401 - 2</t>
-  </si>
-  <si>
-    <t>102501 - 2</t>
-  </si>
-  <si>
-    <t>102501 - 3</t>
-  </si>
-  <si>
-    <t>18/10/2026</t>
-  </si>
-  <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>12 - 8</t>
-  </si>
-  <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>PFR-Previsões Financeiras a Receber</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>Simples Nacional - DAS</t>
-  </si>
-  <si>
-    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
-  </si>
-  <si>
-    <t>22/10/2026</t>
-  </si>
-  <si>
-    <t>64 - 4</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>23/10/2026</t>
-  </si>
-  <si>
-    <t>102301 - 3</t>
-  </si>
-  <si>
-    <t>25/10/2026</t>
-  </si>
-  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -441,9 +471,6 @@
     <t>100901 - 3</t>
   </si>
   <si>
-    <t>100901 - 4</t>
-  </si>
-  <si>
     <t>29/10/2026</t>
   </si>
   <si>
@@ -456,12 +483,12 @@
     <t>GABRIEL DE CARVALHO MELLO</t>
   </si>
   <si>
+    <t>Facebook</t>
+  </si>
+  <si>
     <t>SEFAZ SP DARE - ICMS</t>
   </si>
   <si>
-    <t>Facebook</t>
-  </si>
-  <si>
     <t>31/10/2026</t>
   </si>
   <si>
@@ -477,13 +504,13 @@
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>261.055,13</t>
+    <t>261.986,79</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-254.898,60</t>
+    <t>-255.830,26</t>
   </si>
 </sst>
 </file>
@@ -551,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H138"/>
+  <dimension ref="A2:H149"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -852,10 +879,10 @@
         <v>0.0</v>
       </c>
       <c r="G25" t="n" s="1">
-        <v>2536.0</v>
+        <v>9.99</v>
       </c>
       <c r="H25" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="26">
@@ -878,10 +905,10 @@
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>9.99</v>
+        <v>2536.0</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-9.99</v>
+        <v>-2536.0</v>
       </c>
     </row>
     <row r="27">
@@ -947,19 +974,19 @@
         <v>36</v>
       </c>
       <c r="D29" t="s" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s" s="1">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F29" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>607.95</v>
+        <v>1215.9</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-607.95</v>
+        <v>-1215.9</v>
       </c>
     </row>
     <row r="30">
@@ -973,19 +1000,19 @@
         <v>36</v>
       </c>
       <c r="D30" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E30" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="E30" t="s" s="1">
-        <v>39</v>
-      </c>
       <c r="F30" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G30" t="n" s="1">
-        <v>1215.9</v>
+        <v>607.95</v>
       </c>
       <c r="H30" t="n" s="1">
-        <v>-1215.9</v>
+        <v>-607.95</v>
       </c>
     </row>
     <row r="31">
@@ -999,10 +1026,10 @@
         <v>36</v>
       </c>
       <c r="D31" t="s" s="1">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s" s="1">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F31" t="n" s="1">
         <v>0.0</v>
@@ -1025,10 +1052,10 @@
         <v>36</v>
       </c>
       <c r="D32" t="s" s="1">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E32" t="s" s="1">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F32" t="n" s="1">
         <v>0.0</v>
@@ -1054,7 +1081,7 @@
         <v>41</v>
       </c>
       <c r="E33" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F33" t="n" s="1">
         <v>0.0</v>
@@ -1080,16 +1107,16 @@
         <v>48</v>
       </c>
       <c r="E34" t="s" s="1">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G34" t="n" s="1">
-        <v>6079.52</v>
+        <v>1823.86</v>
       </c>
       <c r="H34" t="n" s="1">
-        <v>-6079.52</v>
+        <v>-1823.86</v>
       </c>
     </row>
     <row r="35">
@@ -1106,16 +1133,16 @@
         <v>48</v>
       </c>
       <c r="E35" t="s" s="1">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F35" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G35" t="n" s="1">
-        <v>1823.86</v>
+        <v>6079.52</v>
       </c>
       <c r="H35" t="n" s="1">
-        <v>-1823.86</v>
+        <v>-6079.52</v>
       </c>
     </row>
     <row r="36">
@@ -1158,16 +1185,16 @@
         <v>41</v>
       </c>
       <c r="E37" t="s" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F37" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G37" t="n" s="1">
-        <v>666.18</v>
+        <v>1554.41</v>
       </c>
       <c r="H37" t="n" s="1">
-        <v>-666.18</v>
+        <v>-1554.41</v>
       </c>
     </row>
     <row r="38">
@@ -1184,16 +1211,16 @@
         <v>41</v>
       </c>
       <c r="E38" t="s" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F38" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G38" t="n" s="1">
-        <v>1554.41</v>
+        <v>666.18</v>
       </c>
       <c r="H38" t="n" s="1">
-        <v>-1554.41</v>
+        <v>-666.18</v>
       </c>
     </row>
     <row r="39">
@@ -1288,7 +1315,7 @@
         <v>59</v>
       </c>
       <c r="E42" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F42" t="n" s="1">
         <v>0.0</v>
@@ -1314,7 +1341,7 @@
         <v>60</v>
       </c>
       <c r="E43" t="s" s="1">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F43" t="n" s="1">
         <v>0.0</v>
@@ -1340,7 +1367,7 @@
         <v>61</v>
       </c>
       <c r="E44" t="s" s="1">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F44" t="n" s="1">
         <v>0.0</v>
@@ -1363,10 +1390,10 @@
         <v>36</v>
       </c>
       <c r="D45" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E45" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F45" t="n" s="1">
         <v>0.0</v>
@@ -1418,16 +1445,16 @@
         <v>59</v>
       </c>
       <c r="E47" t="s" s="1">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F47" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G47" t="n" s="1">
-        <v>12.47</v>
+        <v>17.81</v>
       </c>
       <c r="H47" t="n" s="1">
-        <v>-12.47</v>
+        <v>-17.81</v>
       </c>
     </row>
     <row r="48">
@@ -1444,16 +1471,16 @@
         <v>59</v>
       </c>
       <c r="E48" t="s" s="1">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F48" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G48" t="n" s="1">
-        <v>17.81</v>
+        <v>12.47</v>
       </c>
       <c r="H48" t="n" s="1">
-        <v>-17.81</v>
+        <v>-12.47</v>
       </c>
     </row>
     <row r="49">
@@ -1467,19 +1494,19 @@
         <v>36</v>
       </c>
       <c r="D49" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E49" t="s" s="1">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F49" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G49" t="n" s="1">
-        <v>332.0</v>
+        <v>232.4</v>
       </c>
       <c r="H49" t="n" s="1">
-        <v>-332.0</v>
+        <v>-232.4</v>
       </c>
     </row>
     <row r="50">
@@ -1493,19 +1520,19 @@
         <v>36</v>
       </c>
       <c r="D50" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E50" t="s" s="1">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F50" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G50" t="n" s="1">
-        <v>99.6</v>
+        <v>332.0</v>
       </c>
       <c r="H50" t="n" s="1">
-        <v>-99.6</v>
+        <v>-332.0</v>
       </c>
     </row>
     <row r="51">
@@ -1519,19 +1546,19 @@
         <v>36</v>
       </c>
       <c r="D51" t="s" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E51" t="s" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F51" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G51" t="n" s="1">
-        <v>232.4</v>
+        <v>99.6</v>
       </c>
       <c r="H51" t="n" s="1">
-        <v>-232.4</v>
+        <v>-99.6</v>
       </c>
     </row>
     <row r="52">
@@ -1600,16 +1627,16 @@
         <v>68</v>
       </c>
       <c r="E54" t="s" s="1">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F54" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G54" t="n" s="1">
-        <v>1039.5</v>
+        <v>12242.58</v>
       </c>
       <c r="H54" t="n" s="1">
-        <v>-1039.5</v>
+        <v>-12242.58</v>
       </c>
     </row>
     <row r="55">
@@ -1626,16 +1653,16 @@
         <v>68</v>
       </c>
       <c r="E55" t="s" s="1">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F55" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G55" t="n" s="1">
-        <v>12242.58</v>
+        <v>1039.5</v>
       </c>
       <c r="H55" t="n" s="1">
-        <v>-12242.58</v>
+        <v>-1039.5</v>
       </c>
     </row>
     <row r="56">
@@ -1704,16 +1731,16 @@
         <v>73</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F58" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G58" t="n" s="1">
-        <v>1237.52</v>
+        <v>1214.79</v>
       </c>
       <c r="H58" t="n" s="1">
-        <v>-1237.52</v>
+        <v>-1214.79</v>
       </c>
     </row>
     <row r="59">
@@ -1730,16 +1757,16 @@
         <v>74</v>
       </c>
       <c r="E59" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>1214.79</v>
+        <v>1237.52</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>-1214.79</v>
+        <v>-1237.52</v>
       </c>
     </row>
     <row r="60">
@@ -1886,16 +1913,16 @@
         <v>79</v>
       </c>
       <c r="E65" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>686.33</v>
+        <v>699.37</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-686.33</v>
+        <v>-699.37</v>
       </c>
     </row>
     <row r="66">
@@ -1912,16 +1939,16 @@
         <v>80</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>699.37</v>
+        <v>686.33</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-699.37</v>
+        <v>-686.33</v>
       </c>
     </row>
     <row r="67">
@@ -1958,22 +1985,22 @@
         <v>82</v>
       </c>
       <c r="C68" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D68" t="s" s="1">
         <v>83</v>
       </c>
       <c r="E68" t="s" s="1">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>750.0</v>
+        <v>260.15</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-750.0</v>
+        <v>-260.15</v>
       </c>
     </row>
     <row r="69">
@@ -1981,13 +2008,13 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E69" t="s" s="1">
         <v>30</v>
@@ -1996,10 +2023,10 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>260.15</v>
+        <v>560.42</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-260.15</v>
+        <v>-560.42</v>
       </c>
     </row>
     <row r="70">
@@ -2007,13 +2034,13 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E70" t="s" s="1">
         <v>30</v>
@@ -2022,10 +2049,10 @@
         <v>0.0</v>
       </c>
       <c r="G70" t="n" s="1">
-        <v>560.42</v>
+        <v>8758.14</v>
       </c>
       <c r="H70" t="n" s="1">
-        <v>-560.42</v>
+        <v>-8758.14</v>
       </c>
     </row>
     <row r="71">
@@ -2033,25 +2060,25 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C71" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D71" t="s" s="1">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E71" t="s" s="1">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F71" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G71" t="n" s="1">
-        <v>8758.14</v>
+        <v>1336.5</v>
       </c>
       <c r="H71" t="n" s="1">
-        <v>-8758.14</v>
+        <v>-1336.5</v>
       </c>
     </row>
     <row r="72">
@@ -2059,25 +2086,25 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C72" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D72" t="s" s="1">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E72" t="s" s="1">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F72" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G72" t="n" s="1">
-        <v>1336.5</v>
+        <v>9559.08</v>
       </c>
       <c r="H72" t="n" s="1">
-        <v>-1336.5</v>
+        <v>-9559.08</v>
       </c>
     </row>
     <row r="73">
@@ -2085,25 +2112,25 @@
         <v>26</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C73" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D73" t="s" s="1">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E73" t="s" s="1">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F73" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G73" t="n" s="1">
-        <v>9559.08</v>
+        <v>891.0</v>
       </c>
       <c r="H73" t="n" s="1">
-        <v>-9559.08</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="74">
@@ -2111,25 +2138,25 @@
         <v>26</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C74" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D74" t="s" s="1">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E74" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G74" t="n" s="1">
-        <v>891.0</v>
+        <v>21.19</v>
       </c>
       <c r="H74" t="n" s="1">
-        <v>-891.0</v>
+        <v>-21.19</v>
       </c>
     </row>
     <row r="75">
@@ -2137,25 +2164,25 @@
         <v>26</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C75" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D75" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E75" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F75" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G75" t="n" s="1">
-        <v>21.19</v>
+        <v>20.82</v>
       </c>
       <c r="H75" t="n" s="1">
-        <v>-21.19</v>
+        <v>-20.82</v>
       </c>
     </row>
     <row r="76">
@@ -2163,13 +2190,13 @@
         <v>26</v>
       </c>
       <c r="B76" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C76" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D76" t="s" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E76" t="s" s="1">
         <v>33</v>
@@ -2178,10 +2205,10 @@
         <v>0.0</v>
       </c>
       <c r="G76" t="n" s="1">
-        <v>20.82</v>
+        <v>700.72</v>
       </c>
       <c r="H76" t="n" s="1">
-        <v>-20.82</v>
+        <v>-700.72</v>
       </c>
     </row>
     <row r="77">
@@ -2189,25 +2216,25 @@
         <v>26</v>
       </c>
       <c r="B77" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D77" t="s" s="1">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E77" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F77" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G77" t="n" s="1">
-        <v>700.72</v>
+        <v>714.08</v>
       </c>
       <c r="H77" t="n" s="1">
-        <v>-700.72</v>
+        <v>-714.08</v>
       </c>
     </row>
     <row r="78">
@@ -2215,25 +2242,25 @@
         <v>26</v>
       </c>
       <c r="B78" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C78" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D78" t="s" s="1">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E78" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G78" t="n" s="1">
-        <v>714.08</v>
+        <v>764.9</v>
       </c>
       <c r="H78" t="n" s="1">
-        <v>-714.08</v>
+        <v>-764.9</v>
       </c>
     </row>
     <row r="79">
@@ -2241,25 +2268,25 @@
         <v>26</v>
       </c>
       <c r="B79" t="s" s="1">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D79" t="s" s="1">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E79" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G79" t="n" s="1">
-        <v>764.9</v>
+        <v>779.41</v>
       </c>
       <c r="H79" t="n" s="1">
-        <v>-764.9</v>
+        <v>-779.41</v>
       </c>
     </row>
     <row r="80">
@@ -2267,25 +2294,25 @@
         <v>26</v>
       </c>
       <c r="B80" t="s" s="1">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C80" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D80" t="s" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E80" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F80" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G80" t="n" s="1">
-        <v>779.41</v>
+        <v>744.28</v>
       </c>
       <c r="H80" t="n" s="1">
-        <v>-779.41</v>
+        <v>-744.28</v>
       </c>
     </row>
     <row r="81">
@@ -2293,25 +2320,25 @@
         <v>26</v>
       </c>
       <c r="B81" t="s" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C81" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D81" t="s" s="1">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E81" t="s" s="1">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F81" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G81" t="n" s="1">
-        <v>544.5</v>
+        <v>228.78</v>
       </c>
       <c r="H81" t="n" s="1">
-        <v>-544.5</v>
+        <v>-228.78</v>
       </c>
     </row>
     <row r="82">
@@ -2319,13 +2346,13 @@
         <v>26</v>
       </c>
       <c r="B82" t="s" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C82" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D82" t="s" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E82" t="s" s="1">
         <v>30</v>
@@ -2334,10 +2361,10 @@
         <v>0.0</v>
       </c>
       <c r="G82" t="n" s="1">
-        <v>6118.3</v>
+        <v>378.27</v>
       </c>
       <c r="H82" t="n" s="1">
-        <v>-6118.3</v>
+        <v>-378.27</v>
       </c>
     </row>
     <row r="83">
@@ -2345,25 +2372,25 @@
         <v>26</v>
       </c>
       <c r="B83" t="s" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C83" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D83" t="s" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E83" t="s" s="1">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F83" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G83" t="n" s="1">
-        <v>891.0</v>
+        <v>96.52</v>
       </c>
       <c r="H83" t="n" s="1">
-        <v>-891.0</v>
+        <v>-96.52</v>
       </c>
     </row>
     <row r="84">
@@ -2371,25 +2398,25 @@
         <v>26</v>
       </c>
       <c r="B84" t="s" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C84" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D84" t="s" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E84" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F84" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G84" t="n" s="1">
-        <v>498.88</v>
+        <v>544.5</v>
       </c>
       <c r="H84" t="n" s="1">
-        <v>-498.88</v>
+        <v>-544.5</v>
       </c>
     </row>
     <row r="85">
@@ -2397,25 +2424,25 @@
         <v>26</v>
       </c>
       <c r="B85" t="s" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C85" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D85" t="s" s="1">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E85" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F85" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G85" t="n" s="1">
-        <v>489.47</v>
+        <v>6118.3</v>
       </c>
       <c r="H85" t="n" s="1">
-        <v>-489.47</v>
+        <v>-6118.3</v>
       </c>
     </row>
     <row r="86">
@@ -2423,25 +2450,25 @@
         <v>26</v>
       </c>
       <c r="B86" t="s" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C86" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D86" t="s" s="1">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E86" t="s" s="1">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F86" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G86" t="n" s="1">
-        <v>632.51</v>
+        <v>891.0</v>
       </c>
       <c r="H86" t="n" s="1">
-        <v>-632.51</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="87">
@@ -2449,25 +2476,25 @@
         <v>26</v>
       </c>
       <c r="B87" t="s" s="1">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C87" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D87" t="s" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E87" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F87" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G87" t="n" s="1">
-        <v>644.44</v>
+        <v>59.56</v>
       </c>
       <c r="H87" t="n" s="1">
-        <v>-644.44</v>
+        <v>-59.56</v>
       </c>
     </row>
     <row r="88">
@@ -2475,25 +2502,25 @@
         <v>26</v>
       </c>
       <c r="B88" t="s" s="1">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C88" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D88" t="s" s="1">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E88" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F88" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G88" t="n" s="1">
-        <v>21486.12</v>
+        <v>60.64</v>
       </c>
       <c r="H88" t="n" s="1">
-        <v>-21486.12</v>
+        <v>-60.64</v>
       </c>
     </row>
     <row r="89">
@@ -2501,25 +2528,25 @@
         <v>26</v>
       </c>
       <c r="B89" t="s" s="1">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D89" t="s" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E89" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F89" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G89" t="n" s="1">
-        <v>2227.5</v>
+        <v>18.64</v>
       </c>
       <c r="H89" t="n" s="1">
-        <v>-2227.5</v>
+        <v>-18.64</v>
       </c>
     </row>
     <row r="90">
@@ -2527,25 +2554,25 @@
         <v>26</v>
       </c>
       <c r="B90" t="s" s="1">
+        <v>93</v>
+      </c>
+      <c r="C90" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D90" t="s" s="1">
         <v>103</v>
       </c>
-      <c r="C90" t="s" s="1">
-        <v>105</v>
-      </c>
-      <c r="D90" t="s" s="1">
-        <v>106</v>
-      </c>
       <c r="E90" t="s" s="1">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="F90" t="n" s="1">
-        <v>3500.0</v>
+        <v>0.0</v>
       </c>
       <c r="G90" t="n" s="1">
-        <v>0.0</v>
+        <v>18.3</v>
       </c>
       <c r="H90" t="n" s="1">
-        <v>3500.0</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="91">
@@ -2553,25 +2580,25 @@
         <v>26</v>
       </c>
       <c r="B91" t="s" s="1">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C91" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D91" t="s" s="1">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E91" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F91" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G91" t="n" s="1">
-        <v>1718.89</v>
+        <v>30.82</v>
       </c>
       <c r="H91" t="n" s="1">
-        <v>-1718.89</v>
+        <v>-30.82</v>
       </c>
     </row>
     <row r="92">
@@ -2579,25 +2606,25 @@
         <v>26</v>
       </c>
       <c r="B92" t="s" s="1">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C92" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D92" t="s" s="1">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E92" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F92" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G92" t="n" s="1">
-        <v>1751.0</v>
+        <v>30.25</v>
       </c>
       <c r="H92" t="n" s="1">
-        <v>-1751.0</v>
+        <v>-30.25</v>
       </c>
     </row>
     <row r="93">
@@ -2605,25 +2632,25 @@
         <v>26</v>
       </c>
       <c r="B93" t="s" s="1">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C93" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s" s="1">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E93" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F93" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G93" t="n" s="1">
-        <v>155.01</v>
+        <v>7.86</v>
       </c>
       <c r="H93" t="n" s="1">
-        <v>-155.01</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="94">
@@ -2631,25 +2658,25 @@
         <v>26</v>
       </c>
       <c r="B94" t="s" s="1">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C94" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s" s="1">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E94" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F94" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G94" t="n" s="1">
-        <v>15066.07</v>
+        <v>7.74</v>
       </c>
       <c r="H94" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="95">
@@ -2657,25 +2684,25 @@
         <v>26</v>
       </c>
       <c r="B95" t="s" s="1">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C95" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D95" t="s" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E95" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F95" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G95" t="n" s="1">
-        <v>1435.5</v>
+        <v>498.88</v>
       </c>
       <c r="H95" t="n" s="1">
-        <v>-1435.5</v>
+        <v>-498.88</v>
       </c>
     </row>
     <row r="96">
@@ -2683,25 +2710,25 @@
         <v>26</v>
       </c>
       <c r="B96" t="s" s="1">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C96" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D96" t="s" s="1">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E96" t="s" s="1">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F96" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G96" t="n" s="1">
-        <v>297.0</v>
+        <v>489.47</v>
       </c>
       <c r="H96" t="n" s="1">
-        <v>-297.0</v>
+        <v>-489.47</v>
       </c>
     </row>
     <row r="97">
@@ -2709,25 +2736,25 @@
         <v>26</v>
       </c>
       <c r="B97" t="s" s="1">
+        <v>93</v>
+      </c>
+      <c r="C97" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D97" t="s" s="1">
         <v>110</v>
       </c>
-      <c r="C97" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D97" t="s" s="1">
-        <v>113</v>
-      </c>
       <c r="E97" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F97" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G97" t="n" s="1">
-        <v>2283.05</v>
+        <v>644.44</v>
       </c>
       <c r="H97" t="n" s="1">
-        <v>-2283.05</v>
+        <v>-644.44</v>
       </c>
     </row>
     <row r="98">
@@ -2735,25 +2762,25 @@
         <v>26</v>
       </c>
       <c r="B98" t="s" s="1">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C98" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D98" t="s" s="1">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E98" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F98" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G98" t="n" s="1">
-        <v>1227.73</v>
+        <v>632.51</v>
       </c>
       <c r="H98" t="n" s="1">
-        <v>-1227.73</v>
+        <v>-632.51</v>
       </c>
     </row>
     <row r="99">
@@ -2761,25 +2788,25 @@
         <v>26</v>
       </c>
       <c r="B99" t="s" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C99" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D99" t="s" s="1">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E99" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F99" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G99" t="n" s="1">
-        <v>1205.61</v>
+        <v>21486.12</v>
       </c>
       <c r="H99" t="n" s="1">
-        <v>-1205.61</v>
+        <v>-21486.12</v>
       </c>
     </row>
     <row r="100">
@@ -2787,25 +2814,25 @@
         <v>26</v>
       </c>
       <c r="B100" t="s" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C100" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D100" t="s" s="1">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E100" t="s" s="1">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F100" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G100" t="n" s="1">
-        <v>182.66</v>
+        <v>2227.5</v>
       </c>
       <c r="H100" t="n" s="1">
-        <v>-182.66</v>
+        <v>-2227.5</v>
       </c>
     </row>
     <row r="101">
@@ -2813,25 +2840,25 @@
         <v>26</v>
       </c>
       <c r="B101" t="s" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C101" t="s" s="1">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="D101" t="s" s="1">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E101" t="s" s="1">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="F101" t="n" s="1">
-        <v>0.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G101" t="n" s="1">
-        <v>186.06</v>
+        <v>0.0</v>
       </c>
       <c r="H101" t="n" s="1">
-        <v>-186.06</v>
+        <v>3500.0</v>
       </c>
     </row>
     <row r="102">
@@ -2839,25 +2866,25 @@
         <v>26</v>
       </c>
       <c r="B102" t="s" s="1">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C102" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D102" t="s" s="1">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="E102" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F102" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G102" t="n" s="1">
-        <v>100.0</v>
+        <v>1751.0</v>
       </c>
       <c r="H102" t="n" s="1">
-        <v>-100.0</v>
+        <v>-1751.0</v>
       </c>
     </row>
     <row r="103">
@@ -2865,25 +2892,25 @@
         <v>26</v>
       </c>
       <c r="B103" t="s" s="1">
+        <v>112</v>
+      </c>
+      <c r="C103" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D103" t="s" s="1">
         <v>118</v>
       </c>
-      <c r="C103" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D103" t="s" s="1">
-        <v>44</v>
-      </c>
       <c r="E103" t="s" s="1">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="F103" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G103" t="n" s="1">
-        <v>4588.5</v>
+        <v>1718.89</v>
       </c>
       <c r="H103" t="n" s="1">
-        <v>-4588.5</v>
+        <v>-1718.89</v>
       </c>
     </row>
     <row r="104">
@@ -2891,25 +2918,25 @@
         <v>26</v>
       </c>
       <c r="B104" t="s" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C104" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D104" t="s" s="1">
         <v>120</v>
       </c>
       <c r="E104" t="s" s="1">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="F104" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G104" t="n" s="1">
-        <v>239.58</v>
+        <v>155.01</v>
       </c>
       <c r="H104" t="n" s="1">
-        <v>-239.58</v>
+        <v>-155.01</v>
       </c>
     </row>
     <row r="105">
@@ -2917,25 +2944,25 @@
         <v>26</v>
       </c>
       <c r="B105" t="s" s="1">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C105" t="s" s="1">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="D105" t="s" s="1">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="E105" t="s" s="1">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="F105" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G105" t="n" s="1">
-        <v>0.0</v>
+        <v>15066.07</v>
       </c>
       <c r="H105" t="n" s="1">
-        <v>840.0</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="106">
@@ -2943,25 +2970,25 @@
         <v>26</v>
       </c>
       <c r="B106" t="s" s="1">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C106" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D106" t="s" s="1">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="E106" t="s" s="1">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="F106" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G106" t="n" s="1">
-        <v>1500.0</v>
+        <v>1435.5</v>
       </c>
       <c r="H106" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-1435.5</v>
       </c>
     </row>
     <row r="107">
@@ -2969,25 +2996,25 @@
         <v>26</v>
       </c>
       <c r="B107" t="s" s="1">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C107" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D107" t="s" s="1">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="E107" t="s" s="1">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="F107" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G107" t="n" s="1">
-        <v>4500.0</v>
+        <v>297.0</v>
       </c>
       <c r="H107" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-297.0</v>
       </c>
     </row>
     <row r="108">
@@ -2995,25 +3022,25 @@
         <v>26</v>
       </c>
       <c r="B108" t="s" s="1">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C108" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D108" t="s" s="1">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="E108" t="s" s="1">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="F108" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G108" t="n" s="1">
-        <v>15000.0</v>
+        <v>2283.05</v>
       </c>
       <c r="H108" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-2283.05</v>
       </c>
     </row>
     <row r="109">
@@ -3021,25 +3048,25 @@
         <v>26</v>
       </c>
       <c r="B109" t="s" s="1">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C109" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D109" t="s" s="1">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="E109" t="s" s="1">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="F109" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G109" t="n" s="1">
-        <v>2000.0</v>
+        <v>1227.73</v>
       </c>
       <c r="H109" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-1227.73</v>
       </c>
     </row>
     <row r="110">
@@ -3047,25 +3074,25 @@
         <v>26</v>
       </c>
       <c r="B110" t="s" s="1">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C110" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D110" t="s" s="1">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E110" t="s" s="1">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="F110" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G110" t="n" s="1">
-        <v>146.67</v>
+        <v>1205.61</v>
       </c>
       <c r="H110" t="n" s="1">
-        <v>-146.67</v>
+        <v>-1205.61</v>
       </c>
     </row>
     <row r="111">
@@ -3073,25 +3100,25 @@
         <v>26</v>
       </c>
       <c r="B111" t="s" s="1">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C111" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D111" t="s" s="1">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="E111" t="s" s="1">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F111" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G111" t="n" s="1">
-        <v>180.0</v>
+        <v>182.66</v>
       </c>
       <c r="H111" t="n" s="1">
-        <v>-180.0</v>
+        <v>-182.66</v>
       </c>
     </row>
     <row r="112">
@@ -3099,25 +3126,25 @@
         <v>26</v>
       </c>
       <c r="B112" t="s" s="1">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D112" t="s" s="1">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="E112" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F112" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G112" t="n" s="1">
-        <v>9216.24</v>
+        <v>186.06</v>
       </c>
       <c r="H112" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-186.06</v>
       </c>
     </row>
     <row r="113">
@@ -3125,13 +3152,13 @@
         <v>26</v>
       </c>
       <c r="B113" t="s" s="1">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C113" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D113" t="s" s="1">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E113" t="s" s="1">
         <v>39</v>
@@ -3140,10 +3167,10 @@
         <v>0.0</v>
       </c>
       <c r="G113" t="n" s="1">
-        <v>891.0</v>
+        <v>100.0</v>
       </c>
       <c r="H113" t="n" s="1">
-        <v>-891.0</v>
+        <v>-100.0</v>
       </c>
     </row>
     <row r="114">
@@ -3151,25 +3178,25 @@
         <v>26</v>
       </c>
       <c r="B114" t="s" s="1">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C114" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D114" t="s" s="1">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E114" t="s" s="1">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="F114" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G114" t="n" s="1">
-        <v>737.28</v>
+        <v>4588.5</v>
       </c>
       <c r="H114" t="n" s="1">
-        <v>-737.28</v>
+        <v>-4588.5</v>
       </c>
     </row>
     <row r="115">
@@ -3177,25 +3204,25 @@
         <v>26</v>
       </c>
       <c r="B115" t="s" s="1">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C115" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D115" t="s" s="1">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E115" t="s" s="1">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="F115" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G115" t="n" s="1">
-        <v>750.99</v>
+        <v>239.58</v>
       </c>
       <c r="H115" t="n" s="1">
-        <v>-750.99</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="116">
@@ -3203,25 +3230,25 @@
         <v>26</v>
       </c>
       <c r="B116" t="s" s="1">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C116" t="s" s="1">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="D116" t="s" s="1">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E116" t="s" s="1">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="F116" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G116" t="n" s="1">
-        <v>1544.4</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n" s="1">
-        <v>-1544.4</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="117">
@@ -3229,25 +3256,25 @@
         <v>26</v>
       </c>
       <c r="B117" t="s" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C117" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D117" t="s" s="1">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="E117" t="s" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F117" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G117" t="n" s="1">
-        <v>180.06</v>
+        <v>1500.0</v>
       </c>
       <c r="H117" t="n" s="1">
-        <v>-180.06</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="118">
@@ -3255,25 +3282,25 @@
         <v>26</v>
       </c>
       <c r="B118" t="s" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C118" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D118" t="s" s="1">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="E118" t="s" s="1">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F118" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G118" t="n" s="1">
-        <v>1925.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H118" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="119">
@@ -3281,25 +3308,25 @@
         <v>26</v>
       </c>
       <c r="B119" t="s" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C119" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D119" t="s" s="1">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E119" t="s" s="1">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F119" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G119" t="n" s="1">
-        <v>180.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H119" t="n" s="1">
-        <v>-180.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="120">
@@ -3307,25 +3334,25 @@
         <v>26</v>
       </c>
       <c r="B120" t="s" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C120" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D120" t="s" s="1">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="E120" t="s" s="1">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="F120" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G120" t="n" s="1">
-        <v>180.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H120" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="121">
@@ -3339,19 +3366,19 @@
         <v>43</v>
       </c>
       <c r="D121" t="s" s="1">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E121" t="s" s="1">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F121" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G121" t="n" s="1">
-        <v>1201.89</v>
+        <v>146.67</v>
       </c>
       <c r="H121" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="122">
@@ -3365,7 +3392,7 @@
         <v>43</v>
       </c>
       <c r="D122" t="s" s="1">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="E122" t="s" s="1">
         <v>64</v>
@@ -3385,25 +3412,25 @@
         <v>26</v>
       </c>
       <c r="B123" t="s" s="1">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C123" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D123" t="s" s="1">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>180.0</v>
+        <v>9216.24</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-180.0</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="124">
@@ -3411,25 +3438,25 @@
         <v>26</v>
       </c>
       <c r="B124" t="s" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C124" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D124" t="s" s="1">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>25504.78</v>
+        <v>891.0</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="125">
@@ -3437,13 +3464,13 @@
         <v>26</v>
       </c>
       <c r="B125" t="s" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C125" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D125" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E125" t="s" s="1">
         <v>33</v>
@@ -3452,10 +3479,10 @@
         <v>0.0</v>
       </c>
       <c r="G125" t="n" s="1">
-        <v>2040.52</v>
+        <v>737.28</v>
       </c>
       <c r="H125" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="126">
@@ -3463,13 +3490,13 @@
         <v>26</v>
       </c>
       <c r="B126" t="s" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C126" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D126" t="s" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E126" t="s" s="1">
         <v>35</v>
@@ -3478,10 +3505,10 @@
         <v>0.0</v>
       </c>
       <c r="G126" t="n" s="1">
-        <v>2078.64</v>
+        <v>750.99</v>
       </c>
       <c r="H126" t="n" s="1">
-        <v>-2078.64</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="127">
@@ -3489,13 +3516,13 @@
         <v>26</v>
       </c>
       <c r="B127" t="s" s="1">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C127" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D127" t="s" s="1">
-        <v>142</v>
+        <v>60</v>
       </c>
       <c r="E127" t="s" s="1">
         <v>39</v>
@@ -3504,10 +3531,10 @@
         <v>0.0</v>
       </c>
       <c r="G127" t="n" s="1">
-        <v>2277.0</v>
+        <v>1544.4</v>
       </c>
       <c r="H127" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="128">
@@ -3515,25 +3542,25 @@
         <v>26</v>
       </c>
       <c r="B128" t="s" s="1">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C128" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D128" t="s" s="1">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="E128" t="s" s="1">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="F128" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G128" t="n" s="1">
-        <v>180.0</v>
+        <v>180.06</v>
       </c>
       <c r="H128" t="n" s="1">
-        <v>-180.0</v>
+        <v>-180.06</v>
       </c>
     </row>
     <row r="129">
@@ -3547,19 +3574,19 @@
         <v>43</v>
       </c>
       <c r="D129" t="s" s="1">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>180.0</v>
+        <v>1925.0</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="130">
@@ -3567,25 +3594,25 @@
         <v>26</v>
       </c>
       <c r="B130" t="s" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C130" t="s" s="1">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="D130" t="s" s="1">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="F130" t="n" s="1">
-        <v>1816.53</v>
+        <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>1816.53</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="131">
@@ -3593,25 +3620,25 @@
         <v>26</v>
       </c>
       <c r="B131" t="s" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C131" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D131" t="s" s="1">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="E131" t="s" s="1">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="F131" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G131" t="n" s="1">
-        <v>1000.0</v>
+        <v>180.0</v>
       </c>
       <c r="H131" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="132">
@@ -3619,25 +3646,25 @@
         <v>26</v>
       </c>
       <c r="B132" t="s" s="1">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C132" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D132" t="s" s="1">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G132" t="n" s="1">
-        <v>3750.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H132" t="n" s="1">
-        <v>-3750.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="133">
@@ -3645,49 +3672,335 @@
         <v>26</v>
       </c>
       <c r="B133" t="s" s="1">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C133" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D133" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="E133" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F133" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G133" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H133" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B134" t="s" s="1">
+        <v>148</v>
+      </c>
+      <c r="C134" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D134" t="s" s="1">
+        <v>99</v>
+      </c>
+      <c r="E134" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F134" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G134" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H134" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B135" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C135" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D133" t="s" s="1">
+      <c r="D135" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E135" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="F135" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G135" t="n" s="1">
+        <v>25504.78</v>
+      </c>
+      <c r="H135" t="n" s="1">
+        <v>-25504.78</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B136" t="s" s="1">
         <v>150</v>
       </c>
-      <c r="E133" t="s" s="1">
+      <c r="C136" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D136" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E136" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="F136" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G136" t="n" s="1">
+        <v>2277.0</v>
+      </c>
+      <c r="H136" t="n" s="1">
+        <v>-2277.0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B137" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C137" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D137" t="s" s="1">
+        <v>151</v>
+      </c>
+      <c r="E137" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F137" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G137" t="n" s="1">
+        <v>2078.64</v>
+      </c>
+      <c r="H137" t="n" s="1">
+        <v>-2078.64</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B138" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C138" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D138" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="E138" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F138" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G138" t="n" s="1">
+        <v>2040.52</v>
+      </c>
+      <c r="H138" t="n" s="1">
+        <v>-2040.52</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B139" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="C139" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D139" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="E139" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F139" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G139" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H139" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B140" t="s" s="1">
+        <v>152</v>
+      </c>
+      <c r="C140" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D140" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="E140" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F140" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G140" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H140" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B141" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="C141" t="s" s="1">
+        <v>114</v>
+      </c>
+      <c r="D141" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="E141" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="F141" t="n" s="1">
+        <v>1816.53</v>
+      </c>
+      <c r="G141" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H141" t="n" s="1">
+        <v>1816.53</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B142" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="C142" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D142" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="E142" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="F142" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G142" t="n" s="1">
+        <v>3750.0</v>
+      </c>
+      <c r="H142" t="n" s="1">
+        <v>-3750.0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B143" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="C143" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D143" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="E143" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="F143" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G143" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H143" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B144" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="C144" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D144" t="s" s="1">
+        <v>159</v>
+      </c>
+      <c r="E144" t="s" s="1">
         <v>30</v>
       </c>
-      <c r="F133" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G133" t="n" s="1">
+      <c r="F144" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G144" t="n" s="1">
         <v>1255.07</v>
       </c>
-      <c r="H133" t="n" s="1">
+      <c r="H144" t="n" s="1">
         <v>-1255.07</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>156</v>
+    <row r="147">
+      <c r="A147" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="166">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -111,30 +111,30 @@
     <t>PCP-Previsão do Contas a Pagar</t>
   </si>
   <si>
+    <t>1629 - 3</t>
+  </si>
+  <si>
+    <t>RODAG TRANSPORTES LTDA*</t>
+  </si>
+  <si>
     <t>1629 - 2</t>
   </si>
   <si>
     <t>ENTREGADORA NOVO RUMO LTDA ME</t>
   </si>
   <si>
-    <t>1629 - 3</t>
-  </si>
-  <si>
-    <t>RODAG TRANSPORTES LTDA*</t>
-  </si>
-  <si>
     <t>PPC-Previsão de Pagamento de Comissão</t>
   </si>
   <si>
     <t>101701 - 1</t>
   </si>
   <si>
+    <t>DECORA INTERIORES LTDA</t>
+  </si>
+  <si>
     <t>Victor Costa</t>
   </si>
   <si>
-    <t>DECORA INTERIORES LTDA</t>
-  </si>
-  <si>
     <t>05/10/2026</t>
   </si>
   <si>
@@ -162,27 +162,27 @@
     <t>100901 - 1</t>
   </si>
   <si>
+    <t>TERESINHA ELVIRA MAXIMINO DE MENEZES</t>
+  </si>
+  <si>
     <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
   </si>
   <si>
     <t>100901 - 2</t>
   </si>
   <si>
-    <t>TERESINHA ELVIRA MAXIMINO DE MENEZES</t>
-  </si>
-  <si>
     <t>102301 - 2</t>
   </si>
   <si>
     <t>06/10/2026</t>
   </si>
   <si>
+    <t>ROSANGELA PACHECO</t>
+  </si>
+  <si>
     <t>FELIPE DOMINGOS BARBOSA</t>
   </si>
   <si>
-    <t>ROSANGELA PACHECO</t>
-  </si>
-  <si>
     <t>BIANCA RODRIGUES</t>
   </si>
   <si>
@@ -240,33 +240,27 @@
     <t>96601 - 3</t>
   </si>
   <si>
+    <t>101401 - 3</t>
+  </si>
+  <si>
     <t>101401 - 2</t>
   </si>
   <si>
-    <t>101401 - 3</t>
-  </si>
-  <si>
     <t>10/10/2026</t>
   </si>
   <si>
     <t>100501 - 1</t>
   </si>
   <si>
+    <t>100501 - 2</t>
+  </si>
+  <si>
     <t>100501 - 3</t>
   </si>
   <si>
-    <t>100501 - 2</t>
-  </si>
-  <si>
-    <t>PREFEITURA SP- ISS</t>
-  </si>
-  <si>
     <t>13/10/2026</t>
   </si>
   <si>
-    <t>1630 - 1</t>
-  </si>
-  <si>
     <t>49501 - 2</t>
   </si>
   <si>
@@ -276,18 +270,12 @@
     <t>102101 - 1</t>
   </si>
   <si>
-    <t>1630 - 3</t>
-  </si>
-  <si>
-    <t>1630 - 2</t>
+    <t>100301 - 3</t>
   </si>
   <si>
     <t>100301 - 2</t>
   </si>
   <si>
-    <t>100301 - 3</t>
-  </si>
-  <si>
     <t>102101 - 2</t>
   </si>
   <si>
@@ -333,18 +321,18 @@
     <t>1633 - 2</t>
   </si>
   <si>
+    <t>1634 - 2</t>
+  </si>
+  <si>
     <t>1634 - 3</t>
   </si>
   <si>
-    <t>1634 - 2</t>
+    <t>101201 - 2</t>
   </si>
   <si>
     <t>101201 - 3</t>
   </si>
   <si>
-    <t>101201 - 2</t>
-  </si>
-  <si>
     <t>101801 - 3</t>
   </si>
   <si>
@@ -360,6 +348,12 @@
     <t>DUP-Duplicata de Contrato</t>
   </si>
   <si>
+    <t>29001 - 11</t>
+  </si>
+  <si>
+    <t>GABRIEL DE CARVALHO MELLO</t>
+  </si>
+  <si>
     <t>103501 - 0</t>
   </si>
   <si>
@@ -372,6 +366,30 @@
     <t>101101 - 2</t>
   </si>
   <si>
+    <t>103801 - 1</t>
+  </si>
+  <si>
+    <t>104701 - 2</t>
+  </si>
+  <si>
+    <t>104701 - 1</t>
+  </si>
+  <si>
+    <t>104801 - 1</t>
+  </si>
+  <si>
+    <t>104801 - 2</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>103801 - 2</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
     <t>17/10/2026</t>
   </si>
   <si>
@@ -390,18 +408,15 @@
     <t>102401 - 2</t>
   </si>
   <si>
+    <t>102501 - 3</t>
+  </si>
+  <si>
     <t>102501 - 2</t>
   </si>
   <si>
-    <t>102501 - 3</t>
-  </si>
-  <si>
     <t>18/10/2026</t>
   </si>
   <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
     <t>12 - 8</t>
   </si>
   <si>
@@ -417,15 +432,15 @@
     <t>20/10/2026</t>
   </si>
   <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>Simples Nacional - DAS</t>
+  </si>
+  <si>
     <t>INSS- Previdenciária</t>
   </si>
   <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>Simples Nacional - DAS</t>
-  </si>
-  <si>
     <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
   </si>
   <si>
@@ -447,21 +462,18 @@
     <t>25/10/2026</t>
   </si>
   <si>
+    <t>68 - 3</t>
+  </si>
+  <si>
+    <t>Luis Carlos Alves de Oliveira</t>
+  </si>
+  <si>
+    <t>26/10/2026</t>
+  </si>
+  <si>
     <t>2 - 9</t>
   </si>
   <si>
-    <t>Vivo</t>
-  </si>
-  <si>
-    <t>68 - 3</t>
-  </si>
-  <si>
-    <t>Luis Carlos Alves de Oliveira</t>
-  </si>
-  <si>
-    <t>26/10/2026</t>
-  </si>
-  <si>
     <t>EM SOLUCOES INTEGRADAS DE SISTEMAS LTDA ME</t>
   </si>
   <si>
@@ -477,24 +489,12 @@
     <t>30/10/2026</t>
   </si>
   <si>
-    <t>29001 - 12</t>
-  </si>
-  <si>
-    <t>GABRIEL DE CARVALHO MELLO</t>
+    <t>SEFAZ SP DARE - ICMS</t>
   </si>
   <si>
     <t>Facebook</t>
   </si>
   <si>
-    <t>SEFAZ SP DARE - ICMS</t>
-  </si>
-  <si>
-    <t>31/10/2026</t>
-  </si>
-  <si>
-    <t>96101 - 2</t>
-  </si>
-  <si>
     <t>Total Geral Crédito</t>
   </si>
   <si>
@@ -504,13 +504,13 @@
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>261.986,79</t>
+    <t>247.751,73</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-255.830,26</t>
+    <t>-241.595,20</t>
   </si>
 </sst>
 </file>
@@ -578,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H149"/>
+  <dimension ref="A2:H158"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -749,10 +749,10 @@
         <v>0.0</v>
       </c>
       <c r="G20" t="n" s="1">
-        <v>32.31</v>
+        <v>32.88</v>
       </c>
       <c r="H20" t="n" s="1">
-        <v>-32.31</v>
+        <v>-32.88</v>
       </c>
     </row>
     <row r="21">
@@ -775,10 +775,10 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n" s="1">
-        <v>32.88</v>
+        <v>32.31</v>
       </c>
       <c r="H21" t="n" s="1">
-        <v>-32.88</v>
+        <v>-32.31</v>
       </c>
     </row>
     <row r="22">
@@ -801,10 +801,10 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n" s="1">
-        <v>21.0</v>
+        <v>30.0</v>
       </c>
       <c r="H22" t="n" s="1">
-        <v>-21.0</v>
+        <v>-30.0</v>
       </c>
     </row>
     <row r="23">
@@ -827,10 +827,10 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n" s="1">
-        <v>30.0</v>
+        <v>21.0</v>
       </c>
       <c r="H23" t="n" s="1">
-        <v>-30.0</v>
+        <v>-21.0</v>
       </c>
     </row>
     <row r="24">
@@ -925,7 +925,7 @@
         <v>47</v>
       </c>
       <c r="E27" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n" s="1">
         <v>0.0</v>
@@ -957,10 +957,10 @@
         <v>0.0</v>
       </c>
       <c r="G28" t="n" s="1">
-        <v>1215.9</v>
+        <v>607.95</v>
       </c>
       <c r="H28" t="n" s="1">
-        <v>-1215.9</v>
+        <v>-607.95</v>
       </c>
     </row>
     <row r="29">
@@ -974,10 +974,10 @@
         <v>36</v>
       </c>
       <c r="D29" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E29" t="s" s="1">
         <v>50</v>
-      </c>
-      <c r="E29" t="s" s="1">
-        <v>39</v>
       </c>
       <c r="F29" t="n" s="1">
         <v>0.0</v>
@@ -1000,19 +1000,19 @@
         <v>36</v>
       </c>
       <c r="D30" t="s" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s" s="1">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F30" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G30" t="n" s="1">
-        <v>607.95</v>
+        <v>1215.9</v>
       </c>
       <c r="H30" t="n" s="1">
-        <v>-607.95</v>
+        <v>-1215.9</v>
       </c>
     </row>
     <row r="31">
@@ -1029,7 +1029,7 @@
         <v>52</v>
       </c>
       <c r="E31" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F31" t="n" s="1">
         <v>0.0</v>
@@ -1061,10 +1061,10 @@
         <v>0.0</v>
       </c>
       <c r="G32" t="n" s="1">
-        <v>444.12</v>
+        <v>222.06</v>
       </c>
       <c r="H32" t="n" s="1">
-        <v>-444.12</v>
+        <v>-222.06</v>
       </c>
     </row>
     <row r="33">
@@ -1081,16 +1081,16 @@
         <v>41</v>
       </c>
       <c r="E33" t="s" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G33" t="n" s="1">
-        <v>222.06</v>
+        <v>444.12</v>
       </c>
       <c r="H33" t="n" s="1">
-        <v>-222.06</v>
+        <v>-444.12</v>
       </c>
     </row>
     <row r="34">
@@ -1113,10 +1113,10 @@
         <v>0.0</v>
       </c>
       <c r="G34" t="n" s="1">
-        <v>1823.86</v>
+        <v>4255.67</v>
       </c>
       <c r="H34" t="n" s="1">
-        <v>-1823.86</v>
+        <v>-4255.67</v>
       </c>
     </row>
     <row r="35">
@@ -1133,16 +1133,16 @@
         <v>48</v>
       </c>
       <c r="E35" t="s" s="1">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F35" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G35" t="n" s="1">
-        <v>6079.52</v>
+        <v>1823.86</v>
       </c>
       <c r="H35" t="n" s="1">
-        <v>-6079.52</v>
+        <v>-1823.86</v>
       </c>
     </row>
     <row r="36">
@@ -1159,16 +1159,16 @@
         <v>48</v>
       </c>
       <c r="E36" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F36" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G36" t="n" s="1">
-        <v>4255.67</v>
+        <v>6079.52</v>
       </c>
       <c r="H36" t="n" s="1">
-        <v>-4255.67</v>
+        <v>-6079.52</v>
       </c>
     </row>
     <row r="37">
@@ -1185,16 +1185,16 @@
         <v>41</v>
       </c>
       <c r="E37" t="s" s="1">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F37" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G37" t="n" s="1">
-        <v>1554.41</v>
+        <v>2220.59</v>
       </c>
       <c r="H37" t="n" s="1">
-        <v>-1554.41</v>
+        <v>-2220.59</v>
       </c>
     </row>
     <row r="38">
@@ -1211,16 +1211,16 @@
         <v>41</v>
       </c>
       <c r="E38" t="s" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F38" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G38" t="n" s="1">
-        <v>666.18</v>
+        <v>1554.41</v>
       </c>
       <c r="H38" t="n" s="1">
-        <v>-666.18</v>
+        <v>-1554.41</v>
       </c>
     </row>
     <row r="39">
@@ -1237,16 +1237,16 @@
         <v>41</v>
       </c>
       <c r="E39" t="s" s="1">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F39" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G39" t="n" s="1">
-        <v>2220.59</v>
+        <v>666.18</v>
       </c>
       <c r="H39" t="n" s="1">
-        <v>-2220.59</v>
+        <v>-666.18</v>
       </c>
     </row>
     <row r="40">
@@ -1263,7 +1263,7 @@
         <v>58</v>
       </c>
       <c r="E40" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F40" t="n" s="1">
         <v>0.0</v>
@@ -1289,7 +1289,7 @@
         <v>59</v>
       </c>
       <c r="E41" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n" s="1">
         <v>0.0</v>
@@ -1315,7 +1315,7 @@
         <v>59</v>
       </c>
       <c r="E42" t="s" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F42" t="n" s="1">
         <v>0.0</v>
@@ -1347,10 +1347,10 @@
         <v>0.0</v>
       </c>
       <c r="G43" t="n" s="1">
-        <v>66.4</v>
+        <v>33.2</v>
       </c>
       <c r="H43" t="n" s="1">
-        <v>-66.4</v>
+        <v>-33.2</v>
       </c>
     </row>
     <row r="44">
@@ -1367,7 +1367,7 @@
         <v>61</v>
       </c>
       <c r="E44" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F44" t="n" s="1">
         <v>0.0</v>
@@ -1393,16 +1393,16 @@
         <v>60</v>
       </c>
       <c r="E45" t="s" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F45" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G45" t="n" s="1">
-        <v>33.2</v>
+        <v>66.4</v>
       </c>
       <c r="H45" t="n" s="1">
-        <v>-33.2</v>
+        <v>-66.4</v>
       </c>
     </row>
     <row r="46">
@@ -1445,16 +1445,16 @@
         <v>59</v>
       </c>
       <c r="E47" t="s" s="1">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F47" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G47" t="n" s="1">
-        <v>17.81</v>
+        <v>12.47</v>
       </c>
       <c r="H47" t="n" s="1">
-        <v>-17.81</v>
+        <v>-12.47</v>
       </c>
     </row>
     <row r="48">
@@ -1471,16 +1471,16 @@
         <v>59</v>
       </c>
       <c r="E48" t="s" s="1">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F48" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G48" t="n" s="1">
-        <v>12.47</v>
+        <v>17.81</v>
       </c>
       <c r="H48" t="n" s="1">
-        <v>-12.47</v>
+        <v>-17.81</v>
       </c>
     </row>
     <row r="49">
@@ -1497,7 +1497,7 @@
         <v>60</v>
       </c>
       <c r="E49" t="s" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F49" t="n" s="1">
         <v>0.0</v>
@@ -1523,16 +1523,16 @@
         <v>60</v>
       </c>
       <c r="E50" t="s" s="1">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F50" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G50" t="n" s="1">
-        <v>332.0</v>
+        <v>99.6</v>
       </c>
       <c r="H50" t="n" s="1">
-        <v>-332.0</v>
+        <v>-99.6</v>
       </c>
     </row>
     <row r="51">
@@ -1549,16 +1549,16 @@
         <v>60</v>
       </c>
       <c r="E51" t="s" s="1">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F51" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G51" t="n" s="1">
-        <v>99.6</v>
+        <v>332.0</v>
       </c>
       <c r="H51" t="n" s="1">
-        <v>-99.6</v>
+        <v>-332.0</v>
       </c>
     </row>
     <row r="52">
@@ -1575,7 +1575,7 @@
         <v>67</v>
       </c>
       <c r="E52" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F52" t="n" s="1">
         <v>0.0</v>
@@ -1653,7 +1653,7 @@
         <v>68</v>
       </c>
       <c r="E55" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F55" t="n" s="1">
         <v>0.0</v>
@@ -1731,7 +1731,7 @@
         <v>73</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F58" t="n" s="1">
         <v>0.0</v>
@@ -1757,7 +1757,7 @@
         <v>74</v>
       </c>
       <c r="E59" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F59" t="n" s="1">
         <v>0.0</v>
@@ -1815,10 +1815,10 @@
         <v>0.0</v>
       </c>
       <c r="G61" t="n" s="1">
-        <v>979.59</v>
+        <v>997.38</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>-979.59</v>
+        <v>-997.38</v>
       </c>
     </row>
     <row r="62">
@@ -1841,10 +1841,10 @@
         <v>0.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>997.38</v>
+        <v>979.59</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>-997.38</v>
+        <v>-979.59</v>
       </c>
     </row>
     <row r="63">
@@ -1861,16 +1861,16 @@
         <v>78</v>
       </c>
       <c r="E63" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>8578.28</v>
+        <v>1019.7</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-8578.28</v>
+        <v>-1019.7</v>
       </c>
     </row>
     <row r="64">
@@ -1881,22 +1881,22 @@
         <v>77</v>
       </c>
       <c r="C64" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E64" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>1019.7</v>
+        <v>686.33</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-1019.7</v>
+        <v>-686.33</v>
       </c>
     </row>
     <row r="65">
@@ -1910,10 +1910,10 @@
         <v>31</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E65" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
@@ -1930,25 +1930,25 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C66" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>686.33</v>
+        <v>560.42</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-686.33</v>
+        <v>-560.42</v>
       </c>
     </row>
     <row r="67">
@@ -1956,25 +1956,25 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C67" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>4.16</v>
+        <v>8758.14</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-4.16</v>
+        <v>-8758.14</v>
       </c>
     </row>
     <row r="68">
@@ -1982,7 +1982,7 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C68" t="s" s="1">
         <v>28</v>
@@ -1991,16 +1991,16 @@
         <v>83</v>
       </c>
       <c r="E68" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>260.15</v>
+        <v>1336.5</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-260.15</v>
+        <v>-1336.5</v>
       </c>
     </row>
     <row r="69">
@@ -2008,7 +2008,7 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
@@ -2017,16 +2017,16 @@
         <v>84</v>
       </c>
       <c r="E69" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F69" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>560.42</v>
+        <v>891.0</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-560.42</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="70">
@@ -2034,13 +2034,13 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E70" t="s" s="1">
         <v>30</v>
@@ -2049,10 +2049,10 @@
         <v>0.0</v>
       </c>
       <c r="G70" t="n" s="1">
-        <v>8758.14</v>
+        <v>9559.08</v>
       </c>
       <c r="H70" t="n" s="1">
-        <v>-8758.14</v>
+        <v>-9559.08</v>
       </c>
     </row>
     <row r="71">
@@ -2060,25 +2060,25 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s" s="1">
         <v>85</v>
       </c>
       <c r="E71" t="s" s="1">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F71" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G71" t="n" s="1">
-        <v>1336.5</v>
+        <v>714.08</v>
       </c>
       <c r="H71" t="n" s="1">
-        <v>-1336.5</v>
+        <v>-714.08</v>
       </c>
     </row>
     <row r="72">
@@ -2086,25 +2086,25 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C72" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D72" t="s" s="1">
         <v>86</v>
       </c>
       <c r="E72" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F72" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G72" t="n" s="1">
-        <v>9559.08</v>
+        <v>700.72</v>
       </c>
       <c r="H72" t="n" s="1">
-        <v>-9559.08</v>
+        <v>-700.72</v>
       </c>
     </row>
     <row r="73">
@@ -2112,25 +2112,25 @@
         <v>26</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C73" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E73" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G73" t="n" s="1">
-        <v>891.0</v>
+        <v>764.9</v>
       </c>
       <c r="H73" t="n" s="1">
-        <v>-891.0</v>
+        <v>-764.9</v>
       </c>
     </row>
     <row r="74">
@@ -2138,25 +2138,25 @@
         <v>26</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C74" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D74" t="s" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E74" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F74" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G74" t="n" s="1">
-        <v>21.19</v>
+        <v>779.41</v>
       </c>
       <c r="H74" t="n" s="1">
-        <v>-21.19</v>
+        <v>-779.41</v>
       </c>
     </row>
     <row r="75">
@@ -2164,25 +2164,25 @@
         <v>26</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C75" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D75" t="s" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E75" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F75" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G75" t="n" s="1">
-        <v>20.82</v>
+        <v>744.28</v>
       </c>
       <c r="H75" t="n" s="1">
-        <v>-20.82</v>
+        <v>-744.28</v>
       </c>
     </row>
     <row r="76">
@@ -2190,25 +2190,25 @@
         <v>26</v>
       </c>
       <c r="B76" t="s" s="1">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C76" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D76" t="s" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E76" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F76" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G76" t="n" s="1">
-        <v>700.72</v>
+        <v>228.78</v>
       </c>
       <c r="H76" t="n" s="1">
-        <v>-700.72</v>
+        <v>-228.78</v>
       </c>
     </row>
     <row r="77">
@@ -2216,25 +2216,25 @@
         <v>26</v>
       </c>
       <c r="B77" t="s" s="1">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C77" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D77" t="s" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E77" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F77" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G77" t="n" s="1">
-        <v>714.08</v>
+        <v>378.27</v>
       </c>
       <c r="H77" t="n" s="1">
-        <v>-714.08</v>
+        <v>-378.27</v>
       </c>
     </row>
     <row r="78">
@@ -2242,25 +2242,25 @@
         <v>26</v>
       </c>
       <c r="B78" t="s" s="1">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C78" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D78" t="s" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E78" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F78" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G78" t="n" s="1">
-        <v>764.9</v>
+        <v>96.52</v>
       </c>
       <c r="H78" t="n" s="1">
-        <v>-764.9</v>
+        <v>-96.52</v>
       </c>
     </row>
     <row r="79">
@@ -2268,25 +2268,25 @@
         <v>26</v>
       </c>
       <c r="B79" t="s" s="1">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C79" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D79" t="s" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E79" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F79" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G79" t="n" s="1">
-        <v>779.41</v>
+        <v>544.5</v>
       </c>
       <c r="H79" t="n" s="1">
-        <v>-779.41</v>
+        <v>-544.5</v>
       </c>
     </row>
     <row r="80">
@@ -2294,7 +2294,7 @@
         <v>26</v>
       </c>
       <c r="B80" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C80" t="s" s="1">
         <v>28</v>
@@ -2309,10 +2309,10 @@
         <v>0.0</v>
       </c>
       <c r="G80" t="n" s="1">
-        <v>744.28</v>
+        <v>6118.3</v>
       </c>
       <c r="H80" t="n" s="1">
-        <v>-744.28</v>
+        <v>-6118.3</v>
       </c>
     </row>
     <row r="81">
@@ -2320,7 +2320,7 @@
         <v>26</v>
       </c>
       <c r="B81" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C81" t="s" s="1">
         <v>28</v>
@@ -2329,16 +2329,16 @@
         <v>95</v>
       </c>
       <c r="E81" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F81" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G81" t="n" s="1">
-        <v>228.78</v>
+        <v>891.0</v>
       </c>
       <c r="H81" t="n" s="1">
-        <v>-228.78</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="82">
@@ -2346,25 +2346,25 @@
         <v>26</v>
       </c>
       <c r="B82" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C82" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D82" t="s" s="1">
         <v>96</v>
       </c>
       <c r="E82" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F82" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G82" t="n" s="1">
-        <v>378.27</v>
+        <v>59.56</v>
       </c>
       <c r="H82" t="n" s="1">
-        <v>-378.27</v>
+        <v>-59.56</v>
       </c>
     </row>
     <row r="83">
@@ -2372,25 +2372,25 @@
         <v>26</v>
       </c>
       <c r="B83" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C83" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D83" t="s" s="1">
         <v>97</v>
       </c>
       <c r="E83" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F83" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G83" t="n" s="1">
-        <v>96.52</v>
+        <v>60.64</v>
       </c>
       <c r="H83" t="n" s="1">
-        <v>-96.52</v>
+        <v>-60.64</v>
       </c>
     </row>
     <row r="84">
@@ -2398,25 +2398,25 @@
         <v>26</v>
       </c>
       <c r="B84" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C84" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D84" t="s" s="1">
         <v>98</v>
       </c>
       <c r="E84" t="s" s="1">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F84" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G84" t="n" s="1">
-        <v>544.5</v>
+        <v>18.64</v>
       </c>
       <c r="H84" t="n" s="1">
-        <v>-544.5</v>
+        <v>-18.64</v>
       </c>
     </row>
     <row r="85">
@@ -2424,25 +2424,25 @@
         <v>26</v>
       </c>
       <c r="B85" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C85" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D85" t="s" s="1">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E85" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G85" t="n" s="1">
-        <v>6118.3</v>
+        <v>18.3</v>
       </c>
       <c r="H85" t="n" s="1">
-        <v>-6118.3</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="86">
@@ -2450,25 +2450,25 @@
         <v>26</v>
       </c>
       <c r="B86" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C86" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D86" t="s" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E86" t="s" s="1">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F86" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G86" t="n" s="1">
-        <v>891.0</v>
+        <v>30.82</v>
       </c>
       <c r="H86" t="n" s="1">
-        <v>-891.0</v>
+        <v>-30.82</v>
       </c>
     </row>
     <row r="87">
@@ -2476,25 +2476,25 @@
         <v>26</v>
       </c>
       <c r="B87" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C87" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D87" t="s" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E87" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F87" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G87" t="n" s="1">
-        <v>59.56</v>
+        <v>30.25</v>
       </c>
       <c r="H87" t="n" s="1">
-        <v>-59.56</v>
+        <v>-30.25</v>
       </c>
     </row>
     <row r="88">
@@ -2502,13 +2502,13 @@
         <v>26</v>
       </c>
       <c r="B88" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C88" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D88" t="s" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E88" t="s" s="1">
         <v>35</v>
@@ -2517,10 +2517,10 @@
         <v>0.0</v>
       </c>
       <c r="G88" t="n" s="1">
-        <v>60.64</v>
+        <v>7.74</v>
       </c>
       <c r="H88" t="n" s="1">
-        <v>-60.64</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="89">
@@ -2528,25 +2528,25 @@
         <v>26</v>
       </c>
       <c r="B89" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D89" t="s" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E89" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F89" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G89" t="n" s="1">
-        <v>18.64</v>
+        <v>7.86</v>
       </c>
       <c r="H89" t="n" s="1">
-        <v>-18.64</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="90">
@@ -2554,25 +2554,25 @@
         <v>26</v>
       </c>
       <c r="B90" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C90" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D90" t="s" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E90" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F90" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G90" t="n" s="1">
-        <v>18.3</v>
+        <v>489.47</v>
       </c>
       <c r="H90" t="n" s="1">
-        <v>-18.3</v>
+        <v>-489.47</v>
       </c>
     </row>
     <row r="91">
@@ -2580,25 +2580,25 @@
         <v>26</v>
       </c>
       <c r="B91" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C91" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D91" t="s" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E91" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F91" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G91" t="n" s="1">
-        <v>30.82</v>
+        <v>498.88</v>
       </c>
       <c r="H91" t="n" s="1">
-        <v>-30.82</v>
+        <v>-498.88</v>
       </c>
     </row>
     <row r="92">
@@ -2606,13 +2606,13 @@
         <v>26</v>
       </c>
       <c r="B92" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C92" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D92" t="s" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E92" t="s" s="1">
         <v>33</v>
@@ -2621,10 +2621,10 @@
         <v>0.0</v>
       </c>
       <c r="G92" t="n" s="1">
-        <v>30.25</v>
+        <v>644.44</v>
       </c>
       <c r="H92" t="n" s="1">
-        <v>-30.25</v>
+        <v>-644.44</v>
       </c>
     </row>
     <row r="93">
@@ -2632,13 +2632,13 @@
         <v>26</v>
       </c>
       <c r="B93" t="s" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C93" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D93" t="s" s="1">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E93" t="s" s="1">
         <v>35</v>
@@ -2647,10 +2647,10 @@
         <v>0.0</v>
       </c>
       <c r="G93" t="n" s="1">
-        <v>7.86</v>
+        <v>632.51</v>
       </c>
       <c r="H93" t="n" s="1">
-        <v>-7.86</v>
+        <v>-632.51</v>
       </c>
     </row>
     <row r="94">
@@ -2658,25 +2658,25 @@
         <v>26</v>
       </c>
       <c r="B94" t="s" s="1">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C94" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D94" t="s" s="1">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E94" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F94" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G94" t="n" s="1">
-        <v>7.74</v>
+        <v>21486.12</v>
       </c>
       <c r="H94" t="n" s="1">
-        <v>-7.74</v>
+        <v>-21486.12</v>
       </c>
     </row>
     <row r="95">
@@ -2684,25 +2684,25 @@
         <v>26</v>
       </c>
       <c r="B95" t="s" s="1">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D95" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E95" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F95" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G95" t="n" s="1">
-        <v>498.88</v>
+        <v>2227.5</v>
       </c>
       <c r="H95" t="n" s="1">
-        <v>-498.88</v>
+        <v>-2227.5</v>
       </c>
     </row>
     <row r="96">
@@ -2710,25 +2710,25 @@
         <v>26</v>
       </c>
       <c r="B96" t="s" s="1">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s" s="1">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="D96" t="s" s="1">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E96" t="s" s="1">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="F96" t="n" s="1">
-        <v>0.0</v>
+        <v>1816.53</v>
       </c>
       <c r="G96" t="n" s="1">
-        <v>489.47</v>
+        <v>0.0</v>
       </c>
       <c r="H96" t="n" s="1">
-        <v>-489.47</v>
+        <v>1816.53</v>
       </c>
     </row>
     <row r="97">
@@ -2736,25 +2736,25 @@
         <v>26</v>
       </c>
       <c r="B97" t="s" s="1">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C97" t="s" s="1">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="D97" t="s" s="1">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E97" t="s" s="1">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="F97" t="n" s="1">
-        <v>0.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G97" t="n" s="1">
-        <v>644.44</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n" s="1">
-        <v>-644.44</v>
+        <v>3500.0</v>
       </c>
     </row>
     <row r="98">
@@ -2762,13 +2762,13 @@
         <v>26</v>
       </c>
       <c r="B98" t="s" s="1">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C98" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D98" t="s" s="1">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E98" t="s" s="1">
         <v>33</v>
@@ -2777,10 +2777,10 @@
         <v>0.0</v>
       </c>
       <c r="G98" t="n" s="1">
-        <v>632.51</v>
+        <v>1751.0</v>
       </c>
       <c r="H98" t="n" s="1">
-        <v>-632.51</v>
+        <v>-1751.0</v>
       </c>
     </row>
     <row r="99">
@@ -2788,25 +2788,25 @@
         <v>26</v>
       </c>
       <c r="B99" t="s" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C99" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D99" t="s" s="1">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E99" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F99" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G99" t="n" s="1">
-        <v>21486.12</v>
+        <v>1718.89</v>
       </c>
       <c r="H99" t="n" s="1">
-        <v>-21486.12</v>
+        <v>-1718.89</v>
       </c>
     </row>
     <row r="100">
@@ -2814,25 +2814,25 @@
         <v>26</v>
       </c>
       <c r="B100" t="s" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C100" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D100" t="s" s="1">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E100" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F100" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G100" t="n" s="1">
-        <v>2227.5</v>
+        <v>30.4</v>
       </c>
       <c r="H100" t="n" s="1">
-        <v>-2227.5</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="101">
@@ -2840,25 +2840,25 @@
         <v>26</v>
       </c>
       <c r="B101" t="s" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C101" t="s" s="1">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s" s="1">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E101" t="s" s="1">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F101" t="n" s="1">
-        <v>3500.0</v>
+        <v>0.0</v>
       </c>
       <c r="G101" t="n" s="1">
-        <v>0.0</v>
+        <v>30.4</v>
       </c>
       <c r="H101" t="n" s="1">
-        <v>3500.0</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="102">
@@ -2866,25 +2866,25 @@
         <v>26</v>
       </c>
       <c r="B102" t="s" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C102" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D102" t="s" s="1">
         <v>117</v>
       </c>
       <c r="E102" t="s" s="1">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F102" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G102" t="n" s="1">
-        <v>1751.0</v>
+        <v>15.2</v>
       </c>
       <c r="H102" t="n" s="1">
-        <v>-1751.0</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="103">
@@ -2892,25 +2892,25 @@
         <v>26</v>
       </c>
       <c r="B103" t="s" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C103" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s" s="1">
         <v>118</v>
       </c>
       <c r="E103" t="s" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F103" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G103" t="n" s="1">
-        <v>1718.89</v>
+        <v>17.46</v>
       </c>
       <c r="H103" t="n" s="1">
-        <v>-1718.89</v>
+        <v>-17.46</v>
       </c>
     </row>
     <row r="104">
@@ -2918,25 +2918,25 @@
         <v>26</v>
       </c>
       <c r="B104" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="C104" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D104" t="s" s="1">
         <v>119</v>
       </c>
-      <c r="C104" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D104" t="s" s="1">
-        <v>120</v>
-      </c>
       <c r="E104" t="s" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F104" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G104" t="n" s="1">
-        <v>155.01</v>
+        <v>17.46</v>
       </c>
       <c r="H104" t="n" s="1">
-        <v>-155.01</v>
+        <v>-17.46</v>
       </c>
     </row>
     <row r="105">
@@ -2944,25 +2944,25 @@
         <v>26</v>
       </c>
       <c r="B105" t="s" s="1">
+        <v>108</v>
+      </c>
+      <c r="C105" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D105" t="s" s="1">
         <v>119</v>
       </c>
-      <c r="C105" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D105" t="s" s="1">
-        <v>121</v>
-      </c>
       <c r="E105" t="s" s="1">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F105" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G105" t="n" s="1">
-        <v>15066.07</v>
+        <v>8.73</v>
       </c>
       <c r="H105" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="106">
@@ -2970,25 +2970,25 @@
         <v>26</v>
       </c>
       <c r="B106" t="s" s="1">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C106" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D106" t="s" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E106" t="s" s="1">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F106" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G106" t="n" s="1">
-        <v>1435.5</v>
+        <v>6.81</v>
       </c>
       <c r="H106" t="n" s="1">
-        <v>-1435.5</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="107">
@@ -2996,25 +2996,25 @@
         <v>26</v>
       </c>
       <c r="B107" t="s" s="1">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C107" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s" s="1">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E107" t="s" s="1">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F107" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G107" t="n" s="1">
-        <v>297.0</v>
+        <v>3.41</v>
       </c>
       <c r="H107" t="n" s="1">
-        <v>-297.0</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="108">
@@ -3022,25 +3022,25 @@
         <v>26</v>
       </c>
       <c r="B108" t="s" s="1">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C108" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D108" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E108" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F108" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G108" t="n" s="1">
-        <v>2283.05</v>
+        <v>6.81</v>
       </c>
       <c r="H108" t="n" s="1">
-        <v>-2283.05</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="109">
@@ -3048,25 +3048,25 @@
         <v>26</v>
       </c>
       <c r="B109" t="s" s="1">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C109" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D109" t="s" s="1">
         <v>123</v>
       </c>
       <c r="E109" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F109" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G109" t="n" s="1">
-        <v>1227.73</v>
+        <v>152.0</v>
       </c>
       <c r="H109" t="n" s="1">
-        <v>-1227.73</v>
+        <v>-152.0</v>
       </c>
     </row>
     <row r="110">
@@ -3074,25 +3074,25 @@
         <v>26</v>
       </c>
       <c r="B110" t="s" s="1">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C110" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D110" t="s" s="1">
+        <v>117</v>
+      </c>
+      <c r="E110" t="s" s="1">
         <v>124</v>
       </c>
-      <c r="E110" t="s" s="1">
-        <v>33</v>
-      </c>
       <c r="F110" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G110" t="n" s="1">
-        <v>1205.61</v>
+        <v>106.4</v>
       </c>
       <c r="H110" t="n" s="1">
-        <v>-1205.61</v>
+        <v>-106.4</v>
       </c>
     </row>
     <row r="111">
@@ -3100,25 +3100,25 @@
         <v>26</v>
       </c>
       <c r="B111" t="s" s="1">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C111" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s" s="1">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E111" t="s" s="1">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="F111" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G111" t="n" s="1">
-        <v>182.66</v>
+        <v>45.6</v>
       </c>
       <c r="H111" t="n" s="1">
-        <v>-182.66</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="112">
@@ -3126,25 +3126,25 @@
         <v>26</v>
       </c>
       <c r="B112" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C112" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D112" t="s" s="1">
         <v>119</v>
       </c>
-      <c r="C112" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D112" t="s" s="1">
-        <v>126</v>
-      </c>
       <c r="E112" t="s" s="1">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F112" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G112" t="n" s="1">
-        <v>186.06</v>
+        <v>61.11</v>
       </c>
       <c r="H112" t="n" s="1">
-        <v>-186.06</v>
+        <v>-61.11</v>
       </c>
     </row>
     <row r="113">
@@ -3152,25 +3152,25 @@
         <v>26</v>
       </c>
       <c r="B113" t="s" s="1">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C113" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s" s="1">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="E113" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F113" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G113" t="n" s="1">
-        <v>100.0</v>
+        <v>87.3</v>
       </c>
       <c r="H113" t="n" s="1">
-        <v>-100.0</v>
+        <v>-87.3</v>
       </c>
     </row>
     <row r="114">
@@ -3178,25 +3178,25 @@
         <v>26</v>
       </c>
       <c r="B114" t="s" s="1">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C114" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D114" t="s" s="1">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="E114" t="s" s="1">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="F114" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G114" t="n" s="1">
-        <v>4588.5</v>
+        <v>26.19</v>
       </c>
       <c r="H114" t="n" s="1">
-        <v>-4588.5</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="115">
@@ -3204,25 +3204,25 @@
         <v>26</v>
       </c>
       <c r="B115" t="s" s="1">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C115" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D115" t="s" s="1">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E115" t="s" s="1">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="F115" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G115" t="n" s="1">
-        <v>239.58</v>
+        <v>23.84</v>
       </c>
       <c r="H115" t="n" s="1">
-        <v>-239.58</v>
+        <v>-23.84</v>
       </c>
     </row>
     <row r="116">
@@ -3230,25 +3230,25 @@
         <v>26</v>
       </c>
       <c r="B116" t="s" s="1">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C116" t="s" s="1">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="D116" t="s" s="1">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="E116" t="s" s="1">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="F116" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G116" t="n" s="1">
-        <v>0.0</v>
+        <v>34.05</v>
       </c>
       <c r="H116" t="n" s="1">
-        <v>840.0</v>
+        <v>-34.05</v>
       </c>
     </row>
     <row r="117">
@@ -3256,25 +3256,25 @@
         <v>26</v>
       </c>
       <c r="B117" t="s" s="1">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C117" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D117" t="s" s="1">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E117" t="s" s="1">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="F117" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G117" t="n" s="1">
-        <v>1500.0</v>
+        <v>155.01</v>
       </c>
       <c r="H117" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-155.01</v>
       </c>
     </row>
     <row r="118">
@@ -3282,25 +3282,25 @@
         <v>26</v>
       </c>
       <c r="B118" t="s" s="1">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C118" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D118" t="s" s="1">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="E118" t="s" s="1">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="F118" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G118" t="n" s="1">
-        <v>4500.0</v>
+        <v>15066.07</v>
       </c>
       <c r="H118" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="119">
@@ -3308,25 +3308,25 @@
         <v>26</v>
       </c>
       <c r="B119" t="s" s="1">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C119" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D119" t="s" s="1">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="E119" t="s" s="1">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="F119" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G119" t="n" s="1">
-        <v>15000.0</v>
+        <v>1435.5</v>
       </c>
       <c r="H119" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-1435.5</v>
       </c>
     </row>
     <row r="120">
@@ -3334,25 +3334,25 @@
         <v>26</v>
       </c>
       <c r="B120" t="s" s="1">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C120" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D120" t="s" s="1">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="E120" t="s" s="1">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="F120" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G120" t="n" s="1">
-        <v>2000.0</v>
+        <v>297.0</v>
       </c>
       <c r="H120" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-297.0</v>
       </c>
     </row>
     <row r="121">
@@ -3360,25 +3360,25 @@
         <v>26</v>
       </c>
       <c r="B121" t="s" s="1">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C121" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D121" t="s" s="1">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E121" t="s" s="1">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="F121" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G121" t="n" s="1">
-        <v>146.67</v>
+        <v>2283.05</v>
       </c>
       <c r="H121" t="n" s="1">
-        <v>-146.67</v>
+        <v>-2283.05</v>
       </c>
     </row>
     <row r="122">
@@ -3386,25 +3386,25 @@
         <v>26</v>
       </c>
       <c r="B122" t="s" s="1">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C122" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D122" t="s" s="1">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="E122" t="s" s="1">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F122" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G122" t="n" s="1">
-        <v>180.0</v>
+        <v>1227.73</v>
       </c>
       <c r="H122" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1227.73</v>
       </c>
     </row>
     <row r="123">
@@ -3412,25 +3412,25 @@
         <v>26</v>
       </c>
       <c r="B123" t="s" s="1">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C123" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D123" t="s" s="1">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>9216.24</v>
+        <v>1205.61</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-1205.61</v>
       </c>
     </row>
     <row r="124">
@@ -3438,25 +3438,25 @@
         <v>26</v>
       </c>
       <c r="B124" t="s" s="1">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C124" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D124" t="s" s="1">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>891.0</v>
+        <v>186.06</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-891.0</v>
+        <v>-186.06</v>
       </c>
     </row>
     <row r="125">
@@ -3464,25 +3464,25 @@
         <v>26</v>
       </c>
       <c r="B125" t="s" s="1">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C125" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D125" t="s" s="1">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="E125" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F125" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G125" t="n" s="1">
-        <v>737.28</v>
+        <v>182.66</v>
       </c>
       <c r="H125" t="n" s="1">
-        <v>-737.28</v>
+        <v>-182.66</v>
       </c>
     </row>
     <row r="126">
@@ -3490,25 +3490,25 @@
         <v>26</v>
       </c>
       <c r="B126" t="s" s="1">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C126" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D126" t="s" s="1">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="E126" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F126" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G126" t="n" s="1">
-        <v>750.99</v>
+        <v>100.0</v>
       </c>
       <c r="H126" t="n" s="1">
-        <v>-750.99</v>
+        <v>-100.0</v>
       </c>
     </row>
     <row r="127">
@@ -3516,25 +3516,25 @@
         <v>26</v>
       </c>
       <c r="B127" t="s" s="1">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C127" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D127" t="s" s="1">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="E127" t="s" s="1">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="F127" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G127" t="n" s="1">
-        <v>1544.4</v>
+        <v>239.58</v>
       </c>
       <c r="H127" t="n" s="1">
-        <v>-1544.4</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="128">
@@ -3542,25 +3542,25 @@
         <v>26</v>
       </c>
       <c r="B128" t="s" s="1">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C128" t="s" s="1">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="D128" t="s" s="1">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="E128" t="s" s="1">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F128" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G128" t="n" s="1">
-        <v>180.06</v>
+        <v>0.0</v>
       </c>
       <c r="H128" t="n" s="1">
-        <v>-180.06</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="129">
@@ -3568,25 +3568,25 @@
         <v>26</v>
       </c>
       <c r="B129" t="s" s="1">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C129" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D129" t="s" s="1">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>1925.0</v>
+        <v>4500.0</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="130">
@@ -3594,25 +3594,25 @@
         <v>26</v>
       </c>
       <c r="B130" t="s" s="1">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C130" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D130" t="s" s="1">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="F130" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>180.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>-180.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="131">
@@ -3620,25 +3620,25 @@
         <v>26</v>
       </c>
       <c r="B131" t="s" s="1">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C131" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D131" t="s" s="1">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="E131" t="s" s="1">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="F131" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G131" t="n" s="1">
-        <v>180.0</v>
+        <v>1500.0</v>
       </c>
       <c r="H131" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="132">
@@ -3646,25 +3646,25 @@
         <v>26</v>
       </c>
       <c r="B132" t="s" s="1">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C132" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D132" t="s" s="1">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G132" t="n" s="1">
-        <v>1201.89</v>
+        <v>2000.0</v>
       </c>
       <c r="H132" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="133">
@@ -3672,25 +3672,25 @@
         <v>26</v>
       </c>
       <c r="B133" t="s" s="1">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C133" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D133" t="s" s="1">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="E133" t="s" s="1">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="F133" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G133" t="n" s="1">
-        <v>180.0</v>
+        <v>146.67</v>
       </c>
       <c r="H133" t="n" s="1">
-        <v>-180.0</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="134">
@@ -3698,13 +3698,13 @@
         <v>26</v>
       </c>
       <c r="B134" t="s" s="1">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C134" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D134" t="s" s="1">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E134" t="s" s="1">
         <v>64</v>
@@ -3724,13 +3724,13 @@
         <v>26</v>
       </c>
       <c r="B135" t="s" s="1">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C135" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D135" t="s" s="1">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E135" t="s" s="1">
         <v>30</v>
@@ -3739,10 +3739,10 @@
         <v>0.0</v>
       </c>
       <c r="G135" t="n" s="1">
-        <v>25504.78</v>
+        <v>9216.24</v>
       </c>
       <c r="H135" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="136">
@@ -3750,25 +3750,25 @@
         <v>26</v>
       </c>
       <c r="B136" t="s" s="1">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C136" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D136" t="s" s="1">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E136" t="s" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F136" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G136" t="n" s="1">
-        <v>2277.0</v>
+        <v>891.0</v>
       </c>
       <c r="H136" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="137">
@@ -3776,13 +3776,13 @@
         <v>26</v>
       </c>
       <c r="B137" t="s" s="1">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C137" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D137" t="s" s="1">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="E137" t="s" s="1">
         <v>35</v>
@@ -3791,10 +3791,10 @@
         <v>0.0</v>
       </c>
       <c r="G137" t="n" s="1">
-        <v>2078.64</v>
+        <v>737.28</v>
       </c>
       <c r="H137" t="n" s="1">
-        <v>-2078.64</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="138">
@@ -3802,13 +3802,13 @@
         <v>26</v>
       </c>
       <c r="B138" t="s" s="1">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C138" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D138" t="s" s="1">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="E138" t="s" s="1">
         <v>33</v>
@@ -3817,10 +3817,10 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n" s="1">
-        <v>2040.52</v>
+        <v>750.99</v>
       </c>
       <c r="H138" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="139">
@@ -3828,25 +3828,25 @@
         <v>26</v>
       </c>
       <c r="B139" t="s" s="1">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C139" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D139" t="s" s="1">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="E139" t="s" s="1">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F139" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G139" t="n" s="1">
-        <v>180.0</v>
+        <v>1544.4</v>
       </c>
       <c r="H139" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="140">
@@ -3854,25 +3854,25 @@
         <v>26</v>
       </c>
       <c r="B140" t="s" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C140" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D140" t="s" s="1">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="E140" t="s" s="1">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="F140" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G140" t="n" s="1">
-        <v>180.0</v>
+        <v>1925.0</v>
       </c>
       <c r="H140" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="141">
@@ -3880,25 +3880,25 @@
         <v>26</v>
       </c>
       <c r="B141" t="s" s="1">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C141" t="s" s="1">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="D141" t="s" s="1">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="E141" t="s" s="1">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="F141" t="n" s="1">
-        <v>1816.53</v>
+        <v>0.0</v>
       </c>
       <c r="G141" t="n" s="1">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="H141" t="n" s="1">
-        <v>1816.53</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="142">
@@ -3906,25 +3906,25 @@
         <v>26</v>
       </c>
       <c r="B142" t="s" s="1">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C142" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D142" t="s" s="1">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="E142" t="s" s="1">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="F142" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G142" t="n" s="1">
-        <v>3750.0</v>
+        <v>180.0</v>
       </c>
       <c r="H142" t="n" s="1">
-        <v>-3750.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="143">
@@ -3932,25 +3932,25 @@
         <v>26</v>
       </c>
       <c r="B143" t="s" s="1">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C143" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D143" t="s" s="1">
-        <v>44</v>
+        <v>152</v>
       </c>
       <c r="E143" t="s" s="1">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F143" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G143" t="n" s="1">
-        <v>1000.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H143" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="144">
@@ -3958,48 +3958,282 @@
         <v>26</v>
       </c>
       <c r="B144" t="s" s="1">
+        <v>151</v>
+      </c>
+      <c r="C144" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D144" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="E144" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F144" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G144" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H144" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B145" t="s" s="1">
+        <v>151</v>
+      </c>
+      <c r="C145" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D145" t="s" s="1">
+        <v>95</v>
+      </c>
+      <c r="E145" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F145" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G145" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H145" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B146" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="C146" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D146" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E146" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F146" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G146" t="n" s="1">
+        <v>2277.0</v>
+      </c>
+      <c r="H146" t="n" s="1">
+        <v>-2277.0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B147" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="C147" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D147" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E147" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="F147" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G147" t="n" s="1">
+        <v>25504.78</v>
+      </c>
+      <c r="H147" t="n" s="1">
+        <v>-25504.78</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B148" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="C148" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D148" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="E148" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F148" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G148" t="n" s="1">
+        <v>2078.64</v>
+      </c>
+      <c r="H148" t="n" s="1">
+        <v>-2078.64</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B149" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="C149" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D149" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="E149" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F149" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G149" t="n" s="1">
+        <v>2040.52</v>
+      </c>
+      <c r="H149" t="n" s="1">
+        <v>-2040.52</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B150" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="C150" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D150" t="s" s="1">
+        <v>109</v>
+      </c>
+      <c r="E150" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F150" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G150" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H150" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B151" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C151" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D151" t="s" s="1">
+        <v>128</v>
+      </c>
+      <c r="E151" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="F151" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G151" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H151" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B152" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="C152" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D152" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="E152" t="s" s="1">
         <v>158</v>
       </c>
-      <c r="C144" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D144" t="s" s="1">
+      <c r="F152" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G152" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H152" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B153" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="C153" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D153" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="E153" t="s" s="1">
         <v>159</v>
       </c>
-      <c r="E144" t="s" s="1">
-        <v>30</v>
-      </c>
-      <c r="F144" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G144" t="n" s="1">
-        <v>1255.07</v>
-      </c>
-      <c r="H144" t="n" s="1">
-        <v>-1255.07</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="s">
+      <c r="F153" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G153" t="n" s="1">
+        <v>3750.0</v>
+      </c>
+      <c r="H153" t="n" s="1">
+        <v>-3750.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B156" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="s">
+    <row r="157">
+      <c r="A157" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B157" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="s">
+    <row r="158">
+      <c r="A158" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B158" s="3" t="s">
         <v>165</v>
       </c>
     </row>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="175">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -201,6 +201,9 @@
     <t>103501 - 2</t>
   </si>
   <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
     <t>08/10/2026</t>
   </si>
   <si>
@@ -321,24 +324,24 @@
     <t>1633 - 2</t>
   </si>
   <si>
+    <t>1634 - 3</t>
+  </si>
+  <si>
     <t>1634 - 2</t>
   </si>
   <si>
-    <t>1634 - 3</t>
+    <t>101201 - 3</t>
   </si>
   <si>
     <t>101201 - 2</t>
   </si>
   <si>
-    <t>101201 - 3</t>
+    <t>101801 - 2</t>
   </si>
   <si>
     <t>101801 - 3</t>
   </si>
   <si>
-    <t>101801 - 2</t>
-  </si>
-  <si>
     <t>15/10/2026</t>
   </si>
   <si>
@@ -348,39 +351,33 @@
     <t>DUP-Duplicata de Contrato</t>
   </si>
   <si>
-    <t>29001 - 11</t>
-  </si>
-  <si>
-    <t>GABRIEL DE CARVALHO MELLO</t>
-  </si>
-  <si>
     <t>103501 - 0</t>
   </si>
   <si>
     <t>IL HEE PARK</t>
   </si>
   <si>
+    <t>101101 - 2</t>
+  </si>
+  <si>
     <t>101101 - 3</t>
   </si>
   <si>
-    <t>101101 - 2</t>
-  </si>
-  <si>
     <t>103801 - 1</t>
   </si>
   <si>
+    <t>104701 - 1</t>
+  </si>
+  <si>
     <t>104701 - 2</t>
   </si>
   <si>
-    <t>104701 - 1</t>
+    <t>104801 - 2</t>
   </si>
   <si>
     <t>104801 - 1</t>
   </si>
   <si>
-    <t>104801 - 2</t>
-  </si>
-  <si>
     <t>16/10/2026</t>
   </si>
   <si>
@@ -390,6 +387,12 @@
     <t>RAYSSA BARBOSA SILVA</t>
   </si>
   <si>
+    <t>105001 - 1</t>
+  </si>
+  <si>
+    <t>105001 - 2</t>
+  </si>
+  <si>
     <t>17/10/2026</t>
   </si>
   <si>
@@ -402,18 +405,33 @@
     <t>102501 - 1</t>
   </si>
   <si>
+    <t>102401 - 2</t>
+  </si>
+  <si>
     <t>102401 - 3</t>
   </si>
   <si>
-    <t>102401 - 2</t>
-  </si>
-  <si>
     <t>102501 - 3</t>
   </si>
   <si>
     <t>102501 - 2</t>
   </si>
   <si>
+    <t>105101 - 1</t>
+  </si>
+  <si>
+    <t>PAGSEGURO</t>
+  </si>
+  <si>
+    <t>105301 - 1</t>
+  </si>
+  <si>
+    <t>105101 - 2</t>
+  </si>
+  <si>
+    <t>105301 - 2</t>
+  </si>
+  <si>
     <t>18/10/2026</t>
   </si>
   <si>
@@ -429,9 +447,18 @@
     <t>MP Interiores e Serv Ltda</t>
   </si>
   <si>
+    <t>ERIC SERPA</t>
+  </si>
+  <si>
     <t>20/10/2026</t>
   </si>
   <si>
+    <t>105001 - 0</t>
+  </si>
+  <si>
+    <t>Patricia Souza Fernandez</t>
+  </si>
+  <si>
     <t>IRRF- darf</t>
   </si>
   <si>
@@ -498,19 +525,19 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>6.156,53</t>
+    <t>6.271,16</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>247.751,73</t>
+    <t>265.670,42</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-241.595,20</t>
+    <t>-259.399,26</t>
   </si>
 </sst>
 </file>
@@ -578,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H158"/>
+  <dimension ref="A2:H178"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -1367,7 +1394,7 @@
         <v>61</v>
       </c>
       <c r="E44" t="s" s="1">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="F44" t="n" s="1">
         <v>0.0</v>
@@ -1410,16 +1437,16 @@
         <v>26</v>
       </c>
       <c r="B46" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D46" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F46" t="n" s="1">
         <v>0.0</v>
@@ -1436,7 +1463,7 @@
         <v>26</v>
       </c>
       <c r="B47" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C47" t="s" s="1">
         <v>36</v>
@@ -1445,7 +1472,7 @@
         <v>59</v>
       </c>
       <c r="E47" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F47" t="n" s="1">
         <v>0.0</v>
@@ -1462,7 +1489,7 @@
         <v>26</v>
       </c>
       <c r="B48" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s" s="1">
         <v>36</v>
@@ -1488,7 +1515,7 @@
         <v>26</v>
       </c>
       <c r="B49" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C49" t="s" s="1">
         <v>36</v>
@@ -1514,7 +1541,7 @@
         <v>26</v>
       </c>
       <c r="B50" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C50" t="s" s="1">
         <v>36</v>
@@ -1540,7 +1567,7 @@
         <v>26</v>
       </c>
       <c r="B51" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C51" t="s" s="1">
         <v>36</v>
@@ -1566,13 +1593,13 @@
         <v>26</v>
       </c>
       <c r="B52" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C52" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D52" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E52" t="s" s="1">
         <v>38</v>
@@ -1592,13 +1619,13 @@
         <v>26</v>
       </c>
       <c r="B53" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D53" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E53" t="s" s="1">
         <v>30</v>
@@ -1618,13 +1645,13 @@
         <v>26</v>
       </c>
       <c r="B54" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C54" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D54" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E54" t="s" s="1">
         <v>30</v>
@@ -1644,13 +1671,13 @@
         <v>26</v>
       </c>
       <c r="B55" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C55" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D55" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E55" t="s" s="1">
         <v>38</v>
@@ -1670,16 +1697,16 @@
         <v>26</v>
       </c>
       <c r="B56" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D56" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E56" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F56" t="n" s="1">
         <v>0.0</v>
@@ -1696,16 +1723,16 @@
         <v>26</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C57" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D57" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="E57" t="s" s="1">
         <v>72</v>
-      </c>
-      <c r="E57" t="s" s="1">
-        <v>71</v>
       </c>
       <c r="F57" t="n" s="1">
         <v>0.0</v>
@@ -1722,13 +1749,13 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C58" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E58" t="s" s="1">
         <v>35</v>
@@ -1748,13 +1775,13 @@
         <v>26</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E59" t="s" s="1">
         <v>33</v>
@@ -1774,7 +1801,7 @@
         <v>26</v>
       </c>
       <c r="B60" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" t="s" s="1">
         <v>31</v>
@@ -1800,13 +1827,13 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C61" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D61" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E61" t="s" s="1">
         <v>33</v>
@@ -1826,13 +1853,13 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D62" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E62" t="s" s="1">
         <v>35</v>
@@ -1852,13 +1879,13 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D63" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E63" t="s" s="1">
         <v>38</v>
@@ -1878,13 +1905,13 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C64" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E64" t="s" s="1">
         <v>35</v>
@@ -1904,13 +1931,13 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E65" t="s" s="1">
         <v>33</v>
@@ -1930,13 +1957,13 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E66" t="s" s="1">
         <v>30</v>
@@ -1956,13 +1983,13 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C67" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E67" t="s" s="1">
         <v>30</v>
@@ -1982,13 +2009,13 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C68" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D68" t="s" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E68" t="s" s="1">
         <v>38</v>
@@ -2008,13 +2035,13 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E69" t="s" s="1">
         <v>38</v>
@@ -2034,13 +2061,13 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E70" t="s" s="1">
         <v>30</v>
@@ -2060,13 +2087,13 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C71" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D71" t="s" s="1">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E71" t="s" s="1">
         <v>33</v>
@@ -2086,13 +2113,13 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C72" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D72" t="s" s="1">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E72" t="s" s="1">
         <v>35</v>
@@ -2112,13 +2139,13 @@
         <v>26</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C73" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D73" t="s" s="1">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E73" t="s" s="1">
         <v>35</v>
@@ -2138,13 +2165,13 @@
         <v>26</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C74" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D74" t="s" s="1">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E74" t="s" s="1">
         <v>33</v>
@@ -2164,13 +2191,13 @@
         <v>26</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C75" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D75" t="s" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E75" t="s" s="1">
         <v>30</v>
@@ -2190,13 +2217,13 @@
         <v>26</v>
       </c>
       <c r="B76" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C76" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D76" t="s" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E76" t="s" s="1">
         <v>30</v>
@@ -2216,13 +2243,13 @@
         <v>26</v>
       </c>
       <c r="B77" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C77" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D77" t="s" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E77" t="s" s="1">
         <v>30</v>
@@ -2242,13 +2269,13 @@
         <v>26</v>
       </c>
       <c r="B78" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C78" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D78" t="s" s="1">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E78" t="s" s="1">
         <v>30</v>
@@ -2268,25 +2295,25 @@
         <v>26</v>
       </c>
       <c r="B79" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C79" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D79" t="s" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E79" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F79" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G79" t="n" s="1">
-        <v>544.5</v>
+        <v>6118.3</v>
       </c>
       <c r="H79" t="n" s="1">
-        <v>-544.5</v>
+        <v>-6118.3</v>
       </c>
     </row>
     <row r="80">
@@ -2294,25 +2321,25 @@
         <v>26</v>
       </c>
       <c r="B80" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C80" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D80" t="s" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F80" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G80" t="n" s="1">
-        <v>6118.3</v>
+        <v>544.5</v>
       </c>
       <c r="H80" t="n" s="1">
-        <v>-6118.3</v>
+        <v>-544.5</v>
       </c>
     </row>
     <row r="81">
@@ -2320,13 +2347,13 @@
         <v>26</v>
       </c>
       <c r="B81" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C81" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D81" t="s" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E81" t="s" s="1">
         <v>38</v>
@@ -2346,13 +2373,13 @@
         <v>26</v>
       </c>
       <c r="B82" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C82" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D82" t="s" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E82" t="s" s="1">
         <v>35</v>
@@ -2372,13 +2399,13 @@
         <v>26</v>
       </c>
       <c r="B83" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D83" t="s" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E83" t="s" s="1">
         <v>33</v>
@@ -2398,13 +2425,13 @@
         <v>26</v>
       </c>
       <c r="B84" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C84" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D84" t="s" s="1">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E84" t="s" s="1">
         <v>33</v>
@@ -2424,13 +2451,13 @@
         <v>26</v>
       </c>
       <c r="B85" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C85" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D85" t="s" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E85" t="s" s="1">
         <v>35</v>
@@ -2450,13 +2477,13 @@
         <v>26</v>
       </c>
       <c r="B86" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C86" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D86" t="s" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E86" t="s" s="1">
         <v>33</v>
@@ -2476,13 +2503,13 @@
         <v>26</v>
       </c>
       <c r="B87" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C87" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D87" t="s" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E87" t="s" s="1">
         <v>35</v>
@@ -2502,25 +2529,25 @@
         <v>26</v>
       </c>
       <c r="B88" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C88" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D88" t="s" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E88" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F88" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G88" t="n" s="1">
-        <v>7.74</v>
+        <v>7.86</v>
       </c>
       <c r="H88" t="n" s="1">
-        <v>-7.74</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="89">
@@ -2528,25 +2555,25 @@
         <v>26</v>
       </c>
       <c r="B89" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C89" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D89" t="s" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E89" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F89" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G89" t="n" s="1">
-        <v>7.86</v>
+        <v>7.74</v>
       </c>
       <c r="H89" t="n" s="1">
-        <v>-7.86</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="90">
@@ -2554,25 +2581,25 @@
         <v>26</v>
       </c>
       <c r="B90" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C90" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D90" t="s" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E90" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F90" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G90" t="n" s="1">
-        <v>489.47</v>
+        <v>498.88</v>
       </c>
       <c r="H90" t="n" s="1">
-        <v>-489.47</v>
+        <v>-498.88</v>
       </c>
     </row>
     <row r="91">
@@ -2580,25 +2607,25 @@
         <v>26</v>
       </c>
       <c r="B91" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C91" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D91" t="s" s="1">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E91" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F91" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G91" t="n" s="1">
-        <v>498.88</v>
+        <v>489.47</v>
       </c>
       <c r="H91" t="n" s="1">
-        <v>-498.88</v>
+        <v>-489.47</v>
       </c>
     </row>
     <row r="92">
@@ -2606,25 +2633,25 @@
         <v>26</v>
       </c>
       <c r="B92" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C92" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D92" t="s" s="1">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E92" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F92" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G92" t="n" s="1">
-        <v>644.44</v>
+        <v>632.51</v>
       </c>
       <c r="H92" t="n" s="1">
-        <v>-644.44</v>
+        <v>-632.51</v>
       </c>
     </row>
     <row r="93">
@@ -2632,25 +2659,25 @@
         <v>26</v>
       </c>
       <c r="B93" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C93" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D93" t="s" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E93" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F93" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G93" t="n" s="1">
-        <v>632.51</v>
+        <v>644.44</v>
       </c>
       <c r="H93" t="n" s="1">
-        <v>-632.51</v>
+        <v>-644.44</v>
       </c>
     </row>
     <row r="94">
@@ -2658,13 +2685,13 @@
         <v>26</v>
       </c>
       <c r="B94" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C94" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D94" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E94" t="s" s="1">
         <v>30</v>
@@ -2684,13 +2711,13 @@
         <v>26</v>
       </c>
       <c r="B95" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C95" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D95" t="s" s="1">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E95" t="s" s="1">
         <v>38</v>
@@ -2710,25 +2737,25 @@
         <v>26</v>
       </c>
       <c r="B96" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D96" t="s" s="1">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E96" t="s" s="1">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F96" t="n" s="1">
-        <v>1816.53</v>
+        <v>3500.0</v>
       </c>
       <c r="G96" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="H96" t="n" s="1">
-        <v>1816.53</v>
+        <v>3500.0</v>
       </c>
     </row>
     <row r="97">
@@ -2736,25 +2763,25 @@
         <v>26</v>
       </c>
       <c r="B97" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s" s="1">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="D97" t="s" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E97" t="s" s="1">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="F97" t="n" s="1">
-        <v>3500.0</v>
+        <v>0.0</v>
       </c>
       <c r="G97" t="n" s="1">
-        <v>0.0</v>
+        <v>1718.89</v>
       </c>
       <c r="H97" t="n" s="1">
-        <v>3500.0</v>
+        <v>-1718.89</v>
       </c>
     </row>
     <row r="98">
@@ -2762,7 +2789,7 @@
         <v>26</v>
       </c>
       <c r="B98" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C98" t="s" s="1">
         <v>31</v>
@@ -2788,25 +2815,25 @@
         <v>26</v>
       </c>
       <c r="B99" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C99" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s" s="1">
         <v>116</v>
       </c>
       <c r="E99" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F99" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G99" t="n" s="1">
-        <v>1718.89</v>
+        <v>30.4</v>
       </c>
       <c r="H99" t="n" s="1">
-        <v>-1718.89</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="100">
@@ -2814,25 +2841,25 @@
         <v>26</v>
       </c>
       <c r="B100" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C100" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D100" t="s" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E100" t="s" s="1">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F100" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G100" t="n" s="1">
-        <v>30.4</v>
+        <v>15.2</v>
       </c>
       <c r="H100" t="n" s="1">
-        <v>-30.4</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="101">
@@ -2840,13 +2867,13 @@
         <v>26</v>
       </c>
       <c r="B101" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C101" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D101" t="s" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E101" t="s" s="1">
         <v>50</v>
@@ -2866,7 +2893,7 @@
         <v>26</v>
       </c>
       <c r="B102" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C102" t="s" s="1">
         <v>36</v>
@@ -2881,10 +2908,10 @@
         <v>0.0</v>
       </c>
       <c r="G102" t="n" s="1">
-        <v>15.2</v>
+        <v>8.73</v>
       </c>
       <c r="H102" t="n" s="1">
-        <v>-15.2</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="103">
@@ -2892,7 +2919,7 @@
         <v>26</v>
       </c>
       <c r="B103" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C103" t="s" s="1">
         <v>36</v>
@@ -2918,13 +2945,13 @@
         <v>26</v>
       </c>
       <c r="B104" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C104" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D104" t="s" s="1">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E104" t="s" s="1">
         <v>50</v>
@@ -2944,7 +2971,7 @@
         <v>26</v>
       </c>
       <c r="B105" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C105" t="s" s="1">
         <v>36</v>
@@ -2953,16 +2980,16 @@
         <v>119</v>
       </c>
       <c r="E105" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F105" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G105" t="n" s="1">
-        <v>8.73</v>
+        <v>6.81</v>
       </c>
       <c r="H105" t="n" s="1">
-        <v>-8.73</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="106">
@@ -2970,7 +2997,7 @@
         <v>26</v>
       </c>
       <c r="B106" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C106" t="s" s="1">
         <v>36</v>
@@ -2996,7 +3023,7 @@
         <v>26</v>
       </c>
       <c r="B107" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C107" t="s" s="1">
         <v>36</v>
@@ -3022,13 +3049,13 @@
         <v>26</v>
       </c>
       <c r="B108" t="s" s="1">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C108" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D108" t="s" s="1">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E108" t="s" s="1">
         <v>38</v>
@@ -3037,10 +3064,10 @@
         <v>0.0</v>
       </c>
       <c r="G108" t="n" s="1">
-        <v>6.81</v>
+        <v>152.0</v>
       </c>
       <c r="H108" t="n" s="1">
-        <v>-6.81</v>
+        <v>-152.0</v>
       </c>
     </row>
     <row r="109">
@@ -3048,25 +3075,25 @@
         <v>26</v>
       </c>
       <c r="B109" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C109" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D109" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="E109" t="s" s="1">
         <v>123</v>
       </c>
-      <c r="E109" t="s" s="1">
-        <v>38</v>
-      </c>
       <c r="F109" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G109" t="n" s="1">
-        <v>152.0</v>
+        <v>106.4</v>
       </c>
       <c r="H109" t="n" s="1">
-        <v>-152.0</v>
+        <v>-106.4</v>
       </c>
     </row>
     <row r="110">
@@ -3074,25 +3101,25 @@
         <v>26</v>
       </c>
       <c r="B110" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C110" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D110" t="s" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E110" t="s" s="1">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="F110" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G110" t="n" s="1">
-        <v>106.4</v>
+        <v>45.6</v>
       </c>
       <c r="H110" t="n" s="1">
-        <v>-106.4</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="111">
@@ -3100,7 +3127,7 @@
         <v>26</v>
       </c>
       <c r="B111" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C111" t="s" s="1">
         <v>36</v>
@@ -3109,16 +3136,16 @@
         <v>117</v>
       </c>
       <c r="E111" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F111" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G111" t="n" s="1">
-        <v>45.6</v>
+        <v>61.11</v>
       </c>
       <c r="H111" t="n" s="1">
-        <v>-45.6</v>
+        <v>-61.11</v>
       </c>
     </row>
     <row r="112">
@@ -3126,25 +3153,25 @@
         <v>26</v>
       </c>
       <c r="B112" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C112" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D112" t="s" s="1">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E112" t="s" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F112" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G112" t="n" s="1">
-        <v>61.11</v>
+        <v>26.19</v>
       </c>
       <c r="H112" t="n" s="1">
-        <v>-61.11</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="113">
@@ -3152,13 +3179,13 @@
         <v>26</v>
       </c>
       <c r="B113" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C113" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D113" t="s" s="1">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E113" t="s" s="1">
         <v>38</v>
@@ -3178,25 +3205,25 @@
         <v>26</v>
       </c>
       <c r="B114" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C114" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D114" t="s" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E114" t="s" s="1">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F114" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G114" t="n" s="1">
-        <v>26.19</v>
+        <v>23.84</v>
       </c>
       <c r="H114" t="n" s="1">
-        <v>-26.19</v>
+        <v>-23.84</v>
       </c>
     </row>
     <row r="115">
@@ -3204,7 +3231,7 @@
         <v>26</v>
       </c>
       <c r="B115" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C115" t="s" s="1">
         <v>36</v>
@@ -3213,16 +3240,16 @@
         <v>120</v>
       </c>
       <c r="E115" t="s" s="1">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F115" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G115" t="n" s="1">
-        <v>23.84</v>
+        <v>34.05</v>
       </c>
       <c r="H115" t="n" s="1">
-        <v>-23.84</v>
+        <v>-34.05</v>
       </c>
     </row>
     <row r="116">
@@ -3230,25 +3257,25 @@
         <v>26</v>
       </c>
       <c r="B116" t="s" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C116" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D116" t="s" s="1">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E116" t="s" s="1">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F116" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G116" t="n" s="1">
-        <v>34.05</v>
+        <v>135.18</v>
       </c>
       <c r="H116" t="n" s="1">
-        <v>-34.05</v>
+        <v>-135.18</v>
       </c>
     </row>
     <row r="117">
@@ -3256,25 +3283,25 @@
         <v>26</v>
       </c>
       <c r="B117" t="s" s="1">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s" s="1">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E117" t="s" s="1">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F117" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G117" t="n" s="1">
-        <v>155.01</v>
+        <v>57.93</v>
       </c>
       <c r="H117" t="n" s="1">
-        <v>-155.01</v>
+        <v>-57.93</v>
       </c>
     </row>
     <row r="118">
@@ -3282,25 +3309,25 @@
         <v>26</v>
       </c>
       <c r="B118" t="s" s="1">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s" s="1">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E118" t="s" s="1">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F118" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G118" t="n" s="1">
-        <v>15066.07</v>
+        <v>19.31</v>
       </c>
       <c r="H118" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-19.31</v>
       </c>
     </row>
     <row r="119">
@@ -3308,13 +3335,13 @@
         <v>26</v>
       </c>
       <c r="B119" t="s" s="1">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C119" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s" s="1">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E119" t="s" s="1">
         <v>38</v>
@@ -3323,10 +3350,10 @@
         <v>0.0</v>
       </c>
       <c r="G119" t="n" s="1">
-        <v>1435.5</v>
+        <v>193.12</v>
       </c>
       <c r="H119" t="n" s="1">
-        <v>-1435.5</v>
+        <v>-193.12</v>
       </c>
     </row>
     <row r="120">
@@ -3334,13 +3361,13 @@
         <v>26</v>
       </c>
       <c r="B120" t="s" s="1">
+        <v>121</v>
+      </c>
+      <c r="C120" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D120" t="s" s="1">
         <v>125</v>
-      </c>
-      <c r="C120" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D120" t="s" s="1">
-        <v>128</v>
       </c>
       <c r="E120" t="s" s="1">
         <v>38</v>
@@ -3349,10 +3376,10 @@
         <v>0.0</v>
       </c>
       <c r="G120" t="n" s="1">
-        <v>297.0</v>
+        <v>38.62</v>
       </c>
       <c r="H120" t="n" s="1">
-        <v>-297.0</v>
+        <v>-38.62</v>
       </c>
     </row>
     <row r="121">
@@ -3360,25 +3387,25 @@
         <v>26</v>
       </c>
       <c r="B121" t="s" s="1">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s" s="1">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E121" t="s" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F121" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G121" t="n" s="1">
-        <v>2283.05</v>
+        <v>38.62</v>
       </c>
       <c r="H121" t="n" s="1">
-        <v>-2283.05</v>
+        <v>-38.62</v>
       </c>
     </row>
     <row r="122">
@@ -3386,25 +3413,25 @@
         <v>26</v>
       </c>
       <c r="B122" t="s" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C122" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D122" t="s" s="1">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E122" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F122" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G122" t="n" s="1">
-        <v>1227.73</v>
+        <v>155.01</v>
       </c>
       <c r="H122" t="n" s="1">
-        <v>-1227.73</v>
+        <v>-155.01</v>
       </c>
     </row>
     <row r="123">
@@ -3412,25 +3439,25 @@
         <v>26</v>
       </c>
       <c r="B123" t="s" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C123" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D123" t="s" s="1">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>1205.61</v>
+        <v>1435.5</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-1205.61</v>
+        <v>-1435.5</v>
       </c>
     </row>
     <row r="124">
@@ -3438,25 +3465,25 @@
         <v>26</v>
       </c>
       <c r="B124" t="s" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C124" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D124" t="s" s="1">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>186.06</v>
+        <v>15066.07</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-186.06</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="125">
@@ -3464,25 +3491,25 @@
         <v>26</v>
       </c>
       <c r="B125" t="s" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C125" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D125" t="s" s="1">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E125" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F125" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G125" t="n" s="1">
-        <v>182.66</v>
+        <v>297.0</v>
       </c>
       <c r="H125" t="n" s="1">
-        <v>-182.66</v>
+        <v>-297.0</v>
       </c>
     </row>
     <row r="126">
@@ -3490,25 +3517,25 @@
         <v>26</v>
       </c>
       <c r="B126" t="s" s="1">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C126" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D126" t="s" s="1">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="E126" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F126" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G126" t="n" s="1">
-        <v>100.0</v>
+        <v>2283.05</v>
       </c>
       <c r="H126" t="n" s="1">
-        <v>-100.0</v>
+        <v>-2283.05</v>
       </c>
     </row>
     <row r="127">
@@ -3516,25 +3543,25 @@
         <v>26</v>
       </c>
       <c r="B127" t="s" s="1">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C127" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D127" t="s" s="1">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E127" t="s" s="1">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="F127" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G127" t="n" s="1">
-        <v>239.58</v>
+        <v>1205.61</v>
       </c>
       <c r="H127" t="n" s="1">
-        <v>-239.58</v>
+        <v>-1205.61</v>
       </c>
     </row>
     <row r="128">
@@ -3542,25 +3569,25 @@
         <v>26</v>
       </c>
       <c r="B128" t="s" s="1">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C128" t="s" s="1">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="D128" t="s" s="1">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="E128" t="s" s="1">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="F128" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G128" t="n" s="1">
-        <v>0.0</v>
+        <v>1227.73</v>
       </c>
       <c r="H128" t="n" s="1">
-        <v>840.0</v>
+        <v>-1227.73</v>
       </c>
     </row>
     <row r="129">
@@ -3568,25 +3595,25 @@
         <v>26</v>
       </c>
       <c r="B129" t="s" s="1">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C129" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D129" t="s" s="1">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>4500.0</v>
+        <v>245.34</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-245.34</v>
       </c>
     </row>
     <row r="130">
@@ -3594,25 +3621,25 @@
         <v>26</v>
       </c>
       <c r="B130" t="s" s="1">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C130" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D130" t="s" s="1">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="F130" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>15000.0</v>
+        <v>240.77</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-240.77</v>
       </c>
     </row>
     <row r="131">
@@ -3620,25 +3647,25 @@
         <v>26</v>
       </c>
       <c r="B131" t="s" s="1">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C131" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D131" t="s" s="1">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="E131" t="s" s="1">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F131" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G131" t="n" s="1">
-        <v>1500.0</v>
+        <v>5165.75</v>
       </c>
       <c r="H131" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-5165.75</v>
       </c>
     </row>
     <row r="132">
@@ -3646,25 +3673,25 @@
         <v>26</v>
       </c>
       <c r="B132" t="s" s="1">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C132" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D132" t="s" s="1">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G132" t="n" s="1">
-        <v>2000.0</v>
+        <v>376.9</v>
       </c>
       <c r="H132" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-376.9</v>
       </c>
     </row>
     <row r="133">
@@ -3672,25 +3699,25 @@
         <v>26</v>
       </c>
       <c r="B133" t="s" s="1">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C133" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D133" t="s" s="1">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E133" t="s" s="1">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="F133" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G133" t="n" s="1">
-        <v>146.67</v>
+        <v>423.0</v>
       </c>
       <c r="H133" t="n" s="1">
-        <v>-146.67</v>
+        <v>-423.0</v>
       </c>
     </row>
     <row r="134">
@@ -3698,25 +3725,25 @@
         <v>26</v>
       </c>
       <c r="B134" t="s" s="1">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C134" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D134" t="s" s="1">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E134" t="s" s="1">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F134" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G134" t="n" s="1">
-        <v>180.0</v>
+        <v>846.01</v>
       </c>
       <c r="H134" t="n" s="1">
-        <v>-180.0</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="135">
@@ -3724,25 +3751,25 @@
         <v>26</v>
       </c>
       <c r="B135" t="s" s="1">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C135" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D135" t="s" s="1">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="E135" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F135" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G135" t="n" s="1">
-        <v>9216.24</v>
+        <v>846.01</v>
       </c>
       <c r="H135" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="136">
@@ -3750,13 +3777,13 @@
         <v>26</v>
       </c>
       <c r="B136" t="s" s="1">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C136" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D136" t="s" s="1">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="E136" t="s" s="1">
         <v>38</v>
@@ -3765,10 +3792,10 @@
         <v>0.0</v>
       </c>
       <c r="G136" t="n" s="1">
-        <v>891.0</v>
+        <v>96.06</v>
       </c>
       <c r="H136" t="n" s="1">
-        <v>-891.0</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="137">
@@ -3776,25 +3803,25 @@
         <v>26</v>
       </c>
       <c r="B137" t="s" s="1">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C137" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s" s="1">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="E137" t="s" s="1">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F137" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G137" t="n" s="1">
-        <v>737.28</v>
+        <v>48.03</v>
       </c>
       <c r="H137" t="n" s="1">
-        <v>-737.28</v>
+        <v>-48.03</v>
       </c>
     </row>
     <row r="138">
@@ -3802,25 +3829,25 @@
         <v>26</v>
       </c>
       <c r="B138" t="s" s="1">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C138" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D138" t="s" s="1">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E138" t="s" s="1">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F138" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G138" t="n" s="1">
-        <v>750.99</v>
+        <v>96.06</v>
       </c>
       <c r="H138" t="n" s="1">
-        <v>-750.99</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="139">
@@ -3828,13 +3855,13 @@
         <v>26</v>
       </c>
       <c r="B139" t="s" s="1">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C139" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D139" t="s" s="1">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="E139" t="s" s="1">
         <v>38</v>
@@ -3843,10 +3870,10 @@
         <v>0.0</v>
       </c>
       <c r="G139" t="n" s="1">
-        <v>1544.4</v>
+        <v>100.0</v>
       </c>
       <c r="H139" t="n" s="1">
-        <v>-1544.4</v>
+        <v>-100.0</v>
       </c>
     </row>
     <row r="140">
@@ -3854,25 +3881,25 @@
         <v>26</v>
       </c>
       <c r="B140" t="s" s="1">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C140" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D140" t="s" s="1">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E140" t="s" s="1">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F140" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G140" t="n" s="1">
-        <v>1925.0</v>
+        <v>239.58</v>
       </c>
       <c r="H140" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="141">
@@ -3880,25 +3907,25 @@
         <v>26</v>
       </c>
       <c r="B141" t="s" s="1">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C141" t="s" s="1">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="D141" t="s" s="1">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="E141" t="s" s="1">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="F141" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G141" t="n" s="1">
-        <v>180.0</v>
+        <v>0.0</v>
       </c>
       <c r="H141" t="n" s="1">
-        <v>-180.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="142">
@@ -3906,25 +3933,25 @@
         <v>26</v>
       </c>
       <c r="B142" t="s" s="1">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C142" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s" s="1">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="E142" t="s" s="1">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F142" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G142" t="n" s="1">
-        <v>180.0</v>
+        <v>2961.03</v>
       </c>
       <c r="H142" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2961.03</v>
       </c>
     </row>
     <row r="143">
@@ -3932,25 +3959,25 @@
         <v>26</v>
       </c>
       <c r="B143" t="s" s="1">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C143" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s" s="1">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="E143" t="s" s="1">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F143" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G143" t="n" s="1">
-        <v>1201.89</v>
+        <v>1269.01</v>
       </c>
       <c r="H143" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-1269.01</v>
       </c>
     </row>
     <row r="144">
@@ -3958,25 +3985,25 @@
         <v>26</v>
       </c>
       <c r="B144" t="s" s="1">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C144" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D144" t="s" s="1">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="E144" t="s" s="1">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F144" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G144" t="n" s="1">
-        <v>180.0</v>
+        <v>4230.04</v>
       </c>
       <c r="H144" t="n" s="1">
-        <v>-180.0</v>
+        <v>-4230.04</v>
       </c>
     </row>
     <row r="145">
@@ -3984,25 +4011,25 @@
         <v>26</v>
       </c>
       <c r="B145" t="s" s="1">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C145" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D145" t="s" s="1">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="E145" t="s" s="1">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="F145" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G145" t="n" s="1">
-        <v>180.0</v>
+        <v>336.22</v>
       </c>
       <c r="H145" t="n" s="1">
-        <v>-180.0</v>
+        <v>-336.22</v>
       </c>
     </row>
     <row r="146">
@@ -4010,25 +4037,25 @@
         <v>26</v>
       </c>
       <c r="B146" t="s" s="1">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C146" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D146" t="s" s="1">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="E146" t="s" s="1">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F146" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G146" t="n" s="1">
-        <v>2277.0</v>
+        <v>144.09</v>
       </c>
       <c r="H146" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-144.09</v>
       </c>
     </row>
     <row r="147">
@@ -4036,25 +4063,25 @@
         <v>26</v>
       </c>
       <c r="B147" t="s" s="1">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C147" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D147" t="s" s="1">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="E147" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F147" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G147" t="n" s="1">
-        <v>25504.78</v>
+        <v>480.31</v>
       </c>
       <c r="H147" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-480.31</v>
       </c>
     </row>
     <row r="148">
@@ -4062,25 +4089,25 @@
         <v>26</v>
       </c>
       <c r="B148" t="s" s="1">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C148" t="s" s="1">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="D148" t="s" s="1">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E148" t="s" s="1">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="F148" t="n" s="1">
-        <v>0.0</v>
+        <v>1931.16</v>
       </c>
       <c r="G148" t="n" s="1">
-        <v>2078.64</v>
+        <v>0.0</v>
       </c>
       <c r="H148" t="n" s="1">
-        <v>-2078.64</v>
+        <v>1931.16</v>
       </c>
     </row>
     <row r="149">
@@ -4088,25 +4115,25 @@
         <v>26</v>
       </c>
       <c r="B149" t="s" s="1">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C149" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D149" t="s" s="1">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E149" t="s" s="1">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="F149" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G149" t="n" s="1">
-        <v>2040.52</v>
+        <v>4500.0</v>
       </c>
       <c r="H149" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="150">
@@ -4114,25 +4141,25 @@
         <v>26</v>
       </c>
       <c r="B150" t="s" s="1">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C150" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D150" t="s" s="1">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="E150" t="s" s="1">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="F150" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G150" t="n" s="1">
-        <v>180.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H150" t="n" s="1">
-        <v>-180.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="151">
@@ -4140,25 +4167,25 @@
         <v>26</v>
       </c>
       <c r="B151" t="s" s="1">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C151" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D151" t="s" s="1">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="E151" t="s" s="1">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="F151" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G151" t="n" s="1">
-        <v>180.0</v>
+        <v>1500.0</v>
       </c>
       <c r="H151" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="152">
@@ -4166,25 +4193,25 @@
         <v>26</v>
       </c>
       <c r="B152" t="s" s="1">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C152" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D152" t="s" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E152" t="s" s="1">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F152" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G152" t="n" s="1">
-        <v>1000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H152" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="153">
@@ -4192,49 +4219,569 @@
         <v>26</v>
       </c>
       <c r="B153" t="s" s="1">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C153" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D153" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="E153" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="F153" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G153" t="n" s="1">
+        <v>146.67</v>
+      </c>
+      <c r="H153" t="n" s="1">
+        <v>-146.67</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B154" t="s" s="1">
+        <v>152</v>
+      </c>
+      <c r="C154" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D154" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="E154" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F154" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G154" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H154" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B155" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="C155" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D155" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E155" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="F155" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G155" t="n" s="1">
+        <v>9216.24</v>
+      </c>
+      <c r="H155" t="n" s="1">
+        <v>-9216.24</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B156" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="C156" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D156" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E156" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F156" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G156" t="n" s="1">
+        <v>891.0</v>
+      </c>
+      <c r="H156" t="n" s="1">
+        <v>-891.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B157" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="C157" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D157" t="s" s="1">
+        <v>52</v>
+      </c>
+      <c r="E157" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F157" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G157" t="n" s="1">
+        <v>737.28</v>
+      </c>
+      <c r="H157" t="n" s="1">
+        <v>-737.28</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B158" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="C158" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D158" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="E158" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F158" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G158" t="n" s="1">
+        <v>750.99</v>
+      </c>
+      <c r="H158" t="n" s="1">
+        <v>-750.99</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B159" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="C159" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D159" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="E159" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F159" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G159" t="n" s="1">
+        <v>1544.4</v>
+      </c>
+      <c r="H159" t="n" s="1">
+        <v>-1544.4</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B160" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="C160" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D160" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="E160" t="s" s="1">
+        <v>159</v>
+      </c>
+      <c r="F160" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G160" t="n" s="1">
+        <v>1925.0</v>
+      </c>
+      <c r="H160" t="n" s="1">
+        <v>-1925.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B161" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="C161" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D161" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="E161" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F161" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G161" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H161" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B162" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="C162" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D162" t="s" s="1">
+        <v>85</v>
+      </c>
+      <c r="E162" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F162" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G162" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H162" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B163" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C163" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D163" t="s" s="1">
+        <v>161</v>
+      </c>
+      <c r="E163" t="s" s="1">
+        <v>162</v>
+      </c>
+      <c r="F163" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G163" t="n" s="1">
+        <v>1201.89</v>
+      </c>
+      <c r="H163" t="n" s="1">
+        <v>-1201.89</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B164" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C164" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D164" t="s" s="1">
+        <v>95</v>
+      </c>
+      <c r="E164" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F164" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G164" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H164" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B165" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C165" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D165" t="s" s="1">
+        <v>96</v>
+      </c>
+      <c r="E165" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F165" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G165" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H165" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B166" t="s" s="1">
+        <v>163</v>
+      </c>
+      <c r="C166" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D166" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E166" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="F166" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G166" t="n" s="1">
+        <v>25504.78</v>
+      </c>
+      <c r="H166" t="n" s="1">
+        <v>-25504.78</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B167" t="s" s="1">
+        <v>163</v>
+      </c>
+      <c r="C167" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D167" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E167" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F167" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G167" t="n" s="1">
+        <v>2277.0</v>
+      </c>
+      <c r="H167" t="n" s="1">
+        <v>-2277.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B168" t="s" s="1">
+        <v>163</v>
+      </c>
+      <c r="C168" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D168" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="E168" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F168" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G168" t="n" s="1">
+        <v>2078.64</v>
+      </c>
+      <c r="H168" t="n" s="1">
+        <v>-2078.64</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B169" t="s" s="1">
+        <v>163</v>
+      </c>
+      <c r="C169" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D169" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="E169" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F169" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G169" t="n" s="1">
+        <v>2040.52</v>
+      </c>
+      <c r="H169" t="n" s="1">
+        <v>-2040.52</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B170" t="s" s="1">
+        <v>163</v>
+      </c>
+      <c r="C170" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D170" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="E170" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F170" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G170" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H170" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B171" t="s" s="1">
+        <v>165</v>
+      </c>
+      <c r="C171" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D171" t="s" s="1">
+        <v>129</v>
+      </c>
+      <c r="E171" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F171" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G171" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H171" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B172" t="s" s="1">
+        <v>166</v>
+      </c>
+      <c r="C172" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D172" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="E172" t="s" s="1">
+        <v>167</v>
+      </c>
+      <c r="F172" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G172" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H172" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B173" t="s" s="1">
+        <v>166</v>
+      </c>
+      <c r="C173" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D173" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="E153" t="s" s="1">
-        <v>159</v>
-      </c>
-      <c r="F153" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G153" t="n" s="1">
+      <c r="E173" t="s" s="1">
+        <v>168</v>
+      </c>
+      <c r="F173" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G173" t="n" s="1">
         <v>3750.0</v>
       </c>
-      <c r="H153" t="n" s="1">
+      <c r="H173" t="n" s="1">
         <v>-3750.0</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>165</v>
+    <row r="176">
+      <c r="A176" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -336,12 +336,12 @@
     <t>101201 - 2</t>
   </si>
   <si>
+    <t>101801 - 3</t>
+  </si>
+  <si>
     <t>101801 - 2</t>
   </si>
   <si>
-    <t>101801 - 3</t>
-  </si>
-  <si>
     <t>15/10/2026</t>
   </si>
   <si>
@@ -411,12 +411,12 @@
     <t>102401 - 3</t>
   </si>
   <si>
+    <t>102501 - 2</t>
+  </si>
+  <si>
     <t>102501 - 3</t>
   </si>
   <si>
-    <t>102501 - 2</t>
-  </si>
-  <si>
     <t>105101 - 1</t>
   </si>
   <si>
@@ -465,12 +465,12 @@
     <t>Simples Nacional - DAS</t>
   </si>
   <si>
+    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
+  </si>
+  <si>
     <t>INSS- Previdenciária</t>
   </si>
   <si>
-    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
-  </si>
-  <si>
     <t>22/10/2026</t>
   </si>
   <si>
@@ -516,10 +516,10 @@
     <t>30/10/2026</t>
   </si>
   <si>
+    <t>Facebook</t>
+  </si>
+  <si>
     <t>SEFAZ SP DARE - ICMS</t>
-  </si>
-  <si>
-    <t>Facebook</t>
   </si>
   <si>
     <t>Total Geral Crédito</t>
@@ -2304,16 +2304,16 @@
         <v>95</v>
       </c>
       <c r="E79" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F79" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G79" t="n" s="1">
-        <v>6118.3</v>
+        <v>544.5</v>
       </c>
       <c r="H79" t="n" s="1">
-        <v>-6118.3</v>
+        <v>-544.5</v>
       </c>
     </row>
     <row r="80">
@@ -2330,16 +2330,16 @@
         <v>95</v>
       </c>
       <c r="E80" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F80" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G80" t="n" s="1">
-        <v>544.5</v>
+        <v>6118.3</v>
       </c>
       <c r="H80" t="n" s="1">
-        <v>-544.5</v>
+        <v>-6118.3</v>
       </c>
     </row>
     <row r="81">
@@ -2642,16 +2642,16 @@
         <v>107</v>
       </c>
       <c r="E92" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F92" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G92" t="n" s="1">
-        <v>632.51</v>
+        <v>644.44</v>
       </c>
       <c r="H92" t="n" s="1">
-        <v>-632.51</v>
+        <v>-644.44</v>
       </c>
     </row>
     <row r="93">
@@ -2668,16 +2668,16 @@
         <v>108</v>
       </c>
       <c r="E93" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F93" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G93" t="n" s="1">
-        <v>644.44</v>
+        <v>632.51</v>
       </c>
       <c r="H93" t="n" s="1">
-        <v>-644.44</v>
+        <v>-632.51</v>
       </c>
     </row>
     <row r="94">
@@ -3448,16 +3448,16 @@
         <v>128</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>1435.5</v>
+        <v>15066.07</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-1435.5</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="124">
@@ -3474,16 +3474,16 @@
         <v>128</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>15066.07</v>
+        <v>1435.5</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-1435.5</v>
       </c>
     </row>
     <row r="125">
@@ -3500,16 +3500,16 @@
         <v>129</v>
       </c>
       <c r="E125" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F125" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G125" t="n" s="1">
-        <v>297.0</v>
+        <v>2283.05</v>
       </c>
       <c r="H125" t="n" s="1">
-        <v>-297.0</v>
+        <v>-2283.05</v>
       </c>
     </row>
     <row r="126">
@@ -3526,16 +3526,16 @@
         <v>129</v>
       </c>
       <c r="E126" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F126" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G126" t="n" s="1">
-        <v>2283.05</v>
+        <v>297.0</v>
       </c>
       <c r="H126" t="n" s="1">
-        <v>-2283.05</v>
+        <v>-297.0</v>
       </c>
     </row>
     <row r="127">
@@ -3604,16 +3604,16 @@
         <v>132</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>245.34</v>
+        <v>240.77</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-245.34</v>
+        <v>-240.77</v>
       </c>
     </row>
     <row r="130">
@@ -3630,16 +3630,16 @@
         <v>133</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F130" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>240.77</v>
+        <v>245.34</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>-240.77</v>
+        <v>-245.34</v>
       </c>
     </row>
     <row r="131">
@@ -3783,19 +3783,19 @@
         <v>36</v>
       </c>
       <c r="D136" t="s" s="1">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E136" t="s" s="1">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F136" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G136" t="n" s="1">
-        <v>96.06</v>
+        <v>48.03</v>
       </c>
       <c r="H136" t="n" s="1">
-        <v>-96.06</v>
+        <v>-48.03</v>
       </c>
     </row>
     <row r="137">
@@ -3809,19 +3809,19 @@
         <v>36</v>
       </c>
       <c r="D137" t="s" s="1">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E137" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F137" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G137" t="n" s="1">
-        <v>48.03</v>
+        <v>96.06</v>
       </c>
       <c r="H137" t="n" s="1">
-        <v>-48.03</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="138">
@@ -3942,16 +3942,16 @@
         <v>134</v>
       </c>
       <c r="E142" t="s" s="1">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F142" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G142" t="n" s="1">
-        <v>2961.03</v>
+        <v>4230.04</v>
       </c>
       <c r="H142" t="n" s="1">
-        <v>-2961.03</v>
+        <v>-4230.04</v>
       </c>
     </row>
     <row r="143">
@@ -3994,16 +3994,16 @@
         <v>134</v>
       </c>
       <c r="E144" t="s" s="1">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F144" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G144" t="n" s="1">
-        <v>4230.04</v>
+        <v>2961.03</v>
       </c>
       <c r="H144" t="n" s="1">
-        <v>-4230.04</v>
+        <v>-2961.03</v>
       </c>
     </row>
     <row r="145">
@@ -4020,16 +4020,16 @@
         <v>136</v>
       </c>
       <c r="E145" t="s" s="1">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F145" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G145" t="n" s="1">
-        <v>336.22</v>
+        <v>144.09</v>
       </c>
       <c r="H145" t="n" s="1">
-        <v>-336.22</v>
+        <v>-144.09</v>
       </c>
     </row>
     <row r="146">
@@ -4046,16 +4046,16 @@
         <v>136</v>
       </c>
       <c r="E146" t="s" s="1">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="F146" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G146" t="n" s="1">
-        <v>144.09</v>
+        <v>336.22</v>
       </c>
       <c r="H146" t="n" s="1">
-        <v>-144.09</v>
+        <v>-336.22</v>
       </c>
     </row>
     <row r="147">
@@ -4182,10 +4182,10 @@
         <v>0.0</v>
       </c>
       <c r="G151" t="n" s="1">
-        <v>1500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H151" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="152">
@@ -4208,10 +4208,10 @@
         <v>0.0</v>
       </c>
       <c r="G152" t="n" s="1">
-        <v>2000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="H152" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="153">
@@ -4280,16 +4280,16 @@
         <v>41</v>
       </c>
       <c r="E155" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F155" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G155" t="n" s="1">
-        <v>9216.24</v>
+        <v>891.0</v>
       </c>
       <c r="H155" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="156">
@@ -4306,16 +4306,16 @@
         <v>41</v>
       </c>
       <c r="E156" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F156" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G156" t="n" s="1">
-        <v>891.0</v>
+        <v>9216.24</v>
       </c>
       <c r="H156" t="n" s="1">
-        <v>-891.0</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="157">
@@ -4329,19 +4329,19 @@
         <v>31</v>
       </c>
       <c r="D157" t="s" s="1">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="E157" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F157" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G157" t="n" s="1">
-        <v>737.28</v>
+        <v>750.99</v>
       </c>
       <c r="H157" t="n" s="1">
-        <v>-737.28</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="158">
@@ -4355,19 +4355,19 @@
         <v>31</v>
       </c>
       <c r="D158" t="s" s="1">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="E158" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F158" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G158" t="n" s="1">
-        <v>750.99</v>
+        <v>737.28</v>
       </c>
       <c r="H158" t="n" s="1">
-        <v>-750.99</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="159">
@@ -4719,7 +4719,7 @@
         <v>43</v>
       </c>
       <c r="D172" t="s" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E172" t="s" s="1">
         <v>167</v>
@@ -4728,10 +4728,10 @@
         <v>0.0</v>
       </c>
       <c r="G172" t="n" s="1">
-        <v>1000.0</v>
+        <v>3750.0</v>
       </c>
       <c r="H172" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-3750.0</v>
       </c>
     </row>
     <row r="173">
@@ -4745,7 +4745,7 @@
         <v>43</v>
       </c>
       <c r="D173" t="s" s="1">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E173" t="s" s="1">
         <v>168</v>
@@ -4754,10 +4754,10 @@
         <v>0.0</v>
       </c>
       <c r="G173" t="n" s="1">
-        <v>3750.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H173" t="n" s="1">
-        <v>-3750.0</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="176">

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="178">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -405,49 +405,58 @@
     <t>102501 - 1</t>
   </si>
   <si>
+    <t>102401 - 3</t>
+  </si>
+  <si>
     <t>102401 - 2</t>
   </si>
   <si>
-    <t>102401 - 3</t>
+    <t>102501 - 3</t>
   </si>
   <si>
     <t>102501 - 2</t>
   </si>
   <si>
-    <t>102501 - 3</t>
+    <t>105301 - 1</t>
   </si>
   <si>
     <t>105101 - 1</t>
   </si>
   <si>
+    <t>105101 - 2</t>
+  </si>
+  <si>
+    <t>105301 - 2</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>12 - 8</t>
+  </si>
+  <si>
+    <t>VERISURE</t>
+  </si>
+  <si>
+    <t>PFR-Previsões Financeiras a Receber</t>
+  </si>
+  <si>
+    <t>MP Interiores e Serv Ltda</t>
+  </si>
+  <si>
+    <t>ERIC SERPA</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>104401 - 1</t>
+  </si>
+  <si>
     <t>PAGSEGURO</t>
   </si>
   <si>
-    <t>105301 - 1</t>
-  </si>
-  <si>
-    <t>105101 - 2</t>
-  </si>
-  <si>
-    <t>105301 - 2</t>
-  </si>
-  <si>
-    <t>18/10/2026</t>
-  </si>
-  <si>
-    <t>12 - 8</t>
-  </si>
-  <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>PFR-Previsões Financeiras a Receber</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>ERIC SERPA</t>
+    <t>104401 - 2</t>
   </si>
   <si>
     <t>20/10/2026</t>
@@ -462,15 +471,15 @@
     <t>IRRF- darf</t>
   </si>
   <si>
+    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
+  </si>
+  <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
     <t>Simples Nacional - DAS</t>
   </si>
   <si>
-    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
-  </si>
-  <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
     <t>22/10/2026</t>
   </si>
   <si>
@@ -516,12 +525,12 @@
     <t>30/10/2026</t>
   </si>
   <si>
+    <t>SEFAZ SP DARE - ICMS</t>
+  </si>
+  <si>
     <t>Facebook</t>
   </si>
   <si>
-    <t>SEFAZ SP DARE - ICMS</t>
-  </si>
-  <si>
     <t>Total Geral Crédito</t>
   </si>
   <si>
@@ -531,13 +540,13 @@
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>265.670,42</t>
+    <t>273.279,33</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-259.399,26</t>
+    <t>-267.008,17</t>
   </si>
 </sst>
 </file>
@@ -605,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H178"/>
+  <dimension ref="A2:H184"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -3448,16 +3457,16 @@
         <v>128</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>15066.07</v>
+        <v>1435.5</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-1435.5</v>
       </c>
     </row>
     <row r="124">
@@ -3474,16 +3483,16 @@
         <v>128</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>1435.5</v>
+        <v>15066.07</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-1435.5</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="125">
@@ -3552,16 +3561,16 @@
         <v>130</v>
       </c>
       <c r="E127" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F127" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G127" t="n" s="1">
-        <v>1205.61</v>
+        <v>1227.73</v>
       </c>
       <c r="H127" t="n" s="1">
-        <v>-1205.61</v>
+        <v>-1227.73</v>
       </c>
     </row>
     <row r="128">
@@ -3578,16 +3587,16 @@
         <v>131</v>
       </c>
       <c r="E128" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F128" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G128" t="n" s="1">
-        <v>1227.73</v>
+        <v>1205.61</v>
       </c>
       <c r="H128" t="n" s="1">
-        <v>-1227.73</v>
+        <v>-1205.61</v>
       </c>
     </row>
     <row r="129">
@@ -3604,16 +3613,16 @@
         <v>132</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>240.77</v>
+        <v>245.34</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-240.77</v>
+        <v>-245.34</v>
       </c>
     </row>
     <row r="130">
@@ -3630,16 +3639,16 @@
         <v>133</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F130" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>245.34</v>
+        <v>240.77</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>-245.34</v>
+        <v>-240.77</v>
       </c>
     </row>
     <row r="131">
@@ -3656,16 +3665,16 @@
         <v>134</v>
       </c>
       <c r="E131" t="s" s="1">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G131" t="n" s="1">
-        <v>5165.75</v>
+        <v>376.9</v>
       </c>
       <c r="H131" t="n" s="1">
-        <v>-5165.75</v>
+        <v>-376.9</v>
       </c>
     </row>
     <row r="132">
@@ -3676,22 +3685,22 @@
         <v>126</v>
       </c>
       <c r="C132" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D132" t="s" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G132" t="n" s="1">
-        <v>376.9</v>
+        <v>423.0</v>
       </c>
       <c r="H132" t="n" s="1">
-        <v>-376.9</v>
+        <v>-423.0</v>
       </c>
     </row>
     <row r="133">
@@ -3705,19 +3714,19 @@
         <v>36</v>
       </c>
       <c r="D133" t="s" s="1">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E133" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F133" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G133" t="n" s="1">
-        <v>423.0</v>
+        <v>846.01</v>
       </c>
       <c r="H133" t="n" s="1">
-        <v>-423.0</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="134">
@@ -3731,10 +3740,10 @@
         <v>36</v>
       </c>
       <c r="D134" t="s" s="1">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E134" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F134" t="n" s="1">
         <v>0.0</v>
@@ -3757,19 +3766,19 @@
         <v>36</v>
       </c>
       <c r="D135" t="s" s="1">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E135" t="s" s="1">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F135" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G135" t="n" s="1">
-        <v>846.01</v>
+        <v>96.06</v>
       </c>
       <c r="H135" t="n" s="1">
-        <v>-846.01</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="136">
@@ -3783,19 +3792,19 @@
         <v>36</v>
       </c>
       <c r="D136" t="s" s="1">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E136" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F136" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G136" t="n" s="1">
-        <v>48.03</v>
+        <v>96.06</v>
       </c>
       <c r="H136" t="n" s="1">
-        <v>-48.03</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="137">
@@ -3809,19 +3818,19 @@
         <v>36</v>
       </c>
       <c r="D137" t="s" s="1">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E137" t="s" s="1">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F137" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G137" t="n" s="1">
-        <v>96.06</v>
+        <v>48.03</v>
       </c>
       <c r="H137" t="n" s="1">
-        <v>-96.06</v>
+        <v>-48.03</v>
       </c>
     </row>
     <row r="138">
@@ -3829,25 +3838,25 @@
         <v>26</v>
       </c>
       <c r="B138" t="s" s="1">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C138" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D138" t="s" s="1">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="E138" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F138" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G138" t="n" s="1">
-        <v>96.06</v>
+        <v>100.0</v>
       </c>
       <c r="H138" t="n" s="1">
-        <v>-96.06</v>
+        <v>-100.0</v>
       </c>
     </row>
     <row r="139">
@@ -3855,25 +3864,25 @@
         <v>26</v>
       </c>
       <c r="B139" t="s" s="1">
+        <v>138</v>
+      </c>
+      <c r="C139" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D139" t="s" s="1">
         <v>139</v>
       </c>
-      <c r="C139" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D139" t="s" s="1">
-        <v>37</v>
-      </c>
       <c r="E139" t="s" s="1">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="F139" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G139" t="n" s="1">
-        <v>100.0</v>
+        <v>239.58</v>
       </c>
       <c r="H139" t="n" s="1">
-        <v>-100.0</v>
+        <v>-239.58</v>
       </c>
     </row>
     <row r="140">
@@ -3881,25 +3890,25 @@
         <v>26</v>
       </c>
       <c r="B140" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C140" t="s" s="1">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="D140" t="s" s="1">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="E140" t="s" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F140" t="n" s="1">
-        <v>0.0</v>
+        <v>840.0</v>
       </c>
       <c r="G140" t="n" s="1">
-        <v>239.58</v>
+        <v>0.0</v>
       </c>
       <c r="H140" t="n" s="1">
-        <v>-239.58</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="141">
@@ -3907,25 +3916,25 @@
         <v>26</v>
       </c>
       <c r="B141" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C141" t="s" s="1">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="D141" t="s" s="1">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="E141" t="s" s="1">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="F141" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G141" t="n" s="1">
-        <v>0.0</v>
+        <v>4230.04</v>
       </c>
       <c r="H141" t="n" s="1">
-        <v>840.0</v>
+        <v>-4230.04</v>
       </c>
     </row>
     <row r="142">
@@ -3933,25 +3942,25 @@
         <v>26</v>
       </c>
       <c r="B142" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C142" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D142" t="s" s="1">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E142" t="s" s="1">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F142" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G142" t="n" s="1">
-        <v>4230.04</v>
+        <v>1269.01</v>
       </c>
       <c r="H142" t="n" s="1">
-        <v>-4230.04</v>
+        <v>-1269.01</v>
       </c>
     </row>
     <row r="143">
@@ -3959,25 +3968,25 @@
         <v>26</v>
       </c>
       <c r="B143" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C143" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D143" t="s" s="1">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E143" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F143" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G143" t="n" s="1">
-        <v>1269.01</v>
+        <v>2961.03</v>
       </c>
       <c r="H143" t="n" s="1">
-        <v>-1269.01</v>
+        <v>-2961.03</v>
       </c>
     </row>
     <row r="144">
@@ -3985,7 +3994,7 @@
         <v>26</v>
       </c>
       <c r="B144" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C144" t="s" s="1">
         <v>36</v>
@@ -3994,16 +4003,16 @@
         <v>134</v>
       </c>
       <c r="E144" t="s" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F144" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G144" t="n" s="1">
-        <v>2961.03</v>
+        <v>144.09</v>
       </c>
       <c r="H144" t="n" s="1">
-        <v>-2961.03</v>
+        <v>-144.09</v>
       </c>
     </row>
     <row r="145">
@@ -4011,25 +4020,25 @@
         <v>26</v>
       </c>
       <c r="B145" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C145" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D145" t="s" s="1">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E145" t="s" s="1">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="F145" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G145" t="n" s="1">
-        <v>144.09</v>
+        <v>336.22</v>
       </c>
       <c r="H145" t="n" s="1">
-        <v>-144.09</v>
+        <v>-336.22</v>
       </c>
     </row>
     <row r="146">
@@ -4037,25 +4046,25 @@
         <v>26</v>
       </c>
       <c r="B146" t="s" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C146" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D146" t="s" s="1">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E146" t="s" s="1">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="F146" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G146" t="n" s="1">
-        <v>336.22</v>
+        <v>480.31</v>
       </c>
       <c r="H146" t="n" s="1">
-        <v>-336.22</v>
+        <v>-480.31</v>
       </c>
     </row>
     <row r="147">
@@ -4063,25 +4072,25 @@
         <v>26</v>
       </c>
       <c r="B147" t="s" s="1">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C147" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s" s="1">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E147" t="s" s="1">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F147" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G147" t="n" s="1">
-        <v>480.31</v>
+        <v>1801.15</v>
       </c>
       <c r="H147" t="n" s="1">
-        <v>-480.31</v>
+        <v>-1801.15</v>
       </c>
     </row>
     <row r="148">
@@ -4089,25 +4098,25 @@
         <v>26</v>
       </c>
       <c r="B148" t="s" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C148" t="s" s="1">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="D148" t="s" s="1">
+        <v>135</v>
+      </c>
+      <c r="E148" t="s" s="1">
         <v>146</v>
       </c>
-      <c r="E148" t="s" s="1">
-        <v>147</v>
-      </c>
       <c r="F148" t="n" s="1">
-        <v>1931.16</v>
+        <v>0.0</v>
       </c>
       <c r="G148" t="n" s="1">
-        <v>0.0</v>
+        <v>5165.75</v>
       </c>
       <c r="H148" t="n" s="1">
-        <v>1931.16</v>
+        <v>-5165.75</v>
       </c>
     </row>
     <row r="149">
@@ -4115,25 +4124,25 @@
         <v>26</v>
       </c>
       <c r="B149" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C149" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D149" t="s" s="1">
         <v>145</v>
       </c>
-      <c r="C149" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D149" t="s" s="1">
-        <v>47</v>
-      </c>
       <c r="E149" t="s" s="1">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="F149" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G149" t="n" s="1">
-        <v>4500.0</v>
+        <v>263.99</v>
       </c>
       <c r="H149" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-263.99</v>
       </c>
     </row>
     <row r="150">
@@ -4141,25 +4150,25 @@
         <v>26</v>
       </c>
       <c r="B150" t="s" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C150" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D150" t="s" s="1">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="E150" t="s" s="1">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c r="F150" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G150" t="n" s="1">
-        <v>15000.0</v>
+        <v>527.98</v>
       </c>
       <c r="H150" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-527.98</v>
       </c>
     </row>
     <row r="151">
@@ -4167,25 +4176,25 @@
         <v>26</v>
       </c>
       <c r="B151" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C151" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D151" t="s" s="1">
         <v>145</v>
       </c>
-      <c r="C151" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D151" t="s" s="1">
-        <v>47</v>
-      </c>
       <c r="E151" t="s" s="1">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F151" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G151" t="n" s="1">
-        <v>2000.0</v>
+        <v>527.98</v>
       </c>
       <c r="H151" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-527.98</v>
       </c>
     </row>
     <row r="152">
@@ -4193,25 +4202,25 @@
         <v>26</v>
       </c>
       <c r="B152" t="s" s="1">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C152" t="s" s="1">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="D152" t="s" s="1">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="E152" t="s" s="1">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F152" t="n" s="1">
-        <v>0.0</v>
+        <v>1931.16</v>
       </c>
       <c r="G152" t="n" s="1">
-        <v>1500.0</v>
+        <v>0.0</v>
       </c>
       <c r="H152" t="n" s="1">
-        <v>-1500.0</v>
+        <v>1931.16</v>
       </c>
     </row>
     <row r="153">
@@ -4219,25 +4228,25 @@
         <v>26</v>
       </c>
       <c r="B153" t="s" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C153" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D153" t="s" s="1">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="E153" t="s" s="1">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F153" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G153" t="n" s="1">
-        <v>146.67</v>
+        <v>4500.0</v>
       </c>
       <c r="H153" t="n" s="1">
-        <v>-146.67</v>
+        <v>-4500.0</v>
       </c>
     </row>
     <row r="154">
@@ -4245,25 +4254,25 @@
         <v>26</v>
       </c>
       <c r="B154" t="s" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C154" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D154" t="s" s="1">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E154" t="s" s="1">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="F154" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G154" t="n" s="1">
-        <v>180.0</v>
+        <v>2000.0</v>
       </c>
       <c r="H154" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2000.0</v>
       </c>
     </row>
     <row r="155">
@@ -4271,25 +4280,25 @@
         <v>26</v>
       </c>
       <c r="B155" t="s" s="1">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C155" t="s" s="1">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D155" t="s" s="1">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E155" t="s" s="1">
-        <v>38</v>
+        <v>153</v>
       </c>
       <c r="F155" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G155" t="n" s="1">
-        <v>891.0</v>
+        <v>1500.0</v>
       </c>
       <c r="H155" t="n" s="1">
-        <v>-891.0</v>
+        <v>-1500.0</v>
       </c>
     </row>
     <row r="156">
@@ -4297,25 +4306,25 @@
         <v>26</v>
       </c>
       <c r="B156" t="s" s="1">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C156" t="s" s="1">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D156" t="s" s="1">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E156" t="s" s="1">
-        <v>30</v>
+        <v>154</v>
       </c>
       <c r="F156" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G156" t="n" s="1">
-        <v>9216.24</v>
+        <v>15000.0</v>
       </c>
       <c r="H156" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="157">
@@ -4323,25 +4332,25 @@
         <v>26</v>
       </c>
       <c r="B157" t="s" s="1">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C157" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D157" t="s" s="1">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E157" t="s" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F157" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G157" t="n" s="1">
-        <v>750.99</v>
+        <v>2639.89</v>
       </c>
       <c r="H157" t="n" s="1">
-        <v>-750.99</v>
+        <v>-2639.89</v>
       </c>
     </row>
     <row r="158">
@@ -4349,25 +4358,25 @@
         <v>26</v>
       </c>
       <c r="B158" t="s" s="1">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C158" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D158" t="s" s="1">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="E158" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F158" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G158" t="n" s="1">
-        <v>737.28</v>
+        <v>1847.92</v>
       </c>
       <c r="H158" t="n" s="1">
-        <v>-737.28</v>
+        <v>-1847.92</v>
       </c>
     </row>
     <row r="159">
@@ -4375,25 +4384,25 @@
         <v>26</v>
       </c>
       <c r="B159" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="C159" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D159" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="E159" t="s" s="1">
         <v>157</v>
       </c>
-      <c r="C159" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D159" t="s" s="1">
-        <v>60</v>
-      </c>
-      <c r="E159" t="s" s="1">
-        <v>38</v>
-      </c>
       <c r="F159" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G159" t="n" s="1">
-        <v>1544.4</v>
+        <v>146.67</v>
       </c>
       <c r="H159" t="n" s="1">
-        <v>-1544.4</v>
+        <v>-146.67</v>
       </c>
     </row>
     <row r="160">
@@ -4401,25 +4410,25 @@
         <v>26</v>
       </c>
       <c r="B160" t="s" s="1">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C160" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D160" t="s" s="1">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="E160" t="s" s="1">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="F160" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G160" t="n" s="1">
-        <v>1925.0</v>
+        <v>180.0</v>
       </c>
       <c r="H160" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="161">
@@ -4427,25 +4436,25 @@
         <v>26</v>
       </c>
       <c r="B161" t="s" s="1">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C161" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D161" t="s" s="1">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="E161" t="s" s="1">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F161" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G161" t="n" s="1">
-        <v>180.0</v>
+        <v>891.0</v>
       </c>
       <c r="H161" t="n" s="1">
-        <v>-180.0</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="162">
@@ -4453,25 +4462,25 @@
         <v>26</v>
       </c>
       <c r="B162" t="s" s="1">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C162" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D162" t="s" s="1">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E162" t="s" s="1">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F162" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G162" t="n" s="1">
-        <v>180.0</v>
+        <v>9216.24</v>
       </c>
       <c r="H162" t="n" s="1">
-        <v>-180.0</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="163">
@@ -4479,25 +4488,25 @@
         <v>26</v>
       </c>
       <c r="B163" t="s" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C163" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D163" t="s" s="1">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="E163" t="s" s="1">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="F163" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G163" t="n" s="1">
-        <v>1201.89</v>
+        <v>737.28</v>
       </c>
       <c r="H163" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="164">
@@ -4505,25 +4514,25 @@
         <v>26</v>
       </c>
       <c r="B164" t="s" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C164" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D164" t="s" s="1">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="E164" t="s" s="1">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="F164" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G164" t="n" s="1">
-        <v>180.0</v>
+        <v>750.99</v>
       </c>
       <c r="H164" t="n" s="1">
-        <v>-180.0</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="165">
@@ -4534,22 +4543,22 @@
         <v>160</v>
       </c>
       <c r="C165" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D165" t="s" s="1">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="E165" t="s" s="1">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F165" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G165" t="n" s="1">
-        <v>180.0</v>
+        <v>1544.4</v>
       </c>
       <c r="H165" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="166">
@@ -4557,25 +4566,25 @@
         <v>26</v>
       </c>
       <c r="B166" t="s" s="1">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C166" t="s" s="1">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D166" t="s" s="1">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="E166" t="s" s="1">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="F166" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G166" t="n" s="1">
-        <v>25504.78</v>
+        <v>1925.0</v>
       </c>
       <c r="H166" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="167">
@@ -4583,25 +4592,25 @@
         <v>26</v>
       </c>
       <c r="B167" t="s" s="1">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C167" t="s" s="1">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D167" t="s" s="1">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="E167" t="s" s="1">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F167" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G167" t="n" s="1">
-        <v>2277.0</v>
+        <v>180.0</v>
       </c>
       <c r="H167" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="168">
@@ -4609,25 +4618,25 @@
         <v>26</v>
       </c>
       <c r="B168" t="s" s="1">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C168" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D168" t="s" s="1">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="E168" t="s" s="1">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F168" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G168" t="n" s="1">
-        <v>2078.64</v>
+        <v>180.0</v>
       </c>
       <c r="H168" t="n" s="1">
-        <v>-2078.64</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="169">
@@ -4638,22 +4647,22 @@
         <v>163</v>
       </c>
       <c r="C169" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D169" t="s" s="1">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="E169" t="s" s="1">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="F169" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G169" t="n" s="1">
-        <v>2040.52</v>
+        <v>1201.89</v>
       </c>
       <c r="H169" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="170">
@@ -4667,7 +4676,7 @@
         <v>43</v>
       </c>
       <c r="D170" t="s" s="1">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E170" t="s" s="1">
         <v>65</v>
@@ -4687,13 +4696,13 @@
         <v>26</v>
       </c>
       <c r="B171" t="s" s="1">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C171" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D171" t="s" s="1">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="E171" t="s" s="1">
         <v>65</v>
@@ -4716,22 +4725,22 @@
         <v>166</v>
       </c>
       <c r="C172" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D172" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E172" t="s" s="1">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="F172" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G172" t="n" s="1">
-        <v>3750.0</v>
+        <v>2277.0</v>
       </c>
       <c r="H172" t="n" s="1">
-        <v>-3750.0</v>
+        <v>-2277.0</v>
       </c>
     </row>
     <row r="173">
@@ -4742,46 +4751,202 @@
         <v>166</v>
       </c>
       <c r="C173" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D173" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="E173" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="F173" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G173" t="n" s="1">
+        <v>25504.78</v>
+      </c>
+      <c r="H173" t="n" s="1">
+        <v>-25504.78</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B174" t="s" s="1">
+        <v>166</v>
+      </c>
+      <c r="C174" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D174" t="s" s="1">
+        <v>167</v>
+      </c>
+      <c r="E174" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F174" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G174" t="n" s="1">
+        <v>2078.64</v>
+      </c>
+      <c r="H174" t="n" s="1">
+        <v>-2078.64</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B175" t="s" s="1">
+        <v>166</v>
+      </c>
+      <c r="C175" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D175" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="E175" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F175" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G175" t="n" s="1">
+        <v>2040.52</v>
+      </c>
+      <c r="H175" t="n" s="1">
+        <v>-2040.52</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B176" t="s" s="1">
+        <v>166</v>
+      </c>
+      <c r="C176" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="D173" t="s" s="1">
+      <c r="D176" t="s" s="1">
+        <v>110</v>
+      </c>
+      <c r="E176" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F176" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G176" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H176" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B177" t="s" s="1">
+        <v>168</v>
+      </c>
+      <c r="C177" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D177" t="s" s="1">
+        <v>129</v>
+      </c>
+      <c r="E177" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F177" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G177" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H177" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B178" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="C178" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D178" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="E173" t="s" s="1">
-        <v>168</v>
-      </c>
-      <c r="F173" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G173" t="n" s="1">
+      <c r="E178" t="s" s="1">
+        <v>170</v>
+      </c>
+      <c r="F178" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G178" t="n" s="1">
         <v>1000.0</v>
       </c>
-      <c r="H173" t="n" s="1">
+      <c r="H178" t="n" s="1">
         <v>-1000.0</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="s">
+    <row r="179">
+      <c r="A179" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B179" t="s" s="1">
         <v>169</v>
       </c>
-      <c r="B176" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="s">
+      <c r="C179" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D179" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="E179" t="s" s="1">
         <v>171</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="F179" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G179" t="n" s="1">
+        <v>3750.0</v>
+      </c>
+      <c r="H179" t="n" s="1">
+        <v>-3750.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="s">
+      <c r="B182" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B178" s="3" t="s">
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="s">
         <v>174</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="174">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -183,7 +183,7 @@
     <t>FELIPE DOMINGOS BARBOSA</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>07/10/2026</t>
@@ -336,18 +336,135 @@
     <t>101201 - 2</t>
   </si>
   <si>
+    <t>101801 - 2</t>
+  </si>
+  <si>
     <t>101801 - 3</t>
   </si>
   <si>
-    <t>101801 - 2</t>
-  </si>
-  <si>
     <t>15/10/2026</t>
   </si>
   <si>
     <t>101101 - 1</t>
   </si>
   <si>
+    <t>101101 - 3</t>
+  </si>
+  <si>
+    <t>101101 - 2</t>
+  </si>
+  <si>
+    <t>103801 - 1</t>
+  </si>
+  <si>
+    <t>104701 - 1</t>
+  </si>
+  <si>
+    <t>104701 - 2</t>
+  </si>
+  <si>
+    <t>104801 - 2</t>
+  </si>
+  <si>
+    <t>104801 - 1</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>103801 - 2</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>105001 - 1</t>
+  </si>
+  <si>
+    <t>105001 - 2</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>92001 - 2</t>
+  </si>
+  <si>
+    <t>102401 - 1</t>
+  </si>
+  <si>
+    <t>102501 - 1</t>
+  </si>
+  <si>
+    <t>102401 - 2</t>
+  </si>
+  <si>
+    <t>102401 - 3</t>
+  </si>
+  <si>
+    <t>102501 - 3</t>
+  </si>
+  <si>
+    <t>102501 - 2</t>
+  </si>
+  <si>
+    <t>105301 - 1</t>
+  </si>
+  <si>
+    <t>105101 - 1</t>
+  </si>
+  <si>
+    <t>105101 - 2</t>
+  </si>
+  <si>
+    <t>105301 - 2</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>ERIC SERPA</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>104401 - 1</t>
+  </si>
+  <si>
+    <t>PAGSEGURO</t>
+  </si>
+  <si>
+    <t>104401 - 2</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>1630 - 1</t>
+  </si>
+  <si>
+    <t>1635 - 1</t>
+  </si>
+  <si>
+    <t>1630 - 3</t>
+  </si>
+  <si>
+    <t>1630 - 2</t>
+  </si>
+  <si>
+    <t>1635 - 2</t>
+  </si>
+  <si>
+    <t>1635 - 3</t>
+  </si>
+  <si>
+    <t>Simples Nacional - DAS</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
+  </si>
+  <si>
     <t>DUP-Duplicata de Contrato</t>
   </si>
   <si>
@@ -357,138 +474,9 @@
     <t>IL HEE PARK</t>
   </si>
   <si>
-    <t>101101 - 2</t>
-  </si>
-  <si>
-    <t>101101 - 3</t>
-  </si>
-  <si>
-    <t>103801 - 1</t>
-  </si>
-  <si>
-    <t>104701 - 1</t>
-  </si>
-  <si>
-    <t>104701 - 2</t>
-  </si>
-  <si>
-    <t>104801 - 2</t>
-  </si>
-  <si>
-    <t>104801 - 1</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>103801 - 2</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>105001 - 1</t>
-  </si>
-  <si>
-    <t>105001 - 2</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>92001 - 2</t>
-  </si>
-  <si>
-    <t>102401 - 1</t>
-  </si>
-  <si>
-    <t>102501 - 1</t>
-  </si>
-  <si>
-    <t>102401 - 3</t>
-  </si>
-  <si>
-    <t>102401 - 2</t>
-  </si>
-  <si>
-    <t>102501 - 3</t>
-  </si>
-  <si>
-    <t>102501 - 2</t>
-  </si>
-  <si>
-    <t>105301 - 1</t>
-  </si>
-  <si>
-    <t>105101 - 1</t>
-  </si>
-  <si>
-    <t>105101 - 2</t>
-  </si>
-  <si>
-    <t>105301 - 2</t>
-  </si>
-  <si>
-    <t>18/10/2026</t>
-  </si>
-  <si>
-    <t>12 - 8</t>
-  </si>
-  <si>
-    <t>VERISURE</t>
-  </si>
-  <si>
-    <t>PFR-Previsões Financeiras a Receber</t>
-  </si>
-  <si>
-    <t>MP Interiores e Serv Ltda</t>
-  </si>
-  <si>
-    <t>ERIC SERPA</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>104401 - 1</t>
-  </si>
-  <si>
-    <t>PAGSEGURO</t>
-  </si>
-  <si>
-    <t>104401 - 2</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>105001 - 0</t>
-  </si>
-  <si>
-    <t>Patricia Souza Fernandez</t>
-  </si>
-  <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>CAIXA ECONOMICA FEDERAL- FGTS</t>
-  </si>
-  <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
-    <t>Simples Nacional - DAS</t>
-  </si>
-  <si>
     <t>22/10/2026</t>
   </si>
   <si>
-    <t>64 - 4</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
     <t>23/10/2026</t>
   </si>
   <si>
@@ -534,19 +522,19 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>6.271,16</t>
+    <t>3.500,00</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>273.279,33</t>
+    <t>262.963,46</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-267.008,17</t>
+    <t>-259.463,46</t>
   </si>
 </sst>
 </file>
@@ -614,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H184"/>
+  <dimension ref="A2:H182"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -2651,16 +2639,16 @@
         <v>107</v>
       </c>
       <c r="E92" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F92" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G92" t="n" s="1">
-        <v>644.44</v>
+        <v>632.51</v>
       </c>
       <c r="H92" t="n" s="1">
-        <v>-644.44</v>
+        <v>-632.51</v>
       </c>
     </row>
     <row r="93">
@@ -2677,16 +2665,16 @@
         <v>108</v>
       </c>
       <c r="E93" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F93" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G93" t="n" s="1">
-        <v>632.51</v>
+        <v>644.44</v>
       </c>
       <c r="H93" t="n" s="1">
-        <v>-632.51</v>
+        <v>-644.44</v>
       </c>
     </row>
     <row r="94">
@@ -2749,22 +2737,22 @@
         <v>109</v>
       </c>
       <c r="C96" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D96" t="s" s="1">
         <v>111</v>
       </c>
-      <c r="D96" t="s" s="1">
-        <v>112</v>
-      </c>
       <c r="E96" t="s" s="1">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="F96" t="n" s="1">
-        <v>3500.0</v>
+        <v>0.0</v>
       </c>
       <c r="G96" t="n" s="1">
-        <v>0.0</v>
+        <v>1751.0</v>
       </c>
       <c r="H96" t="n" s="1">
-        <v>3500.0</v>
+        <v>-1751.0</v>
       </c>
     </row>
     <row r="97">
@@ -2778,7 +2766,7 @@
         <v>31</v>
       </c>
       <c r="D97" t="s" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E97" t="s" s="1">
         <v>35</v>
@@ -2801,22 +2789,22 @@
         <v>109</v>
       </c>
       <c r="C98" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D98" t="s" s="1">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E98" t="s" s="1">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="F98" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G98" t="n" s="1">
-        <v>1751.0</v>
+        <v>15.2</v>
       </c>
       <c r="H98" t="n" s="1">
-        <v>-1751.0</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="99">
@@ -2830,7 +2818,7 @@
         <v>36</v>
       </c>
       <c r="D99" t="s" s="1">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E99" t="s" s="1">
         <v>38</v>
@@ -2856,19 +2844,19 @@
         <v>36</v>
       </c>
       <c r="D100" t="s" s="1">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E100" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F100" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G100" t="n" s="1">
-        <v>15.2</v>
+        <v>30.4</v>
       </c>
       <c r="H100" t="n" s="1">
-        <v>-15.2</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="101">
@@ -2882,19 +2870,19 @@
         <v>36</v>
       </c>
       <c r="D101" t="s" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E101" t="s" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F101" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G101" t="n" s="1">
-        <v>30.4</v>
+        <v>8.73</v>
       </c>
       <c r="H101" t="n" s="1">
-        <v>-30.4</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="102">
@@ -2908,19 +2896,19 @@
         <v>36</v>
       </c>
       <c r="D102" t="s" s="1">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E102" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F102" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G102" t="n" s="1">
-        <v>8.73</v>
+        <v>17.46</v>
       </c>
       <c r="H102" t="n" s="1">
-        <v>-8.73</v>
+        <v>-17.46</v>
       </c>
     </row>
     <row r="103">
@@ -2934,10 +2922,10 @@
         <v>36</v>
       </c>
       <c r="D103" t="s" s="1">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E103" t="s" s="1">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F103" t="n" s="1">
         <v>0.0</v>
@@ -2960,19 +2948,19 @@
         <v>36</v>
       </c>
       <c r="D104" t="s" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E104" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F104" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G104" t="n" s="1">
-        <v>17.46</v>
+        <v>6.81</v>
       </c>
       <c r="H104" t="n" s="1">
-        <v>-17.46</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="105">
@@ -2986,10 +2974,10 @@
         <v>36</v>
       </c>
       <c r="D105" t="s" s="1">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E105" t="s" s="1">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F105" t="n" s="1">
         <v>0.0</v>
@@ -3012,19 +3000,19 @@
         <v>36</v>
       </c>
       <c r="D106" t="s" s="1">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E106" t="s" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F106" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G106" t="n" s="1">
-        <v>6.81</v>
+        <v>3.41</v>
       </c>
       <c r="H106" t="n" s="1">
-        <v>-6.81</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="107">
@@ -3032,25 +3020,25 @@
         <v>26</v>
       </c>
       <c r="B107" t="s" s="1">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C107" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D107" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E107" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F107" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G107" t="n" s="1">
-        <v>3.41</v>
+        <v>152.0</v>
       </c>
       <c r="H107" t="n" s="1">
-        <v>-3.41</v>
+        <v>-152.0</v>
       </c>
     </row>
     <row r="108">
@@ -3058,25 +3046,25 @@
         <v>26</v>
       </c>
       <c r="B108" t="s" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C108" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D108" t="s" s="1">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E108" t="s" s="1">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F108" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G108" t="n" s="1">
-        <v>152.0</v>
+        <v>106.4</v>
       </c>
       <c r="H108" t="n" s="1">
-        <v>-152.0</v>
+        <v>-106.4</v>
       </c>
     </row>
     <row r="109">
@@ -3084,25 +3072,25 @@
         <v>26</v>
       </c>
       <c r="B109" t="s" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C109" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D109" t="s" s="1">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E109" t="s" s="1">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="F109" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G109" t="n" s="1">
-        <v>106.4</v>
+        <v>45.6</v>
       </c>
       <c r="H109" t="n" s="1">
-        <v>-106.4</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="110">
@@ -3110,25 +3098,25 @@
         <v>26</v>
       </c>
       <c r="B110" t="s" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C110" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D110" t="s" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E110" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F110" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G110" t="n" s="1">
-        <v>45.6</v>
+        <v>61.11</v>
       </c>
       <c r="H110" t="n" s="1">
-        <v>-45.6</v>
+        <v>-61.11</v>
       </c>
     </row>
     <row r="111">
@@ -3136,25 +3124,25 @@
         <v>26</v>
       </c>
       <c r="B111" t="s" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C111" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D111" t="s" s="1">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E111" t="s" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F111" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G111" t="n" s="1">
-        <v>61.11</v>
+        <v>26.19</v>
       </c>
       <c r="H111" t="n" s="1">
-        <v>-61.11</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="112">
@@ -3162,25 +3150,25 @@
         <v>26</v>
       </c>
       <c r="B112" t="s" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C112" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D112" t="s" s="1">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E112" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F112" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G112" t="n" s="1">
-        <v>26.19</v>
+        <v>87.3</v>
       </c>
       <c r="H112" t="n" s="1">
-        <v>-26.19</v>
+        <v>-87.3</v>
       </c>
     </row>
     <row r="113">
@@ -3188,7 +3176,7 @@
         <v>26</v>
       </c>
       <c r="B113" t="s" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C113" t="s" s="1">
         <v>36</v>
@@ -3197,16 +3185,16 @@
         <v>117</v>
       </c>
       <c r="E113" t="s" s="1">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="F113" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G113" t="n" s="1">
-        <v>87.3</v>
+        <v>23.84</v>
       </c>
       <c r="H113" t="n" s="1">
-        <v>-87.3</v>
+        <v>-23.84</v>
       </c>
     </row>
     <row r="114">
@@ -3214,25 +3202,25 @@
         <v>26</v>
       </c>
       <c r="B114" t="s" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C114" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D114" t="s" s="1">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E114" t="s" s="1">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F114" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G114" t="n" s="1">
-        <v>23.84</v>
+        <v>34.05</v>
       </c>
       <c r="H114" t="n" s="1">
-        <v>-23.84</v>
+        <v>-34.05</v>
       </c>
     </row>
     <row r="115">
@@ -3240,25 +3228,25 @@
         <v>26</v>
       </c>
       <c r="B115" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C115" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D115" t="s" s="1">
         <v>121</v>
       </c>
-      <c r="C115" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D115" t="s" s="1">
-        <v>120</v>
-      </c>
       <c r="E115" t="s" s="1">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F115" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G115" t="n" s="1">
-        <v>34.05</v>
+        <v>135.18</v>
       </c>
       <c r="H115" t="n" s="1">
-        <v>-34.05</v>
+        <v>-135.18</v>
       </c>
     </row>
     <row r="116">
@@ -3266,25 +3254,25 @@
         <v>26</v>
       </c>
       <c r="B116" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C116" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D116" t="s" s="1">
         <v>121</v>
       </c>
-      <c r="C116" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D116" t="s" s="1">
-        <v>124</v>
-      </c>
       <c r="E116" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F116" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G116" t="n" s="1">
-        <v>135.18</v>
+        <v>57.93</v>
       </c>
       <c r="H116" t="n" s="1">
-        <v>-135.18</v>
+        <v>-57.93</v>
       </c>
     </row>
     <row r="117">
@@ -3292,25 +3280,25 @@
         <v>26</v>
       </c>
       <c r="B117" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C117" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D117" t="s" s="1">
         <v>121</v>
       </c>
-      <c r="C117" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D117" t="s" s="1">
-        <v>124</v>
-      </c>
       <c r="E117" t="s" s="1">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F117" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G117" t="n" s="1">
-        <v>57.93</v>
+        <v>19.31</v>
       </c>
       <c r="H117" t="n" s="1">
-        <v>-57.93</v>
+        <v>-19.31</v>
       </c>
     </row>
     <row r="118">
@@ -3318,25 +3306,25 @@
         <v>26</v>
       </c>
       <c r="B118" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C118" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D118" t="s" s="1">
         <v>121</v>
       </c>
-      <c r="C118" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D118" t="s" s="1">
-        <v>124</v>
-      </c>
       <c r="E118" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F118" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G118" t="n" s="1">
-        <v>19.31</v>
+        <v>193.12</v>
       </c>
       <c r="H118" t="n" s="1">
-        <v>-19.31</v>
+        <v>-193.12</v>
       </c>
     </row>
     <row r="119">
@@ -3344,13 +3332,13 @@
         <v>26</v>
       </c>
       <c r="B119" t="s" s="1">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C119" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D119" t="s" s="1">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E119" t="s" s="1">
         <v>38</v>
@@ -3359,10 +3347,10 @@
         <v>0.0</v>
       </c>
       <c r="G119" t="n" s="1">
-        <v>193.12</v>
+        <v>38.62</v>
       </c>
       <c r="H119" t="n" s="1">
-        <v>-193.12</v>
+        <v>-38.62</v>
       </c>
     </row>
     <row r="120">
@@ -3370,16 +3358,16 @@
         <v>26</v>
       </c>
       <c r="B120" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C120" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D120" t="s" s="1">
         <v>121</v>
       </c>
-      <c r="C120" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D120" t="s" s="1">
-        <v>125</v>
-      </c>
       <c r="E120" t="s" s="1">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F120" t="n" s="1">
         <v>0.0</v>
@@ -3396,25 +3384,25 @@
         <v>26</v>
       </c>
       <c r="B121" t="s" s="1">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C121" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D121" t="s" s="1">
         <v>124</v>
       </c>
       <c r="E121" t="s" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F121" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G121" t="n" s="1">
-        <v>38.62</v>
+        <v>155.01</v>
       </c>
       <c r="H121" t="n" s="1">
-        <v>-38.62</v>
+        <v>-155.01</v>
       </c>
     </row>
     <row r="122">
@@ -3422,25 +3410,25 @@
         <v>26</v>
       </c>
       <c r="B122" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C122" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D122" t="s" s="1">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E122" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F122" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G122" t="n" s="1">
-        <v>155.01</v>
+        <v>1435.5</v>
       </c>
       <c r="H122" t="n" s="1">
-        <v>-155.01</v>
+        <v>-1435.5</v>
       </c>
     </row>
     <row r="123">
@@ -3448,25 +3436,25 @@
         <v>26</v>
       </c>
       <c r="B123" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C123" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D123" t="s" s="1">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>1435.5</v>
+        <v>15066.07</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-1435.5</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="124">
@@ -3474,25 +3462,25 @@
         <v>26</v>
       </c>
       <c r="B124" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C124" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D124" t="s" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>15066.07</v>
+        <v>297.0</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-297.0</v>
       </c>
     </row>
     <row r="125">
@@ -3500,25 +3488,25 @@
         <v>26</v>
       </c>
       <c r="B125" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C125" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D125" t="s" s="1">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E125" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F125" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G125" t="n" s="1">
-        <v>2283.05</v>
+        <v>1205.61</v>
       </c>
       <c r="H125" t="n" s="1">
-        <v>-2283.05</v>
+        <v>-1205.61</v>
       </c>
     </row>
     <row r="126">
@@ -3526,25 +3514,25 @@
         <v>26</v>
       </c>
       <c r="B126" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C126" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D126" t="s" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E126" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F126" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G126" t="n" s="1">
-        <v>297.0</v>
+        <v>1227.73</v>
       </c>
       <c r="H126" t="n" s="1">
-        <v>-297.0</v>
+        <v>-1227.73</v>
       </c>
     </row>
     <row r="127">
@@ -3552,13 +3540,13 @@
         <v>26</v>
       </c>
       <c r="B127" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C127" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D127" t="s" s="1">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E127" t="s" s="1">
         <v>33</v>
@@ -3567,10 +3555,10 @@
         <v>0.0</v>
       </c>
       <c r="G127" t="n" s="1">
-        <v>1227.73</v>
+        <v>245.34</v>
       </c>
       <c r="H127" t="n" s="1">
-        <v>-1227.73</v>
+        <v>-245.34</v>
       </c>
     </row>
     <row r="128">
@@ -3578,13 +3566,13 @@
         <v>26</v>
       </c>
       <c r="B128" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C128" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D128" t="s" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E128" t="s" s="1">
         <v>35</v>
@@ -3593,10 +3581,10 @@
         <v>0.0</v>
       </c>
       <c r="G128" t="n" s="1">
-        <v>1205.61</v>
+        <v>240.77</v>
       </c>
       <c r="H128" t="n" s="1">
-        <v>-1205.61</v>
+        <v>-240.77</v>
       </c>
     </row>
     <row r="129">
@@ -3604,25 +3592,25 @@
         <v>26</v>
       </c>
       <c r="B129" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C129" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D129" t="s" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>245.34</v>
+        <v>376.9</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-245.34</v>
+        <v>-376.9</v>
       </c>
     </row>
     <row r="130">
@@ -3630,25 +3618,25 @@
         <v>26</v>
       </c>
       <c r="B130" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C130" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D130" t="s" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F130" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>240.77</v>
+        <v>423.0</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>-240.77</v>
+        <v>-423.0</v>
       </c>
     </row>
     <row r="131">
@@ -3656,25 +3644,25 @@
         <v>26</v>
       </c>
       <c r="B131" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C131" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E131" t="s" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F131" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G131" t="n" s="1">
-        <v>376.9</v>
+        <v>846.01</v>
       </c>
       <c r="H131" t="n" s="1">
-        <v>-376.9</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="132">
@@ -3682,25 +3670,25 @@
         <v>26</v>
       </c>
       <c r="B132" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C132" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D132" t="s" s="1">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G132" t="n" s="1">
-        <v>423.0</v>
+        <v>846.01</v>
       </c>
       <c r="H132" t="n" s="1">
-        <v>-423.0</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="133">
@@ -3708,25 +3696,25 @@
         <v>26</v>
       </c>
       <c r="B133" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C133" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D133" t="s" s="1">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E133" t="s" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F133" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G133" t="n" s="1">
-        <v>846.01</v>
+        <v>48.03</v>
       </c>
       <c r="H133" t="n" s="1">
-        <v>-846.01</v>
+        <v>-48.03</v>
       </c>
     </row>
     <row r="134">
@@ -3734,13 +3722,13 @@
         <v>26</v>
       </c>
       <c r="B134" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C134" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D134" t="s" s="1">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E134" t="s" s="1">
         <v>38</v>
@@ -3749,10 +3737,10 @@
         <v>0.0</v>
       </c>
       <c r="G134" t="n" s="1">
-        <v>846.01</v>
+        <v>96.06</v>
       </c>
       <c r="H134" t="n" s="1">
-        <v>-846.01</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="135">
@@ -3760,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="B135" t="s" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C135" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D135" t="s" s="1">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E135" t="s" s="1">
         <v>50</v>
@@ -3786,13 +3774,13 @@
         <v>26</v>
       </c>
       <c r="B136" t="s" s="1">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C136" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D136" t="s" s="1">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="E136" t="s" s="1">
         <v>38</v>
@@ -3801,10 +3789,10 @@
         <v>0.0</v>
       </c>
       <c r="G136" t="n" s="1">
-        <v>96.06</v>
+        <v>100.0</v>
       </c>
       <c r="H136" t="n" s="1">
-        <v>-96.06</v>
+        <v>-100.0</v>
       </c>
     </row>
     <row r="137">
@@ -3812,25 +3800,25 @@
         <v>26</v>
       </c>
       <c r="B137" t="s" s="1">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C137" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D137" t="s" s="1">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E137" t="s" s="1">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F137" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G137" t="n" s="1">
-        <v>48.03</v>
+        <v>1269.01</v>
       </c>
       <c r="H137" t="n" s="1">
-        <v>-48.03</v>
+        <v>-1269.01</v>
       </c>
     </row>
     <row r="138">
@@ -3838,25 +3826,25 @@
         <v>26</v>
       </c>
       <c r="B138" t="s" s="1">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C138" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D138" t="s" s="1">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="E138" t="s" s="1">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F138" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G138" t="n" s="1">
-        <v>100.0</v>
+        <v>2961.03</v>
       </c>
       <c r="H138" t="n" s="1">
-        <v>-100.0</v>
+        <v>-2961.03</v>
       </c>
     </row>
     <row r="139">
@@ -3864,25 +3852,25 @@
         <v>26</v>
       </c>
       <c r="B139" t="s" s="1">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C139" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D139" t="s" s="1">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E139" t="s" s="1">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="F139" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G139" t="n" s="1">
-        <v>239.58</v>
+        <v>4230.04</v>
       </c>
       <c r="H139" t="n" s="1">
-        <v>-239.58</v>
+        <v>-4230.04</v>
       </c>
     </row>
     <row r="140">
@@ -3890,25 +3878,25 @@
         <v>26</v>
       </c>
       <c r="B140" t="s" s="1">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C140" t="s" s="1">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s" s="1">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="E140" t="s" s="1">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F140" t="n" s="1">
-        <v>840.0</v>
+        <v>0.0</v>
       </c>
       <c r="G140" t="n" s="1">
-        <v>0.0</v>
+        <v>336.22</v>
       </c>
       <c r="H140" t="n" s="1">
-        <v>840.0</v>
+        <v>-336.22</v>
       </c>
     </row>
     <row r="141">
@@ -3916,25 +3904,25 @@
         <v>26</v>
       </c>
       <c r="B141" t="s" s="1">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C141" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D141" t="s" s="1">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E141" t="s" s="1">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F141" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G141" t="n" s="1">
-        <v>4230.04</v>
+        <v>144.09</v>
       </c>
       <c r="H141" t="n" s="1">
-        <v>-4230.04</v>
+        <v>-144.09</v>
       </c>
     </row>
     <row r="142">
@@ -3942,25 +3930,25 @@
         <v>26</v>
       </c>
       <c r="B142" t="s" s="1">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C142" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D142" t="s" s="1">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E142" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F142" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G142" t="n" s="1">
-        <v>1269.01</v>
+        <v>480.31</v>
       </c>
       <c r="H142" t="n" s="1">
-        <v>-1269.01</v>
+        <v>-480.31</v>
       </c>
     </row>
     <row r="143">
@@ -3968,25 +3956,25 @@
         <v>26</v>
       </c>
       <c r="B143" t="s" s="1">
+        <v>137</v>
+      </c>
+      <c r="C143" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D143" t="s" s="1">
         <v>138</v>
       </c>
-      <c r="C143" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D143" t="s" s="1">
-        <v>135</v>
-      </c>
       <c r="E143" t="s" s="1">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F143" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G143" t="n" s="1">
-        <v>2961.03</v>
+        <v>1801.15</v>
       </c>
       <c r="H143" t="n" s="1">
-        <v>-2961.03</v>
+        <v>-1801.15</v>
       </c>
     </row>
     <row r="144">
@@ -3994,25 +3982,25 @@
         <v>26</v>
       </c>
       <c r="B144" t="s" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C144" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D144" t="s" s="1">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E144" t="s" s="1">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="F144" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G144" t="n" s="1">
-        <v>144.09</v>
+        <v>5165.75</v>
       </c>
       <c r="H144" t="n" s="1">
-        <v>-144.09</v>
+        <v>-5165.75</v>
       </c>
     </row>
     <row r="145">
@@ -4020,25 +4008,25 @@
         <v>26</v>
       </c>
       <c r="B145" t="s" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C145" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D145" t="s" s="1">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E145" t="s" s="1">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="F145" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G145" t="n" s="1">
-        <v>336.22</v>
+        <v>527.98</v>
       </c>
       <c r="H145" t="n" s="1">
-        <v>-336.22</v>
+        <v>-527.98</v>
       </c>
     </row>
     <row r="146">
@@ -4046,25 +4034,25 @@
         <v>26</v>
       </c>
       <c r="B146" t="s" s="1">
+        <v>137</v>
+      </c>
+      <c r="C146" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D146" t="s" s="1">
         <v>138</v>
       </c>
-      <c r="C146" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D146" t="s" s="1">
-        <v>134</v>
-      </c>
       <c r="E146" t="s" s="1">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F146" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G146" t="n" s="1">
-        <v>480.31</v>
+        <v>263.99</v>
       </c>
       <c r="H146" t="n" s="1">
-        <v>-480.31</v>
+        <v>-263.99</v>
       </c>
     </row>
     <row r="147">
@@ -4072,25 +4060,25 @@
         <v>26</v>
       </c>
       <c r="B147" t="s" s="1">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C147" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D147" t="s" s="1">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E147" t="s" s="1">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F147" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G147" t="n" s="1">
-        <v>1801.15</v>
+        <v>527.98</v>
       </c>
       <c r="H147" t="n" s="1">
-        <v>-1801.15</v>
+        <v>-527.98</v>
       </c>
     </row>
     <row r="148">
@@ -4098,25 +4086,25 @@
         <v>26</v>
       </c>
       <c r="B148" t="s" s="1">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C148" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D148" t="s" s="1">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E148" t="s" s="1">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="F148" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G148" t="n" s="1">
-        <v>5165.75</v>
+        <v>113.21</v>
       </c>
       <c r="H148" t="n" s="1">
-        <v>-5165.75</v>
+        <v>-113.21</v>
       </c>
     </row>
     <row r="149">
@@ -4124,25 +4112,25 @@
         <v>26</v>
       </c>
       <c r="B149" t="s" s="1">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C149" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D149" t="s" s="1">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E149" t="s" s="1">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F149" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G149" t="n" s="1">
-        <v>263.99</v>
+        <v>191.08</v>
       </c>
       <c r="H149" t="n" s="1">
-        <v>-263.99</v>
+        <v>-191.08</v>
       </c>
     </row>
     <row r="150">
@@ -4150,25 +4138,25 @@
         <v>26</v>
       </c>
       <c r="B150" t="s" s="1">
+        <v>141</v>
+      </c>
+      <c r="C150" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D150" t="s" s="1">
         <v>144</v>
       </c>
-      <c r="C150" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D150" t="s" s="1">
-        <v>147</v>
-      </c>
       <c r="E150" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F150" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G150" t="n" s="1">
-        <v>527.98</v>
+        <v>9.23</v>
       </c>
       <c r="H150" t="n" s="1">
-        <v>-527.98</v>
+        <v>-9.23</v>
       </c>
     </row>
     <row r="151">
@@ -4176,25 +4164,25 @@
         <v>26</v>
       </c>
       <c r="B151" t="s" s="1">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C151" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D151" t="s" s="1">
         <v>145</v>
       </c>
       <c r="E151" t="s" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F151" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G151" t="n" s="1">
-        <v>527.98</v>
+        <v>9.05</v>
       </c>
       <c r="H151" t="n" s="1">
-        <v>-527.98</v>
+        <v>-9.05</v>
       </c>
     </row>
     <row r="152">
@@ -4202,25 +4190,25 @@
         <v>26</v>
       </c>
       <c r="B152" t="s" s="1">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C152" t="s" s="1">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="D152" t="s" s="1">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E152" t="s" s="1">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="F152" t="n" s="1">
-        <v>1931.16</v>
+        <v>0.0</v>
       </c>
       <c r="G152" t="n" s="1">
-        <v>0.0</v>
+        <v>15.3</v>
       </c>
       <c r="H152" t="n" s="1">
-        <v>1931.16</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="153">
@@ -4228,25 +4216,25 @@
         <v>26</v>
       </c>
       <c r="B153" t="s" s="1">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C153" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D153" t="s" s="1">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="E153" t="s" s="1">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="F153" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G153" t="n" s="1">
-        <v>4500.0</v>
+        <v>15.56</v>
       </c>
       <c r="H153" t="n" s="1">
-        <v>-4500.0</v>
+        <v>-15.56</v>
       </c>
     </row>
     <row r="154">
@@ -4254,7 +4242,7 @@
         <v>26</v>
       </c>
       <c r="B154" t="s" s="1">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C154" t="s" s="1">
         <v>43</v>
@@ -4263,16 +4251,16 @@
         <v>47</v>
       </c>
       <c r="E154" t="s" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F154" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G154" t="n" s="1">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="H154" t="n" s="1">
-        <v>-2000.0</v>
+        <v>-15000.0</v>
       </c>
     </row>
     <row r="155">
@@ -4280,25 +4268,25 @@
         <v>26</v>
       </c>
       <c r="B155" t="s" s="1">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C155" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s" s="1">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="E155" t="s" s="1">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="F155" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G155" t="n" s="1">
-        <v>1500.0</v>
+        <v>2639.89</v>
       </c>
       <c r="H155" t="n" s="1">
-        <v>-1500.0</v>
+        <v>-2639.89</v>
       </c>
     </row>
     <row r="156">
@@ -4306,25 +4294,25 @@
         <v>26</v>
       </c>
       <c r="B156" t="s" s="1">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C156" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s" s="1">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="E156" t="s" s="1">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="F156" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G156" t="n" s="1">
-        <v>15000.0</v>
+        <v>1847.92</v>
       </c>
       <c r="H156" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-1847.92</v>
       </c>
     </row>
     <row r="157">
@@ -4332,25 +4320,25 @@
         <v>26</v>
       </c>
       <c r="B157" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C157" t="s" s="1">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="D157" t="s" s="1">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E157" t="s" s="1">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="F157" t="n" s="1">
-        <v>0.0</v>
+        <v>3500.0</v>
       </c>
       <c r="G157" t="n" s="1">
-        <v>2639.89</v>
+        <v>0.0</v>
       </c>
       <c r="H157" t="n" s="1">
-        <v>-2639.89</v>
+        <v>3500.0</v>
       </c>
     </row>
     <row r="158">
@@ -4358,25 +4346,25 @@
         <v>26</v>
       </c>
       <c r="B158" t="s" s="1">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C158" t="s" s="1">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D158" t="s" s="1">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="E158" t="s" s="1">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F158" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G158" t="n" s="1">
-        <v>1847.92</v>
+        <v>180.0</v>
       </c>
       <c r="H158" t="n" s="1">
-        <v>-1847.92</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="159">
@@ -4384,25 +4372,25 @@
         <v>26</v>
       </c>
       <c r="B159" t="s" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C159" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D159" t="s" s="1">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E159" t="s" s="1">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="F159" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G159" t="n" s="1">
-        <v>146.67</v>
+        <v>9216.24</v>
       </c>
       <c r="H159" t="n" s="1">
-        <v>-146.67</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="160">
@@ -4410,25 +4398,25 @@
         <v>26</v>
       </c>
       <c r="B160" t="s" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C160" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D160" t="s" s="1">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E160" t="s" s="1">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F160" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G160" t="n" s="1">
-        <v>180.0</v>
+        <v>891.0</v>
       </c>
       <c r="H160" t="n" s="1">
-        <v>-180.0</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="161">
@@ -4436,25 +4424,25 @@
         <v>26</v>
       </c>
       <c r="B161" t="s" s="1">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C161" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D161" t="s" s="1">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E161" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F161" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G161" t="n" s="1">
-        <v>891.0</v>
+        <v>737.28</v>
       </c>
       <c r="H161" t="n" s="1">
-        <v>-891.0</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="162">
@@ -4462,25 +4450,25 @@
         <v>26</v>
       </c>
       <c r="B162" t="s" s="1">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C162" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D162" t="s" s="1">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="E162" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F162" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G162" t="n" s="1">
-        <v>9216.24</v>
+        <v>750.99</v>
       </c>
       <c r="H162" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="163">
@@ -4488,25 +4476,25 @@
         <v>26</v>
       </c>
       <c r="B163" t="s" s="1">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C163" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D163" t="s" s="1">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E163" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F163" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G163" t="n" s="1">
-        <v>737.28</v>
+        <v>1544.4</v>
       </c>
       <c r="H163" t="n" s="1">
-        <v>-737.28</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="164">
@@ -4514,25 +4502,25 @@
         <v>26</v>
       </c>
       <c r="B164" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C164" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="D164" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="E164" t="s" s="1">
         <v>158</v>
       </c>
-      <c r="C164" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D164" t="s" s="1">
-        <v>159</v>
-      </c>
-      <c r="E164" t="s" s="1">
-        <v>33</v>
-      </c>
       <c r="F164" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G164" t="n" s="1">
-        <v>750.99</v>
+        <v>1925.0</v>
       </c>
       <c r="H164" t="n" s="1">
-        <v>-750.99</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="165">
@@ -4540,25 +4528,25 @@
         <v>26</v>
       </c>
       <c r="B165" t="s" s="1">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C165" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D165" t="s" s="1">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E165" t="s" s="1">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F165" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G165" t="n" s="1">
-        <v>1544.4</v>
+        <v>180.0</v>
       </c>
       <c r="H165" t="n" s="1">
-        <v>-1544.4</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="166">
@@ -4566,25 +4554,25 @@
         <v>26</v>
       </c>
       <c r="B166" t="s" s="1">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C166" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D166" t="s" s="1">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="E166" t="s" s="1">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="F166" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G166" t="n" s="1">
-        <v>1925.0</v>
+        <v>180.0</v>
       </c>
       <c r="H166" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="167">
@@ -4592,25 +4580,25 @@
         <v>26</v>
       </c>
       <c r="B167" t="s" s="1">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C167" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D167" t="s" s="1">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="E167" t="s" s="1">
-        <v>65</v>
+        <v>161</v>
       </c>
       <c r="F167" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G167" t="n" s="1">
-        <v>180.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H167" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="168">
@@ -4618,13 +4606,13 @@
         <v>26</v>
       </c>
       <c r="B168" t="s" s="1">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C168" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D168" t="s" s="1">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E168" t="s" s="1">
         <v>65</v>
@@ -4644,25 +4632,25 @@
         <v>26</v>
       </c>
       <c r="B169" t="s" s="1">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C169" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D169" t="s" s="1">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="E169" t="s" s="1">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="F169" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G169" t="n" s="1">
-        <v>1201.89</v>
+        <v>180.0</v>
       </c>
       <c r="H169" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="170">
@@ -4670,25 +4658,25 @@
         <v>26</v>
       </c>
       <c r="B170" t="s" s="1">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C170" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D170" t="s" s="1">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="E170" t="s" s="1">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F170" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G170" t="n" s="1">
-        <v>180.0</v>
+        <v>25504.78</v>
       </c>
       <c r="H170" t="n" s="1">
-        <v>-180.0</v>
+        <v>-25504.78</v>
       </c>
     </row>
     <row r="171">
@@ -4696,25 +4684,25 @@
         <v>26</v>
       </c>
       <c r="B171" t="s" s="1">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C171" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D171" t="s" s="1">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="E171" t="s" s="1">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F171" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G171" t="n" s="1">
-        <v>180.0</v>
+        <v>2277.0</v>
       </c>
       <c r="H171" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2277.0</v>
       </c>
     </row>
     <row r="172">
@@ -4722,25 +4710,25 @@
         <v>26</v>
       </c>
       <c r="B172" t="s" s="1">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C172" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D172" t="s" s="1">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="E172" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F172" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G172" t="n" s="1">
-        <v>2277.0</v>
+        <v>2078.64</v>
       </c>
       <c r="H172" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-2078.64</v>
       </c>
     </row>
     <row r="173">
@@ -4748,25 +4736,25 @@
         <v>26</v>
       </c>
       <c r="B173" t="s" s="1">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C173" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D173" t="s" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E173" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F173" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G173" t="n" s="1">
-        <v>25504.78</v>
+        <v>2040.52</v>
       </c>
       <c r="H173" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-2040.52</v>
       </c>
     </row>
     <row r="174">
@@ -4774,25 +4762,25 @@
         <v>26</v>
       </c>
       <c r="B174" t="s" s="1">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C174" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D174" t="s" s="1">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="E174" t="s" s="1">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F174" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G174" t="n" s="1">
-        <v>2078.64</v>
+        <v>180.0</v>
       </c>
       <c r="H174" t="n" s="1">
-        <v>-2078.64</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="175">
@@ -4800,25 +4788,25 @@
         <v>26</v>
       </c>
       <c r="B175" t="s" s="1">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C175" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D175" t="s" s="1">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="E175" t="s" s="1">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="F175" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G175" t="n" s="1">
-        <v>2040.52</v>
+        <v>180.0</v>
       </c>
       <c r="H175" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="176">
@@ -4826,25 +4814,25 @@
         <v>26</v>
       </c>
       <c r="B176" t="s" s="1">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C176" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D176" t="s" s="1">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="E176" t="s" s="1">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="F176" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G176" t="n" s="1">
-        <v>180.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H176" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="177">
@@ -4852,77 +4840,41 @@
         <v>26</v>
       </c>
       <c r="B177" t="s" s="1">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C177" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D177" t="s" s="1">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="E177" t="s" s="1">
-        <v>65</v>
+        <v>167</v>
       </c>
       <c r="F177" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G177" t="n" s="1">
-        <v>180.0</v>
+        <v>3750.0</v>
       </c>
       <c r="H177" t="n" s="1">
-        <v>-180.0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B178" t="s" s="1">
+        <v>-3750.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B180" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C178" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D178" t="s" s="1">
-        <v>44</v>
-      </c>
-      <c r="E178" t="s" s="1">
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F178" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G178" t="n" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="H178" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B179" t="s" s="1">
-        <v>169</v>
-      </c>
-      <c r="C179" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D179" t="s" s="1">
-        <v>47</v>
-      </c>
-      <c r="E179" t="s" s="1">
+      <c r="B181" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="F179" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G179" t="n" s="1">
-        <v>3750.0</v>
-      </c>
-      <c r="H179" t="n" s="1">
-        <v>-3750.0</v>
       </c>
     </row>
     <row r="182">
@@ -4931,22 +4883,6 @@
       </c>
       <c r="B182" s="3" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="168">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -153,9 +153,6 @@
     <t>Hostgator</t>
   </si>
   <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
     <t>1 - 9</t>
   </si>
   <si>
@@ -165,12 +162,12 @@
     <t>TERESINHA ELVIRA MAXIMINO DE MENEZES</t>
   </si>
   <si>
+    <t>100901 - 2</t>
+  </si>
+  <si>
     <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
   </si>
   <si>
-    <t>100901 - 2</t>
-  </si>
-  <si>
     <t>102301 - 2</t>
   </si>
   <si>
@@ -243,273 +240,258 @@
     <t>96601 - 3</t>
   </si>
   <si>
+    <t>101401 - 2</t>
+  </si>
+  <si>
     <t>101401 - 3</t>
   </si>
   <si>
-    <t>101401 - 2</t>
-  </si>
-  <si>
     <t>10/10/2026</t>
   </si>
   <si>
+    <t>100501 - 3</t>
+  </si>
+  <si>
+    <t>100501 - 2</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>49501 - 2</t>
+  </si>
+  <si>
+    <t>100301 - 1</t>
+  </si>
+  <si>
+    <t>102101 - 1</t>
+  </si>
+  <si>
+    <t>100301 - 3</t>
+  </si>
+  <si>
+    <t>100301 - 2</t>
+  </si>
+  <si>
+    <t>102101 - 2</t>
+  </si>
+  <si>
+    <t>102101 - 3</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>1631 - 1</t>
+  </si>
+  <si>
+    <t>1632 - 1</t>
+  </si>
+  <si>
+    <t>1633 - 1</t>
+  </si>
+  <si>
+    <t>1634 - 1</t>
+  </si>
+  <si>
+    <t>101201 - 1</t>
+  </si>
+  <si>
+    <t>1631 - 2</t>
+  </si>
+  <si>
+    <t>1631 - 3</t>
+  </si>
+  <si>
+    <t>1632 - 3</t>
+  </si>
+  <si>
+    <t>1632 - 2</t>
+  </si>
+  <si>
+    <t>1633 - 3</t>
+  </si>
+  <si>
+    <t>1633 - 2</t>
+  </si>
+  <si>
+    <t>1634 - 3</t>
+  </si>
+  <si>
+    <t>1634 - 2</t>
+  </si>
+  <si>
+    <t>101201 - 2</t>
+  </si>
+  <si>
+    <t>101201 - 3</t>
+  </si>
+  <si>
+    <t>101801 - 2</t>
+  </si>
+  <si>
+    <t>101801 - 3</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>101101 - 1</t>
+  </si>
+  <si>
+    <t>101101 - 3</t>
+  </si>
+  <si>
+    <t>101101 - 2</t>
+  </si>
+  <si>
+    <t>103801 - 1</t>
+  </si>
+  <si>
+    <t>104701 - 1</t>
+  </si>
+  <si>
+    <t>104701 - 2</t>
+  </si>
+  <si>
+    <t>104801 - 2</t>
+  </si>
+  <si>
+    <t>104801 - 1</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>103801 - 2</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>105001 - 1</t>
+  </si>
+  <si>
+    <t>105001 - 2</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>92001 - 2</t>
+  </si>
+  <si>
+    <t>102401 - 1</t>
+  </si>
+  <si>
+    <t>102401 - 2</t>
+  </si>
+  <si>
+    <t>102401 - 3</t>
+  </si>
+  <si>
+    <t>102501 - 2</t>
+  </si>
+  <si>
+    <t>102501 - 3</t>
+  </si>
+  <si>
+    <t>105301 - 1</t>
+  </si>
+  <si>
+    <t>105101 - 1</t>
+  </si>
+  <si>
+    <t>105101 - 2</t>
+  </si>
+  <si>
+    <t>105301 - 2</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>ERIC SERPA</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>104401 - 1</t>
+  </si>
+  <si>
+    <t>PAGSEGURO</t>
+  </si>
+  <si>
+    <t>104401 - 2</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>1630 - 1</t>
+  </si>
+  <si>
+    <t>1635 - 1</t>
+  </si>
+  <si>
+    <t>1630 - 3</t>
+  </si>
+  <si>
+    <t>1630 - 2</t>
+  </si>
+  <si>
+    <t>1635 - 2</t>
+  </si>
+  <si>
+    <t>1635 - 3</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
     <t>100501 - 1</t>
   </si>
   <si>
-    <t>100501 - 2</t>
-  </si>
-  <si>
-    <t>100501 - 3</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>49501 - 2</t>
-  </si>
-  <si>
-    <t>100301 - 1</t>
-  </si>
-  <si>
-    <t>102101 - 1</t>
-  </si>
-  <si>
-    <t>100301 - 3</t>
-  </si>
-  <si>
-    <t>100301 - 2</t>
-  </si>
-  <si>
-    <t>102101 - 2</t>
-  </si>
-  <si>
-    <t>102101 - 3</t>
-  </si>
-  <si>
-    <t>14/10/2026</t>
-  </si>
-  <si>
-    <t>1631 - 1</t>
-  </si>
-  <si>
-    <t>1632 - 1</t>
-  </si>
-  <si>
-    <t>1633 - 1</t>
-  </si>
-  <si>
-    <t>1634 - 1</t>
-  </si>
-  <si>
-    <t>101201 - 1</t>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>102301 - 3</t>
+  </si>
+  <si>
+    <t>25/10/2026</t>
+  </si>
+  <si>
+    <t>68 - 3</t>
+  </si>
+  <si>
+    <t>Luis Carlos Alves de Oliveira</t>
+  </si>
+  <si>
+    <t>26/10/2026</t>
+  </si>
+  <si>
+    <t>2 - 9</t>
+  </si>
+  <si>
+    <t>EM SOLUCOES INTEGRADAS DE SISTEMAS LTDA ME</t>
   </si>
   <si>
     <t>101801 - 1</t>
   </si>
   <si>
-    <t>1631 - 2</t>
-  </si>
-  <si>
-    <t>1631 - 3</t>
-  </si>
-  <si>
-    <t>1632 - 3</t>
-  </si>
-  <si>
-    <t>1632 - 2</t>
-  </si>
-  <si>
-    <t>1633 - 3</t>
-  </si>
-  <si>
-    <t>1633 - 2</t>
-  </si>
-  <si>
-    <t>1634 - 3</t>
-  </si>
-  <si>
-    <t>1634 - 2</t>
-  </si>
-  <si>
-    <t>101201 - 3</t>
-  </si>
-  <si>
-    <t>101201 - 2</t>
-  </si>
-  <si>
-    <t>101801 - 2</t>
-  </si>
-  <si>
-    <t>101801 - 3</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>101101 - 1</t>
-  </si>
-  <si>
-    <t>101101 - 3</t>
-  </si>
-  <si>
-    <t>101101 - 2</t>
-  </si>
-  <si>
-    <t>103801 - 1</t>
-  </si>
-  <si>
-    <t>104701 - 1</t>
-  </si>
-  <si>
-    <t>104701 - 2</t>
-  </si>
-  <si>
-    <t>104801 - 2</t>
-  </si>
-  <si>
-    <t>104801 - 1</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>103801 - 2</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>105001 - 1</t>
-  </si>
-  <si>
-    <t>105001 - 2</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>92001 - 2</t>
-  </si>
-  <si>
-    <t>102401 - 1</t>
+    <t>27/10/2026</t>
+  </si>
+  <si>
+    <t>100901 - 3</t>
+  </si>
+  <si>
+    <t>29/10/2026</t>
   </si>
   <si>
     <t>102501 - 1</t>
   </si>
   <si>
-    <t>102401 - 2</t>
-  </si>
-  <si>
-    <t>102401 - 3</t>
-  </si>
-  <si>
-    <t>102501 - 3</t>
-  </si>
-  <si>
-    <t>102501 - 2</t>
-  </si>
-  <si>
-    <t>105301 - 1</t>
-  </si>
-  <si>
-    <t>105101 - 1</t>
-  </si>
-  <si>
-    <t>105101 - 2</t>
-  </si>
-  <si>
-    <t>105301 - 2</t>
-  </si>
-  <si>
-    <t>18/10/2026</t>
-  </si>
-  <si>
-    <t>ERIC SERPA</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>104401 - 1</t>
-  </si>
-  <si>
-    <t>PAGSEGURO</t>
-  </si>
-  <si>
-    <t>104401 - 2</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>1630 - 1</t>
-  </si>
-  <si>
-    <t>1635 - 1</t>
-  </si>
-  <si>
-    <t>1630 - 3</t>
-  </si>
-  <si>
-    <t>1630 - 2</t>
-  </si>
-  <si>
-    <t>1635 - 2</t>
-  </si>
-  <si>
-    <t>1635 - 3</t>
-  </si>
-  <si>
-    <t>Simples Nacional - DAS</t>
-  </si>
-  <si>
-    <t>21/10/2026</t>
-  </si>
-  <si>
-    <t>DUP-Duplicata de Contrato</t>
-  </si>
-  <si>
-    <t>103501 - 0</t>
-  </si>
-  <si>
-    <t>IL HEE PARK</t>
-  </si>
-  <si>
-    <t>22/10/2026</t>
-  </si>
-  <si>
-    <t>23/10/2026</t>
-  </si>
-  <si>
-    <t>102301 - 3</t>
-  </si>
-  <si>
-    <t>25/10/2026</t>
-  </si>
-  <si>
-    <t>68 - 3</t>
-  </si>
-  <si>
-    <t>Luis Carlos Alves de Oliveira</t>
-  </si>
-  <si>
-    <t>26/10/2026</t>
-  </si>
-  <si>
-    <t>2 - 9</t>
-  </si>
-  <si>
-    <t>EM SOLUCOES INTEGRADAS DE SISTEMAS LTDA ME</t>
-  </si>
-  <si>
-    <t>27/10/2026</t>
-  </si>
-  <si>
-    <t>100901 - 3</t>
-  </si>
-  <si>
-    <t>29/10/2026</t>
-  </si>
-  <si>
     <t>30/10/2026</t>
   </si>
   <si>
@@ -522,19 +504,19 @@
     <t>Total Geral Crédito</t>
   </si>
   <si>
-    <t>3.500,00</t>
+    <t>0,00</t>
   </si>
   <si>
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>262.963,46</t>
+    <t>234.605,76</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-259.463,46</t>
+    <t>-234.605,76</t>
   </si>
 </sst>
 </file>
@@ -602,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H182"/>
+  <dimension ref="A2:H168"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -920,19 +902,19 @@
         <v>43</v>
       </c>
       <c r="D26" t="s" s="1">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s" s="1">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F26" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>2536.0</v>
+        <v>14250.0</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-2536.0</v>
+        <v>-14250.0</v>
       </c>
     </row>
     <row r="27">
@@ -943,22 +925,22 @@
         <v>40</v>
       </c>
       <c r="C27" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s" s="1">
         <v>47</v>
       </c>
       <c r="E27" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G27" t="n" s="1">
-        <v>14250.0</v>
+        <v>607.95</v>
       </c>
       <c r="H27" t="n" s="1">
-        <v>-14250.0</v>
+        <v>-607.95</v>
       </c>
     </row>
     <row r="28">
@@ -972,19 +954,19 @@
         <v>36</v>
       </c>
       <c r="D28" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F28" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G28" t="n" s="1">
-        <v>607.95</v>
+        <v>1215.9</v>
       </c>
       <c r="H28" t="n" s="1">
-        <v>-607.95</v>
+        <v>-1215.9</v>
       </c>
     </row>
     <row r="29">
@@ -998,7 +980,7 @@
         <v>36</v>
       </c>
       <c r="D29" t="s" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s" s="1">
         <v>50</v>
@@ -1024,19 +1006,19 @@
         <v>36</v>
       </c>
       <c r="D30" t="s" s="1">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F30" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G30" t="n" s="1">
-        <v>1215.9</v>
+        <v>222.06</v>
       </c>
       <c r="H30" t="n" s="1">
-        <v>-1215.9</v>
+        <v>-222.06</v>
       </c>
     </row>
     <row r="31">
@@ -1050,7 +1032,7 @@
         <v>36</v>
       </c>
       <c r="D31" t="s" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s" s="1">
         <v>38</v>
@@ -1079,16 +1061,16 @@
         <v>41</v>
       </c>
       <c r="E32" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F32" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G32" t="n" s="1">
-        <v>222.06</v>
+        <v>444.12</v>
       </c>
       <c r="H32" t="n" s="1">
-        <v>-222.06</v>
+        <v>-444.12</v>
       </c>
     </row>
     <row r="33">
@@ -1096,25 +1078,25 @@
         <v>26</v>
       </c>
       <c r="B33" t="s" s="1">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D33" t="s" s="1">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F33" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G33" t="n" s="1">
-        <v>444.12</v>
+        <v>4255.67</v>
       </c>
       <c r="H33" t="n" s="1">
-        <v>-444.12</v>
+        <v>-4255.67</v>
       </c>
     </row>
     <row r="34">
@@ -1122,13 +1104,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D34" t="s" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E34" t="s" s="1">
         <v>54</v>
@@ -1137,10 +1119,10 @@
         <v>0.0</v>
       </c>
       <c r="G34" t="n" s="1">
-        <v>4255.67</v>
+        <v>1823.86</v>
       </c>
       <c r="H34" t="n" s="1">
-        <v>-4255.67</v>
+        <v>-1823.86</v>
       </c>
     </row>
     <row r="35">
@@ -1148,25 +1130,25 @@
         <v>26</v>
       </c>
       <c r="B35" t="s" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D35" t="s" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E35" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F35" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G35" t="n" s="1">
-        <v>1823.86</v>
+        <v>6079.52</v>
       </c>
       <c r="H35" t="n" s="1">
-        <v>-1823.86</v>
+        <v>-6079.52</v>
       </c>
     </row>
     <row r="36">
@@ -1174,13 +1156,13 @@
         <v>26</v>
       </c>
       <c r="B36" t="s" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D36" t="s" s="1">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E36" t="s" s="1">
         <v>38</v>
@@ -1189,10 +1171,10 @@
         <v>0.0</v>
       </c>
       <c r="G36" t="n" s="1">
-        <v>6079.52</v>
+        <v>2220.59</v>
       </c>
       <c r="H36" t="n" s="1">
-        <v>-6079.52</v>
+        <v>-2220.59</v>
       </c>
     </row>
     <row r="37">
@@ -1200,7 +1182,7 @@
         <v>26</v>
       </c>
       <c r="B37" t="s" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s" s="1">
         <v>36</v>
@@ -1209,16 +1191,16 @@
         <v>41</v>
       </c>
       <c r="E37" t="s" s="1">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F37" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G37" t="n" s="1">
-        <v>2220.59</v>
+        <v>1554.41</v>
       </c>
       <c r="H37" t="n" s="1">
-        <v>-2220.59</v>
+        <v>-1554.41</v>
       </c>
     </row>
     <row r="38">
@@ -1226,7 +1208,7 @@
         <v>26</v>
       </c>
       <c r="B38" t="s" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s" s="1">
         <v>36</v>
@@ -1235,16 +1217,16 @@
         <v>41</v>
       </c>
       <c r="E38" t="s" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F38" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G38" t="n" s="1">
-        <v>1554.41</v>
+        <v>666.18</v>
       </c>
       <c r="H38" t="n" s="1">
-        <v>-1554.41</v>
+        <v>-666.18</v>
       </c>
     </row>
     <row r="39">
@@ -1252,25 +1234,25 @@
         <v>26</v>
       </c>
       <c r="B39" t="s" s="1">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D39" t="s" s="1">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E39" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F39" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G39" t="n" s="1">
-        <v>666.18</v>
+        <v>3.56</v>
       </c>
       <c r="H39" t="n" s="1">
-        <v>-666.18</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="40">
@@ -1278,7 +1260,7 @@
         <v>26</v>
       </c>
       <c r="B40" t="s" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s" s="1">
         <v>36</v>
@@ -1287,7 +1269,7 @@
         <v>58</v>
       </c>
       <c r="E40" t="s" s="1">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F40" t="n" s="1">
         <v>0.0</v>
@@ -1304,25 +1286,25 @@
         <v>26</v>
       </c>
       <c r="B41" t="s" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D41" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F41" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G41" t="n" s="1">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="H41" t="n" s="1">
-        <v>-3.56</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="42">
@@ -1330,7 +1312,7 @@
         <v>26</v>
       </c>
       <c r="B42" t="s" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s" s="1">
         <v>36</v>
@@ -1339,16 +1321,16 @@
         <v>59</v>
       </c>
       <c r="E42" t="s" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F42" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G42" t="n" s="1">
-        <v>1.78</v>
+        <v>33.2</v>
       </c>
       <c r="H42" t="n" s="1">
-        <v>-1.78</v>
+        <v>-33.2</v>
       </c>
     </row>
     <row r="43">
@@ -1356,7 +1338,7 @@
         <v>26</v>
       </c>
       <c r="B43" t="s" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s" s="1">
         <v>36</v>
@@ -1365,16 +1347,16 @@
         <v>60</v>
       </c>
       <c r="E43" t="s" s="1">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F43" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G43" t="n" s="1">
-        <v>33.2</v>
+        <v>66.4</v>
       </c>
       <c r="H43" t="n" s="1">
-        <v>-33.2</v>
+        <v>-66.4</v>
       </c>
     </row>
     <row r="44">
@@ -1382,16 +1364,16 @@
         <v>26</v>
       </c>
       <c r="B44" t="s" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D44" t="s" s="1">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E44" t="s" s="1">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F44" t="n" s="1">
         <v>0.0</v>
@@ -1408,25 +1390,25 @@
         <v>26</v>
       </c>
       <c r="B45" t="s" s="1">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s" s="1">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s" s="1">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s" s="1">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F45" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G45" t="n" s="1">
-        <v>66.4</v>
+        <v>180.0</v>
       </c>
       <c r="H45" t="n" s="1">
-        <v>-66.4</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="46">
@@ -1434,13 +1416,13 @@
         <v>26</v>
       </c>
       <c r="B46" t="s" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s" s="1">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E46" t="s" s="1">
         <v>65</v>
@@ -1449,10 +1431,10 @@
         <v>0.0</v>
       </c>
       <c r="G46" t="n" s="1">
-        <v>180.0</v>
+        <v>12.47</v>
       </c>
       <c r="H46" t="n" s="1">
-        <v>-180.0</v>
+        <v>-12.47</v>
       </c>
     </row>
     <row r="47">
@@ -1460,25 +1442,25 @@
         <v>26</v>
       </c>
       <c r="B47" t="s" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D47" t="s" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E47" t="s" s="1">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F47" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G47" t="n" s="1">
-        <v>12.47</v>
+        <v>17.81</v>
       </c>
       <c r="H47" t="n" s="1">
-        <v>-12.47</v>
+        <v>-17.81</v>
       </c>
     </row>
     <row r="48">
@@ -1486,7 +1468,7 @@
         <v>26</v>
       </c>
       <c r="B48" t="s" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s" s="1">
         <v>36</v>
@@ -1495,16 +1477,16 @@
         <v>59</v>
       </c>
       <c r="E48" t="s" s="1">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F48" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G48" t="n" s="1">
-        <v>17.81</v>
+        <v>232.4</v>
       </c>
       <c r="H48" t="n" s="1">
-        <v>-17.81</v>
+        <v>-232.4</v>
       </c>
     </row>
     <row r="49">
@@ -1512,13 +1494,13 @@
         <v>26</v>
       </c>
       <c r="B49" t="s" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D49" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E49" t="s" s="1">
         <v>54</v>
@@ -1527,10 +1509,10 @@
         <v>0.0</v>
       </c>
       <c r="G49" t="n" s="1">
-        <v>232.4</v>
+        <v>99.6</v>
       </c>
       <c r="H49" t="n" s="1">
-        <v>-232.4</v>
+        <v>-99.6</v>
       </c>
     </row>
     <row r="50">
@@ -1538,25 +1520,25 @@
         <v>26</v>
       </c>
       <c r="B50" t="s" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D50" t="s" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F50" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G50" t="n" s="1">
-        <v>99.6</v>
+        <v>332.0</v>
       </c>
       <c r="H50" t="n" s="1">
-        <v>-99.6</v>
+        <v>-332.0</v>
       </c>
     </row>
     <row r="51">
@@ -1564,25 +1546,25 @@
         <v>26</v>
       </c>
       <c r="B51" t="s" s="1">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C51" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D51" t="s" s="1">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F51" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G51" t="n" s="1">
-        <v>332.0</v>
+        <v>15184.14</v>
       </c>
       <c r="H51" t="n" s="1">
-        <v>-332.0</v>
+        <v>-15184.14</v>
       </c>
     </row>
     <row r="52">
@@ -1590,7 +1572,7 @@
         <v>26</v>
       </c>
       <c r="B52" t="s" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s" s="1">
         <v>28</v>
@@ -1599,16 +1581,16 @@
         <v>68</v>
       </c>
       <c r="E52" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F52" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G52" t="n" s="1">
-        <v>1039.5</v>
+        <v>12242.58</v>
       </c>
       <c r="H52" t="n" s="1">
-        <v>-1039.5</v>
+        <v>-12242.58</v>
       </c>
     </row>
     <row r="53">
@@ -1616,25 +1598,25 @@
         <v>26</v>
       </c>
       <c r="B53" t="s" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s" s="1">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s" s="1">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E53" t="s" s="1">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="F53" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G53" t="n" s="1">
-        <v>15184.14</v>
+        <v>2163.0</v>
       </c>
       <c r="H53" t="n" s="1">
-        <v>-15184.14</v>
+        <v>-2163.0</v>
       </c>
     </row>
     <row r="54">
@@ -1642,25 +1624,25 @@
         <v>26</v>
       </c>
       <c r="B54" t="s" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54" t="s" s="1">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s" s="1">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E54" t="s" s="1">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="F54" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G54" t="n" s="1">
-        <v>12242.58</v>
+        <v>1821.02</v>
       </c>
       <c r="H54" t="n" s="1">
-        <v>-12242.58</v>
+        <v>-1821.02</v>
       </c>
     </row>
     <row r="55">
@@ -1668,25 +1650,25 @@
         <v>26</v>
       </c>
       <c r="B55" t="s" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s" s="1">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E55" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F55" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G55" t="n" s="1">
-        <v>1039.5</v>
+        <v>1214.79</v>
       </c>
       <c r="H55" t="n" s="1">
-        <v>-1039.5</v>
+        <v>-1214.79</v>
       </c>
     </row>
     <row r="56">
@@ -1694,25 +1676,25 @@
         <v>26</v>
       </c>
       <c r="B56" t="s" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" t="s" s="1">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D56" t="s" s="1">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E56" t="s" s="1">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="F56" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G56" t="n" s="1">
-        <v>2163.0</v>
+        <v>1237.52</v>
       </c>
       <c r="H56" t="n" s="1">
-        <v>-2163.0</v>
+        <v>-1237.52</v>
       </c>
     </row>
     <row r="57">
@@ -1720,25 +1702,25 @@
         <v>26</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" t="s" s="1">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s" s="1">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="E57" t="s" s="1">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="F57" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>1821.02</v>
+        <v>3683.86</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>-1821.02</v>
+        <v>-3683.86</v>
       </c>
     </row>
     <row r="58">
@@ -1746,13 +1728,13 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E58" t="s" s="1">
         <v>35</v>
@@ -1761,10 +1743,10 @@
         <v>0.0</v>
       </c>
       <c r="G58" t="n" s="1">
-        <v>1214.79</v>
+        <v>979.59</v>
       </c>
       <c r="H58" t="n" s="1">
-        <v>-1214.79</v>
+        <v>-979.59</v>
       </c>
     </row>
     <row r="59">
@@ -1772,13 +1754,13 @@
         <v>26</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E59" t="s" s="1">
         <v>33</v>
@@ -1787,10 +1769,10 @@
         <v>0.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>1237.52</v>
+        <v>997.38</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>-1237.52</v>
+        <v>-997.38</v>
       </c>
     </row>
     <row r="60">
@@ -1798,25 +1780,25 @@
         <v>26</v>
       </c>
       <c r="B60" t="s" s="1">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D60" t="s" s="1">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E60" t="s" s="1">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F60" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G60" t="n" s="1">
-        <v>3683.86</v>
+        <v>699.37</v>
       </c>
       <c r="H60" t="n" s="1">
-        <v>-3683.86</v>
+        <v>-699.37</v>
       </c>
     </row>
     <row r="61">
@@ -1824,25 +1806,25 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D61" t="s" s="1">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E61" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F61" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G61" t="n" s="1">
-        <v>997.38</v>
+        <v>686.33</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>-997.38</v>
+        <v>-686.33</v>
       </c>
     </row>
     <row r="62">
@@ -1850,25 +1832,25 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s" s="1">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E62" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F62" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>979.59</v>
+        <v>560.42</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>-979.59</v>
+        <v>-560.42</v>
       </c>
     </row>
     <row r="63">
@@ -1876,25 +1858,25 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D63" t="s" s="1">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E63" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>1019.7</v>
+        <v>8758.14</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-1019.7</v>
+        <v>-8758.14</v>
       </c>
     </row>
     <row r="64">
@@ -1902,25 +1884,25 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C64" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E64" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>686.33</v>
+        <v>9559.08</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-686.33</v>
+        <v>-9559.08</v>
       </c>
     </row>
     <row r="65">
@@ -1928,13 +1910,13 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E65" t="s" s="1">
         <v>33</v>
@@ -1943,10 +1925,10 @@
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>699.37</v>
+        <v>714.08</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-699.37</v>
+        <v>-714.08</v>
       </c>
     </row>
     <row r="66">
@@ -1954,25 +1936,25 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C66" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>560.42</v>
+        <v>700.72</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-560.42</v>
+        <v>-700.72</v>
       </c>
     </row>
     <row r="67">
@@ -1980,25 +1962,25 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>8758.14</v>
+        <v>764.9</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-8758.14</v>
+        <v>-764.9</v>
       </c>
     </row>
     <row r="68">
@@ -2006,25 +1988,25 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D68" t="s" s="1">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E68" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>1336.5</v>
+        <v>779.41</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-1336.5</v>
+        <v>-779.41</v>
       </c>
     </row>
     <row r="69">
@@ -2032,25 +2014,25 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E69" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F69" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>891.0</v>
+        <v>744.28</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-891.0</v>
+        <v>-744.28</v>
       </c>
     </row>
     <row r="70">
@@ -2058,13 +2040,13 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E70" t="s" s="1">
         <v>30</v>
@@ -2073,10 +2055,10 @@
         <v>0.0</v>
       </c>
       <c r="G70" t="n" s="1">
-        <v>9559.08</v>
+        <v>228.78</v>
       </c>
       <c r="H70" t="n" s="1">
-        <v>-9559.08</v>
+        <v>-228.78</v>
       </c>
     </row>
     <row r="71">
@@ -2084,25 +2066,25 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C71" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D71" t="s" s="1">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E71" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F71" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G71" t="n" s="1">
-        <v>714.08</v>
+        <v>378.27</v>
       </c>
       <c r="H71" t="n" s="1">
-        <v>-714.08</v>
+        <v>-378.27</v>
       </c>
     </row>
     <row r="72">
@@ -2110,25 +2092,25 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C72" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s" s="1">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E72" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F72" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G72" t="n" s="1">
-        <v>700.72</v>
+        <v>96.52</v>
       </c>
       <c r="H72" t="n" s="1">
-        <v>-700.72</v>
+        <v>-96.52</v>
       </c>
     </row>
     <row r="73">
@@ -2136,25 +2118,25 @@
         <v>26</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C73" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D73" t="s" s="1">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E73" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G73" t="n" s="1">
-        <v>764.9</v>
+        <v>6118.3</v>
       </c>
       <c r="H73" t="n" s="1">
-        <v>-764.9</v>
+        <v>-6118.3</v>
       </c>
     </row>
     <row r="74">
@@ -2162,25 +2144,25 @@
         <v>26</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C74" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D74" t="s" s="1">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E74" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G74" t="n" s="1">
-        <v>779.41</v>
+        <v>59.56</v>
       </c>
       <c r="H74" t="n" s="1">
-        <v>-779.41</v>
+        <v>-59.56</v>
       </c>
     </row>
     <row r="75">
@@ -2188,25 +2170,25 @@
         <v>26</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C75" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D75" t="s" s="1">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E75" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F75" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G75" t="n" s="1">
-        <v>744.28</v>
+        <v>60.64</v>
       </c>
       <c r="H75" t="n" s="1">
-        <v>-744.28</v>
+        <v>-60.64</v>
       </c>
     </row>
     <row r="76">
@@ -2214,25 +2196,25 @@
         <v>26</v>
       </c>
       <c r="B76" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C76" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D76" t="s" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E76" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F76" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G76" t="n" s="1">
-        <v>228.78</v>
+        <v>18.64</v>
       </c>
       <c r="H76" t="n" s="1">
-        <v>-228.78</v>
+        <v>-18.64</v>
       </c>
     </row>
     <row r="77">
@@ -2240,25 +2222,25 @@
         <v>26</v>
       </c>
       <c r="B77" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C77" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D77" t="s" s="1">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E77" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F77" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G77" t="n" s="1">
-        <v>378.27</v>
+        <v>18.3</v>
       </c>
       <c r="H77" t="n" s="1">
-        <v>-378.27</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="78">
@@ -2266,25 +2248,25 @@
         <v>26</v>
       </c>
       <c r="B78" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C78" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D78" t="s" s="1">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E78" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F78" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G78" t="n" s="1">
-        <v>96.52</v>
+        <v>30.82</v>
       </c>
       <c r="H78" t="n" s="1">
-        <v>-96.52</v>
+        <v>-30.82</v>
       </c>
     </row>
     <row r="79">
@@ -2292,25 +2274,25 @@
         <v>26</v>
       </c>
       <c r="B79" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C79" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D79" t="s" s="1">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E79" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G79" t="n" s="1">
-        <v>544.5</v>
+        <v>30.25</v>
       </c>
       <c r="H79" t="n" s="1">
-        <v>-544.5</v>
+        <v>-30.25</v>
       </c>
     </row>
     <row r="80">
@@ -2318,25 +2300,25 @@
         <v>26</v>
       </c>
       <c r="B80" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C80" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D80" t="s" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E80" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F80" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G80" t="n" s="1">
-        <v>6118.3</v>
+        <v>7.86</v>
       </c>
       <c r="H80" t="n" s="1">
-        <v>-6118.3</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="81">
@@ -2344,25 +2326,25 @@
         <v>26</v>
       </c>
       <c r="B81" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C81" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D81" t="s" s="1">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E81" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F81" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G81" t="n" s="1">
-        <v>891.0</v>
+        <v>7.74</v>
       </c>
       <c r="H81" t="n" s="1">
-        <v>-891.0</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="82">
@@ -2370,13 +2352,13 @@
         <v>26</v>
       </c>
       <c r="B82" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C82" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D82" t="s" s="1">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E82" t="s" s="1">
         <v>35</v>
@@ -2385,10 +2367,10 @@
         <v>0.0</v>
       </c>
       <c r="G82" t="n" s="1">
-        <v>59.56</v>
+        <v>489.47</v>
       </c>
       <c r="H82" t="n" s="1">
-        <v>-59.56</v>
+        <v>-489.47</v>
       </c>
     </row>
     <row r="83">
@@ -2396,13 +2378,13 @@
         <v>26</v>
       </c>
       <c r="B83" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C83" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D83" t="s" s="1">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E83" t="s" s="1">
         <v>33</v>
@@ -2411,10 +2393,10 @@
         <v>0.0</v>
       </c>
       <c r="G83" t="n" s="1">
-        <v>60.64</v>
+        <v>498.88</v>
       </c>
       <c r="H83" t="n" s="1">
-        <v>-60.64</v>
+        <v>-498.88</v>
       </c>
     </row>
     <row r="84">
@@ -2422,25 +2404,25 @@
         <v>26</v>
       </c>
       <c r="B84" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C84" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D84" t="s" s="1">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E84" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F84" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G84" t="n" s="1">
-        <v>18.64</v>
+        <v>632.51</v>
       </c>
       <c r="H84" t="n" s="1">
-        <v>-18.64</v>
+        <v>-632.51</v>
       </c>
     </row>
     <row r="85">
@@ -2448,25 +2430,25 @@
         <v>26</v>
       </c>
       <c r="B85" t="s" s="1">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C85" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D85" t="s" s="1">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E85" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F85" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G85" t="n" s="1">
-        <v>18.3</v>
+        <v>644.44</v>
       </c>
       <c r="H85" t="n" s="1">
-        <v>-18.3</v>
+        <v>-644.44</v>
       </c>
     </row>
     <row r="86">
@@ -2474,25 +2456,25 @@
         <v>26</v>
       </c>
       <c r="B86" t="s" s="1">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C86" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D86" t="s" s="1">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E86" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F86" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G86" t="n" s="1">
-        <v>30.82</v>
+        <v>21486.12</v>
       </c>
       <c r="H86" t="n" s="1">
-        <v>-30.82</v>
+        <v>-21486.12</v>
       </c>
     </row>
     <row r="87">
@@ -2500,25 +2482,25 @@
         <v>26</v>
       </c>
       <c r="B87" t="s" s="1">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C87" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D87" t="s" s="1">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E87" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F87" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G87" t="n" s="1">
-        <v>30.25</v>
+        <v>1751.0</v>
       </c>
       <c r="H87" t="n" s="1">
-        <v>-30.25</v>
+        <v>-1751.0</v>
       </c>
     </row>
     <row r="88">
@@ -2526,25 +2508,25 @@
         <v>26</v>
       </c>
       <c r="B88" t="s" s="1">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C88" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D88" t="s" s="1">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E88" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F88" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G88" t="n" s="1">
-        <v>7.86</v>
+        <v>1718.89</v>
       </c>
       <c r="H88" t="n" s="1">
-        <v>-7.86</v>
+        <v>-1718.89</v>
       </c>
     </row>
     <row r="89">
@@ -2552,25 +2534,25 @@
         <v>26</v>
       </c>
       <c r="B89" t="s" s="1">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C89" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s" s="1">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E89" t="s" s="1">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F89" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G89" t="n" s="1">
-        <v>7.74</v>
+        <v>15.2</v>
       </c>
       <c r="H89" t="n" s="1">
-        <v>-7.74</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="90">
@@ -2578,25 +2560,25 @@
         <v>26</v>
       </c>
       <c r="B90" t="s" s="1">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C90" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D90" t="s" s="1">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E90" t="s" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F90" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G90" t="n" s="1">
-        <v>498.88</v>
+        <v>30.4</v>
       </c>
       <c r="H90" t="n" s="1">
-        <v>-498.88</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="91">
@@ -2604,25 +2586,25 @@
         <v>26</v>
       </c>
       <c r="B91" t="s" s="1">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C91" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s" s="1">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E91" t="s" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F91" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G91" t="n" s="1">
-        <v>489.47</v>
+        <v>30.4</v>
       </c>
       <c r="H91" t="n" s="1">
-        <v>-489.47</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="92">
@@ -2630,25 +2612,25 @@
         <v>26</v>
       </c>
       <c r="B92" t="s" s="1">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C92" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D92" t="s" s="1">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E92" t="s" s="1">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F92" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G92" t="n" s="1">
-        <v>632.51</v>
+        <v>8.73</v>
       </c>
       <c r="H92" t="n" s="1">
-        <v>-632.51</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="93">
@@ -2656,25 +2638,25 @@
         <v>26</v>
       </c>
       <c r="B93" t="s" s="1">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E93" t="s" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F93" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G93" t="n" s="1">
-        <v>644.44</v>
+        <v>17.46</v>
       </c>
       <c r="H93" t="n" s="1">
-        <v>-644.44</v>
+        <v>-17.46</v>
       </c>
     </row>
     <row r="94">
@@ -2682,25 +2664,25 @@
         <v>26</v>
       </c>
       <c r="B94" t="s" s="1">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E94" t="s" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G94" t="n" s="1">
-        <v>21486.12</v>
+        <v>17.46</v>
       </c>
       <c r="H94" t="n" s="1">
-        <v>-21486.12</v>
+        <v>-17.46</v>
       </c>
     </row>
     <row r="95">
@@ -2708,13 +2690,13 @@
         <v>26</v>
       </c>
       <c r="B95" t="s" s="1">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C95" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D95" t="s" s="1">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E95" t="s" s="1">
         <v>38</v>
@@ -2723,10 +2705,10 @@
         <v>0.0</v>
       </c>
       <c r="G95" t="n" s="1">
-        <v>2227.5</v>
+        <v>6.81</v>
       </c>
       <c r="H95" t="n" s="1">
-        <v>-2227.5</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="96">
@@ -2734,25 +2716,25 @@
         <v>26</v>
       </c>
       <c r="B96" t="s" s="1">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C96" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D96" t="s" s="1">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E96" t="s" s="1">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G96" t="n" s="1">
-        <v>1751.0</v>
+        <v>6.81</v>
       </c>
       <c r="H96" t="n" s="1">
-        <v>-1751.0</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="97">
@@ -2760,25 +2742,25 @@
         <v>26</v>
       </c>
       <c r="B97" t="s" s="1">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C97" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D97" t="s" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E97" t="s" s="1">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F97" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G97" t="n" s="1">
-        <v>1718.89</v>
+        <v>3.41</v>
       </c>
       <c r="H97" t="n" s="1">
-        <v>-1718.89</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="98">
@@ -2786,25 +2768,25 @@
         <v>26</v>
       </c>
       <c r="B98" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C98" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D98" t="s" s="1">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E98" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F98" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G98" t="n" s="1">
-        <v>15.2</v>
+        <v>152.0</v>
       </c>
       <c r="H98" t="n" s="1">
-        <v>-15.2</v>
+        <v>-152.0</v>
       </c>
     </row>
     <row r="99">
@@ -2812,25 +2794,25 @@
         <v>26</v>
       </c>
       <c r="B99" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C99" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D99" t="s" s="1">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E99" t="s" s="1">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="F99" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G99" t="n" s="1">
-        <v>30.4</v>
+        <v>106.4</v>
       </c>
       <c r="H99" t="n" s="1">
-        <v>-30.4</v>
+        <v>-106.4</v>
       </c>
     </row>
     <row r="100">
@@ -2838,25 +2820,25 @@
         <v>26</v>
       </c>
       <c r="B100" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C100" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D100" t="s" s="1">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E100" t="s" s="1">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F100" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G100" t="n" s="1">
-        <v>30.4</v>
+        <v>45.6</v>
       </c>
       <c r="H100" t="n" s="1">
-        <v>-30.4</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="101">
@@ -2864,25 +2846,25 @@
         <v>26</v>
       </c>
       <c r="B101" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C101" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D101" t="s" s="1">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E101" t="s" s="1">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F101" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G101" t="n" s="1">
-        <v>8.73</v>
+        <v>61.11</v>
       </c>
       <c r="H101" t="n" s="1">
-        <v>-8.73</v>
+        <v>-61.11</v>
       </c>
     </row>
     <row r="102">
@@ -2890,25 +2872,25 @@
         <v>26</v>
       </c>
       <c r="B102" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C102" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D102" t="s" s="1">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E102" t="s" s="1">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F102" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G102" t="n" s="1">
-        <v>17.46</v>
+        <v>26.19</v>
       </c>
       <c r="H102" t="n" s="1">
-        <v>-17.46</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="103">
@@ -2916,25 +2898,25 @@
         <v>26</v>
       </c>
       <c r="B103" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C103" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D103" t="s" s="1">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E103" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F103" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G103" t="n" s="1">
-        <v>17.46</v>
+        <v>87.3</v>
       </c>
       <c r="H103" t="n" s="1">
-        <v>-17.46</v>
+        <v>-87.3</v>
       </c>
     </row>
     <row r="104">
@@ -2942,25 +2924,25 @@
         <v>26</v>
       </c>
       <c r="B104" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C104" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D104" t="s" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E104" t="s" s="1">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F104" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G104" t="n" s="1">
-        <v>6.81</v>
+        <v>23.84</v>
       </c>
       <c r="H104" t="n" s="1">
-        <v>-6.81</v>
+        <v>-23.84</v>
       </c>
     </row>
     <row r="105">
@@ -2968,25 +2950,25 @@
         <v>26</v>
       </c>
       <c r="B105" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C105" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D105" t="s" s="1">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E105" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F105" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G105" t="n" s="1">
-        <v>6.81</v>
+        <v>34.05</v>
       </c>
       <c r="H105" t="n" s="1">
-        <v>-6.81</v>
+        <v>-34.05</v>
       </c>
     </row>
     <row r="106">
@@ -2994,25 +2976,25 @@
         <v>26</v>
       </c>
       <c r="B106" t="s" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C106" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D106" t="s" s="1">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E106" t="s" s="1">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F106" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G106" t="n" s="1">
-        <v>3.41</v>
+        <v>135.18</v>
       </c>
       <c r="H106" t="n" s="1">
-        <v>-3.41</v>
+        <v>-135.18</v>
       </c>
     </row>
     <row r="107">
@@ -3020,25 +3002,25 @@
         <v>26</v>
       </c>
       <c r="B107" t="s" s="1">
+        <v>115</v>
+      </c>
+      <c r="C107" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D107" t="s" s="1">
         <v>118</v>
       </c>
-      <c r="C107" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D107" t="s" s="1">
-        <v>119</v>
-      </c>
       <c r="E107" t="s" s="1">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F107" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G107" t="n" s="1">
-        <v>152.0</v>
+        <v>57.93</v>
       </c>
       <c r="H107" t="n" s="1">
-        <v>-152.0</v>
+        <v>-57.93</v>
       </c>
     </row>
     <row r="108">
@@ -3046,25 +3028,25 @@
         <v>26</v>
       </c>
       <c r="B108" t="s" s="1">
+        <v>115</v>
+      </c>
+      <c r="C108" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D108" t="s" s="1">
         <v>118</v>
       </c>
-      <c r="C108" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D108" t="s" s="1">
-        <v>113</v>
-      </c>
       <c r="E108" t="s" s="1">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="F108" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G108" t="n" s="1">
-        <v>106.4</v>
+        <v>19.31</v>
       </c>
       <c r="H108" t="n" s="1">
-        <v>-106.4</v>
+        <v>-19.31</v>
       </c>
     </row>
     <row r="109">
@@ -3072,25 +3054,25 @@
         <v>26</v>
       </c>
       <c r="B109" t="s" s="1">
+        <v>115</v>
+      </c>
+      <c r="C109" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D109" t="s" s="1">
         <v>118</v>
       </c>
-      <c r="C109" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D109" t="s" s="1">
-        <v>113</v>
-      </c>
       <c r="E109" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F109" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G109" t="n" s="1">
-        <v>45.6</v>
+        <v>193.12</v>
       </c>
       <c r="H109" t="n" s="1">
-        <v>-45.6</v>
+        <v>-193.12</v>
       </c>
     </row>
     <row r="110">
@@ -3098,25 +3080,25 @@
         <v>26</v>
       </c>
       <c r="B110" t="s" s="1">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C110" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D110" t="s" s="1">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E110" t="s" s="1">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F110" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G110" t="n" s="1">
-        <v>61.11</v>
+        <v>38.62</v>
       </c>
       <c r="H110" t="n" s="1">
-        <v>-61.11</v>
+        <v>-38.62</v>
       </c>
     </row>
     <row r="111">
@@ -3124,25 +3106,25 @@
         <v>26</v>
       </c>
       <c r="B111" t="s" s="1">
+        <v>115</v>
+      </c>
+      <c r="C111" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D111" t="s" s="1">
         <v>118</v>
       </c>
-      <c r="C111" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D111" t="s" s="1">
-        <v>114</v>
-      </c>
       <c r="E111" t="s" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F111" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G111" t="n" s="1">
-        <v>26.19</v>
+        <v>38.62</v>
       </c>
       <c r="H111" t="n" s="1">
-        <v>-26.19</v>
+        <v>-38.62</v>
       </c>
     </row>
     <row r="112">
@@ -3150,25 +3132,25 @@
         <v>26</v>
       </c>
       <c r="B112" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C112" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D112" t="s" s="1">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E112" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F112" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G112" t="n" s="1">
-        <v>87.3</v>
+        <v>155.01</v>
       </c>
       <c r="H112" t="n" s="1">
-        <v>-87.3</v>
+        <v>-155.01</v>
       </c>
     </row>
     <row r="113">
@@ -3176,25 +3158,25 @@
         <v>26</v>
       </c>
       <c r="B113" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C113" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D113" t="s" s="1">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E113" t="s" s="1">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F113" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G113" t="n" s="1">
-        <v>23.84</v>
+        <v>15066.07</v>
       </c>
       <c r="H113" t="n" s="1">
-        <v>-23.84</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="114">
@@ -3202,25 +3184,25 @@
         <v>26</v>
       </c>
       <c r="B114" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C114" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D114" t="s" s="1">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E114" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F114" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G114" t="n" s="1">
-        <v>34.05</v>
+        <v>1205.61</v>
       </c>
       <c r="H114" t="n" s="1">
-        <v>-34.05</v>
+        <v>-1205.61</v>
       </c>
     </row>
     <row r="115">
@@ -3228,25 +3210,25 @@
         <v>26</v>
       </c>
       <c r="B115" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C115" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D115" t="s" s="1">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E115" t="s" s="1">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="F115" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G115" t="n" s="1">
-        <v>135.18</v>
+        <v>1227.73</v>
       </c>
       <c r="H115" t="n" s="1">
-        <v>-135.18</v>
+        <v>-1227.73</v>
       </c>
     </row>
     <row r="116">
@@ -3254,25 +3236,25 @@
         <v>26</v>
       </c>
       <c r="B116" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D116" t="s" s="1">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E116" t="s" s="1">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F116" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G116" t="n" s="1">
-        <v>57.93</v>
+        <v>240.77</v>
       </c>
       <c r="H116" t="n" s="1">
-        <v>-57.93</v>
+        <v>-240.77</v>
       </c>
     </row>
     <row r="117">
@@ -3280,25 +3262,25 @@
         <v>26</v>
       </c>
       <c r="B117" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C117" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D117" t="s" s="1">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E117" t="s" s="1">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="F117" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G117" t="n" s="1">
-        <v>19.31</v>
+        <v>245.34</v>
       </c>
       <c r="H117" t="n" s="1">
-        <v>-19.31</v>
+        <v>-245.34</v>
       </c>
     </row>
     <row r="118">
@@ -3306,25 +3288,25 @@
         <v>26</v>
       </c>
       <c r="B118" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C118" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D118" t="s" s="1">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E118" t="s" s="1">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F118" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G118" t="n" s="1">
-        <v>193.12</v>
+        <v>376.9</v>
       </c>
       <c r="H118" t="n" s="1">
-        <v>-193.12</v>
+        <v>-376.9</v>
       </c>
     </row>
     <row r="119">
@@ -3332,25 +3314,25 @@
         <v>26</v>
       </c>
       <c r="B119" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C119" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D119" t="s" s="1">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E119" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F119" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G119" t="n" s="1">
-        <v>38.62</v>
+        <v>423.0</v>
       </c>
       <c r="H119" t="n" s="1">
-        <v>-38.62</v>
+        <v>-423.0</v>
       </c>
     </row>
     <row r="120">
@@ -3358,13 +3340,13 @@
         <v>26</v>
       </c>
       <c r="B120" t="s" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C120" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D120" t="s" s="1">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E120" t="s" s="1">
         <v>50</v>
@@ -3373,10 +3355,10 @@
         <v>0.0</v>
       </c>
       <c r="G120" t="n" s="1">
-        <v>38.62</v>
+        <v>846.01</v>
       </c>
       <c r="H120" t="n" s="1">
-        <v>-38.62</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="121">
@@ -3384,25 +3366,25 @@
         <v>26</v>
       </c>
       <c r="B121" t="s" s="1">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C121" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s" s="1">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E121" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F121" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G121" t="n" s="1">
-        <v>155.01</v>
+        <v>846.01</v>
       </c>
       <c r="H121" t="n" s="1">
-        <v>-155.01</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="122">
@@ -3410,13 +3392,13 @@
         <v>26</v>
       </c>
       <c r="B122" t="s" s="1">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C122" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D122" t="s" s="1">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E122" t="s" s="1">
         <v>38</v>
@@ -3425,10 +3407,10 @@
         <v>0.0</v>
       </c>
       <c r="G122" t="n" s="1">
-        <v>1435.5</v>
+        <v>96.06</v>
       </c>
       <c r="H122" t="n" s="1">
-        <v>-1435.5</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="123">
@@ -3436,25 +3418,25 @@
         <v>26</v>
       </c>
       <c r="B123" t="s" s="1">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C123" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D123" t="s" s="1">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>15066.07</v>
+        <v>48.03</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-48.03</v>
       </c>
     </row>
     <row r="124">
@@ -3462,25 +3444,25 @@
         <v>26</v>
       </c>
       <c r="B124" t="s" s="1">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C124" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D124" t="s" s="1">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>297.0</v>
+        <v>96.06</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-297.0</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="125">
@@ -3488,25 +3470,25 @@
         <v>26</v>
       </c>
       <c r="B125" t="s" s="1">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C125" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E125" t="s" s="1">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F125" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G125" t="n" s="1">
-        <v>1205.61</v>
+        <v>2961.03</v>
       </c>
       <c r="H125" t="n" s="1">
-        <v>-1205.61</v>
+        <v>-2961.03</v>
       </c>
     </row>
     <row r="126">
@@ -3514,25 +3496,25 @@
         <v>26</v>
       </c>
       <c r="B126" t="s" s="1">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C126" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D126" t="s" s="1">
         <v>128</v>
       </c>
       <c r="E126" t="s" s="1">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="F126" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G126" t="n" s="1">
-        <v>1227.73</v>
+        <v>1269.01</v>
       </c>
       <c r="H126" t="n" s="1">
-        <v>-1227.73</v>
+        <v>-1269.01</v>
       </c>
     </row>
     <row r="127">
@@ -3540,25 +3522,25 @@
         <v>26</v>
       </c>
       <c r="B127" t="s" s="1">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C127" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E127" t="s" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F127" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G127" t="n" s="1">
-        <v>245.34</v>
+        <v>4230.04</v>
       </c>
       <c r="H127" t="n" s="1">
-        <v>-245.34</v>
+        <v>-4230.04</v>
       </c>
     </row>
     <row r="128">
@@ -3566,25 +3548,25 @@
         <v>26</v>
       </c>
       <c r="B128" t="s" s="1">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C128" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D128" t="s" s="1">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E128" t="s" s="1">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="F128" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G128" t="n" s="1">
-        <v>240.77</v>
+        <v>336.22</v>
       </c>
       <c r="H128" t="n" s="1">
-        <v>-240.77</v>
+        <v>-336.22</v>
       </c>
     </row>
     <row r="129">
@@ -3592,25 +3574,25 @@
         <v>26</v>
       </c>
       <c r="B129" t="s" s="1">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C129" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D129" t="s" s="1">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>376.9</v>
+        <v>144.09</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-376.9</v>
+        <v>-144.09</v>
       </c>
     </row>
     <row r="130">
@@ -3618,25 +3600,25 @@
         <v>26</v>
       </c>
       <c r="B130" t="s" s="1">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C130" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D130" t="s" s="1">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F130" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>423.0</v>
+        <v>480.31</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>-423.0</v>
+        <v>-480.31</v>
       </c>
     </row>
     <row r="131">
@@ -3644,25 +3626,25 @@
         <v>26</v>
       </c>
       <c r="B131" t="s" s="1">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C131" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D131" t="s" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E131" t="s" s="1">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F131" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G131" t="n" s="1">
-        <v>846.01</v>
+        <v>1801.15</v>
       </c>
       <c r="H131" t="n" s="1">
-        <v>-846.01</v>
+        <v>-1801.15</v>
       </c>
     </row>
     <row r="132">
@@ -3670,25 +3652,25 @@
         <v>26</v>
       </c>
       <c r="B132" t="s" s="1">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C132" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D132" t="s" s="1">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G132" t="n" s="1">
-        <v>846.01</v>
+        <v>5165.75</v>
       </c>
       <c r="H132" t="n" s="1">
-        <v>-846.01</v>
+        <v>-5165.75</v>
       </c>
     </row>
     <row r="133">
@@ -3696,25 +3678,25 @@
         <v>26</v>
       </c>
       <c r="B133" t="s" s="1">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C133" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D133" t="s" s="1">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E133" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F133" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G133" t="n" s="1">
-        <v>48.03</v>
+        <v>527.98</v>
       </c>
       <c r="H133" t="n" s="1">
-        <v>-48.03</v>
+        <v>-527.98</v>
       </c>
     </row>
     <row r="134">
@@ -3722,7 +3704,7 @@
         <v>26</v>
       </c>
       <c r="B134" t="s" s="1">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C134" t="s" s="1">
         <v>36</v>
@@ -3731,16 +3713,16 @@
         <v>134</v>
       </c>
       <c r="E134" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F134" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G134" t="n" s="1">
-        <v>96.06</v>
+        <v>263.99</v>
       </c>
       <c r="H134" t="n" s="1">
-        <v>-96.06</v>
+        <v>-263.99</v>
       </c>
     </row>
     <row r="135">
@@ -3748,13 +3730,13 @@
         <v>26</v>
       </c>
       <c r="B135" t="s" s="1">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C135" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D135" t="s" s="1">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E135" t="s" s="1">
         <v>50</v>
@@ -3763,10 +3745,10 @@
         <v>0.0</v>
       </c>
       <c r="G135" t="n" s="1">
-        <v>96.06</v>
+        <v>527.98</v>
       </c>
       <c r="H135" t="n" s="1">
-        <v>-96.06</v>
+        <v>-527.98</v>
       </c>
     </row>
     <row r="136">
@@ -3774,25 +3756,25 @@
         <v>26</v>
       </c>
       <c r="B136" t="s" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C136" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D136" t="s" s="1">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="E136" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F136" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G136" t="n" s="1">
-        <v>100.0</v>
+        <v>113.21</v>
       </c>
       <c r="H136" t="n" s="1">
-        <v>-100.0</v>
+        <v>-113.21</v>
       </c>
     </row>
     <row r="137">
@@ -3800,25 +3782,25 @@
         <v>26</v>
       </c>
       <c r="B137" t="s" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C137" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D137" t="s" s="1">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E137" t="s" s="1">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F137" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G137" t="n" s="1">
-        <v>1269.01</v>
+        <v>191.08</v>
       </c>
       <c r="H137" t="n" s="1">
-        <v>-1269.01</v>
+        <v>-191.08</v>
       </c>
     </row>
     <row r="138">
@@ -3826,25 +3808,25 @@
         <v>26</v>
       </c>
       <c r="B138" t="s" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C138" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D138" t="s" s="1">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E138" t="s" s="1">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="F138" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G138" t="n" s="1">
-        <v>2961.03</v>
+        <v>9.23</v>
       </c>
       <c r="H138" t="n" s="1">
-        <v>-2961.03</v>
+        <v>-9.23</v>
       </c>
     </row>
     <row r="139">
@@ -3852,25 +3834,25 @@
         <v>26</v>
       </c>
       <c r="B139" t="s" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C139" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D139" t="s" s="1">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E139" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F139" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G139" t="n" s="1">
-        <v>4230.04</v>
+        <v>9.05</v>
       </c>
       <c r="H139" t="n" s="1">
-        <v>-4230.04</v>
+        <v>-9.05</v>
       </c>
     </row>
     <row r="140">
@@ -3878,25 +3860,25 @@
         <v>26</v>
       </c>
       <c r="B140" t="s" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C140" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D140" t="s" s="1">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E140" t="s" s="1">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="F140" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G140" t="n" s="1">
-        <v>336.22</v>
+        <v>15.3</v>
       </c>
       <c r="H140" t="n" s="1">
-        <v>-336.22</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="141">
@@ -3904,25 +3886,25 @@
         <v>26</v>
       </c>
       <c r="B141" t="s" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C141" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D141" t="s" s="1">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E141" t="s" s="1">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F141" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G141" t="n" s="1">
-        <v>144.09</v>
+        <v>15.56</v>
       </c>
       <c r="H141" t="n" s="1">
-        <v>-144.09</v>
+        <v>-15.56</v>
       </c>
     </row>
     <row r="142">
@@ -3930,25 +3912,25 @@
         <v>26</v>
       </c>
       <c r="B142" t="s" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C142" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D142" t="s" s="1">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E142" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F142" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G142" t="n" s="1">
-        <v>480.31</v>
+        <v>1847.92</v>
       </c>
       <c r="H142" t="n" s="1">
-        <v>-480.31</v>
+        <v>-1847.92</v>
       </c>
     </row>
     <row r="143">
@@ -3959,22 +3941,22 @@
         <v>137</v>
       </c>
       <c r="C143" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s" s="1">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E143" t="s" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F143" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G143" t="n" s="1">
-        <v>1801.15</v>
+        <v>2639.89</v>
       </c>
       <c r="H143" t="n" s="1">
-        <v>-1801.15</v>
+        <v>-2639.89</v>
       </c>
     </row>
     <row r="144">
@@ -3982,25 +3964,25 @@
         <v>26</v>
       </c>
       <c r="B144" t="s" s="1">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C144" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D144" t="s" s="1">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E144" t="s" s="1">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="F144" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G144" t="n" s="1">
-        <v>5165.75</v>
+        <v>180.0</v>
       </c>
       <c r="H144" t="n" s="1">
-        <v>-5165.75</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="145">
@@ -4008,25 +3990,25 @@
         <v>26</v>
       </c>
       <c r="B145" t="s" s="1">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C145" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D145" t="s" s="1">
-        <v>140</v>
+        <v>41</v>
       </c>
       <c r="E145" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F145" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G145" t="n" s="1">
-        <v>527.98</v>
+        <v>9216.24</v>
       </c>
       <c r="H145" t="n" s="1">
-        <v>-527.98</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="146">
@@ -4034,25 +4016,25 @@
         <v>26</v>
       </c>
       <c r="B146" t="s" s="1">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C146" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D146" t="s" s="1">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="E146" t="s" s="1">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F146" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G146" t="n" s="1">
-        <v>263.99</v>
+        <v>891.0</v>
       </c>
       <c r="H146" t="n" s="1">
-        <v>-263.99</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="147">
@@ -4060,25 +4042,25 @@
         <v>26</v>
       </c>
       <c r="B147" t="s" s="1">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C147" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s" s="1">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="E147" t="s" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F147" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G147" t="n" s="1">
-        <v>527.98</v>
+        <v>737.28</v>
       </c>
       <c r="H147" t="n" s="1">
-        <v>-527.98</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="148">
@@ -4086,25 +4068,25 @@
         <v>26</v>
       </c>
       <c r="B148" t="s" s="1">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C148" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D148" t="s" s="1">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E148" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F148" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G148" t="n" s="1">
-        <v>113.21</v>
+        <v>750.99</v>
       </c>
       <c r="H148" t="n" s="1">
-        <v>-113.21</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="149">
@@ -4112,25 +4094,25 @@
         <v>26</v>
       </c>
       <c r="B149" t="s" s="1">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C149" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D149" t="s" s="1">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="E149" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F149" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G149" t="n" s="1">
-        <v>191.08</v>
+        <v>1544.4</v>
       </c>
       <c r="H149" t="n" s="1">
-        <v>-191.08</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="150">
@@ -4138,25 +4120,25 @@
         <v>26</v>
       </c>
       <c r="B150" t="s" s="1">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C150" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D150" t="s" s="1">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E150" t="s" s="1">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="F150" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G150" t="n" s="1">
-        <v>9.23</v>
+        <v>1925.0</v>
       </c>
       <c r="H150" t="n" s="1">
-        <v>-9.23</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="151">
@@ -4164,25 +4146,25 @@
         <v>26</v>
       </c>
       <c r="B151" t="s" s="1">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C151" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D151" t="s" s="1">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="E151" t="s" s="1">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F151" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G151" t="n" s="1">
-        <v>9.05</v>
+        <v>180.0</v>
       </c>
       <c r="H151" t="n" s="1">
-        <v>-9.05</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="152">
@@ -4190,25 +4172,25 @@
         <v>26</v>
       </c>
       <c r="B152" t="s" s="1">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C152" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D152" t="s" s="1">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="E152" t="s" s="1">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F152" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G152" t="n" s="1">
-        <v>15.3</v>
+        <v>180.0</v>
       </c>
       <c r="H152" t="n" s="1">
-        <v>-15.3</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="153">
@@ -4216,25 +4198,25 @@
         <v>26</v>
       </c>
       <c r="B153" t="s" s="1">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C153" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D153" t="s" s="1">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E153" t="s" s="1">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="F153" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G153" t="n" s="1">
-        <v>15.56</v>
+        <v>1201.89</v>
       </c>
       <c r="H153" t="n" s="1">
-        <v>-15.56</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="154">
@@ -4242,25 +4224,25 @@
         <v>26</v>
       </c>
       <c r="B154" t="s" s="1">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C154" t="s" s="1">
         <v>43</v>
       </c>
       <c r="D154" t="s" s="1">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="E154" t="s" s="1">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="F154" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G154" t="n" s="1">
-        <v>15000.0</v>
+        <v>180.0</v>
       </c>
       <c r="H154" t="n" s="1">
-        <v>-15000.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="155">
@@ -4268,25 +4250,25 @@
         <v>26</v>
       </c>
       <c r="B155" t="s" s="1">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C155" t="s" s="1">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D155" t="s" s="1">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E155" t="s" s="1">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F155" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G155" t="n" s="1">
-        <v>2639.89</v>
+        <v>180.0</v>
       </c>
       <c r="H155" t="n" s="1">
-        <v>-2639.89</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="156">
@@ -4294,25 +4276,25 @@
         <v>26</v>
       </c>
       <c r="B156" t="s" s="1">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C156" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D156" t="s" s="1">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="E156" t="s" s="1">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F156" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G156" t="n" s="1">
-        <v>1847.92</v>
+        <v>25504.78</v>
       </c>
       <c r="H156" t="n" s="1">
-        <v>-1847.92</v>
+        <v>-25504.78</v>
       </c>
     </row>
     <row r="157">
@@ -4320,25 +4302,25 @@
         <v>26</v>
       </c>
       <c r="B157" t="s" s="1">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C157" t="s" s="1">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="D157" t="s" s="1">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="E157" t="s" s="1">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="F157" t="n" s="1">
-        <v>3500.0</v>
+        <v>0.0</v>
       </c>
       <c r="G157" t="n" s="1">
-        <v>0.0</v>
+        <v>2277.0</v>
       </c>
       <c r="H157" t="n" s="1">
-        <v>3500.0</v>
+        <v>-2277.0</v>
       </c>
     </row>
     <row r="158">
@@ -4346,25 +4328,25 @@
         <v>26</v>
       </c>
       <c r="B158" t="s" s="1">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C158" t="s" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D158" t="s" s="1">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="E158" t="s" s="1">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="F158" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G158" t="n" s="1">
-        <v>180.0</v>
+        <v>2078.64</v>
       </c>
       <c r="H158" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2078.64</v>
       </c>
     </row>
     <row r="159">
@@ -4372,25 +4354,25 @@
         <v>26</v>
       </c>
       <c r="B159" t="s" s="1">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C159" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D159" t="s" s="1">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E159" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F159" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G159" t="n" s="1">
-        <v>9216.24</v>
+        <v>2040.52</v>
       </c>
       <c r="H159" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-2040.52</v>
       </c>
     </row>
     <row r="160">
@@ -4398,25 +4380,25 @@
         <v>26</v>
       </c>
       <c r="B160" t="s" s="1">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C160" t="s" s="1">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D160" t="s" s="1">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="E160" t="s" s="1">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F160" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G160" t="n" s="1">
-        <v>891.0</v>
+        <v>180.0</v>
       </c>
       <c r="H160" t="n" s="1">
-        <v>-891.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="161">
@@ -4424,25 +4406,25 @@
         <v>26</v>
       </c>
       <c r="B161" t="s" s="1">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C161" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D161" t="s" s="1">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="E161" t="s" s="1">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F161" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G161" t="n" s="1">
-        <v>737.28</v>
+        <v>180.0</v>
       </c>
       <c r="H161" t="n" s="1">
-        <v>-737.28</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="162">
@@ -4450,25 +4432,25 @@
         <v>26</v>
       </c>
       <c r="B162" t="s" s="1">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C162" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D162" t="s" s="1">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="E162" t="s" s="1">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="F162" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G162" t="n" s="1">
-        <v>750.99</v>
+        <v>1000.0</v>
       </c>
       <c r="H162" t="n" s="1">
-        <v>-750.99</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="163">
@@ -4476,413 +4458,49 @@
         <v>26</v>
       </c>
       <c r="B163" t="s" s="1">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C163" t="s" s="1">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D163" t="s" s="1">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E163" t="s" s="1">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="F163" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G163" t="n" s="1">
-        <v>1544.4</v>
+        <v>3750.0</v>
       </c>
       <c r="H163" t="n" s="1">
-        <v>-1544.4</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B164" t="s" s="1">
-        <v>156</v>
-      </c>
-      <c r="C164" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D164" t="s" s="1">
-        <v>157</v>
-      </c>
-      <c r="E164" t="s" s="1">
-        <v>158</v>
-      </c>
-      <c r="F164" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G164" t="n" s="1">
-        <v>1925.0</v>
-      </c>
-      <c r="H164" t="n" s="1">
-        <v>-1925.0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B165" t="s" s="1">
-        <v>156</v>
-      </c>
-      <c r="C165" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D165" t="s" s="1">
-        <v>84</v>
-      </c>
-      <c r="E165" t="s" s="1">
-        <v>65</v>
-      </c>
-      <c r="F165" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G165" t="n" s="1">
-        <v>180.0</v>
-      </c>
-      <c r="H165" t="n" s="1">
-        <v>-180.0</v>
+        <v>-3750.0</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B166" t="s" s="1">
-        <v>156</v>
-      </c>
-      <c r="C166" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D166" t="s" s="1">
-        <v>85</v>
-      </c>
-      <c r="E166" t="s" s="1">
-        <v>65</v>
-      </c>
-      <c r="F166" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G166" t="n" s="1">
-        <v>180.0</v>
-      </c>
-      <c r="H166" t="n" s="1">
-        <v>-180.0</v>
+      <c r="A166" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B167" t="s" s="1">
-        <v>159</v>
-      </c>
-      <c r="C167" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D167" t="s" s="1">
-        <v>160</v>
-      </c>
-      <c r="E167" t="s" s="1">
-        <v>161</v>
-      </c>
-      <c r="F167" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G167" t="n" s="1">
-        <v>1201.89</v>
-      </c>
-      <c r="H167" t="n" s="1">
-        <v>-1201.89</v>
+      <c r="A167" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B168" t="s" s="1">
-        <v>159</v>
-      </c>
-      <c r="C168" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D168" t="s" s="1">
-        <v>95</v>
-      </c>
-      <c r="E168" t="s" s="1">
-        <v>65</v>
-      </c>
-      <c r="F168" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G168" t="n" s="1">
-        <v>180.0</v>
-      </c>
-      <c r="H168" t="n" s="1">
-        <v>-180.0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B169" t="s" s="1">
-        <v>159</v>
-      </c>
-      <c r="C169" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D169" t="s" s="1">
-        <v>96</v>
-      </c>
-      <c r="E169" t="s" s="1">
-        <v>65</v>
-      </c>
-      <c r="F169" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G169" t="n" s="1">
-        <v>180.0</v>
-      </c>
-      <c r="H169" t="n" s="1">
-        <v>-180.0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B170" t="s" s="1">
-        <v>162</v>
-      </c>
-      <c r="C170" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D170" t="s" s="1">
-        <v>48</v>
-      </c>
-      <c r="E170" t="s" s="1">
-        <v>30</v>
-      </c>
-      <c r="F170" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G170" t="n" s="1">
-        <v>25504.78</v>
-      </c>
-      <c r="H170" t="n" s="1">
-        <v>-25504.78</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B171" t="s" s="1">
-        <v>162</v>
-      </c>
-      <c r="C171" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D171" t="s" s="1">
-        <v>48</v>
-      </c>
-      <c r="E171" t="s" s="1">
-        <v>38</v>
-      </c>
-      <c r="F171" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G171" t="n" s="1">
-        <v>2277.0</v>
-      </c>
-      <c r="H171" t="n" s="1">
-        <v>-2277.0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B172" t="s" s="1">
-        <v>162</v>
-      </c>
-      <c r="C172" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D172" t="s" s="1">
-        <v>163</v>
-      </c>
-      <c r="E172" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="F172" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G172" t="n" s="1">
-        <v>2078.64</v>
-      </c>
-      <c r="H172" t="n" s="1">
-        <v>-2078.64</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B173" t="s" s="1">
-        <v>162</v>
-      </c>
-      <c r="C173" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D173" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="E173" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="F173" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G173" t="n" s="1">
-        <v>2040.52</v>
-      </c>
-      <c r="H173" t="n" s="1">
-        <v>-2040.52</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B174" t="s" s="1">
-        <v>162</v>
-      </c>
-      <c r="C174" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D174" t="s" s="1">
-        <v>110</v>
-      </c>
-      <c r="E174" t="s" s="1">
-        <v>65</v>
-      </c>
-      <c r="F174" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G174" t="n" s="1">
-        <v>180.0</v>
-      </c>
-      <c r="H174" t="n" s="1">
-        <v>-180.0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B175" t="s" s="1">
-        <v>164</v>
-      </c>
-      <c r="C175" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D175" t="s" s="1">
-        <v>126</v>
-      </c>
-      <c r="E175" t="s" s="1">
-        <v>65</v>
-      </c>
-      <c r="F175" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G175" t="n" s="1">
-        <v>180.0</v>
-      </c>
-      <c r="H175" t="n" s="1">
-        <v>-180.0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B176" t="s" s="1">
-        <v>165</v>
-      </c>
-      <c r="C176" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D176" t="s" s="1">
-        <v>44</v>
-      </c>
-      <c r="E176" t="s" s="1">
+      <c r="A168" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F176" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G176" t="n" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="H176" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B177" t="s" s="1">
-        <v>165</v>
-      </c>
-      <c r="C177" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D177" t="s" s="1">
-        <v>47</v>
-      </c>
-      <c r="E177" t="s" s="1">
+      <c r="B168" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="F177" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G177" t="n" s="1">
-        <v>3750.0</v>
-      </c>
-      <c r="H177" t="n" s="1">
-        <v>-3750.0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="168">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -111,18 +111,18 @@
     <t>PCP-Previsão do Contas a Pagar</t>
   </si>
   <si>
+    <t>1629 - 2</t>
+  </si>
+  <si>
+    <t>ENTREGADORA NOVO RUMO LTDA ME</t>
+  </si>
+  <si>
     <t>1629 - 3</t>
   </si>
   <si>
     <t>RODAG TRANSPORTES LTDA*</t>
   </si>
   <si>
-    <t>1629 - 2</t>
-  </si>
-  <si>
-    <t>ENTREGADORA NOVO RUMO LTDA ME</t>
-  </si>
-  <si>
     <t>PPC-Previsão de Pagamento de Comissão</t>
   </si>
   <si>
@@ -138,267 +138,267 @@
     <t>05/10/2026</t>
   </si>
   <si>
+    <t>PFP-Previsões Financeiras a Pagar</t>
+  </si>
+  <si>
+    <t>1 - 8</t>
+  </si>
+  <si>
+    <t>Hostgator</t>
+  </si>
+  <si>
+    <t>1 - 9</t>
+  </si>
+  <si>
+    <t>100901 - 2</t>
+  </si>
+  <si>
+    <t>100901 - 1</t>
+  </si>
+  <si>
+    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
+  </si>
+  <si>
+    <t>TERESINHA ELVIRA MAXIMINO DE MENEZES</t>
+  </si>
+  <si>
     <t>102301 - 1</t>
   </si>
   <si>
+    <t>102301 - 2</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>ROSANGELA PACHECO</t>
+  </si>
+  <si>
+    <t>FELIPE DOMINGOS BARBOSA</t>
+  </si>
+  <si>
+    <t>bianca rodrigues</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>102901 - 1</t>
+  </si>
+  <si>
+    <t>102901 - 2</t>
+  </si>
+  <si>
+    <t>103501 - 2</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>103501 - 1</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>56102 - 1</t>
+  </si>
+  <si>
+    <t>L E A Medicoes Tecnicas LTDA</t>
+  </si>
+  <si>
+    <t>Carina Pereira</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>96601 - 1</t>
+  </si>
+  <si>
+    <t>101401 - 1</t>
+  </si>
+  <si>
+    <t>DMP-Duplicata Manual do Contas a pagar</t>
+  </si>
+  <si>
+    <t>92401 - 0</t>
+  </si>
+  <si>
+    <t>Antonio Jesus</t>
+  </si>
+  <si>
+    <t>92801 - 0</t>
+  </si>
+  <si>
+    <t>96601 - 3</t>
+  </si>
+  <si>
+    <t>96601 - 2</t>
+  </si>
+  <si>
+    <t>101401 - 3</t>
+  </si>
+  <si>
+    <t>101401 - 2</t>
+  </si>
+  <si>
+    <t>10/10/2026</t>
+  </si>
+  <si>
+    <t>100501 - 3</t>
+  </si>
+  <si>
+    <t>100501 - 2</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>49501 - 2</t>
+  </si>
+  <si>
+    <t>100301 - 1</t>
+  </si>
+  <si>
+    <t>102101 - 1</t>
+  </si>
+  <si>
+    <t>100301 - 3</t>
+  </si>
+  <si>
+    <t>100301 - 2</t>
+  </si>
+  <si>
+    <t>102101 - 2</t>
+  </si>
+  <si>
+    <t>102101 - 3</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>1631 - 1</t>
+  </si>
+  <si>
+    <t>1632 - 1</t>
+  </si>
+  <si>
+    <t>1633 - 1</t>
+  </si>
+  <si>
+    <t>1634 - 1</t>
+  </si>
+  <si>
+    <t>101201 - 1</t>
+  </si>
+  <si>
+    <t>1631 - 2</t>
+  </si>
+  <si>
+    <t>1631 - 3</t>
+  </si>
+  <si>
+    <t>1632 - 3</t>
+  </si>
+  <si>
+    <t>1632 - 2</t>
+  </si>
+  <si>
+    <t>1633 - 2</t>
+  </si>
+  <si>
+    <t>1633 - 3</t>
+  </si>
+  <si>
+    <t>1634 - 3</t>
+  </si>
+  <si>
+    <t>1634 - 2</t>
+  </si>
+  <si>
+    <t>101201 - 3</t>
+  </si>
+  <si>
+    <t>101201 - 2</t>
+  </si>
+  <si>
+    <t>101801 - 2</t>
+  </si>
+  <si>
+    <t>101801 - 3</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>101101 - 1</t>
+  </si>
+  <si>
+    <t>101101 - 3</t>
+  </si>
+  <si>
+    <t>101101 - 2</t>
+  </si>
+  <si>
+    <t>103801 - 1</t>
+  </si>
+  <si>
+    <t>104701 - 1</t>
+  </si>
+  <si>
+    <t>104701 - 2</t>
+  </si>
+  <si>
+    <t>104801 - 2</t>
+  </si>
+  <si>
+    <t>104801 - 1</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>103801 - 2</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>105001 - 1</t>
+  </si>
+  <si>
+    <t>105001 - 2</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>92001 - 2</t>
+  </si>
+  <si>
+    <t>102401 - 1</t>
+  </si>
+  <si>
+    <t>102401 - 2</t>
+  </si>
+  <si>
+    <t>102401 - 3</t>
+  </si>
+  <si>
+    <t>102501 - 2</t>
+  </si>
+  <si>
+    <t>102501 - 3</t>
+  </si>
+  <si>
+    <t>105301 - 1</t>
+  </si>
+  <si>
     <t>Italíneacredi</t>
   </si>
   <si>
-    <t>PFP-Previsões Financeiras a Pagar</t>
-  </si>
-  <si>
-    <t>1 - 8</t>
-  </si>
-  <si>
-    <t>Hostgator</t>
-  </si>
-  <si>
-    <t>1 - 9</t>
-  </si>
-  <si>
-    <t>100901 - 1</t>
-  </si>
-  <si>
-    <t>TERESINHA ELVIRA MAXIMINO DE MENEZES</t>
-  </si>
-  <si>
-    <t>100901 - 2</t>
-  </si>
-  <si>
-    <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
-  </si>
-  <si>
-    <t>102301 - 2</t>
-  </si>
-  <si>
-    <t>06/10/2026</t>
-  </si>
-  <si>
-    <t>ROSANGELA PACHECO</t>
-  </si>
-  <si>
-    <t>FELIPE DOMINGOS BARBOSA</t>
-  </si>
-  <si>
-    <t>bianca rodrigues</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t>102901 - 2</t>
-  </si>
-  <si>
-    <t>102901 - 1</t>
-  </si>
-  <si>
-    <t>103501 - 1</t>
-  </si>
-  <si>
-    <t>103501 - 2</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>08/10/2026</t>
-  </si>
-  <si>
-    <t>56102 - 1</t>
-  </si>
-  <si>
-    <t>L E A Medicoes Tecnicas LTDA</t>
-  </si>
-  <si>
-    <t>Carina Pereira</t>
-  </si>
-  <si>
-    <t>09/10/2026</t>
-  </si>
-  <si>
-    <t>96601 - 1</t>
-  </si>
-  <si>
-    <t>101401 - 1</t>
-  </si>
-  <si>
-    <t>DMP-Duplicata Manual do Contas a pagar</t>
-  </si>
-  <si>
-    <t>92401 - 0</t>
-  </si>
-  <si>
-    <t>Antonio Jesus</t>
-  </si>
-  <si>
-    <t>92801 - 0</t>
-  </si>
-  <si>
-    <t>96601 - 2</t>
-  </si>
-  <si>
-    <t>96601 - 3</t>
-  </si>
-  <si>
-    <t>101401 - 2</t>
-  </si>
-  <si>
-    <t>101401 - 3</t>
-  </si>
-  <si>
-    <t>10/10/2026</t>
-  </si>
-  <si>
-    <t>100501 - 3</t>
-  </si>
-  <si>
-    <t>100501 - 2</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>49501 - 2</t>
-  </si>
-  <si>
-    <t>100301 - 1</t>
-  </si>
-  <si>
-    <t>102101 - 1</t>
-  </si>
-  <si>
-    <t>100301 - 3</t>
-  </si>
-  <si>
-    <t>100301 - 2</t>
-  </si>
-  <si>
-    <t>102101 - 2</t>
-  </si>
-  <si>
-    <t>102101 - 3</t>
-  </si>
-  <si>
-    <t>14/10/2026</t>
-  </si>
-  <si>
-    <t>1631 - 1</t>
-  </si>
-  <si>
-    <t>1632 - 1</t>
-  </si>
-  <si>
-    <t>1633 - 1</t>
-  </si>
-  <si>
-    <t>1634 - 1</t>
-  </si>
-  <si>
-    <t>101201 - 1</t>
-  </si>
-  <si>
-    <t>1631 - 2</t>
-  </si>
-  <si>
-    <t>1631 - 3</t>
-  </si>
-  <si>
-    <t>1632 - 3</t>
-  </si>
-  <si>
-    <t>1632 - 2</t>
-  </si>
-  <si>
-    <t>1633 - 3</t>
-  </si>
-  <si>
-    <t>1633 - 2</t>
-  </si>
-  <si>
-    <t>1634 - 3</t>
-  </si>
-  <si>
-    <t>1634 - 2</t>
-  </si>
-  <si>
-    <t>101201 - 2</t>
-  </si>
-  <si>
-    <t>101201 - 3</t>
-  </si>
-  <si>
-    <t>101801 - 2</t>
-  </si>
-  <si>
-    <t>101801 - 3</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>101101 - 1</t>
-  </si>
-  <si>
-    <t>101101 - 3</t>
-  </si>
-  <si>
-    <t>101101 - 2</t>
-  </si>
-  <si>
-    <t>103801 - 1</t>
-  </si>
-  <si>
-    <t>104701 - 1</t>
-  </si>
-  <si>
-    <t>104701 - 2</t>
-  </si>
-  <si>
-    <t>104801 - 2</t>
-  </si>
-  <si>
-    <t>104801 - 1</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>103801 - 2</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>105001 - 1</t>
-  </si>
-  <si>
-    <t>105001 - 2</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>92001 - 2</t>
-  </si>
-  <si>
-    <t>102401 - 1</t>
-  </si>
-  <si>
-    <t>102401 - 2</t>
-  </si>
-  <si>
-    <t>102401 - 3</t>
-  </si>
-  <si>
-    <t>102501 - 2</t>
-  </si>
-  <si>
-    <t>102501 - 3</t>
-  </si>
-  <si>
-    <t>105301 - 1</t>
-  </si>
-  <si>
     <t>105101 - 1</t>
   </si>
   <si>
@@ -510,13 +510,13 @@
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>234.605,76</t>
+    <t>229.463,96</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-234.605,76</t>
+    <t>-229.463,96</t>
   </si>
 </sst>
 </file>
@@ -584,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H168"/>
+  <dimension ref="A2:H166"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -755,10 +755,10 @@
         <v>0.0</v>
       </c>
       <c r="G20" t="n" s="1">
-        <v>32.88</v>
+        <v>32.31</v>
       </c>
       <c r="H20" t="n" s="1">
-        <v>-32.88</v>
+        <v>-32.31</v>
       </c>
     </row>
     <row r="21">
@@ -781,10 +781,10 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n" s="1">
-        <v>32.31</v>
+        <v>32.88</v>
       </c>
       <c r="H21" t="n" s="1">
-        <v>-32.31</v>
+        <v>-32.88</v>
       </c>
     </row>
     <row r="22">
@@ -847,22 +847,22 @@
         <v>40</v>
       </c>
       <c r="C24" t="s" s="1">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G24" t="n" s="1">
-        <v>1503.82</v>
+        <v>9.99</v>
       </c>
       <c r="H24" t="n" s="1">
-        <v>-1503.82</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="25">
@@ -873,22 +873,22 @@
         <v>40</v>
       </c>
       <c r="C25" t="s" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s" s="1">
         <v>44</v>
       </c>
       <c r="E25" t="s" s="1">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F25" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G25" t="n" s="1">
-        <v>9.99</v>
+        <v>14250.0</v>
       </c>
       <c r="H25" t="n" s="1">
-        <v>-9.99</v>
+        <v>-14250.0</v>
       </c>
     </row>
     <row r="26">
@@ -899,10 +899,10 @@
         <v>40</v>
       </c>
       <c r="C26" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s" s="1">
         <v>38</v>
@@ -911,10 +911,10 @@
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>14250.0</v>
+        <v>1215.9</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-14250.0</v>
+        <v>-1215.9</v>
       </c>
     </row>
     <row r="27">
@@ -928,19 +928,19 @@
         <v>36</v>
       </c>
       <c r="D27" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="E27" t="s" s="1">
-        <v>48</v>
-      </c>
       <c r="F27" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G27" t="n" s="1">
-        <v>607.95</v>
+        <v>1215.9</v>
       </c>
       <c r="H27" t="n" s="1">
-        <v>-607.95</v>
+        <v>-1215.9</v>
       </c>
     </row>
     <row r="28">
@@ -954,19 +954,19 @@
         <v>36</v>
       </c>
       <c r="D28" t="s" s="1">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G28" t="n" s="1">
-        <v>1215.9</v>
+        <v>607.95</v>
       </c>
       <c r="H28" t="n" s="1">
-        <v>-1215.9</v>
+        <v>-607.95</v>
       </c>
     </row>
     <row r="29">
@@ -980,19 +980,19 @@
         <v>36</v>
       </c>
       <c r="D29" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="E29" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="E29" t="s" s="1">
-        <v>50</v>
-      </c>
       <c r="F29" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>1215.9</v>
+        <v>444.12</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-1215.9</v>
+        <v>-444.12</v>
       </c>
     </row>
     <row r="30">
@@ -1006,19 +1006,19 @@
         <v>36</v>
       </c>
       <c r="D30" t="s" s="1">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s" s="1">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F30" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G30" t="n" s="1">
-        <v>222.06</v>
+        <v>444.12</v>
       </c>
       <c r="H30" t="n" s="1">
-        <v>-222.06</v>
+        <v>-444.12</v>
       </c>
     </row>
     <row r="31">
@@ -1032,19 +1032,19 @@
         <v>36</v>
       </c>
       <c r="D31" t="s" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G31" t="n" s="1">
-        <v>444.12</v>
+        <v>222.06</v>
       </c>
       <c r="H31" t="n" s="1">
-        <v>-444.12</v>
+        <v>-222.06</v>
       </c>
     </row>
     <row r="32">
@@ -1052,25 +1052,25 @@
         <v>26</v>
       </c>
       <c r="B32" t="s" s="1">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D32" t="s" s="1">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E32" t="s" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F32" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G32" t="n" s="1">
-        <v>444.12</v>
+        <v>4255.67</v>
       </c>
       <c r="H32" t="n" s="1">
-        <v>-444.12</v>
+        <v>-4255.67</v>
       </c>
     </row>
     <row r="33">
@@ -1078,13 +1078,13 @@
         <v>26</v>
       </c>
       <c r="B33" t="s" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D33" t="s" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s" s="1">
         <v>53</v>
@@ -1093,10 +1093,10 @@
         <v>0.0</v>
       </c>
       <c r="G33" t="n" s="1">
-        <v>4255.67</v>
+        <v>1823.86</v>
       </c>
       <c r="H33" t="n" s="1">
-        <v>-4255.67</v>
+        <v>-1823.86</v>
       </c>
     </row>
     <row r="34">
@@ -1104,25 +1104,25 @@
         <v>26</v>
       </c>
       <c r="B34" t="s" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D34" t="s" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s" s="1">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F34" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G34" t="n" s="1">
-        <v>1823.86</v>
+        <v>6079.52</v>
       </c>
       <c r="H34" t="n" s="1">
-        <v>-1823.86</v>
+        <v>-6079.52</v>
       </c>
     </row>
     <row r="35">
@@ -1130,25 +1130,25 @@
         <v>26</v>
       </c>
       <c r="B35" t="s" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D35" t="s" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E35" t="s" s="1">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F35" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G35" t="n" s="1">
-        <v>6079.52</v>
+        <v>1554.41</v>
       </c>
       <c r="H35" t="n" s="1">
-        <v>-6079.52</v>
+        <v>-1554.41</v>
       </c>
     </row>
     <row r="36">
@@ -1156,25 +1156,25 @@
         <v>26</v>
       </c>
       <c r="B36" t="s" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D36" t="s" s="1">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s" s="1">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F36" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G36" t="n" s="1">
-        <v>2220.59</v>
+        <v>666.18</v>
       </c>
       <c r="H36" t="n" s="1">
-        <v>-2220.59</v>
+        <v>-666.18</v>
       </c>
     </row>
     <row r="37">
@@ -1182,25 +1182,25 @@
         <v>26</v>
       </c>
       <c r="B37" t="s" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D37" t="s" s="1">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E37" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F37" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G37" t="n" s="1">
-        <v>1554.41</v>
+        <v>2220.59</v>
       </c>
       <c r="H37" t="n" s="1">
-        <v>-1554.41</v>
+        <v>-2220.59</v>
       </c>
     </row>
     <row r="38">
@@ -1208,25 +1208,25 @@
         <v>26</v>
       </c>
       <c r="B38" t="s" s="1">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D38" t="s" s="1">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E38" t="s" s="1">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F38" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G38" t="n" s="1">
-        <v>666.18</v>
+        <v>3.56</v>
       </c>
       <c r="H38" t="n" s="1">
-        <v>-666.18</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="39">
@@ -1234,25 +1234,25 @@
         <v>26</v>
       </c>
       <c r="B39" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="C39" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="D39" t="s" s="1">
-        <v>57</v>
-      </c>
       <c r="E39" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F39" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G39" t="n" s="1">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="H39" t="n" s="1">
-        <v>-3.56</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="40">
@@ -1260,16 +1260,16 @@
         <v>26</v>
       </c>
       <c r="B40" t="s" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D40" t="s" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E40" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F40" t="n" s="1">
         <v>0.0</v>
@@ -1286,7 +1286,7 @@
         <v>26</v>
       </c>
       <c r="B41" t="s" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s" s="1">
         <v>36</v>
@@ -1295,16 +1295,16 @@
         <v>58</v>
       </c>
       <c r="E41" t="s" s="1">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G41" t="n" s="1">
-        <v>1.78</v>
+        <v>66.4</v>
       </c>
       <c r="H41" t="n" s="1">
-        <v>-1.78</v>
+        <v>-66.4</v>
       </c>
     </row>
     <row r="42">
@@ -1312,25 +1312,25 @@
         <v>26</v>
       </c>
       <c r="B42" t="s" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D42" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E42" t="s" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F42" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G42" t="n" s="1">
-        <v>33.2</v>
+        <v>66.4</v>
       </c>
       <c r="H42" t="n" s="1">
-        <v>-33.2</v>
+        <v>-66.4</v>
       </c>
     </row>
     <row r="43">
@@ -1338,7 +1338,7 @@
         <v>26</v>
       </c>
       <c r="B43" t="s" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s" s="1">
         <v>36</v>
@@ -1347,16 +1347,16 @@
         <v>60</v>
       </c>
       <c r="E43" t="s" s="1">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F43" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G43" t="n" s="1">
-        <v>66.4</v>
+        <v>33.2</v>
       </c>
       <c r="H43" t="n" s="1">
-        <v>-66.4</v>
+        <v>-33.2</v>
       </c>
     </row>
     <row r="44">
@@ -1364,25 +1364,25 @@
         <v>26</v>
       </c>
       <c r="B44" t="s" s="1">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s" s="1">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s" s="1">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F44" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G44" t="n" s="1">
-        <v>66.4</v>
+        <v>180.0</v>
       </c>
       <c r="H44" t="n" s="1">
-        <v>-66.4</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="45">
@@ -1390,13 +1390,13 @@
         <v>26</v>
       </c>
       <c r="B45" t="s" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s" s="1">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E45" t="s" s="1">
         <v>64</v>
@@ -1405,10 +1405,10 @@
         <v>0.0</v>
       </c>
       <c r="G45" t="n" s="1">
-        <v>180.0</v>
+        <v>12.47</v>
       </c>
       <c r="H45" t="n" s="1">
-        <v>-180.0</v>
+        <v>-12.47</v>
       </c>
     </row>
     <row r="46">
@@ -1416,25 +1416,25 @@
         <v>26</v>
       </c>
       <c r="B46" t="s" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D46" t="s" s="1">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E46" t="s" s="1">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F46" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G46" t="n" s="1">
-        <v>12.47</v>
+        <v>17.81</v>
       </c>
       <c r="H46" t="n" s="1">
-        <v>-12.47</v>
+        <v>-17.81</v>
       </c>
     </row>
     <row r="47">
@@ -1442,13 +1442,13 @@
         <v>26</v>
       </c>
       <c r="B47" t="s" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D47" t="s" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E47" t="s" s="1">
         <v>38</v>
@@ -1457,10 +1457,10 @@
         <v>0.0</v>
       </c>
       <c r="G47" t="n" s="1">
-        <v>17.81</v>
+        <v>332.0</v>
       </c>
       <c r="H47" t="n" s="1">
-        <v>-17.81</v>
+        <v>-332.0</v>
       </c>
     </row>
     <row r="48">
@@ -1468,13 +1468,13 @@
         <v>26</v>
       </c>
       <c r="B48" t="s" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D48" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E48" t="s" s="1">
         <v>53</v>
@@ -1483,10 +1483,10 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n" s="1">
-        <v>232.4</v>
+        <v>99.6</v>
       </c>
       <c r="H48" t="n" s="1">
-        <v>-232.4</v>
+        <v>-99.6</v>
       </c>
     </row>
     <row r="49">
@@ -1494,25 +1494,25 @@
         <v>26</v>
       </c>
       <c r="B49" t="s" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D49" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E49" t="s" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F49" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G49" t="n" s="1">
-        <v>99.6</v>
+        <v>232.4</v>
       </c>
       <c r="H49" t="n" s="1">
-        <v>-99.6</v>
+        <v>-232.4</v>
       </c>
     </row>
     <row r="50">
@@ -1520,25 +1520,25 @@
         <v>26</v>
       </c>
       <c r="B50" t="s" s="1">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D50" t="s" s="1">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E50" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F50" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G50" t="n" s="1">
-        <v>332.0</v>
+        <v>15184.14</v>
       </c>
       <c r="H50" t="n" s="1">
-        <v>-332.0</v>
+        <v>-15184.14</v>
       </c>
     </row>
     <row r="51">
@@ -1546,7 +1546,7 @@
         <v>26</v>
       </c>
       <c r="B51" t="s" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s" s="1">
         <v>28</v>
@@ -1561,10 +1561,10 @@
         <v>0.0</v>
       </c>
       <c r="G51" t="n" s="1">
-        <v>15184.14</v>
+        <v>12242.58</v>
       </c>
       <c r="H51" t="n" s="1">
-        <v>-15184.14</v>
+        <v>-12242.58</v>
       </c>
     </row>
     <row r="52">
@@ -1572,25 +1572,25 @@
         <v>26</v>
       </c>
       <c r="B52" t="s" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C52" t="s" s="1">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="D52" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E52" t="s" s="1">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F52" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G52" t="n" s="1">
-        <v>12242.58</v>
+        <v>2163.0</v>
       </c>
       <c r="H52" t="n" s="1">
-        <v>-12242.58</v>
+        <v>-2163.0</v>
       </c>
     </row>
     <row r="53">
@@ -1598,25 +1598,25 @@
         <v>26</v>
       </c>
       <c r="B53" t="s" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D53" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="E53" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="E53" t="s" s="1">
-        <v>71</v>
-      </c>
       <c r="F53" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G53" t="n" s="1">
-        <v>2163.0</v>
+        <v>1821.02</v>
       </c>
       <c r="H53" t="n" s="1">
-        <v>-2163.0</v>
+        <v>-1821.02</v>
       </c>
     </row>
     <row r="54">
@@ -1624,25 +1624,25 @@
         <v>26</v>
       </c>
       <c r="B54" t="s" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s" s="1">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s" s="1">
         <v>72</v>
       </c>
       <c r="E54" t="s" s="1">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F54" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G54" t="n" s="1">
-        <v>1821.02</v>
+        <v>1237.52</v>
       </c>
       <c r="H54" t="n" s="1">
-        <v>-1821.02</v>
+        <v>-1237.52</v>
       </c>
     </row>
     <row r="55">
@@ -1650,7 +1650,7 @@
         <v>26</v>
       </c>
       <c r="B55" t="s" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C55" t="s" s="1">
         <v>31</v>
@@ -1659,7 +1659,7 @@
         <v>73</v>
       </c>
       <c r="E55" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F55" t="n" s="1">
         <v>0.0</v>
@@ -1676,7 +1676,7 @@
         <v>26</v>
       </c>
       <c r="B56" t="s" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s" s="1">
         <v>31</v>
@@ -1685,16 +1685,16 @@
         <v>74</v>
       </c>
       <c r="E56" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F56" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G56" t="n" s="1">
-        <v>1237.52</v>
+        <v>997.38</v>
       </c>
       <c r="H56" t="n" s="1">
-        <v>-1237.52</v>
+        <v>-997.38</v>
       </c>
     </row>
     <row r="57">
@@ -1702,25 +1702,25 @@
         <v>26</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D57" t="s" s="1">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E57" t="s" s="1">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F57" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>3683.86</v>
+        <v>979.59</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>-3683.86</v>
+        <v>-979.59</v>
       </c>
     </row>
     <row r="58">
@@ -1728,13 +1728,13 @@
         <v>26</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C58" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D58" t="s" s="1">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E58" t="s" s="1">
         <v>35</v>
@@ -1743,10 +1743,10 @@
         <v>0.0</v>
       </c>
       <c r="G58" t="n" s="1">
-        <v>979.59</v>
+        <v>699.37</v>
       </c>
       <c r="H58" t="n" s="1">
-        <v>-979.59</v>
+        <v>-699.37</v>
       </c>
     </row>
     <row r="59">
@@ -1754,13 +1754,13 @@
         <v>26</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D59" t="s" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E59" t="s" s="1">
         <v>33</v>
@@ -1769,10 +1769,10 @@
         <v>0.0</v>
       </c>
       <c r="G59" t="n" s="1">
-        <v>997.38</v>
+        <v>686.33</v>
       </c>
       <c r="H59" t="n" s="1">
-        <v>-997.38</v>
+        <v>-686.33</v>
       </c>
     </row>
     <row r="60">
@@ -1780,25 +1780,25 @@
         <v>26</v>
       </c>
       <c r="B60" t="s" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E60" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F60" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G60" t="n" s="1">
-        <v>699.37</v>
+        <v>560.42</v>
       </c>
       <c r="H60" t="n" s="1">
-        <v>-699.37</v>
+        <v>-560.42</v>
       </c>
     </row>
     <row r="61">
@@ -1806,25 +1806,25 @@
         <v>26</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E61" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F61" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G61" t="n" s="1">
-        <v>686.33</v>
+        <v>8758.14</v>
       </c>
       <c r="H61" t="n" s="1">
-        <v>-686.33</v>
+        <v>-8758.14</v>
       </c>
     </row>
     <row r="62">
@@ -1832,13 +1832,13 @@
         <v>26</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D62" t="s" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E62" t="s" s="1">
         <v>30</v>
@@ -1847,10 +1847,10 @@
         <v>0.0</v>
       </c>
       <c r="G62" t="n" s="1">
-        <v>560.42</v>
+        <v>9559.08</v>
       </c>
       <c r="H62" t="n" s="1">
-        <v>-560.42</v>
+        <v>-9559.08</v>
       </c>
     </row>
     <row r="63">
@@ -1858,25 +1858,25 @@
         <v>26</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E63" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>8758.14</v>
+        <v>714.08</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-8758.14</v>
+        <v>-714.08</v>
       </c>
     </row>
     <row r="64">
@@ -1884,25 +1884,25 @@
         <v>26</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E64" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F64" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>9559.08</v>
+        <v>700.72</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-9559.08</v>
+        <v>-700.72</v>
       </c>
     </row>
     <row r="65">
@@ -1910,13 +1910,13 @@
         <v>26</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D65" t="s" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E65" t="s" s="1">
         <v>33</v>
@@ -1925,10 +1925,10 @@
         <v>0.0</v>
       </c>
       <c r="G65" t="n" s="1">
-        <v>714.08</v>
+        <v>787.61</v>
       </c>
       <c r="H65" t="n" s="1">
-        <v>-714.08</v>
+        <v>-787.61</v>
       </c>
     </row>
     <row r="66">
@@ -1936,13 +1936,13 @@
         <v>26</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D66" t="s" s="1">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E66" t="s" s="1">
         <v>35</v>
@@ -1951,10 +1951,10 @@
         <v>0.0</v>
       </c>
       <c r="G66" t="n" s="1">
-        <v>700.72</v>
+        <v>802.58</v>
       </c>
       <c r="H66" t="n" s="1">
-        <v>-700.72</v>
+        <v>-802.58</v>
       </c>
     </row>
     <row r="67">
@@ -1962,25 +1962,25 @@
         <v>26</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C67" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D67" t="s" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E67" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F67" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G67" t="n" s="1">
-        <v>764.9</v>
+        <v>744.28</v>
       </c>
       <c r="H67" t="n" s="1">
-        <v>-764.9</v>
+        <v>-744.28</v>
       </c>
     </row>
     <row r="68">
@@ -1988,25 +1988,25 @@
         <v>26</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D68" t="s" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E68" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F68" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G68" t="n" s="1">
-        <v>779.41</v>
+        <v>228.78</v>
       </c>
       <c r="H68" t="n" s="1">
-        <v>-779.41</v>
+        <v>-228.78</v>
       </c>
     </row>
     <row r="69">
@@ -2014,13 +2014,13 @@
         <v>26</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D69" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E69" t="s" s="1">
         <v>30</v>
@@ -2029,10 +2029,10 @@
         <v>0.0</v>
       </c>
       <c r="G69" t="n" s="1">
-        <v>744.28</v>
+        <v>378.27</v>
       </c>
       <c r="H69" t="n" s="1">
-        <v>-744.28</v>
+        <v>-378.27</v>
       </c>
     </row>
     <row r="70">
@@ -2040,13 +2040,13 @@
         <v>26</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D70" t="s" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E70" t="s" s="1">
         <v>30</v>
@@ -2055,10 +2055,10 @@
         <v>0.0</v>
       </c>
       <c r="G70" t="n" s="1">
-        <v>228.78</v>
+        <v>96.52</v>
       </c>
       <c r="H70" t="n" s="1">
-        <v>-228.78</v>
+        <v>-96.52</v>
       </c>
     </row>
     <row r="71">
@@ -2066,13 +2066,13 @@
         <v>26</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C71" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D71" t="s" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E71" t="s" s="1">
         <v>30</v>
@@ -2081,10 +2081,10 @@
         <v>0.0</v>
       </c>
       <c r="G71" t="n" s="1">
-        <v>378.27</v>
+        <v>6118.3</v>
       </c>
       <c r="H71" t="n" s="1">
-        <v>-378.27</v>
+        <v>-6118.3</v>
       </c>
     </row>
     <row r="72">
@@ -2092,25 +2092,25 @@
         <v>26</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C72" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D72" t="s" s="1">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F72" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G72" t="n" s="1">
-        <v>96.52</v>
+        <v>59.56</v>
       </c>
       <c r="H72" t="n" s="1">
-        <v>-96.52</v>
+        <v>-59.56</v>
       </c>
     </row>
     <row r="73">
@@ -2118,25 +2118,25 @@
         <v>26</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C73" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s" s="1">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E73" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G73" t="n" s="1">
-        <v>6118.3</v>
+        <v>60.64</v>
       </c>
       <c r="H73" t="n" s="1">
-        <v>-6118.3</v>
+        <v>-60.64</v>
       </c>
     </row>
     <row r="74">
@@ -2144,13 +2144,13 @@
         <v>26</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C74" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D74" t="s" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E74" t="s" s="1">
         <v>35</v>
@@ -2159,10 +2159,10 @@
         <v>0.0</v>
       </c>
       <c r="G74" t="n" s="1">
-        <v>59.56</v>
+        <v>18.64</v>
       </c>
       <c r="H74" t="n" s="1">
-        <v>-59.56</v>
+        <v>-18.64</v>
       </c>
     </row>
     <row r="75">
@@ -2170,13 +2170,13 @@
         <v>26</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D75" t="s" s="1">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E75" t="s" s="1">
         <v>33</v>
@@ -2185,10 +2185,10 @@
         <v>0.0</v>
       </c>
       <c r="G75" t="n" s="1">
-        <v>60.64</v>
+        <v>18.3</v>
       </c>
       <c r="H75" t="n" s="1">
-        <v>-60.64</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="76">
@@ -2196,13 +2196,13 @@
         <v>26</v>
       </c>
       <c r="B76" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D76" t="s" s="1">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E76" t="s" s="1">
         <v>33</v>
@@ -2211,10 +2211,10 @@
         <v>0.0</v>
       </c>
       <c r="G76" t="n" s="1">
-        <v>18.64</v>
+        <v>30.25</v>
       </c>
       <c r="H76" t="n" s="1">
-        <v>-18.64</v>
+        <v>-30.25</v>
       </c>
     </row>
     <row r="77">
@@ -2222,13 +2222,13 @@
         <v>26</v>
       </c>
       <c r="B77" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D77" t="s" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E77" t="s" s="1">
         <v>35</v>
@@ -2237,10 +2237,10 @@
         <v>0.0</v>
       </c>
       <c r="G77" t="n" s="1">
-        <v>18.3</v>
+        <v>30.82</v>
       </c>
       <c r="H77" t="n" s="1">
-        <v>-18.3</v>
+        <v>-30.82</v>
       </c>
     </row>
     <row r="78">
@@ -2248,25 +2248,25 @@
         <v>26</v>
       </c>
       <c r="B78" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C78" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D78" t="s" s="1">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E78" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F78" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G78" t="n" s="1">
-        <v>30.82</v>
+        <v>7.86</v>
       </c>
       <c r="H78" t="n" s="1">
-        <v>-30.82</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="79">
@@ -2274,25 +2274,25 @@
         <v>26</v>
       </c>
       <c r="B79" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D79" t="s" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E79" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F79" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G79" t="n" s="1">
-        <v>30.25</v>
+        <v>7.74</v>
       </c>
       <c r="H79" t="n" s="1">
-        <v>-30.25</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="80">
@@ -2300,25 +2300,25 @@
         <v>26</v>
       </c>
       <c r="B80" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D80" t="s" s="1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E80" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F80" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G80" t="n" s="1">
-        <v>7.86</v>
+        <v>498.88</v>
       </c>
       <c r="H80" t="n" s="1">
-        <v>-7.86</v>
+        <v>-498.88</v>
       </c>
     </row>
     <row r="81">
@@ -2326,25 +2326,25 @@
         <v>26</v>
       </c>
       <c r="B81" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C81" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D81" t="s" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E81" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F81" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G81" t="n" s="1">
-        <v>7.74</v>
+        <v>489.47</v>
       </c>
       <c r="H81" t="n" s="1">
-        <v>-7.74</v>
+        <v>-489.47</v>
       </c>
     </row>
     <row r="82">
@@ -2352,25 +2352,25 @@
         <v>26</v>
       </c>
       <c r="B82" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C82" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D82" t="s" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E82" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F82" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G82" t="n" s="1">
-        <v>489.47</v>
+        <v>632.51</v>
       </c>
       <c r="H82" t="n" s="1">
-        <v>-489.47</v>
+        <v>-632.51</v>
       </c>
     </row>
     <row r="83">
@@ -2378,25 +2378,25 @@
         <v>26</v>
       </c>
       <c r="B83" t="s" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D83" t="s" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E83" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F83" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G83" t="n" s="1">
-        <v>498.88</v>
+        <v>644.44</v>
       </c>
       <c r="H83" t="n" s="1">
-        <v>-498.88</v>
+        <v>-644.44</v>
       </c>
     </row>
     <row r="84">
@@ -2404,25 +2404,25 @@
         <v>26</v>
       </c>
       <c r="B84" t="s" s="1">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C84" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D84" t="s" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E84" t="s" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F84" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G84" t="n" s="1">
-        <v>632.51</v>
+        <v>21486.12</v>
       </c>
       <c r="H84" t="n" s="1">
-        <v>-632.51</v>
+        <v>-21486.12</v>
       </c>
     </row>
     <row r="85">
@@ -2430,25 +2430,25 @@
         <v>26</v>
       </c>
       <c r="B85" t="s" s="1">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C85" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D85" t="s" s="1">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E85" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G85" t="n" s="1">
-        <v>644.44</v>
+        <v>1751.0</v>
       </c>
       <c r="H85" t="n" s="1">
-        <v>-644.44</v>
+        <v>-1751.0</v>
       </c>
     </row>
     <row r="86">
@@ -2456,25 +2456,25 @@
         <v>26</v>
       </c>
       <c r="B86" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C86" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D86" t="s" s="1">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E86" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F86" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G86" t="n" s="1">
-        <v>21486.12</v>
+        <v>1718.89</v>
       </c>
       <c r="H86" t="n" s="1">
-        <v>-21486.12</v>
+        <v>-1718.89</v>
       </c>
     </row>
     <row r="87">
@@ -2482,25 +2482,25 @@
         <v>26</v>
       </c>
       <c r="B87" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C87" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D87" t="s" s="1">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E87" t="s" s="1">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F87" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G87" t="n" s="1">
-        <v>1751.0</v>
+        <v>15.2</v>
       </c>
       <c r="H87" t="n" s="1">
-        <v>-1751.0</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="88">
@@ -2508,25 +2508,25 @@
         <v>26</v>
       </c>
       <c r="B88" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C88" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D88" t="s" s="1">
         <v>109</v>
       </c>
       <c r="E88" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F88" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G88" t="n" s="1">
-        <v>1718.89</v>
+        <v>30.4</v>
       </c>
       <c r="H88" t="n" s="1">
-        <v>-1718.89</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="89">
@@ -2534,25 +2534,25 @@
         <v>26</v>
       </c>
       <c r="B89" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C89" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D89" t="s" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E89" t="s" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F89" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G89" t="n" s="1">
-        <v>15.2</v>
+        <v>30.4</v>
       </c>
       <c r="H89" t="n" s="1">
-        <v>-15.2</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="90">
@@ -2560,7 +2560,7 @@
         <v>26</v>
       </c>
       <c r="B90" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C90" t="s" s="1">
         <v>36</v>
@@ -2569,16 +2569,16 @@
         <v>110</v>
       </c>
       <c r="E90" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F90" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G90" t="n" s="1">
-        <v>30.4</v>
+        <v>8.73</v>
       </c>
       <c r="H90" t="n" s="1">
-        <v>-30.4</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="91">
@@ -2586,25 +2586,25 @@
         <v>26</v>
       </c>
       <c r="B91" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C91" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D91" t="s" s="1">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E91" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F91" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G91" t="n" s="1">
-        <v>30.4</v>
+        <v>17.46</v>
       </c>
       <c r="H91" t="n" s="1">
-        <v>-30.4</v>
+        <v>-17.46</v>
       </c>
     </row>
     <row r="92">
@@ -2612,25 +2612,25 @@
         <v>26</v>
       </c>
       <c r="B92" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C92" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D92" t="s" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E92" t="s" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F92" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G92" t="n" s="1">
-        <v>8.73</v>
+        <v>17.46</v>
       </c>
       <c r="H92" t="n" s="1">
-        <v>-8.73</v>
+        <v>-17.46</v>
       </c>
     </row>
     <row r="93">
@@ -2638,7 +2638,7 @@
         <v>26</v>
       </c>
       <c r="B93" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C93" t="s" s="1">
         <v>36</v>
@@ -2653,10 +2653,10 @@
         <v>0.0</v>
       </c>
       <c r="G93" t="n" s="1">
-        <v>17.46</v>
+        <v>6.81</v>
       </c>
       <c r="H93" t="n" s="1">
-        <v>-17.46</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="94">
@@ -2664,25 +2664,25 @@
         <v>26</v>
       </c>
       <c r="B94" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C94" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D94" t="s" s="1">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E94" t="s" s="1">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F94" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G94" t="n" s="1">
-        <v>17.46</v>
+        <v>6.81</v>
       </c>
       <c r="H94" t="n" s="1">
-        <v>-17.46</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="95">
@@ -2690,7 +2690,7 @@
         <v>26</v>
       </c>
       <c r="B95" t="s" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C95" t="s" s="1">
         <v>36</v>
@@ -2699,16 +2699,16 @@
         <v>113</v>
       </c>
       <c r="E95" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F95" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G95" t="n" s="1">
-        <v>6.81</v>
+        <v>3.41</v>
       </c>
       <c r="H95" t="n" s="1">
-        <v>-6.81</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="96">
@@ -2716,25 +2716,25 @@
         <v>26</v>
       </c>
       <c r="B96" t="s" s="1">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C96" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D96" t="s" s="1">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E96" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F96" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G96" t="n" s="1">
-        <v>6.81</v>
+        <v>152.0</v>
       </c>
       <c r="H96" t="n" s="1">
-        <v>-6.81</v>
+        <v>-152.0</v>
       </c>
     </row>
     <row r="97">
@@ -2742,25 +2742,25 @@
         <v>26</v>
       </c>
       <c r="B97" t="s" s="1">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C97" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D97" t="s" s="1">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E97" t="s" s="1">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="F97" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G97" t="n" s="1">
-        <v>3.41</v>
+        <v>106.4</v>
       </c>
       <c r="H97" t="n" s="1">
-        <v>-3.41</v>
+        <v>-106.4</v>
       </c>
     </row>
     <row r="98">
@@ -2768,25 +2768,25 @@
         <v>26</v>
       </c>
       <c r="B98" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C98" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D98" t="s" s="1">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E98" t="s" s="1">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F98" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G98" t="n" s="1">
-        <v>152.0</v>
+        <v>45.6</v>
       </c>
       <c r="H98" t="n" s="1">
-        <v>-152.0</v>
+        <v>-45.6</v>
       </c>
     </row>
     <row r="99">
@@ -2794,7 +2794,7 @@
         <v>26</v>
       </c>
       <c r="B99" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C99" t="s" s="1">
         <v>36</v>
@@ -2803,16 +2803,16 @@
         <v>110</v>
       </c>
       <c r="E99" t="s" s="1">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="F99" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G99" t="n" s="1">
-        <v>106.4</v>
+        <v>61.11</v>
       </c>
       <c r="H99" t="n" s="1">
-        <v>-106.4</v>
+        <v>-61.11</v>
       </c>
     </row>
     <row r="100">
@@ -2820,7 +2820,7 @@
         <v>26</v>
       </c>
       <c r="B100" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C100" t="s" s="1">
         <v>36</v>
@@ -2829,16 +2829,16 @@
         <v>110</v>
       </c>
       <c r="E100" t="s" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F100" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G100" t="n" s="1">
-        <v>45.6</v>
+        <v>26.19</v>
       </c>
       <c r="H100" t="n" s="1">
-        <v>-45.6</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="101">
@@ -2846,25 +2846,25 @@
         <v>26</v>
       </c>
       <c r="B101" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C101" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D101" t="s" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E101" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F101" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G101" t="n" s="1">
-        <v>61.11</v>
+        <v>87.3</v>
       </c>
       <c r="H101" t="n" s="1">
-        <v>-61.11</v>
+        <v>-87.3</v>
       </c>
     </row>
     <row r="102">
@@ -2872,25 +2872,25 @@
         <v>26</v>
       </c>
       <c r="B102" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C102" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D102" t="s" s="1">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E102" t="s" s="1">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F102" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G102" t="n" s="1">
-        <v>26.19</v>
+        <v>23.84</v>
       </c>
       <c r="H102" t="n" s="1">
-        <v>-26.19</v>
+        <v>-23.84</v>
       </c>
     </row>
     <row r="103">
@@ -2898,13 +2898,13 @@
         <v>26</v>
       </c>
       <c r="B103" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C103" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D103" t="s" s="1">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E103" t="s" s="1">
         <v>38</v>
@@ -2913,10 +2913,10 @@
         <v>0.0</v>
       </c>
       <c r="G103" t="n" s="1">
-        <v>87.3</v>
+        <v>34.05</v>
       </c>
       <c r="H103" t="n" s="1">
-        <v>-87.3</v>
+        <v>-34.05</v>
       </c>
     </row>
     <row r="104">
@@ -2924,25 +2924,25 @@
         <v>26</v>
       </c>
       <c r="B104" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C104" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D104" t="s" s="1">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E104" t="s" s="1">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F104" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G104" t="n" s="1">
-        <v>23.84</v>
+        <v>135.18</v>
       </c>
       <c r="H104" t="n" s="1">
-        <v>-23.84</v>
+        <v>-135.18</v>
       </c>
     </row>
     <row r="105">
@@ -2950,25 +2950,25 @@
         <v>26</v>
       </c>
       <c r="B105" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C105" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D105" t="s" s="1">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E105" t="s" s="1">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F105" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G105" t="n" s="1">
-        <v>34.05</v>
+        <v>57.93</v>
       </c>
       <c r="H105" t="n" s="1">
-        <v>-34.05</v>
+        <v>-57.93</v>
       </c>
     </row>
     <row r="106">
@@ -2976,25 +2976,25 @@
         <v>26</v>
       </c>
       <c r="B106" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C106" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D106" t="s" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E106" t="s" s="1">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F106" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G106" t="n" s="1">
-        <v>135.18</v>
+        <v>19.31</v>
       </c>
       <c r="H106" t="n" s="1">
-        <v>-135.18</v>
+        <v>-19.31</v>
       </c>
     </row>
     <row r="107">
@@ -3002,25 +3002,25 @@
         <v>26</v>
       </c>
       <c r="B107" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C107" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D107" t="s" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E107" t="s" s="1">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F107" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G107" t="n" s="1">
-        <v>57.93</v>
+        <v>193.12</v>
       </c>
       <c r="H107" t="n" s="1">
-        <v>-57.93</v>
+        <v>-193.12</v>
       </c>
     </row>
     <row r="108">
@@ -3028,7 +3028,7 @@
         <v>26</v>
       </c>
       <c r="B108" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C108" t="s" s="1">
         <v>36</v>
@@ -3037,16 +3037,16 @@
         <v>118</v>
       </c>
       <c r="E108" t="s" s="1">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F108" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G108" t="n" s="1">
-        <v>19.31</v>
+        <v>38.62</v>
       </c>
       <c r="H108" t="n" s="1">
-        <v>-19.31</v>
+        <v>-38.62</v>
       </c>
     </row>
     <row r="109">
@@ -3054,25 +3054,25 @@
         <v>26</v>
       </c>
       <c r="B109" t="s" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C109" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D109" t="s" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E109" t="s" s="1">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F109" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G109" t="n" s="1">
-        <v>193.12</v>
+        <v>38.62</v>
       </c>
       <c r="H109" t="n" s="1">
-        <v>-193.12</v>
+        <v>-38.62</v>
       </c>
     </row>
     <row r="110">
@@ -3080,25 +3080,25 @@
         <v>26</v>
       </c>
       <c r="B110" t="s" s="1">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C110" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D110" t="s" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E110" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F110" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G110" t="n" s="1">
-        <v>38.62</v>
+        <v>155.01</v>
       </c>
       <c r="H110" t="n" s="1">
-        <v>-38.62</v>
+        <v>-155.01</v>
       </c>
     </row>
     <row r="111">
@@ -3106,25 +3106,25 @@
         <v>26</v>
       </c>
       <c r="B111" t="s" s="1">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C111" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D111" t="s" s="1">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E111" t="s" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F111" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G111" t="n" s="1">
-        <v>38.62</v>
+        <v>15066.07</v>
       </c>
       <c r="H111" t="n" s="1">
-        <v>-38.62</v>
+        <v>-15066.07</v>
       </c>
     </row>
     <row r="112">
@@ -3132,25 +3132,25 @@
         <v>26</v>
       </c>
       <c r="B112" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D112" t="s" s="1">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E112" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F112" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G112" t="n" s="1">
-        <v>155.01</v>
+        <v>1205.61</v>
       </c>
       <c r="H112" t="n" s="1">
-        <v>-155.01</v>
+        <v>-1205.61</v>
       </c>
     </row>
     <row r="113">
@@ -3158,25 +3158,25 @@
         <v>26</v>
       </c>
       <c r="B113" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C113" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D113" t="s" s="1">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E113" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F113" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G113" t="n" s="1">
-        <v>15066.07</v>
+        <v>1227.73</v>
       </c>
       <c r="H113" t="n" s="1">
-        <v>-15066.07</v>
+        <v>-1227.73</v>
       </c>
     </row>
     <row r="114">
@@ -3184,25 +3184,25 @@
         <v>26</v>
       </c>
       <c r="B114" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C114" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D114" t="s" s="1">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E114" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F114" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G114" t="n" s="1">
-        <v>1205.61</v>
+        <v>240.77</v>
       </c>
       <c r="H114" t="n" s="1">
-        <v>-1205.61</v>
+        <v>-240.77</v>
       </c>
     </row>
     <row r="115">
@@ -3210,25 +3210,25 @@
         <v>26</v>
       </c>
       <c r="B115" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C115" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D115" t="s" s="1">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E115" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F115" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G115" t="n" s="1">
-        <v>1227.73</v>
+        <v>245.34</v>
       </c>
       <c r="H115" t="n" s="1">
-        <v>-1227.73</v>
+        <v>-245.34</v>
       </c>
     </row>
     <row r="116">
@@ -3236,25 +3236,25 @@
         <v>26</v>
       </c>
       <c r="B116" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C116" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D116" t="s" s="1">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E116" t="s" s="1">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="F116" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G116" t="n" s="1">
-        <v>240.77</v>
+        <v>376.9</v>
       </c>
       <c r="H116" t="n" s="1">
-        <v>-240.77</v>
+        <v>-376.9</v>
       </c>
     </row>
     <row r="117">
@@ -3262,25 +3262,25 @@
         <v>26</v>
       </c>
       <c r="B117" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C117" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E117" t="s" s="1">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F117" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G117" t="n" s="1">
-        <v>245.34</v>
+        <v>423.0</v>
       </c>
       <c r="H117" t="n" s="1">
-        <v>-245.34</v>
+        <v>-423.0</v>
       </c>
     </row>
     <row r="118">
@@ -3288,25 +3288,25 @@
         <v>26</v>
       </c>
       <c r="B118" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C118" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E118" t="s" s="1">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F118" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G118" t="n" s="1">
-        <v>376.9</v>
+        <v>846.01</v>
       </c>
       <c r="H118" t="n" s="1">
-        <v>-376.9</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="119">
@@ -3314,25 +3314,25 @@
         <v>26</v>
       </c>
       <c r="B119" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C119" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D119" t="s" s="1">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E119" t="s" s="1">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F119" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G119" t="n" s="1">
-        <v>423.0</v>
+        <v>846.01</v>
       </c>
       <c r="H119" t="n" s="1">
-        <v>-423.0</v>
+        <v>-846.01</v>
       </c>
     </row>
     <row r="120">
@@ -3340,25 +3340,25 @@
         <v>26</v>
       </c>
       <c r="B120" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C120" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D120" t="s" s="1">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E120" t="s" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F120" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G120" t="n" s="1">
-        <v>846.01</v>
+        <v>96.06</v>
       </c>
       <c r="H120" t="n" s="1">
-        <v>-846.01</v>
+        <v>-96.06</v>
       </c>
     </row>
     <row r="121">
@@ -3366,25 +3366,25 @@
         <v>26</v>
       </c>
       <c r="B121" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C121" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D121" t="s" s="1">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E121" t="s" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F121" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G121" t="n" s="1">
-        <v>846.01</v>
+        <v>48.03</v>
       </c>
       <c r="H121" t="n" s="1">
-        <v>-846.01</v>
+        <v>-48.03</v>
       </c>
     </row>
     <row r="122">
@@ -3392,16 +3392,16 @@
         <v>26</v>
       </c>
       <c r="B122" t="s" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C122" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D122" t="s" s="1">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E122" t="s" s="1">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F122" t="n" s="1">
         <v>0.0</v>
@@ -3418,25 +3418,25 @@
         <v>26</v>
       </c>
       <c r="B123" t="s" s="1">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C123" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D123" t="s" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E123" t="s" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F123" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G123" t="n" s="1">
-        <v>48.03</v>
+        <v>2961.03</v>
       </c>
       <c r="H123" t="n" s="1">
-        <v>-48.03</v>
+        <v>-2961.03</v>
       </c>
     </row>
     <row r="124">
@@ -3444,25 +3444,25 @@
         <v>26</v>
       </c>
       <c r="B124" t="s" s="1">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C124" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D124" t="s" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E124" t="s" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F124" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G124" t="n" s="1">
-        <v>96.06</v>
+        <v>1269.01</v>
       </c>
       <c r="H124" t="n" s="1">
-        <v>-96.06</v>
+        <v>-1269.01</v>
       </c>
     </row>
     <row r="125">
@@ -3479,16 +3479,16 @@
         <v>128</v>
       </c>
       <c r="E125" t="s" s="1">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F125" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G125" t="n" s="1">
-        <v>2961.03</v>
+        <v>4230.04</v>
       </c>
       <c r="H125" t="n" s="1">
-        <v>-2961.03</v>
+        <v>-4230.04</v>
       </c>
     </row>
     <row r="126">
@@ -3502,19 +3502,19 @@
         <v>36</v>
       </c>
       <c r="D126" t="s" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E126" t="s" s="1">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="F126" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G126" t="n" s="1">
-        <v>1269.01</v>
+        <v>336.22</v>
       </c>
       <c r="H126" t="n" s="1">
-        <v>-1269.01</v>
+        <v>-336.22</v>
       </c>
     </row>
     <row r="127">
@@ -3528,19 +3528,19 @@
         <v>36</v>
       </c>
       <c r="D127" t="s" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E127" t="s" s="1">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F127" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G127" t="n" s="1">
-        <v>4230.04</v>
+        <v>144.09</v>
       </c>
       <c r="H127" t="n" s="1">
-        <v>-4230.04</v>
+        <v>-144.09</v>
       </c>
     </row>
     <row r="128">
@@ -3554,19 +3554,19 @@
         <v>36</v>
       </c>
       <c r="D128" t="s" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E128" t="s" s="1">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="F128" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G128" t="n" s="1">
-        <v>336.22</v>
+        <v>480.31</v>
       </c>
       <c r="H128" t="n" s="1">
-        <v>-336.22</v>
+        <v>-480.31</v>
       </c>
     </row>
     <row r="129">
@@ -3574,25 +3574,25 @@
         <v>26</v>
       </c>
       <c r="B129" t="s" s="1">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C129" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D129" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="E129" t="s" s="1">
         <v>127</v>
       </c>
-      <c r="E129" t="s" s="1">
-        <v>54</v>
-      </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>144.09</v>
+        <v>1801.15</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-144.09</v>
+        <v>-1801.15</v>
       </c>
     </row>
     <row r="130">
@@ -3600,25 +3600,25 @@
         <v>26</v>
       </c>
       <c r="B130" t="s" s="1">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C130" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D130" t="s" s="1">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="F130" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>480.31</v>
+        <v>5165.75</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>-480.31</v>
+        <v>-5165.75</v>
       </c>
     </row>
     <row r="131">
@@ -3629,22 +3629,22 @@
         <v>133</v>
       </c>
       <c r="C131" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s" s="1">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E131" t="s" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F131" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G131" t="n" s="1">
-        <v>1801.15</v>
+        <v>527.98</v>
       </c>
       <c r="H131" t="n" s="1">
-        <v>-1801.15</v>
+        <v>-527.98</v>
       </c>
     </row>
     <row r="132">
@@ -3655,22 +3655,22 @@
         <v>133</v>
       </c>
       <c r="C132" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D132" t="s" s="1">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G132" t="n" s="1">
-        <v>5165.75</v>
+        <v>263.99</v>
       </c>
       <c r="H132" t="n" s="1">
-        <v>-5165.75</v>
+        <v>-263.99</v>
       </c>
     </row>
     <row r="133">
@@ -3684,10 +3684,10 @@
         <v>36</v>
       </c>
       <c r="D133" t="s" s="1">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E133" t="s" s="1">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F133" t="n" s="1">
         <v>0.0</v>
@@ -3704,25 +3704,25 @@
         <v>26</v>
       </c>
       <c r="B134" t="s" s="1">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C134" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D134" t="s" s="1">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E134" t="s" s="1">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F134" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G134" t="n" s="1">
-        <v>263.99</v>
+        <v>113.21</v>
       </c>
       <c r="H134" t="n" s="1">
-        <v>-263.99</v>
+        <v>-113.21</v>
       </c>
     </row>
     <row r="135">
@@ -3730,25 +3730,25 @@
         <v>26</v>
       </c>
       <c r="B135" t="s" s="1">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C135" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D135" t="s" s="1">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E135" t="s" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F135" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G135" t="n" s="1">
-        <v>527.98</v>
+        <v>191.08</v>
       </c>
       <c r="H135" t="n" s="1">
-        <v>-527.98</v>
+        <v>-191.08</v>
       </c>
     </row>
     <row r="136">
@@ -3759,22 +3759,22 @@
         <v>137</v>
       </c>
       <c r="C136" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D136" t="s" s="1">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E136" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F136" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G136" t="n" s="1">
-        <v>113.21</v>
+        <v>9.23</v>
       </c>
       <c r="H136" t="n" s="1">
-        <v>-113.21</v>
+        <v>-9.23</v>
       </c>
     </row>
     <row r="137">
@@ -3785,22 +3785,22 @@
         <v>137</v>
       </c>
       <c r="C137" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D137" t="s" s="1">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E137" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F137" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G137" t="n" s="1">
-        <v>191.08</v>
+        <v>9.05</v>
       </c>
       <c r="H137" t="n" s="1">
-        <v>-191.08</v>
+        <v>-9.05</v>
       </c>
     </row>
     <row r="138">
@@ -3814,7 +3814,7 @@
         <v>31</v>
       </c>
       <c r="D138" t="s" s="1">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E138" t="s" s="1">
         <v>33</v>
@@ -3823,10 +3823,10 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n" s="1">
-        <v>9.23</v>
+        <v>15.3</v>
       </c>
       <c r="H138" t="n" s="1">
-        <v>-9.23</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="139">
@@ -3840,7 +3840,7 @@
         <v>31</v>
       </c>
       <c r="D139" t="s" s="1">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E139" t="s" s="1">
         <v>35</v>
@@ -3849,10 +3849,10 @@
         <v>0.0</v>
       </c>
       <c r="G139" t="n" s="1">
-        <v>9.05</v>
+        <v>15.56</v>
       </c>
       <c r="H139" t="n" s="1">
-        <v>-9.05</v>
+        <v>-15.56</v>
       </c>
     </row>
     <row r="140">
@@ -3863,22 +3863,22 @@
         <v>137</v>
       </c>
       <c r="C140" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s" s="1">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E140" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F140" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G140" t="n" s="1">
-        <v>15.3</v>
+        <v>1847.92</v>
       </c>
       <c r="H140" t="n" s="1">
-        <v>-15.3</v>
+        <v>-1847.92</v>
       </c>
     </row>
     <row r="141">
@@ -3889,22 +3889,22 @@
         <v>137</v>
       </c>
       <c r="C141" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D141" t="s" s="1">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E141" t="s" s="1">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F141" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G141" t="n" s="1">
-        <v>15.56</v>
+        <v>2639.89</v>
       </c>
       <c r="H141" t="n" s="1">
-        <v>-15.56</v>
+        <v>-2639.89</v>
       </c>
     </row>
     <row r="142">
@@ -3912,25 +3912,25 @@
         <v>26</v>
       </c>
       <c r="B142" t="s" s="1">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C142" t="s" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D142" t="s" s="1">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E142" t="s" s="1">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F142" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G142" t="n" s="1">
-        <v>1847.92</v>
+        <v>180.0</v>
       </c>
       <c r="H142" t="n" s="1">
-        <v>-1847.92</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="143">
@@ -3938,25 +3938,25 @@
         <v>26</v>
       </c>
       <c r="B143" t="s" s="1">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C143" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D143" t="s" s="1">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="E143" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F143" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G143" t="n" s="1">
-        <v>2639.89</v>
+        <v>9216.24</v>
       </c>
       <c r="H143" t="n" s="1">
-        <v>-2639.89</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="144">
@@ -3964,25 +3964,25 @@
         <v>26</v>
       </c>
       <c r="B144" t="s" s="1">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C144" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D144" t="s" s="1">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="E144" t="s" s="1">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F144" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G144" t="n" s="1">
-        <v>180.0</v>
+        <v>891.0</v>
       </c>
       <c r="H144" t="n" s="1">
-        <v>-180.0</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="145">
@@ -3993,22 +3993,22 @@
         <v>146</v>
       </c>
       <c r="C145" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D145" t="s" s="1">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E145" t="s" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F145" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G145" t="n" s="1">
-        <v>9216.24</v>
+        <v>737.28</v>
       </c>
       <c r="H145" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="146">
@@ -4019,22 +4019,22 @@
         <v>146</v>
       </c>
       <c r="C146" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D146" t="s" s="1">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="E146" t="s" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F146" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G146" t="n" s="1">
-        <v>891.0</v>
+        <v>750.99</v>
       </c>
       <c r="H146" t="n" s="1">
-        <v>-891.0</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="147">
@@ -4042,25 +4042,25 @@
         <v>26</v>
       </c>
       <c r="B147" t="s" s="1">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C147" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D147" t="s" s="1">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E147" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F147" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G147" t="n" s="1">
-        <v>737.28</v>
+        <v>1544.4</v>
       </c>
       <c r="H147" t="n" s="1">
-        <v>-737.28</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="148">
@@ -4068,25 +4068,25 @@
         <v>26</v>
       </c>
       <c r="B148" t="s" s="1">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C148" t="s" s="1">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D148" t="s" s="1">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E148" t="s" s="1">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="F148" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G148" t="n" s="1">
-        <v>750.99</v>
+        <v>1925.0</v>
       </c>
       <c r="H148" t="n" s="1">
-        <v>-750.99</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="149">
@@ -4097,22 +4097,22 @@
         <v>148</v>
       </c>
       <c r="C149" t="s" s="1">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D149" t="s" s="1">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E149" t="s" s="1">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F149" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G149" t="n" s="1">
-        <v>1544.4</v>
+        <v>180.0</v>
       </c>
       <c r="H149" t="n" s="1">
-        <v>-1544.4</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="150">
@@ -4123,22 +4123,22 @@
         <v>148</v>
       </c>
       <c r="C150" t="s" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D150" t="s" s="1">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E150" t="s" s="1">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="F150" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G150" t="n" s="1">
-        <v>1925.0</v>
+        <v>180.0</v>
       </c>
       <c r="H150" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="151">
@@ -4146,25 +4146,25 @@
         <v>26</v>
       </c>
       <c r="B151" t="s" s="1">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C151" t="s" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D151" t="s" s="1">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="E151" t="s" s="1">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="F151" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G151" t="n" s="1">
-        <v>180.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H151" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="152">
@@ -4172,16 +4172,16 @@
         <v>26</v>
       </c>
       <c r="B152" t="s" s="1">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C152" t="s" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D152" t="s" s="1">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E152" t="s" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F152" t="n" s="1">
         <v>0.0</v>
@@ -4201,22 +4201,22 @@
         <v>151</v>
       </c>
       <c r="C153" t="s" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D153" t="s" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E153" t="s" s="1">
-        <v>153</v>
+        <v>63</v>
       </c>
       <c r="F153" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G153" t="n" s="1">
-        <v>1201.89</v>
+        <v>180.0</v>
       </c>
       <c r="H153" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="154">
@@ -4224,25 +4224,25 @@
         <v>26</v>
       </c>
       <c r="B154" t="s" s="1">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C154" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D154" t="s" s="1">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E154" t="s" s="1">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="F154" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G154" t="n" s="1">
-        <v>180.0</v>
+        <v>25504.78</v>
       </c>
       <c r="H154" t="n" s="1">
-        <v>-180.0</v>
+        <v>-25504.78</v>
       </c>
     </row>
     <row r="155">
@@ -4250,25 +4250,25 @@
         <v>26</v>
       </c>
       <c r="B155" t="s" s="1">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C155" t="s" s="1">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D155" t="s" s="1">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="E155" t="s" s="1">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F155" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G155" t="n" s="1">
-        <v>180.0</v>
+        <v>2277.0</v>
       </c>
       <c r="H155" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2277.0</v>
       </c>
     </row>
     <row r="156">
@@ -4279,22 +4279,22 @@
         <v>155</v>
       </c>
       <c r="C156" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D156" t="s" s="1">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="E156" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F156" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G156" t="n" s="1">
-        <v>25504.78</v>
+        <v>2078.64</v>
       </c>
       <c r="H156" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-2078.64</v>
       </c>
     </row>
     <row r="157">
@@ -4305,22 +4305,22 @@
         <v>155</v>
       </c>
       <c r="C157" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D157" t="s" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E157" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F157" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G157" t="n" s="1">
-        <v>2277.0</v>
+        <v>2040.52</v>
       </c>
       <c r="H157" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-2040.52</v>
       </c>
     </row>
     <row r="158">
@@ -4331,22 +4331,22 @@
         <v>155</v>
       </c>
       <c r="C158" t="s" s="1">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D158" t="s" s="1">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="E158" t="s" s="1">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="F158" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G158" t="n" s="1">
-        <v>2078.64</v>
+        <v>180.0</v>
       </c>
       <c r="H158" t="n" s="1">
-        <v>-2078.64</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="159">
@@ -4354,25 +4354,25 @@
         <v>26</v>
       </c>
       <c r="B159" t="s" s="1">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C159" t="s" s="1">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D159" t="s" s="1">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="E159" t="s" s="1">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F159" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G159" t="n" s="1">
-        <v>2040.52</v>
+        <v>180.0</v>
       </c>
       <c r="H159" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="160">
@@ -4380,25 +4380,25 @@
         <v>26</v>
       </c>
       <c r="B160" t="s" s="1">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C160" t="s" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D160" t="s" s="1">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="E160" t="s" s="1">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="F160" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G160" t="n" s="1">
-        <v>180.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H160" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1000.0</v>
       </c>
     </row>
     <row r="161">
@@ -4406,100 +4406,48 @@
         <v>26</v>
       </c>
       <c r="B161" t="s" s="1">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C161" t="s" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D161" t="s" s="1">
-        <v>158</v>
+        <v>44</v>
       </c>
       <c r="E161" t="s" s="1">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="F161" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G161" t="n" s="1">
-        <v>180.0</v>
+        <v>3750.0</v>
       </c>
       <c r="H161" t="n" s="1">
-        <v>-180.0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B162" t="s" s="1">
-        <v>159</v>
-      </c>
-      <c r="C162" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D162" t="s" s="1">
-        <v>44</v>
-      </c>
-      <c r="E162" t="s" s="1">
-        <v>160</v>
-      </c>
-      <c r="F162" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G162" t="n" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="H162" t="n" s="1">
-        <v>-1000.0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="B163" t="s" s="1">
-        <v>159</v>
-      </c>
-      <c r="C163" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="D163" t="s" s="1">
-        <v>46</v>
-      </c>
-      <c r="E163" t="s" s="1">
-        <v>161</v>
-      </c>
-      <c r="F163" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G163" t="n" s="1">
-        <v>3750.0</v>
-      </c>
-      <c r="H163" t="n" s="1">
         <v>-3750.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B168" s="3" t="s">
         <v>167</v>
       </c>
     </row>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="173">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -111,18 +111,18 @@
     <t>PCP-Previsão do Contas a Pagar</t>
   </si>
   <si>
+    <t>1629 - 3</t>
+  </si>
+  <si>
+    <t>RODAG TRANSPORTES LTDA*</t>
+  </si>
+  <si>
     <t>1629 - 2</t>
   </si>
   <si>
     <t>ENTREGADORA NOVO RUMO LTDA ME</t>
   </si>
   <si>
-    <t>1629 - 3</t>
-  </si>
-  <si>
-    <t>RODAG TRANSPORTES LTDA*</t>
-  </si>
-  <si>
     <t>PPC-Previsão de Pagamento de Comissão</t>
   </si>
   <si>
@@ -150,18 +150,18 @@
     <t>1 - 9</t>
   </si>
   <si>
+    <t>100901 - 1</t>
+  </si>
+  <si>
+    <t>TERESINHA ELVIRA MAXIMINO DE MENEZES</t>
+  </si>
+  <si>
     <t>100901 - 2</t>
   </si>
   <si>
-    <t>100901 - 1</t>
-  </si>
-  <si>
     <t>THIAGO MAXIMINO DE MENEZES PASSOS</t>
   </si>
   <si>
-    <t>TERESINHA ELVIRA MAXIMINO DE MENEZES</t>
-  </si>
-  <si>
     <t>102301 - 1</t>
   </si>
   <si>
@@ -183,10 +183,13 @@
     <t>07/10/2026</t>
   </si>
   <si>
+    <t>102901 - 2</t>
+  </si>
+  <si>
     <t>102901 - 1</t>
   </si>
   <si>
-    <t>102901 - 2</t>
+    <t>103501 - 1</t>
   </si>
   <si>
     <t>103501 - 2</t>
@@ -195,9 +198,6 @@
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
-    <t>103501 - 1</t>
-  </si>
-  <si>
     <t>08/10/2026</t>
   </si>
   <si>
@@ -231,18 +231,18 @@
     <t>92801 - 0</t>
   </si>
   <si>
+    <t>96601 - 2</t>
+  </si>
+  <si>
     <t>96601 - 3</t>
   </si>
   <si>
-    <t>96601 - 2</t>
+    <t>101401 - 2</t>
   </si>
   <si>
     <t>101401 - 3</t>
   </si>
   <si>
-    <t>101401 - 2</t>
-  </si>
-  <si>
     <t>10/10/2026</t>
   </si>
   <si>
@@ -300,30 +300,30 @@
     <t>1631 - 3</t>
   </si>
   <si>
+    <t>1632 - 2</t>
+  </si>
+  <si>
     <t>1632 - 3</t>
   </si>
   <si>
-    <t>1632 - 2</t>
+    <t>1633 - 3</t>
   </si>
   <si>
     <t>1633 - 2</t>
   </si>
   <si>
-    <t>1633 - 3</t>
-  </si>
-  <si>
     <t>1634 - 3</t>
   </si>
   <si>
     <t>1634 - 2</t>
   </si>
   <si>
+    <t>101201 - 2</t>
+  </si>
+  <si>
     <t>101201 - 3</t>
   </si>
   <si>
-    <t>101201 - 2</t>
-  </si>
-  <si>
     <t>101801 - 2</t>
   </si>
   <si>
@@ -459,6 +459,21 @@
     <t>102301 - 3</t>
   </si>
   <si>
+    <t>24/10/2026</t>
+  </si>
+  <si>
+    <t>105501 - 1</t>
+  </si>
+  <si>
+    <t>105701 - 1</t>
+  </si>
+  <si>
+    <t>105501 - 2</t>
+  </si>
+  <si>
+    <t>105701 - 2</t>
+  </si>
+  <si>
     <t>25/10/2026</t>
   </si>
   <si>
@@ -510,13 +525,13 @@
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>229.463,96</t>
+    <t>248.133,43</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-229.463,96</t>
+    <t>-248.133,43</t>
   </si>
 </sst>
 </file>
@@ -584,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H166"/>
+  <dimension ref="A2:H180"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -755,10 +770,10 @@
         <v>0.0</v>
       </c>
       <c r="G20" t="n" s="1">
-        <v>32.31</v>
+        <v>32.88</v>
       </c>
       <c r="H20" t="n" s="1">
-        <v>-32.31</v>
+        <v>-32.88</v>
       </c>
     </row>
     <row r="21">
@@ -781,10 +796,10 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n" s="1">
-        <v>32.88</v>
+        <v>32.31</v>
       </c>
       <c r="H21" t="n" s="1">
-        <v>-32.88</v>
+        <v>-32.31</v>
       </c>
     </row>
     <row r="22">
@@ -905,16 +920,16 @@
         <v>45</v>
       </c>
       <c r="E26" t="s" s="1">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F26" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G26" t="n" s="1">
-        <v>1215.9</v>
+        <v>607.95</v>
       </c>
       <c r="H26" t="n" s="1">
-        <v>-1215.9</v>
+        <v>-607.95</v>
       </c>
     </row>
     <row r="27">
@@ -928,10 +943,10 @@
         <v>36</v>
       </c>
       <c r="D27" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s" s="1">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n" s="1">
         <v>0.0</v>
@@ -954,7 +969,7 @@
         <v>36</v>
       </c>
       <c r="D28" t="s" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s" s="1">
         <v>48</v>
@@ -963,10 +978,10 @@
         <v>0.0</v>
       </c>
       <c r="G28" t="n" s="1">
-        <v>607.95</v>
+        <v>1215.9</v>
       </c>
       <c r="H28" t="n" s="1">
-        <v>-607.95</v>
+        <v>-1215.9</v>
       </c>
     </row>
     <row r="29">
@@ -983,16 +998,16 @@
         <v>49</v>
       </c>
       <c r="E29" t="s" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F29" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G29" t="n" s="1">
-        <v>444.12</v>
+        <v>222.06</v>
       </c>
       <c r="H29" t="n" s="1">
-        <v>-444.12</v>
+        <v>-222.06</v>
       </c>
     </row>
     <row r="30">
@@ -1041,10 +1056,10 @@
         <v>0.0</v>
       </c>
       <c r="G31" t="n" s="1">
-        <v>222.06</v>
+        <v>444.12</v>
       </c>
       <c r="H31" t="n" s="1">
-        <v>-222.06</v>
+        <v>-444.12</v>
       </c>
     </row>
     <row r="32">
@@ -1058,7 +1073,7 @@
         <v>36</v>
       </c>
       <c r="D32" t="s" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s" s="1">
         <v>52</v>
@@ -1084,7 +1099,7 @@
         <v>36</v>
       </c>
       <c r="D33" t="s" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s" s="1">
         <v>53</v>
@@ -1110,7 +1125,7 @@
         <v>36</v>
       </c>
       <c r="D34" t="s" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s" s="1">
         <v>38</v>
@@ -1139,16 +1154,16 @@
         <v>49</v>
       </c>
       <c r="E35" t="s" s="1">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F35" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G35" t="n" s="1">
-        <v>1554.41</v>
+        <v>2220.59</v>
       </c>
       <c r="H35" t="n" s="1">
-        <v>-1554.41</v>
+        <v>-2220.59</v>
       </c>
     </row>
     <row r="36">
@@ -1165,16 +1180,16 @@
         <v>49</v>
       </c>
       <c r="E36" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G36" t="n" s="1">
-        <v>666.18</v>
+        <v>1554.41</v>
       </c>
       <c r="H36" t="n" s="1">
-        <v>-666.18</v>
+        <v>-1554.41</v>
       </c>
     </row>
     <row r="37">
@@ -1191,16 +1206,16 @@
         <v>49</v>
       </c>
       <c r="E37" t="s" s="1">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F37" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G37" t="n" s="1">
-        <v>2220.59</v>
+        <v>666.18</v>
       </c>
       <c r="H37" t="n" s="1">
-        <v>-2220.59</v>
+        <v>-666.18</v>
       </c>
     </row>
     <row r="38">
@@ -1217,7 +1232,7 @@
         <v>56</v>
       </c>
       <c r="E38" t="s" s="1">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F38" t="n" s="1">
         <v>0.0</v>
@@ -1240,7 +1255,7 @@
         <v>36</v>
       </c>
       <c r="D39" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E39" t="s" s="1">
         <v>48</v>
@@ -1249,10 +1264,10 @@
         <v>0.0</v>
       </c>
       <c r="G39" t="n" s="1">
-        <v>1.78</v>
+        <v>3.56</v>
       </c>
       <c r="H39" t="n" s="1">
-        <v>-1.78</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="40">
@@ -1269,16 +1284,16 @@
         <v>57</v>
       </c>
       <c r="E40" t="s" s="1">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F40" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G40" t="n" s="1">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="H40" t="n" s="1">
-        <v>-3.56</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="41">
@@ -1295,16 +1310,16 @@
         <v>58</v>
       </c>
       <c r="E41" t="s" s="1">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F41" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G41" t="n" s="1">
-        <v>66.4</v>
+        <v>33.2</v>
       </c>
       <c r="H41" t="n" s="1">
-        <v>-66.4</v>
+        <v>-33.2</v>
       </c>
     </row>
     <row r="42">
@@ -1318,10 +1333,10 @@
         <v>36</v>
       </c>
       <c r="D42" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="E42" t="s" s="1">
         <v>60</v>
-      </c>
-      <c r="E42" t="s" s="1">
-        <v>47</v>
       </c>
       <c r="F42" t="n" s="1">
         <v>0.0</v>
@@ -1344,7 +1359,7 @@
         <v>36</v>
       </c>
       <c r="D43" t="s" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E43" t="s" s="1">
         <v>48</v>
@@ -1353,10 +1368,10 @@
         <v>0.0</v>
       </c>
       <c r="G43" t="n" s="1">
-        <v>33.2</v>
+        <v>66.4</v>
       </c>
       <c r="H43" t="n" s="1">
-        <v>-33.2</v>
+        <v>-66.4</v>
       </c>
     </row>
     <row r="44">
@@ -1396,7 +1411,7 @@
         <v>36</v>
       </c>
       <c r="D45" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E45" t="s" s="1">
         <v>64</v>
@@ -1422,7 +1437,7 @@
         <v>36</v>
       </c>
       <c r="D46" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E46" t="s" s="1">
         <v>38</v>
@@ -1448,19 +1463,19 @@
         <v>36</v>
       </c>
       <c r="D47" t="s" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E47" t="s" s="1">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F47" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G47" t="n" s="1">
-        <v>332.0</v>
+        <v>232.4</v>
       </c>
       <c r="H47" t="n" s="1">
-        <v>-332.0</v>
+        <v>-232.4</v>
       </c>
     </row>
     <row r="48">
@@ -1474,7 +1489,7 @@
         <v>36</v>
       </c>
       <c r="D48" t="s" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E48" t="s" s="1">
         <v>53</v>
@@ -1500,19 +1515,19 @@
         <v>36</v>
       </c>
       <c r="D49" t="s" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" t="s" s="1">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F49" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G49" t="n" s="1">
-        <v>232.4</v>
+        <v>332.0</v>
       </c>
       <c r="H49" t="n" s="1">
-        <v>-232.4</v>
+        <v>-332.0</v>
       </c>
     </row>
     <row r="50">
@@ -1639,10 +1654,10 @@
         <v>0.0</v>
       </c>
       <c r="G54" t="n" s="1">
-        <v>1237.52</v>
+        <v>1214.79</v>
       </c>
       <c r="H54" t="n" s="1">
-        <v>-1237.52</v>
+        <v>-1214.79</v>
       </c>
     </row>
     <row r="55">
@@ -1665,10 +1680,10 @@
         <v>0.0</v>
       </c>
       <c r="G55" t="n" s="1">
-        <v>1214.79</v>
+        <v>1237.52</v>
       </c>
       <c r="H55" t="n" s="1">
-        <v>-1214.79</v>
+        <v>-1237.52</v>
       </c>
     </row>
     <row r="56">
@@ -1691,10 +1706,10 @@
         <v>0.0</v>
       </c>
       <c r="G56" t="n" s="1">
-        <v>997.38</v>
+        <v>979.59</v>
       </c>
       <c r="H56" t="n" s="1">
-        <v>-997.38</v>
+        <v>-979.59</v>
       </c>
     </row>
     <row r="57">
@@ -1717,10 +1732,10 @@
         <v>0.0</v>
       </c>
       <c r="G57" t="n" s="1">
-        <v>979.59</v>
+        <v>997.38</v>
       </c>
       <c r="H57" t="n" s="1">
-        <v>-979.59</v>
+        <v>-997.38</v>
       </c>
     </row>
     <row r="58">
@@ -1737,7 +1752,7 @@
         <v>77</v>
       </c>
       <c r="E58" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F58" t="n" s="1">
         <v>0.0</v>
@@ -1763,7 +1778,7 @@
         <v>78</v>
       </c>
       <c r="E59" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n" s="1">
         <v>0.0</v>
@@ -1867,7 +1882,7 @@
         <v>83</v>
       </c>
       <c r="E63" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F63" t="n" s="1">
         <v>0.0</v>
@@ -1893,7 +1908,7 @@
         <v>84</v>
       </c>
       <c r="E64" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n" s="1">
         <v>0.0</v>
@@ -1919,7 +1934,7 @@
         <v>85</v>
       </c>
       <c r="E65" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F65" t="n" s="1">
         <v>0.0</v>
@@ -1945,7 +1960,7 @@
         <v>86</v>
       </c>
       <c r="E66" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F66" t="n" s="1">
         <v>0.0</v>
@@ -2101,7 +2116,7 @@
         <v>93</v>
       </c>
       <c r="E72" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F72" t="n" s="1">
         <v>0.0</v>
@@ -2127,7 +2142,7 @@
         <v>94</v>
       </c>
       <c r="E73" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n" s="1">
         <v>0.0</v>
@@ -2159,10 +2174,10 @@
         <v>0.0</v>
       </c>
       <c r="G74" t="n" s="1">
-        <v>18.64</v>
+        <v>18.3</v>
       </c>
       <c r="H74" t="n" s="1">
-        <v>-18.64</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="75">
@@ -2185,10 +2200,10 @@
         <v>0.0</v>
       </c>
       <c r="G75" t="n" s="1">
-        <v>18.3</v>
+        <v>18.64</v>
       </c>
       <c r="H75" t="n" s="1">
-        <v>-18.3</v>
+        <v>-18.64</v>
       </c>
     </row>
     <row r="76">
@@ -2211,10 +2226,10 @@
         <v>0.0</v>
       </c>
       <c r="G76" t="n" s="1">
-        <v>30.25</v>
+        <v>30.82</v>
       </c>
       <c r="H76" t="n" s="1">
-        <v>-30.25</v>
+        <v>-30.82</v>
       </c>
     </row>
     <row r="77">
@@ -2237,10 +2252,10 @@
         <v>0.0</v>
       </c>
       <c r="G77" t="n" s="1">
-        <v>30.82</v>
+        <v>30.25</v>
       </c>
       <c r="H77" t="n" s="1">
-        <v>-30.82</v>
+        <v>-30.25</v>
       </c>
     </row>
     <row r="78">
@@ -2257,7 +2272,7 @@
         <v>99</v>
       </c>
       <c r="E78" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" t="n" s="1">
         <v>0.0</v>
@@ -2283,7 +2298,7 @@
         <v>100</v>
       </c>
       <c r="E79" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n" s="1">
         <v>0.0</v>
@@ -2315,10 +2330,10 @@
         <v>0.0</v>
       </c>
       <c r="G80" t="n" s="1">
-        <v>498.88</v>
+        <v>489.47</v>
       </c>
       <c r="H80" t="n" s="1">
-        <v>-498.88</v>
+        <v>-489.47</v>
       </c>
     </row>
     <row r="81">
@@ -2341,10 +2356,10 @@
         <v>0.0</v>
       </c>
       <c r="G81" t="n" s="1">
-        <v>489.47</v>
+        <v>498.88</v>
       </c>
       <c r="H81" t="n" s="1">
-        <v>-489.47</v>
+        <v>-498.88</v>
       </c>
     </row>
     <row r="82">
@@ -2361,7 +2376,7 @@
         <v>103</v>
       </c>
       <c r="E82" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F82" t="n" s="1">
         <v>0.0</v>
@@ -2387,7 +2402,7 @@
         <v>104</v>
       </c>
       <c r="E83" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F83" t="n" s="1">
         <v>0.0</v>
@@ -2439,7 +2454,7 @@
         <v>107</v>
       </c>
       <c r="E85" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F85" t="n" s="1">
         <v>0.0</v>
@@ -2465,7 +2480,7 @@
         <v>108</v>
       </c>
       <c r="E86" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F86" t="n" s="1">
         <v>0.0</v>
@@ -2491,7 +2506,7 @@
         <v>109</v>
       </c>
       <c r="E87" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F87" t="n" s="1">
         <v>0.0</v>
@@ -2543,7 +2558,7 @@
         <v>109</v>
       </c>
       <c r="E89" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F89" t="n" s="1">
         <v>0.0</v>
@@ -2569,7 +2584,7 @@
         <v>110</v>
       </c>
       <c r="E90" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F90" t="n" s="1">
         <v>0.0</v>
@@ -2621,7 +2636,7 @@
         <v>110</v>
       </c>
       <c r="E92" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F92" t="n" s="1">
         <v>0.0</v>
@@ -2673,7 +2688,7 @@
         <v>113</v>
       </c>
       <c r="E94" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F94" t="n" s="1">
         <v>0.0</v>
@@ -2699,7 +2714,7 @@
         <v>113</v>
       </c>
       <c r="E95" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F95" t="n" s="1">
         <v>0.0</v>
@@ -2985,7 +3000,7 @@
         <v>117</v>
       </c>
       <c r="E106" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F106" t="n" s="1">
         <v>0.0</v>
@@ -3063,7 +3078,7 @@
         <v>117</v>
       </c>
       <c r="E109" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F109" t="n" s="1">
         <v>0.0</v>
@@ -3141,7 +3156,7 @@
         <v>122</v>
       </c>
       <c r="E112" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F112" t="n" s="1">
         <v>0.0</v>
@@ -3167,7 +3182,7 @@
         <v>123</v>
       </c>
       <c r="E113" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F113" t="n" s="1">
         <v>0.0</v>
@@ -3193,7 +3208,7 @@
         <v>124</v>
       </c>
       <c r="E114" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F114" t="n" s="1">
         <v>0.0</v>
@@ -3219,7 +3234,7 @@
         <v>125</v>
       </c>
       <c r="E115" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F115" t="n" s="1">
         <v>0.0</v>
@@ -3271,7 +3286,7 @@
         <v>128</v>
       </c>
       <c r="E117" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F117" t="n" s="1">
         <v>0.0</v>
@@ -3297,7 +3312,7 @@
         <v>128</v>
       </c>
       <c r="E118" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F118" t="n" s="1">
         <v>0.0</v>
@@ -3375,7 +3390,7 @@
         <v>126</v>
       </c>
       <c r="E121" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F121" t="n" s="1">
         <v>0.0</v>
@@ -3401,7 +3416,7 @@
         <v>126</v>
       </c>
       <c r="E122" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F122" t="n" s="1">
         <v>0.0</v>
@@ -3661,7 +3676,7 @@
         <v>134</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
@@ -3687,7 +3702,7 @@
         <v>134</v>
       </c>
       <c r="E133" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F133" t="n" s="1">
         <v>0.0</v>
@@ -3765,7 +3780,7 @@
         <v>140</v>
       </c>
       <c r="E136" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F136" t="n" s="1">
         <v>0.0</v>
@@ -3791,7 +3806,7 @@
         <v>141</v>
       </c>
       <c r="E137" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F137" t="n" s="1">
         <v>0.0</v>
@@ -3817,7 +3832,7 @@
         <v>142</v>
       </c>
       <c r="E138" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F138" t="n" s="1">
         <v>0.0</v>
@@ -3843,7 +3858,7 @@
         <v>143</v>
       </c>
       <c r="E139" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F139" t="n" s="1">
         <v>0.0</v>
@@ -3947,16 +3962,16 @@
         <v>49</v>
       </c>
       <c r="E143" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F143" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G143" t="n" s="1">
-        <v>9216.24</v>
+        <v>891.0</v>
       </c>
       <c r="H143" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="144">
@@ -3973,16 +3988,16 @@
         <v>49</v>
       </c>
       <c r="E144" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F144" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G144" t="n" s="1">
-        <v>891.0</v>
+        <v>9216.24</v>
       </c>
       <c r="H144" t="n" s="1">
-        <v>-891.0</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="145">
@@ -3999,7 +4014,7 @@
         <v>50</v>
       </c>
       <c r="E145" t="s" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F145" t="n" s="1">
         <v>0.0</v>
@@ -4025,7 +4040,7 @@
         <v>147</v>
       </c>
       <c r="E146" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F146" t="n" s="1">
         <v>0.0</v>
@@ -4048,19 +4063,19 @@
         <v>31</v>
       </c>
       <c r="D147" t="s" s="1">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="E147" t="s" s="1">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F147" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G147" t="n" s="1">
-        <v>1544.4</v>
+        <v>7260.81</v>
       </c>
       <c r="H147" t="n" s="1">
-        <v>-1544.4</v>
+        <v>-7260.81</v>
       </c>
     </row>
     <row r="148">
@@ -4071,22 +4086,22 @@
         <v>148</v>
       </c>
       <c r="C148" t="s" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D148" t="s" s="1">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E148" t="s" s="1">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="F148" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G148" t="n" s="1">
-        <v>1925.0</v>
+        <v>1779.4</v>
       </c>
       <c r="H148" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-1779.4</v>
       </c>
     </row>
     <row r="149">
@@ -4097,22 +4112,22 @@
         <v>148</v>
       </c>
       <c r="C149" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D149" t="s" s="1">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="E149" t="s" s="1">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F149" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G149" t="n" s="1">
-        <v>180.0</v>
+        <v>543.98</v>
       </c>
       <c r="H149" t="n" s="1">
-        <v>-180.0</v>
+        <v>-543.98</v>
       </c>
     </row>
     <row r="150">
@@ -4123,22 +4138,22 @@
         <v>148</v>
       </c>
       <c r="C150" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D150" t="s" s="1">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E150" t="s" s="1">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F150" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G150" t="n" s="1">
-        <v>180.0</v>
+        <v>543.98</v>
       </c>
       <c r="H150" t="n" s="1">
-        <v>-180.0</v>
+        <v>-543.98</v>
       </c>
     </row>
     <row r="151">
@@ -4146,25 +4161,25 @@
         <v>26</v>
       </c>
       <c r="B151" t="s" s="1">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C151" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D151" t="s" s="1">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E151" t="s" s="1">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="F151" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G151" t="n" s="1">
-        <v>1201.89</v>
+        <v>271.99</v>
       </c>
       <c r="H151" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-271.99</v>
       </c>
     </row>
     <row r="152">
@@ -4172,25 +4187,25 @@
         <v>26</v>
       </c>
       <c r="B152" t="s" s="1">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C152" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D152" t="s" s="1">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="E152" t="s" s="1">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="F152" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G152" t="n" s="1">
-        <v>180.0</v>
+        <v>113.18</v>
       </c>
       <c r="H152" t="n" s="1">
-        <v>-180.0</v>
+        <v>-113.18</v>
       </c>
     </row>
     <row r="153">
@@ -4198,25 +4213,25 @@
         <v>26</v>
       </c>
       <c r="B153" t="s" s="1">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C153" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D153" t="s" s="1">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E153" t="s" s="1">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F153" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G153" t="n" s="1">
-        <v>180.0</v>
+        <v>226.36</v>
       </c>
       <c r="H153" t="n" s="1">
-        <v>-180.0</v>
+        <v>-226.36</v>
       </c>
     </row>
     <row r="154">
@@ -4224,25 +4239,25 @@
         <v>26</v>
       </c>
       <c r="B154" t="s" s="1">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C154" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D154" t="s" s="1">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="E154" t="s" s="1">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F154" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G154" t="n" s="1">
-        <v>25504.78</v>
+        <v>226.36</v>
       </c>
       <c r="H154" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-226.36</v>
       </c>
     </row>
     <row r="155">
@@ -4250,13 +4265,13 @@
         <v>26</v>
       </c>
       <c r="B155" t="s" s="1">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C155" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D155" t="s" s="1">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E155" t="s" s="1">
         <v>38</v>
@@ -4265,10 +4280,10 @@
         <v>0.0</v>
       </c>
       <c r="G155" t="n" s="1">
-        <v>2277.0</v>
+        <v>1544.4</v>
       </c>
       <c r="H155" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="156">
@@ -4276,25 +4291,25 @@
         <v>26</v>
       </c>
       <c r="B156" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="C156" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D156" t="s" s="1">
+        <v>154</v>
+      </c>
+      <c r="E156" t="s" s="1">
         <v>155</v>
       </c>
-      <c r="C156" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D156" t="s" s="1">
-        <v>156</v>
-      </c>
-      <c r="E156" t="s" s="1">
-        <v>35</v>
-      </c>
       <c r="F156" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G156" t="n" s="1">
-        <v>2078.64</v>
+        <v>1925.0</v>
       </c>
       <c r="H156" t="n" s="1">
-        <v>-2078.64</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="157">
@@ -4302,25 +4317,25 @@
         <v>26</v>
       </c>
       <c r="B157" t="s" s="1">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C157" t="s" s="1">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D157" t="s" s="1">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="E157" t="s" s="1">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="F157" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G157" t="n" s="1">
-        <v>2040.52</v>
+        <v>180.0</v>
       </c>
       <c r="H157" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="158">
@@ -4328,13 +4343,13 @@
         <v>26</v>
       </c>
       <c r="B158" t="s" s="1">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C158" t="s" s="1">
         <v>41</v>
       </c>
       <c r="D158" t="s" s="1">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="E158" t="s" s="1">
         <v>63</v>
@@ -4354,25 +4369,25 @@
         <v>26</v>
       </c>
       <c r="B159" t="s" s="1">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C159" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D159" t="s" s="1">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E159" t="s" s="1">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F159" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G159" t="n" s="1">
-        <v>180.0</v>
+        <v>2719.92</v>
       </c>
       <c r="H159" t="n" s="1">
-        <v>-180.0</v>
+        <v>-2719.92</v>
       </c>
     </row>
     <row r="160">
@@ -4380,25 +4395,25 @@
         <v>26</v>
       </c>
       <c r="B160" t="s" s="1">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C160" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D160" t="s" s="1">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="E160" t="s" s="1">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="F160" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G160" t="n" s="1">
-        <v>1000.0</v>
+        <v>1903.95</v>
       </c>
       <c r="H160" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-1903.95</v>
       </c>
     </row>
     <row r="161">
@@ -4406,49 +4421,413 @@
         <v>26</v>
       </c>
       <c r="B161" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="C161" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D161" t="s" s="1">
+        <v>149</v>
+      </c>
+      <c r="E161" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="F161" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G161" t="n" s="1">
+        <v>815.98</v>
+      </c>
+      <c r="H161" t="n" s="1">
+        <v>-815.98</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B162" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="C162" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D162" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="E162" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F162" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G162" t="n" s="1">
+        <v>1131.78</v>
+      </c>
+      <c r="H162" t="n" s="1">
+        <v>-1131.78</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B163" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="C163" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D163" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="E163" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="F163" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G163" t="n" s="1">
+        <v>792.25</v>
+      </c>
+      <c r="H163" t="n" s="1">
+        <v>-792.25</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B164" t="s" s="1">
+        <v>153</v>
+      </c>
+      <c r="C164" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D164" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="E164" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="F164" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G164" t="n" s="1">
+        <v>339.53</v>
+      </c>
+      <c r="H164" t="n" s="1">
+        <v>-339.53</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B165" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C165" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D165" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="E165" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="F165" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G165" t="n" s="1">
+        <v>1201.89</v>
+      </c>
+      <c r="H165" t="n" s="1">
+        <v>-1201.89</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B166" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C166" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D166" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="E166" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="F166" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G166" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H166" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B167" t="s" s="1">
+        <v>156</v>
+      </c>
+      <c r="C167" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D167" t="s" s="1">
         <v>159</v>
       </c>
-      <c r="C161" t="s" s="1">
+      <c r="E167" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="F167" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G167" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H167" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B168" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C168" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D168" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E168" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F168" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G168" t="n" s="1">
+        <v>2277.0</v>
+      </c>
+      <c r="H168" t="n" s="1">
+        <v>-2277.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B169" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C169" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D169" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="E169" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="F169" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G169" t="n" s="1">
+        <v>25504.78</v>
+      </c>
+      <c r="H169" t="n" s="1">
+        <v>-25504.78</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B170" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C170" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D170" t="s" s="1">
+        <v>161</v>
+      </c>
+      <c r="E170" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F170" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G170" t="n" s="1">
+        <v>2078.64</v>
+      </c>
+      <c r="H170" t="n" s="1">
+        <v>-2078.64</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B171" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C171" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D171" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="E171" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F171" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G171" t="n" s="1">
+        <v>2040.52</v>
+      </c>
+      <c r="H171" t="n" s="1">
+        <v>-2040.52</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B172" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C172" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="D161" t="s" s="1">
+      <c r="D172" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="E172" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="F172" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G172" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H172" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B173" t="s" s="1">
+        <v>162</v>
+      </c>
+      <c r="C173" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D173" t="s" s="1">
+        <v>163</v>
+      </c>
+      <c r="E173" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="F173" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G173" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H173" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B174" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C174" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D174" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E174" t="s" s="1">
+        <v>165</v>
+      </c>
+      <c r="F174" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G174" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H174" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B175" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="C175" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D175" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="E161" t="s" s="1">
-        <v>161</v>
-      </c>
-      <c r="F161" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G161" t="n" s="1">
+      <c r="E175" t="s" s="1">
+        <v>166</v>
+      </c>
+      <c r="F175" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G175" t="n" s="1">
         <v>3750.0</v>
       </c>
-      <c r="H161" t="n" s="1">
+      <c r="H175" t="n" s="1">
         <v>-3750.0</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B166" s="3" t="s">
+    <row r="178">
+      <c r="A178" s="2" t="s">
         <v>167</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
+++ b/xlsx/fluxo_caixa/previsao/Previsao_Out_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="185">
   <si>
     <t>Fluxo de Caixa Previsto</t>
   </si>
@@ -414,91 +414,127 @@
     <t>ERIC SERPA</t>
   </si>
   <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>104401 - 1</t>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>1630 - 1</t>
+  </si>
+  <si>
+    <t>1635 - 1</t>
+  </si>
+  <si>
+    <t>1630 - 3</t>
+  </si>
+  <si>
+    <t>1630 - 2</t>
+  </si>
+  <si>
+    <t>1635 - 3</t>
+  </si>
+  <si>
+    <t>1635 - 2</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>100501 - 1</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>102301 - 3</t>
+  </si>
+  <si>
+    <t>24/10/2026</t>
+  </si>
+  <si>
+    <t>105501 - 1</t>
+  </si>
+  <si>
+    <t>105701 - 1</t>
+  </si>
+  <si>
+    <t>105501 - 2</t>
+  </si>
+  <si>
+    <t>105701 - 2</t>
+  </si>
+  <si>
+    <t>25/10/2026</t>
+  </si>
+  <si>
+    <t>68 - 3</t>
+  </si>
+  <si>
+    <t>Luis Carlos Alves de Oliveira</t>
+  </si>
+  <si>
+    <t>26/10/2026</t>
+  </si>
+  <si>
+    <t>2 - 9</t>
+  </si>
+  <si>
+    <t>EM SOLUCOES INTEGRADAS DE SISTEMAS LTDA ME</t>
+  </si>
+  <si>
+    <t>101801 - 1</t>
+  </si>
+  <si>
+    <t>27/10/2026</t>
+  </si>
+  <si>
+    <t>100901 - 3</t>
+  </si>
+  <si>
+    <t>28/10/2026</t>
+  </si>
+  <si>
+    <t>1556 - 1</t>
+  </si>
+  <si>
+    <t>1636 - 1</t>
+  </si>
+  <si>
+    <t>1637 - 1</t>
+  </si>
+  <si>
+    <t>1638 - 1</t>
+  </si>
+  <si>
+    <t>1556 - 3</t>
+  </si>
+  <si>
+    <t>1556 - 2</t>
+  </si>
+  <si>
+    <t>1636 - 2</t>
+  </si>
+  <si>
+    <t>1636 - 3</t>
+  </si>
+  <si>
+    <t>1637 - 3</t>
+  </si>
+  <si>
+    <t>1637 - 2</t>
+  </si>
+  <si>
+    <t>1638 - 2</t>
+  </si>
+  <si>
+    <t>1638 - 3</t>
+  </si>
+  <si>
+    <t>106001 - 1</t>
   </si>
   <si>
     <t>PAGSEGURO</t>
   </si>
   <si>
-    <t>104401 - 2</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>1630 - 1</t>
-  </si>
-  <si>
-    <t>1635 - 1</t>
-  </si>
-  <si>
-    <t>1630 - 3</t>
-  </si>
-  <si>
-    <t>1630 - 2</t>
-  </si>
-  <si>
-    <t>1635 - 2</t>
-  </si>
-  <si>
-    <t>1635 - 3</t>
-  </si>
-  <si>
-    <t>22/10/2026</t>
-  </si>
-  <si>
-    <t>100501 - 1</t>
-  </si>
-  <si>
-    <t>23/10/2026</t>
-  </si>
-  <si>
-    <t>102301 - 3</t>
-  </si>
-  <si>
-    <t>24/10/2026</t>
-  </si>
-  <si>
-    <t>105501 - 1</t>
-  </si>
-  <si>
-    <t>105701 - 1</t>
-  </si>
-  <si>
-    <t>105501 - 2</t>
-  </si>
-  <si>
-    <t>105701 - 2</t>
-  </si>
-  <si>
-    <t>25/10/2026</t>
-  </si>
-  <si>
-    <t>68 - 3</t>
-  </si>
-  <si>
-    <t>Luis Carlos Alves de Oliveira</t>
-  </si>
-  <si>
-    <t>26/10/2026</t>
-  </si>
-  <si>
-    <t>2 - 9</t>
-  </si>
-  <si>
-    <t>EM SOLUCOES INTEGRADAS DE SISTEMAS LTDA ME</t>
-  </si>
-  <si>
-    <t>101801 - 1</t>
-  </si>
-  <si>
-    <t>27/10/2026</t>
-  </si>
-  <si>
-    <t>100901 - 3</t>
+    <t>106001 - 2</t>
   </si>
   <si>
     <t>29/10/2026</t>
@@ -525,13 +561,13 @@
     <t>Total Geral Débito</t>
   </si>
   <si>
-    <t>248.133,43</t>
+    <t>242.386,59</t>
   </si>
   <si>
     <t>Total Geral Saldo</t>
   </si>
   <si>
-    <t>-248.133,43</t>
+    <t>-242.386,59</t>
   </si>
 </sst>
 </file>
@@ -599,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:H180"/>
+  <dimension ref="A2:H192"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.01953125" customWidth="true" bestFit="true"/>
@@ -1888,10 +1924,10 @@
         <v>0.0</v>
       </c>
       <c r="G63" t="n" s="1">
-        <v>714.08</v>
+        <v>751.98</v>
       </c>
       <c r="H63" t="n" s="1">
-        <v>-714.08</v>
+        <v>-751.98</v>
       </c>
     </row>
     <row r="64">
@@ -1914,10 +1950,10 @@
         <v>0.0</v>
       </c>
       <c r="G64" t="n" s="1">
-        <v>700.72</v>
+        <v>738.01</v>
       </c>
       <c r="H64" t="n" s="1">
-        <v>-700.72</v>
+        <v>-738.01</v>
       </c>
     </row>
     <row r="65">
@@ -2460,10 +2496,10 @@
         <v>0.0</v>
       </c>
       <c r="G85" t="n" s="1">
-        <v>1751.0</v>
+        <v>1674.25</v>
       </c>
       <c r="H85" t="n" s="1">
-        <v>-1751.0</v>
+        <v>-1674.25</v>
       </c>
     </row>
     <row r="86">
@@ -2486,10 +2522,10 @@
         <v>0.0</v>
       </c>
       <c r="G86" t="n" s="1">
-        <v>1718.89</v>
+        <v>1643.57</v>
       </c>
       <c r="H86" t="n" s="1">
-        <v>-1718.89</v>
+        <v>-1643.57</v>
       </c>
     </row>
     <row r="87">
@@ -2506,16 +2542,16 @@
         <v>109</v>
       </c>
       <c r="E87" t="s" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F87" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G87" t="n" s="1">
-        <v>15.2</v>
+        <v>30.4</v>
       </c>
       <c r="H87" t="n" s="1">
-        <v>-15.2</v>
+        <v>-30.4</v>
       </c>
     </row>
     <row r="88">
@@ -2558,16 +2594,16 @@
         <v>109</v>
       </c>
       <c r="E89" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F89" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G89" t="n" s="1">
-        <v>30.4</v>
+        <v>15.2</v>
       </c>
       <c r="H89" t="n" s="1">
-        <v>-30.4</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="90">
@@ -2688,16 +2724,16 @@
         <v>113</v>
       </c>
       <c r="E94" t="s" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F94" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G94" t="n" s="1">
-        <v>6.81</v>
+        <v>3.41</v>
       </c>
       <c r="H94" t="n" s="1">
-        <v>-6.81</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="95">
@@ -2714,16 +2750,16 @@
         <v>113</v>
       </c>
       <c r="E95" t="s" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F95" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G95" t="n" s="1">
-        <v>3.41</v>
+        <v>6.81</v>
       </c>
       <c r="H95" t="n" s="1">
-        <v>-3.41</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="96">
@@ -3592,22 +3628,22 @@
         <v>133</v>
       </c>
       <c r="C129" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D129" t="s" s="1">
         <v>134</v>
       </c>
       <c r="E129" t="s" s="1">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="F129" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G129" t="n" s="1">
-        <v>1801.15</v>
+        <v>113.21</v>
       </c>
       <c r="H129" t="n" s="1">
-        <v>-1801.15</v>
+        <v>-113.21</v>
       </c>
     </row>
     <row r="130">
@@ -3618,22 +3654,22 @@
         <v>133</v>
       </c>
       <c r="C130" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D130" t="s" s="1">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E130" t="s" s="1">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="F130" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G130" t="n" s="1">
-        <v>5165.75</v>
+        <v>191.08</v>
       </c>
       <c r="H130" t="n" s="1">
-        <v>-5165.75</v>
+        <v>-191.08</v>
       </c>
     </row>
     <row r="131">
@@ -3644,22 +3680,22 @@
         <v>133</v>
       </c>
       <c r="C131" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D131" t="s" s="1">
         <v>136</v>
       </c>
       <c r="E131" t="s" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F131" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G131" t="n" s="1">
-        <v>527.98</v>
+        <v>9.23</v>
       </c>
       <c r="H131" t="n" s="1">
-        <v>-527.98</v>
+        <v>-9.23</v>
       </c>
     </row>
     <row r="132">
@@ -3670,22 +3706,22 @@
         <v>133</v>
       </c>
       <c r="C132" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D132" t="s" s="1">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E132" t="s" s="1">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F132" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G132" t="n" s="1">
-        <v>263.99</v>
+        <v>9.05</v>
       </c>
       <c r="H132" t="n" s="1">
-        <v>-263.99</v>
+        <v>-9.05</v>
       </c>
     </row>
     <row r="133">
@@ -3696,22 +3732,22 @@
         <v>133</v>
       </c>
       <c r="C133" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D133" t="s" s="1">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E133" t="s" s="1">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="F133" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G133" t="n" s="1">
-        <v>527.98</v>
+        <v>15.56</v>
       </c>
       <c r="H133" t="n" s="1">
-        <v>-527.98</v>
+        <v>-15.56</v>
       </c>
     </row>
     <row r="134">
@@ -3719,25 +3755,25 @@
         <v>26</v>
       </c>
       <c r="B134" t="s" s="1">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C134" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D134" t="s" s="1">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E134" t="s" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F134" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G134" t="n" s="1">
-        <v>113.21</v>
+        <v>15.3</v>
       </c>
       <c r="H134" t="n" s="1">
-        <v>-113.21</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="135">
@@ -3745,25 +3781,25 @@
         <v>26</v>
       </c>
       <c r="B135" t="s" s="1">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C135" t="s" s="1">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D135" t="s" s="1">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E135" t="s" s="1">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F135" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G135" t="n" s="1">
-        <v>191.08</v>
+        <v>180.0</v>
       </c>
       <c r="H135" t="n" s="1">
-        <v>-191.08</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="136">
@@ -3771,25 +3807,25 @@
         <v>26</v>
       </c>
       <c r="B136" t="s" s="1">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C136" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D136" t="s" s="1">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E136" t="s" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F136" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G136" t="n" s="1">
-        <v>9.23</v>
+        <v>9216.24</v>
       </c>
       <c r="H136" t="n" s="1">
-        <v>-9.23</v>
+        <v>-9216.24</v>
       </c>
     </row>
     <row r="137">
@@ -3797,25 +3833,25 @@
         <v>26</v>
       </c>
       <c r="B137" t="s" s="1">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C137" t="s" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D137" t="s" s="1">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="E137" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F137" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G137" t="n" s="1">
-        <v>9.05</v>
+        <v>891.0</v>
       </c>
       <c r="H137" t="n" s="1">
-        <v>-9.05</v>
+        <v>-891.0</v>
       </c>
     </row>
     <row r="138">
@@ -3823,13 +3859,13 @@
         <v>26</v>
       </c>
       <c r="B138" t="s" s="1">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C138" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D138" t="s" s="1">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="E138" t="s" s="1">
         <v>35</v>
@@ -3838,10 +3874,10 @@
         <v>0.0</v>
       </c>
       <c r="G138" t="n" s="1">
-        <v>15.3</v>
+        <v>737.28</v>
       </c>
       <c r="H138" t="n" s="1">
-        <v>-15.3</v>
+        <v>-737.28</v>
       </c>
     </row>
     <row r="139">
@@ -3849,7 +3885,7 @@
         <v>26</v>
       </c>
       <c r="B139" t="s" s="1">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C139" t="s" s="1">
         <v>31</v>
@@ -3864,10 +3900,10 @@
         <v>0.0</v>
       </c>
       <c r="G139" t="n" s="1">
-        <v>15.56</v>
+        <v>750.99</v>
       </c>
       <c r="H139" t="n" s="1">
-        <v>-15.56</v>
+        <v>-750.99</v>
       </c>
     </row>
     <row r="140">
@@ -3875,25 +3911,25 @@
         <v>26</v>
       </c>
       <c r="B140" t="s" s="1">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C140" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D140" t="s" s="1">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E140" t="s" s="1">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="F140" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G140" t="n" s="1">
-        <v>1847.92</v>
+        <v>7260.81</v>
       </c>
       <c r="H140" t="n" s="1">
-        <v>-1847.92</v>
+        <v>-7260.81</v>
       </c>
     </row>
     <row r="141">
@@ -3901,25 +3937,25 @@
         <v>26</v>
       </c>
       <c r="B141" t="s" s="1">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C141" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D141" t="s" s="1">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E141" t="s" s="1">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F141" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G141" t="n" s="1">
-        <v>2639.89</v>
+        <v>1779.4</v>
       </c>
       <c r="H141" t="n" s="1">
-        <v>-2639.89</v>
+        <v>-1779.4</v>
       </c>
     </row>
     <row r="142">
@@ -3930,22 +3966,22 @@
         <v>144</v>
       </c>
       <c r="C142" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s" s="1">
         <v>145</v>
       </c>
       <c r="E142" t="s" s="1">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="F142" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G142" t="n" s="1">
-        <v>180.0</v>
+        <v>271.99</v>
       </c>
       <c r="H142" t="n" s="1">
-        <v>-180.0</v>
+        <v>-271.99</v>
       </c>
     </row>
     <row r="143">
@@ -3953,13 +3989,13 @@
         <v>26</v>
       </c>
       <c r="B143" t="s" s="1">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C143" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s" s="1">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="E143" t="s" s="1">
         <v>38</v>
@@ -3968,10 +4004,10 @@
         <v>0.0</v>
       </c>
       <c r="G143" t="n" s="1">
-        <v>891.0</v>
+        <v>543.98</v>
       </c>
       <c r="H143" t="n" s="1">
-        <v>-891.0</v>
+        <v>-543.98</v>
       </c>
     </row>
     <row r="144">
@@ -3979,25 +4015,25 @@
         <v>26</v>
       </c>
       <c r="B144" t="s" s="1">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C144" t="s" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D144" t="s" s="1">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="E144" t="s" s="1">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F144" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G144" t="n" s="1">
-        <v>9216.24</v>
+        <v>543.98</v>
       </c>
       <c r="H144" t="n" s="1">
-        <v>-9216.24</v>
+        <v>-543.98</v>
       </c>
     </row>
     <row r="145">
@@ -4005,25 +4041,25 @@
         <v>26</v>
       </c>
       <c r="B145" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C145" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D145" t="s" s="1">
         <v>146</v>
       </c>
-      <c r="C145" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D145" t="s" s="1">
-        <v>50</v>
-      </c>
       <c r="E145" t="s" s="1">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F145" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G145" t="n" s="1">
-        <v>737.28</v>
+        <v>113.18</v>
       </c>
       <c r="H145" t="n" s="1">
-        <v>-737.28</v>
+        <v>-113.18</v>
       </c>
     </row>
     <row r="146">
@@ -4031,25 +4067,25 @@
         <v>26</v>
       </c>
       <c r="B146" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C146" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D146" t="s" s="1">
         <v>146</v>
       </c>
-      <c r="C146" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D146" t="s" s="1">
-        <v>147</v>
-      </c>
       <c r="E146" t="s" s="1">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F146" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G146" t="n" s="1">
-        <v>750.99</v>
+        <v>226.36</v>
       </c>
       <c r="H146" t="n" s="1">
-        <v>-750.99</v>
+        <v>-226.36</v>
       </c>
     </row>
     <row r="147">
@@ -4057,25 +4093,25 @@
         <v>26</v>
       </c>
       <c r="B147" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C147" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D147" t="s" s="1">
         <v>148</v>
       </c>
-      <c r="C147" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="D147" t="s" s="1">
-        <v>149</v>
-      </c>
       <c r="E147" t="s" s="1">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F147" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G147" t="n" s="1">
-        <v>7260.81</v>
+        <v>226.36</v>
       </c>
       <c r="H147" t="n" s="1">
-        <v>-7260.81</v>
+        <v>-226.36</v>
       </c>
     </row>
     <row r="148">
@@ -4083,25 +4119,25 @@
         <v>26</v>
       </c>
       <c r="B148" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C148" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D148" t="s" s="1">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="E148" t="s" s="1">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F148" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G148" t="n" s="1">
-        <v>1779.4</v>
+        <v>1544.4</v>
       </c>
       <c r="H148" t="n" s="1">
-        <v>-1779.4</v>
+        <v>-1544.4</v>
       </c>
     </row>
     <row r="149">
@@ -4109,25 +4145,25 @@
         <v>26</v>
       </c>
       <c r="B149" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C149" t="s" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D149" t="s" s="1">
+        <v>150</v>
+      </c>
+      <c r="E149" t="s" s="1">
         <v>151</v>
       </c>
-      <c r="E149" t="s" s="1">
-        <v>38</v>
-      </c>
       <c r="F149" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G149" t="n" s="1">
-        <v>543.98</v>
+        <v>1925.0</v>
       </c>
       <c r="H149" t="n" s="1">
-        <v>-543.98</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="150">
@@ -4135,25 +4171,25 @@
         <v>26</v>
       </c>
       <c r="B150" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C150" t="s" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D150" t="s" s="1">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="E150" t="s" s="1">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F150" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G150" t="n" s="1">
-        <v>543.98</v>
+        <v>180.0</v>
       </c>
       <c r="H150" t="n" s="1">
-        <v>-543.98</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="151">
@@ -4161,25 +4197,25 @@
         <v>26</v>
       </c>
       <c r="B151" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C151" t="s" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D151" t="s" s="1">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E151" t="s" s="1">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F151" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G151" t="n" s="1">
-        <v>271.99</v>
+        <v>180.0</v>
       </c>
       <c r="H151" t="n" s="1">
-        <v>-271.99</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="152">
@@ -4187,25 +4223,25 @@
         <v>26</v>
       </c>
       <c r="B152" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C152" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D152" t="s" s="1">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E152" t="s" s="1">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F152" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G152" t="n" s="1">
-        <v>113.18</v>
+        <v>815.98</v>
       </c>
       <c r="H152" t="n" s="1">
-        <v>-113.18</v>
+        <v>-815.98</v>
       </c>
     </row>
     <row r="153">
@@ -4213,25 +4249,25 @@
         <v>26</v>
       </c>
       <c r="B153" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C153" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D153" t="s" s="1">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E153" t="s" s="1">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="F153" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G153" t="n" s="1">
-        <v>226.36</v>
+        <v>1903.95</v>
       </c>
       <c r="H153" t="n" s="1">
-        <v>-226.36</v>
+        <v>-1903.95</v>
       </c>
     </row>
     <row r="154">
@@ -4239,13 +4275,13 @@
         <v>26</v>
       </c>
       <c r="B154" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C154" t="s" s="1">
         <v>36</v>
       </c>
       <c r="D154" t="s" s="1">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E154" t="s" s="1">
         <v>38</v>
@@ -4254,10 +4290,10 @@
         <v>0.0</v>
       </c>
       <c r="G154" t="n" s="1">
-        <v>226.36</v>
+        <v>2719.92</v>
       </c>
       <c r="H154" t="n" s="1">
-        <v>-226.36</v>
+        <v>-2719.92</v>
       </c>
     </row>
     <row r="155">
@@ -4265,25 +4301,25 @@
         <v>26</v>
       </c>
       <c r="B155" t="s" s="1">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C155" t="s" s="1">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s" s="1">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E155" t="s" s="1">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F155" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G155" t="n" s="1">
-        <v>1544.4</v>
+        <v>339.53</v>
       </c>
       <c r="H155" t="n" s="1">
-        <v>-1544.4</v>
+        <v>-339.53</v>
       </c>
     </row>
     <row r="156">
@@ -4291,25 +4327,25 @@
         <v>26</v>
       </c>
       <c r="B156" t="s" s="1">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C156" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s" s="1">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E156" t="s" s="1">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="F156" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G156" t="n" s="1">
-        <v>1925.0</v>
+        <v>792.25</v>
       </c>
       <c r="H156" t="n" s="1">
-        <v>-1925.0</v>
+        <v>-792.25</v>
       </c>
     </row>
     <row r="157">
@@ -4317,25 +4353,25 @@
         <v>26</v>
       </c>
       <c r="B157" t="s" s="1">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C157" t="s" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D157" t="s" s="1">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="E157" t="s" s="1">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F157" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G157" t="n" s="1">
-        <v>180.0</v>
+        <v>1131.78</v>
       </c>
       <c r="H157" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1131.78</v>
       </c>
     </row>
     <row r="158">
@@ -4343,25 +4379,25 @@
         <v>26</v>
       </c>
       <c r="B158" t="s" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C158" t="s" s="1">
         <v>41</v>
       </c>
       <c r="D158" t="s" s="1">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="E158" t="s" s="1">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="F158" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G158" t="n" s="1">
-        <v>180.0</v>
+        <v>1201.89</v>
       </c>
       <c r="H158" t="n" s="1">
-        <v>-180.0</v>
+        <v>-1201.89</v>
       </c>
     </row>
     <row r="159">
@@ -4369,25 +4405,25 @@
         <v>26</v>
       </c>
       <c r="B159" t="s" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C159" t="s" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D159" t="s" s="1">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="E159" t="s" s="1">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F159" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G159" t="n" s="1">
-        <v>2719.92</v>
+        <v>180.0</v>
       </c>
       <c r="H159" t="n" s="1">
-        <v>-2719.92</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="160">
@@ -4395,25 +4431,25 @@
         <v>26</v>
       </c>
       <c r="B160" t="s" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C160" t="s" s="1">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D160" t="s" s="1">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E160" t="s" s="1">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="F160" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G160" t="n" s="1">
-        <v>1903.95</v>
+        <v>180.0</v>
       </c>
       <c r="H160" t="n" s="1">
-        <v>-1903.95</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="161">
@@ -4421,25 +4457,25 @@
         <v>26</v>
       </c>
       <c r="B161" t="s" s="1">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C161" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D161" t="s" s="1">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="E161" t="s" s="1">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F161" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G161" t="n" s="1">
-        <v>815.98</v>
+        <v>25504.78</v>
       </c>
       <c r="H161" t="n" s="1">
-        <v>-815.98</v>
+        <v>-25504.78</v>
       </c>
     </row>
     <row r="162">
@@ -4447,13 +4483,13 @@
         <v>26</v>
       </c>
       <c r="B162" t="s" s="1">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C162" t="s" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D162" t="s" s="1">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="E162" t="s" s="1">
         <v>38</v>
@@ -4462,10 +4498,10 @@
         <v>0.0</v>
       </c>
       <c r="G162" t="n" s="1">
-        <v>1131.78</v>
+        <v>2277.0</v>
       </c>
       <c r="H162" t="n" s="1">
-        <v>-1131.78</v>
+        <v>-2277.0</v>
       </c>
     </row>
     <row r="163">
@@ -4473,25 +4509,25 @@
         <v>26</v>
       </c>
       <c r="B163" t="s" s="1">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C163" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D163" t="s" s="1">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E163" t="s" s="1">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="F163" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G163" t="n" s="1">
-        <v>792.25</v>
+        <v>2078.64</v>
       </c>
       <c r="H163" t="n" s="1">
-        <v>-792.25</v>
+        <v>-2078.64</v>
       </c>
     </row>
     <row r="164">
@@ -4499,25 +4535,25 @@
         <v>26</v>
       </c>
       <c r="B164" t="s" s="1">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C164" t="s" s="1">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D164" t="s" s="1">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="E164" t="s" s="1">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F164" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G164" t="n" s="1">
-        <v>339.53</v>
+        <v>2040.52</v>
       </c>
       <c r="H164" t="n" s="1">
-        <v>-339.53</v>
+        <v>-2040.52</v>
       </c>
     </row>
     <row r="165">
@@ -4531,19 +4567,19 @@
         <v>41</v>
       </c>
       <c r="D165" t="s" s="1">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="E165" t="s" s="1">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="F165" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G165" t="n" s="1">
-        <v>1201.89</v>
+        <v>180.0</v>
       </c>
       <c r="H165" t="n" s="1">
-        <v>-1201.89</v>
+        <v>-180.0</v>
       </c>
     </row>
     <row r="166">
@@ -4551,25 +4587,25 @@
         <v>26</v>
       </c>
       <c r="B166" t="s" s="1">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C166" t="s" s="1">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D166" t="s" s="1">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="E166" t="s" s="1">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F166" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G166" t="n" s="1">
-        <v>180.0</v>
+        <v>212.01</v>
       </c>
       <c r="H166" t="n" s="1">
-        <v>-180.0</v>
+        <v>-212.01</v>
       </c>
     </row>
     <row r="167">
@@ -4577,25 +4613,25 @@
         <v>26</v>
       </c>
       <c r="B167" t="s" s="1">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C167" t="s" s="1">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D167" t="s" s="1">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E167" t="s" s="1">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F167" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G167" t="n" s="1">
-        <v>180.0</v>
+        <v>255.77</v>
       </c>
       <c r="H167" t="n" s="1">
-        <v>-180.0</v>
+        <v>-255.77</v>
       </c>
     </row>
     <row r="168">
@@ -4603,25 +4639,25 @@
         <v>26</v>
       </c>
       <c r="B168" t="s" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C168" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D168" t="s" s="1">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="E168" t="s" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F168" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G168" t="n" s="1">
-        <v>2277.0</v>
+        <v>262.41</v>
       </c>
       <c r="H168" t="n" s="1">
-        <v>-2277.0</v>
+        <v>-262.41</v>
       </c>
     </row>
     <row r="169">
@@ -4629,13 +4665,13 @@
         <v>26</v>
       </c>
       <c r="B169" t="s" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C169" t="s" s="1">
         <v>28</v>
       </c>
       <c r="D169" t="s" s="1">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="E169" t="s" s="1">
         <v>30</v>
@@ -4644,10 +4680,10 @@
         <v>0.0</v>
       </c>
       <c r="G169" t="n" s="1">
-        <v>25504.78</v>
+        <v>136.34</v>
       </c>
       <c r="H169" t="n" s="1">
-        <v>-25504.78</v>
+        <v>-136.34</v>
       </c>
     </row>
     <row r="170">
@@ -4655,13 +4691,13 @@
         <v>26</v>
       </c>
       <c r="B170" t="s" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C170" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D170" t="s" s="1">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E170" t="s" s="1">
         <v>33</v>
@@ -4670,10 +4706,10 @@
         <v>0.0</v>
       </c>
       <c r="G170" t="n" s="1">
-        <v>2078.64</v>
+        <v>17.28</v>
       </c>
       <c r="H170" t="n" s="1">
-        <v>-2078.64</v>
+        <v>-17.28</v>
       </c>
     </row>
     <row r="171">
@@ -4681,13 +4717,13 @@
         <v>26</v>
       </c>
       <c r="B171" t="s" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C171" t="s" s="1">
         <v>31</v>
       </c>
       <c r="D171" t="s" s="1">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="E171" t="s" s="1">
         <v>35</v>
@@ -4696,10 +4732,10 @@
         <v>0.0</v>
       </c>
       <c r="G171" t="n" s="1">
-        <v>2040.52</v>
+        <v>16.96</v>
       </c>
       <c r="H171" t="n" s="1">
-        <v>-2040.52</v>
+        <v>-16.96</v>
       </c>
     </row>
     <row r="172">
@@ -4707,25 +4743,25 @@
         <v>26</v>
       </c>
       <c r="B172" t="s" s="1">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C172" t="s" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D172" t="s" s="1">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="E172" t="s" s="1">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F172" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G172" t="n" s="1">
-        <v>180.0</v>
+        <v>20.47</v>
       </c>
       <c r="H172" t="n" s="1">
-        <v>-180.0</v>
+        <v>-20.47</v>
       </c>
     </row>
     <row r="173">
@@ -4733,25 +4769,25 @@
         <v>26</v>
       </c>
       <c r="B173" t="s" s="1">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C173" t="s" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D173" t="s" s="1">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E173" t="s" s="1">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="F173" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G173" t="n" s="1">
-        <v>180.0</v>
+        <v>20.83</v>
       </c>
       <c r="H173" t="n" s="1">
-        <v>-180.0</v>
+        <v>-20.83</v>
       </c>
     </row>
     <row r="174">
@@ -4759,25 +4795,25 @@
         <v>26</v>
       </c>
       <c r="B174" t="s" s="1">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C174" t="s" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D174" t="s" s="1">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="E174" t="s" s="1">
-        <v>165</v>
+        <v>33</v>
       </c>
       <c r="F174" t="n" s="1">
         <v>0.0</v>
       </c>
       <c r="G174" t="n" s="1">
-        <v>1000.0</v>
+        <v>21.38</v>
       </c>
       <c r="H174" t="n" s="1">
-        <v>-1000.0</v>
+        <v>-21.38</v>
       </c>
     </row>
     <row r="175">
@@ -4785,49 +4821,361 @@
         <v>26</v>
       </c>
       <c r="B175" t="s" s="1">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C175" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D175" t="s" s="1">
+        <v>168</v>
+      </c>
+      <c r="E175" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F175" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G175" t="n" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="H175" t="n" s="1">
+        <v>-21.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B176" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="C176" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D176" t="s" s="1">
+        <v>169</v>
+      </c>
+      <c r="E176" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F176" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G176" t="n" s="1">
+        <v>10.88</v>
+      </c>
+      <c r="H176" t="n" s="1">
+        <v>-10.88</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B177" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="C177" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D177" t="s" s="1">
+        <v>170</v>
+      </c>
+      <c r="E177" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F177" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G177" t="n" s="1">
+        <v>11.18</v>
+      </c>
+      <c r="H177" t="n" s="1">
+        <v>-11.18</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B178" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="C178" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D178" t="s" s="1">
+        <v>171</v>
+      </c>
+      <c r="E178" t="s" s="1">
+        <v>172</v>
+      </c>
+      <c r="F178" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G178" t="n" s="1">
+        <v>1962.11</v>
+      </c>
+      <c r="H178" t="n" s="1">
+        <v>-1962.11</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B179" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="C179" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D179" t="s" s="1">
+        <v>171</v>
+      </c>
+      <c r="E179" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="F179" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G179" t="n" s="1">
+        <v>330.89</v>
+      </c>
+      <c r="H179" t="n" s="1">
+        <v>-330.89</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B180" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="C180" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D180" t="s" s="1">
+        <v>171</v>
+      </c>
+      <c r="E180" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="F180" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G180" t="n" s="1">
+        <v>165.44</v>
+      </c>
+      <c r="H180" t="n" s="1">
+        <v>-165.44</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B181" t="s" s="1">
+        <v>158</v>
+      </c>
+      <c r="C181" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D181" t="s" s="1">
+        <v>173</v>
+      </c>
+      <c r="E181" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F181" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G181" t="n" s="1">
+        <v>330.89</v>
+      </c>
+      <c r="H181" t="n" s="1">
+        <v>-330.89</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B182" t="s" s="1">
+        <v>174</v>
+      </c>
+      <c r="C182" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="D175" t="s" s="1">
+      <c r="D182" t="s" s="1">
+        <v>175</v>
+      </c>
+      <c r="E182" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="F182" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G182" t="n" s="1">
+        <v>180.0</v>
+      </c>
+      <c r="H182" t="n" s="1">
+        <v>-180.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B183" t="s" s="1">
+        <v>174</v>
+      </c>
+      <c r="C183" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D183" t="s" s="1">
+        <v>171</v>
+      </c>
+      <c r="E183" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="F183" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G183" t="n" s="1">
+        <v>496.33</v>
+      </c>
+      <c r="H183" t="n" s="1">
+        <v>-496.33</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B184" t="s" s="1">
+        <v>174</v>
+      </c>
+      <c r="C184" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D184" t="s" s="1">
+        <v>171</v>
+      </c>
+      <c r="E184" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F184" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G184" t="n" s="1">
+        <v>1654.43</v>
+      </c>
+      <c r="H184" t="n" s="1">
+        <v>-1654.43</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B185" t="s" s="1">
+        <v>174</v>
+      </c>
+      <c r="C185" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="D185" t="s" s="1">
+        <v>171</v>
+      </c>
+      <c r="E185" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="F185" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G185" t="n" s="1">
+        <v>1158.1</v>
+      </c>
+      <c r="H185" t="n" s="1">
+        <v>-1158.1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B186" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="C186" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D186" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E186" t="s" s="1">
+        <v>177</v>
+      </c>
+      <c r="F186" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G186" t="n" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="H186" t="n" s="1">
+        <v>-1000.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B187" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="C187" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D187" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="E175" t="s" s="1">
-        <v>166</v>
-      </c>
-      <c r="F175" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G175" t="n" s="1">
+      <c r="E187" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="F187" t="n" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G187" t="n" s="1">
         <v>3750.0</v>
       </c>
-      <c r="H175" t="n" s="1">
+      <c r="H187" t="n" s="1">
         <v>-3750.0</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>172</v>
+    <row r="190">
+      <c r="A190" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
